--- a/docs/parts-table.xlsx
+++ b/docs/parts-table.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$936</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$1142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L936"/>
+  <dimension ref="A1:L1142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第1課</t>
+          <t>翰林2上第1課、康軒6上第4課</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課</t>
+          <t>翰林2上第7課、康軒6上第10課</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第9課</t>
+          <t>翰林2上第9課、康軒6上第2課</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第10課</t>
+          <t>翰林2上第10課、康軒6上第12課</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第11課、南一2上第1課(認讀)</t>
+          <t>翰林2上第11課、南一2上第1課(認讀)、康軒6上第4課</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="B347" s="3" t="inlineStr">
         <is>
-          <t>南一2上第7課</t>
+          <t>南一2上第7課、康軒6上第3課</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>南一2上第12課、康軒4上第9課</t>
+          <t>南一2上第12課、康軒4上第9課、康軒6上第12課</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
@@ -21146,7 +21146,7 @@
       </c>
       <c r="B545" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第5課(認讀)</t>
+          <t>康軒2上第5課(認讀)、康軒6上第2課</t>
         </is>
       </c>
       <c r="C545" s="4" t="inlineStr">
@@ -35916,7 +35916,7 @@
       </c>
       <c r="B932" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課</t>
+          <t>康軒4上第12課、康軒6上第6課</t>
         </is>
       </c>
       <c r="C932" s="4" t="inlineStr">
@@ -36098,10 +36098,7854 @@
       <c r="K936" s="5" t="inlineStr"/>
       <c r="L936" s="7" t="inlineStr"/>
     </row>
+    <row r="937">
+      <c r="A937" s="2" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B937" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C937" s="4" t="inlineStr">
+        <is>
+          <t>糹 及</t>
+        </is>
+      </c>
+      <c r="D937" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E937" s="5" t="n"/>
+      <c r="F937" s="5" t="n"/>
+      <c r="G937" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 及</t>
+        </is>
+      </c>
+      <c r="H937" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I937" s="3" t="n"/>
+      <c r="J937" s="5" t="n"/>
+      <c r="K937" s="5" t="n"/>
+      <c r="L937" s="7" t="n"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="inlineStr">
+        <is>
+          <t>軸</t>
+        </is>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C938" s="4" t="inlineStr">
+        <is>
+          <t>車 由</t>
+        </is>
+      </c>
+      <c r="D938" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E938" s="5" t="n"/>
+      <c r="F938" s="5" t="n"/>
+      <c r="G938" s="4" t="inlineStr">
+        <is>
+          <t>車 由</t>
+        </is>
+      </c>
+      <c r="H938" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I938" s="3" t="n"/>
+      <c r="J938" s="5" t="n"/>
+      <c r="K938" s="5" t="n"/>
+      <c r="L938" s="7" t="n"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="inlineStr">
+        <is>
+          <t>奪</t>
+        </is>
+      </c>
+      <c r="B939" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C939" s="4" t="inlineStr">
+        <is>
+          <t>奞 寸</t>
+        </is>
+      </c>
+      <c r="D939" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E939" s="5" t="n"/>
+      <c r="F939" s="5" t="n"/>
+      <c r="G939" s="4" t="inlineStr">
+        <is>
+          <t>奞 大 一 人 隹 寸</t>
+        </is>
+      </c>
+      <c r="H939" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I939" s="3" t="n"/>
+      <c r="J939" s="5" t="n"/>
+      <c r="K939" s="5" t="n"/>
+      <c r="L939" s="7" t="n"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>屈</t>
+        </is>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C940" s="4" t="inlineStr">
+        <is>
+          <t>尸 出</t>
+        </is>
+      </c>
+      <c r="D940" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E940" s="5" t="n"/>
+      <c r="F940" s="5" t="n"/>
+      <c r="G940" s="4" t="inlineStr">
+        <is>
+          <t>尸 出 屮 凵 丨</t>
+        </is>
+      </c>
+      <c r="H940" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I940" s="3" t="n"/>
+      <c r="J940" s="5" t="n"/>
+      <c r="K940" s="5" t="n"/>
+      <c r="L940" s="7" t="n"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="inlineStr">
+        <is>
+          <t>偏</t>
+        </is>
+      </c>
+      <c r="B941" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C941" s="4" t="inlineStr">
+        <is>
+          <t>亻 扁</t>
+        </is>
+      </c>
+      <c r="D941" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E941" s="5" t="n"/>
+      <c r="F941" s="5" t="n"/>
+      <c r="G941" s="4" t="inlineStr">
+        <is>
+          <t>亻 扁 戶 丿 尸 冂 卄 十 丨</t>
+        </is>
+      </c>
+      <c r="H941" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I941" s="3" t="n"/>
+      <c r="J941" s="5" t="n"/>
+      <c r="K941" s="5" t="n"/>
+      <c r="L941" s="7" t="n"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>搬</t>
+        </is>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C942" s="4" t="inlineStr">
+        <is>
+          <t>扌 般</t>
+        </is>
+      </c>
+      <c r="D942" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E942" s="5" t="n"/>
+      <c r="F942" s="5" t="n"/>
+      <c r="G942" s="4" t="inlineStr">
+        <is>
+          <t>扌 般 舟 殳 𠘧 又</t>
+        </is>
+      </c>
+      <c r="H942" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I942" s="3" t="n"/>
+      <c r="J942" s="5" t="n"/>
+      <c r="K942" s="5" t="n"/>
+      <c r="L942" s="7" t="n"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="inlineStr">
+        <is>
+          <t>恨</t>
+        </is>
+      </c>
+      <c r="B943" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C943" s="4" t="inlineStr">
+        <is>
+          <t>忄 艮</t>
+        </is>
+      </c>
+      <c r="D943" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E943" s="5" t="n"/>
+      <c r="F943" s="5" t="n"/>
+      <c r="G943" s="4" t="inlineStr">
+        <is>
+          <t>忄 艮</t>
+        </is>
+      </c>
+      <c r="H943" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I943" s="3" t="n"/>
+      <c r="J943" s="5" t="n"/>
+      <c r="K943" s="5" t="n"/>
+      <c r="L943" s="7" t="n"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>抑</t>
+        </is>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C944" s="4" t="inlineStr">
+        <is>
+          <t>扌 卬</t>
+        </is>
+      </c>
+      <c r="D944" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E944" s="5" t="n"/>
+      <c r="F944" s="5" t="n"/>
+      <c r="G944" s="4" t="inlineStr">
+        <is>
+          <t>扌 卬 卩</t>
+        </is>
+      </c>
+      <c r="H944" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I944" s="3" t="n"/>
+      <c r="J944" s="5" t="n"/>
+      <c r="K944" s="5" t="n"/>
+      <c r="L944" s="7" t="n"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="inlineStr">
+        <is>
+          <t>拒</t>
+        </is>
+      </c>
+      <c r="B945" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C945" s="4" t="inlineStr">
+        <is>
+          <t>扌 巨</t>
+        </is>
+      </c>
+      <c r="D945" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E945" s="5" t="n"/>
+      <c r="F945" s="5" t="n"/>
+      <c r="G945" s="4" t="inlineStr">
+        <is>
+          <t>扌 巨</t>
+        </is>
+      </c>
+      <c r="H945" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I945" s="3" t="n"/>
+      <c r="J945" s="5" t="n"/>
+      <c r="K945" s="5" t="n"/>
+      <c r="L945" s="7" t="n"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="inlineStr">
+        <is>
+          <t>尷</t>
+        </is>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C946" s="4" t="inlineStr">
+        <is>
+          <t>尢 監</t>
+        </is>
+      </c>
+      <c r="D946" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E946" s="5" t="n"/>
+      <c r="F946" s="5" t="n"/>
+      <c r="G946" s="4" t="inlineStr">
+        <is>
+          <t>尢 監 臣 𠂉 一 皿</t>
+        </is>
+      </c>
+      <c r="H946" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I946" s="3" t="n"/>
+      <c r="J946" s="5" t="n"/>
+      <c r="K946" s="5" t="n"/>
+      <c r="L946" s="7" t="n"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="inlineStr">
+        <is>
+          <t>尬</t>
+        </is>
+      </c>
+      <c r="B947" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C947" s="4" t="inlineStr">
+        <is>
+          <t>尢 介</t>
+        </is>
+      </c>
+      <c r="D947" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E947" s="5" t="n"/>
+      <c r="F947" s="5" t="n"/>
+      <c r="G947" s="4" t="inlineStr">
+        <is>
+          <t>尢 介 人 丿 丨</t>
+        </is>
+      </c>
+      <c r="H947" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I947" s="3" t="n"/>
+      <c r="J947" s="5" t="n"/>
+      <c r="K947" s="5" t="n"/>
+      <c r="L947" s="7" t="n"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="inlineStr">
+        <is>
+          <t>悔</t>
+        </is>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C948" s="4" t="inlineStr">
+        <is>
+          <t>忄 每</t>
+        </is>
+      </c>
+      <c r="D948" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E948" s="5" t="n"/>
+      <c r="F948" s="5" t="n"/>
+      <c r="G948" s="4" t="inlineStr">
+        <is>
+          <t>忄 每 𠂉 母</t>
+        </is>
+      </c>
+      <c r="H948" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I948" s="3" t="n"/>
+      <c r="J948" s="5" t="n"/>
+      <c r="K948" s="5" t="n"/>
+      <c r="L948" s="7" t="n"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="inlineStr">
+        <is>
+          <t>拱</t>
+        </is>
+      </c>
+      <c r="B949" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C949" s="4" t="inlineStr">
+        <is>
+          <t>扌 共</t>
+        </is>
+      </c>
+      <c r="D949" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E949" s="5" t="n"/>
+      <c r="F949" s="5" t="n"/>
+      <c r="G949" s="4" t="inlineStr">
+        <is>
+          <t>扌 共 龷 卄 十 丨 一 八</t>
+        </is>
+      </c>
+      <c r="H949" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I949" s="3" t="n"/>
+      <c r="J949" s="5" t="n"/>
+      <c r="K949" s="5" t="n"/>
+      <c r="L949" s="7" t="n"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="inlineStr">
+        <is>
+          <t>距</t>
+        </is>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C950" s="4" t="inlineStr">
+        <is>
+          <t>口 止 巨</t>
+        </is>
+      </c>
+      <c r="D950" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E950" s="5" t="n"/>
+      <c r="F950" s="5" t="n"/>
+      <c r="G950" s="4" t="inlineStr">
+        <is>
+          <t>口 止 巨</t>
+        </is>
+      </c>
+      <c r="H950" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I950" s="3" t="n"/>
+      <c r="J950" s="5" t="n"/>
+      <c r="K950" s="5" t="n"/>
+      <c r="L950" s="7" t="n"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="inlineStr">
+        <is>
+          <t>默</t>
+        </is>
+      </c>
+      <c r="B951" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C951" s="4" t="inlineStr">
+        <is>
+          <t>黑 犬</t>
+        </is>
+      </c>
+      <c r="D951" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E951" s="5" t="n"/>
+      <c r="F951" s="5" t="n"/>
+      <c r="G951" s="4" t="inlineStr">
+        <is>
+          <t>黑 灬 犬</t>
+        </is>
+      </c>
+      <c r="H951" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I951" s="3" t="n"/>
+      <c r="J951" s="5" t="n"/>
+      <c r="K951" s="5" t="n"/>
+      <c r="L951" s="7" t="n"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="inlineStr">
+        <is>
+          <t>鬥</t>
+        </is>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C952" s="4" t="inlineStr">
+        <is>
+          <t>𩰋 𩰊</t>
+        </is>
+      </c>
+      <c r="D952" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E952" s="5" t="n"/>
+      <c r="F952" s="5" t="n"/>
+      <c r="G952" s="4" t="inlineStr">
+        <is>
+          <t>𩰋 𩰊</t>
+        </is>
+      </c>
+      <c r="H952" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I952" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J952" s="5" t="n"/>
+      <c r="K952" s="5" t="n"/>
+      <c r="L952" s="7" t="n"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="inlineStr">
+        <is>
+          <t>扭</t>
+        </is>
+      </c>
+      <c r="B953" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C953" s="4" t="inlineStr">
+        <is>
+          <t>扌 丑</t>
+        </is>
+      </c>
+      <c r="D953" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E953" s="5" t="n"/>
+      <c r="F953" s="5" t="n"/>
+      <c r="G953" s="4" t="inlineStr">
+        <is>
+          <t>扌 丑</t>
+        </is>
+      </c>
+      <c r="H953" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I953" s="3" t="n"/>
+      <c r="J953" s="5" t="n"/>
+      <c r="K953" s="5" t="n"/>
+      <c r="L953" s="7" t="n"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="inlineStr">
+        <is>
+          <t>猛</t>
+        </is>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C954" s="4" t="inlineStr">
+        <is>
+          <t>犭 孟</t>
+        </is>
+      </c>
+      <c r="D954" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E954" s="5" t="n"/>
+      <c r="F954" s="5" t="n"/>
+      <c r="G954" s="4" t="inlineStr">
+        <is>
+          <t>犭 孟 子 皿</t>
+        </is>
+      </c>
+      <c r="H954" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I954" s="3" t="n"/>
+      <c r="J954" s="5" t="n"/>
+      <c r="K954" s="5" t="n"/>
+      <c r="L954" s="7" t="n"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="inlineStr">
+        <is>
+          <t>愣</t>
+        </is>
+      </c>
+      <c r="B955" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C955" s="4" t="inlineStr">
+        <is>
+          <t>忄 罒 方</t>
+        </is>
+      </c>
+      <c r="D955" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E955" s="5" t="n"/>
+      <c r="F955" s="5" t="n"/>
+      <c r="G955" s="4" t="inlineStr">
+        <is>
+          <t>忄 罒 方 亠 丶 一 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H955" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I955" s="3" t="n"/>
+      <c r="J955" s="5" t="n"/>
+      <c r="K955" s="5" t="n"/>
+      <c r="L955" s="7" t="n"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="inlineStr">
+        <is>
+          <t>粥</t>
+        </is>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C956" s="4" t="inlineStr">
+        <is>
+          <t>弓 米 弓</t>
+        </is>
+      </c>
+      <c r="D956" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E956" s="5" t="n"/>
+      <c r="F956" s="5" t="n"/>
+      <c r="G956" s="4" t="inlineStr">
+        <is>
+          <t>弓 米</t>
+        </is>
+      </c>
+      <c r="H956" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I956" s="3" t="n"/>
+      <c r="J956" s="5" t="n"/>
+      <c r="K956" s="5" t="n"/>
+      <c r="L956" s="7" t="n"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="inlineStr">
+        <is>
+          <t>縷</t>
+        </is>
+      </c>
+      <c r="B957" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C957" s="4" t="inlineStr">
+        <is>
+          <t>糹 婁</t>
+        </is>
+      </c>
+      <c r="D957" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E957" s="5" t="n"/>
+      <c r="F957" s="5" t="n"/>
+      <c r="G957" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 婁 女</t>
+        </is>
+      </c>
+      <c r="H957" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I957" s="3" t="n"/>
+      <c r="J957" s="5" t="n"/>
+      <c r="K957" s="5" t="n"/>
+      <c r="L957" s="7" t="n"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="inlineStr">
+        <is>
+          <t>綢</t>
+        </is>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C958" s="4" t="inlineStr">
+        <is>
+          <t>糹 周</t>
+        </is>
+      </c>
+      <c r="D958" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E958" s="5" t="n"/>
+      <c r="F958" s="5" t="n"/>
+      <c r="G958" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 周 ⺆ 土 十 一 口</t>
+        </is>
+      </c>
+      <c r="H958" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I958" s="3" t="n"/>
+      <c r="J958" s="5" t="n"/>
+      <c r="K958" s="5" t="n"/>
+      <c r="L958" s="7" t="n"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="inlineStr">
+        <is>
+          <t>繆</t>
+        </is>
+      </c>
+      <c r="B959" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C959" s="4" t="inlineStr">
+        <is>
+          <t>糹 翏</t>
+        </is>
+      </c>
+      <c r="D959" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E959" s="5" t="n"/>
+      <c r="F959" s="5" t="n"/>
+      <c r="G959" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 翏 羽 习 𠃌 冫 人 彡</t>
+        </is>
+      </c>
+      <c r="H959" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I959" s="3" t="n"/>
+      <c r="J959" s="5" t="n"/>
+      <c r="K959" s="5" t="n"/>
+      <c r="L959" s="7" t="n"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>毋</t>
+        </is>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C960" s="4" t="n"/>
+      <c r="D960" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E960" s="5" t="n"/>
+      <c r="F960" s="5" t="n"/>
+      <c r="G960" s="4" t="n"/>
+      <c r="H960" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I960" s="3" t="n"/>
+      <c r="J960" s="5" t="n"/>
+      <c r="K960" s="5" t="n"/>
+      <c r="L960" s="7" t="n"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="inlineStr">
+        <is>
+          <t>掘</t>
+        </is>
+      </c>
+      <c r="B961" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C961" s="4" t="inlineStr">
+        <is>
+          <t>扌 屈</t>
+        </is>
+      </c>
+      <c r="D961" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E961" s="5" t="n"/>
+      <c r="F961" s="5" t="n"/>
+      <c r="G961" s="4" t="inlineStr">
+        <is>
+          <t>扌 屈 尸 出 屮 凵 丨</t>
+        </is>
+      </c>
+      <c r="H961" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I961" s="3" t="n"/>
+      <c r="J961" s="5" t="n"/>
+      <c r="K961" s="5" t="n"/>
+      <c r="L961" s="7" t="n"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>纏</t>
+        </is>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C962" s="4" t="inlineStr">
+        <is>
+          <t>糹 廛</t>
+        </is>
+      </c>
+      <c r="D962" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E962" s="5" t="n"/>
+      <c r="F962" s="5" t="n"/>
+      <c r="G962" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 廛 广 里 甲 一 儿 丿 乚 土 十</t>
+        </is>
+      </c>
+      <c r="H962" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I962" s="3" t="n"/>
+      <c r="J962" s="5" t="n"/>
+      <c r="K962" s="5" t="n"/>
+      <c r="L962" s="7" t="n"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="inlineStr">
+        <is>
+          <t>縛</t>
+        </is>
+      </c>
+      <c r="B963" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C963" s="4" t="inlineStr">
+        <is>
+          <t>糹 尃</t>
+        </is>
+      </c>
+      <c r="D963" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E963" s="5" t="n"/>
+      <c r="F963" s="5" t="n"/>
+      <c r="G963" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 尃 甫 十 月 寸</t>
+        </is>
+      </c>
+      <c r="H963" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I963" s="3" t="n"/>
+      <c r="J963" s="5" t="n"/>
+      <c r="K963" s="5" t="n"/>
+      <c r="L963" s="7" t="n"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>瓦</t>
+        </is>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C964" s="4" t="n"/>
+      <c r="D964" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E964" s="5" t="n"/>
+      <c r="F964" s="5" t="n"/>
+      <c r="G964" s="4" t="n"/>
+      <c r="H964" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I964" s="3" t="n"/>
+      <c r="J964" s="5" t="n"/>
+      <c r="K964" s="5" t="n"/>
+      <c r="L964" s="7" t="n"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="inlineStr">
+        <is>
+          <t>缶</t>
+        </is>
+      </c>
+      <c r="B965" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C965" s="4" t="n"/>
+      <c r="D965" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E965" s="5" t="n"/>
+      <c r="F965" s="5" t="n"/>
+      <c r="G965" s="4" t="n"/>
+      <c r="H965" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I965" s="3" t="n"/>
+      <c r="J965" s="5" t="n"/>
+      <c r="K965" s="5" t="n"/>
+      <c r="L965" s="7" t="n"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>饈</t>
+        </is>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C966" s="4" t="inlineStr">
+        <is>
+          <t>飠 羞</t>
+        </is>
+      </c>
+      <c r="D966" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E966" s="5" t="n"/>
+      <c r="F966" s="5" t="n"/>
+      <c r="G966" s="4" t="inlineStr">
+        <is>
+          <t>飠 人 丶 羞 丷 一 土 十 丿 丑</t>
+        </is>
+      </c>
+      <c r="H966" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I966" s="3" t="n"/>
+      <c r="J966" s="5" t="n"/>
+      <c r="K966" s="5" t="n"/>
+      <c r="L966" s="7" t="n"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>腹</t>
+        </is>
+      </c>
+      <c r="B967" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C967" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 复</t>
+        </is>
+      </c>
+      <c r="D967" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E967" s="5" t="n"/>
+      <c r="F967" s="5" t="n"/>
+      <c r="G967" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 复 𠂉 日 夊</t>
+        </is>
+      </c>
+      <c r="H967" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I967" s="3" t="n"/>
+      <c r="J967" s="5" t="n"/>
+      <c r="K967" s="5" t="n"/>
+      <c r="L967" s="7" t="n"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>惠</t>
+        </is>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C968" s="4" t="inlineStr">
+        <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="D968" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E968" s="5" t="n"/>
+      <c r="F968" s="5" t="n"/>
+      <c r="G968" s="4" t="inlineStr">
+        <is>
+          <t>心</t>
+        </is>
+      </c>
+      <c r="H968" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I968" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件</t>
+        </is>
+      </c>
+      <c r="J968" s="5" t="n"/>
+      <c r="K968" s="5" t="n"/>
+      <c r="L968" s="7" t="n"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
+        <is>
+          <t>勿</t>
+        </is>
+      </c>
+      <c r="B969" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C969" s="4" t="inlineStr">
+        <is>
+          <t>勹 丿 丿</t>
+        </is>
+      </c>
+      <c r="D969" s="4" t="inlineStr">
+        <is>
+          <t>右上包圍</t>
+        </is>
+      </c>
+      <c r="E969" s="5" t="n"/>
+      <c r="F969" s="5" t="n"/>
+      <c r="G969" s="4" t="inlineStr">
+        <is>
+          <t>勹 丿</t>
+        </is>
+      </c>
+      <c r="H969" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I969" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J969" s="5" t="n"/>
+      <c r="K969" s="5" t="n"/>
+      <c r="L969" s="7" t="n"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>凡</t>
+        </is>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C970" s="4" t="inlineStr">
+        <is>
+          <t>几 丶</t>
+        </is>
+      </c>
+      <c r="D970" s="4" t="inlineStr">
+        <is>
+          <t>上方包圍</t>
+        </is>
+      </c>
+      <c r="E970" s="5" t="n"/>
+      <c r="F970" s="5" t="n"/>
+      <c r="G970" s="4" t="inlineStr">
+        <is>
+          <t>几 丶</t>
+        </is>
+      </c>
+      <c r="H970" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I970" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J970" s="5" t="n"/>
+      <c r="K970" s="5" t="n"/>
+      <c r="L970" s="7" t="n"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>預</t>
+        </is>
+      </c>
+      <c r="B971" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C971" s="4" t="inlineStr">
+        <is>
+          <t>予 頁</t>
+        </is>
+      </c>
+      <c r="D971" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E971" s="5" t="n"/>
+      <c r="F971" s="5" t="n"/>
+      <c r="G971" s="4" t="inlineStr">
+        <is>
+          <t>予 龴 乛 亅 頁</t>
+        </is>
+      </c>
+      <c r="H971" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I971" s="3" t="n"/>
+      <c r="J971" s="5" t="n"/>
+      <c r="K971" s="5" t="n"/>
+      <c r="L971" s="7" t="n"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>悲</t>
+        </is>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C972" s="4" t="inlineStr">
+        <is>
+          <t>非 心</t>
+        </is>
+      </c>
+      <c r="D972" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E972" s="5" t="n"/>
+      <c r="F972" s="5" t="n"/>
+      <c r="G972" s="4" t="inlineStr">
+        <is>
+          <t>非 心</t>
+        </is>
+      </c>
+      <c r="H972" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I972" s="3" t="n"/>
+      <c r="J972" s="5" t="n"/>
+      <c r="K972" s="5" t="n"/>
+      <c r="L972" s="7" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>揭</t>
+        </is>
+      </c>
+      <c r="B973" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C973" s="4" t="inlineStr">
+        <is>
+          <t>扌 曷</t>
+        </is>
+      </c>
+      <c r="D973" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E973" s="5" t="n"/>
+      <c r="F973" s="5" t="n"/>
+      <c r="G973" s="4" t="inlineStr">
+        <is>
+          <t>扌 曷 日 匃 勹 亾 𠃊 人</t>
+        </is>
+      </c>
+      <c r="H973" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I973" s="3" t="n"/>
+      <c r="J973" s="5" t="n"/>
+      <c r="K973" s="5" t="n"/>
+      <c r="L973" s="7" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>卓</t>
+        </is>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C974" s="4" t="inlineStr">
+        <is>
+          <t>⺊ 早</t>
+        </is>
+      </c>
+      <c r="D974" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E974" s="5" t="n"/>
+      <c r="F974" s="5" t="n"/>
+      <c r="G974" s="4" t="inlineStr">
+        <is>
+          <t>⺊ 早 日 十</t>
+        </is>
+      </c>
+      <c r="H974" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I974" s="3" t="n"/>
+      <c r="J974" s="5" t="n"/>
+      <c r="K974" s="5" t="n"/>
+      <c r="L974" s="7" t="n"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="inlineStr">
+        <is>
+          <t>培</t>
+        </is>
+      </c>
+      <c r="B975" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C975" s="4" t="inlineStr">
+        <is>
+          <t>土 咅</t>
+        </is>
+      </c>
+      <c r="D975" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E975" s="5" t="n"/>
+      <c r="F975" s="5" t="n"/>
+      <c r="G975" s="4" t="inlineStr">
+        <is>
+          <t>土 十 一 咅 立 亠 丶 丷 口</t>
+        </is>
+      </c>
+      <c r="H975" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I975" s="3" t="n"/>
+      <c r="J975" s="5" t="n"/>
+      <c r="K975" s="5" t="n"/>
+      <c r="L975" s="7" t="n"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>裁</t>
+        </is>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C976" s="4" t="inlineStr">
+        <is>
+          <t>戈 十 衣</t>
+        </is>
+      </c>
+      <c r="D976" s="4" t="inlineStr">
+        <is>
+          <t>右上包圍</t>
+        </is>
+      </c>
+      <c r="E976" s="5" t="n"/>
+      <c r="F976" s="5" t="n"/>
+      <c r="G976" s="4" t="inlineStr">
+        <is>
+          <t>戈 弋 一 乚 丶 丿 十 衣 亠 𧘇</t>
+        </is>
+      </c>
+      <c r="H976" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I976" s="3" t="n"/>
+      <c r="J976" s="5" t="n"/>
+      <c r="K976" s="5" t="n"/>
+      <c r="L976" s="7" t="n"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="inlineStr">
+        <is>
+          <t>瑣</t>
+        </is>
+      </c>
+      <c r="B977" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C977" s="4" t="inlineStr">
+        <is>
+          <t>王 小 貝</t>
+        </is>
+      </c>
+      <c r="D977" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E977" s="5" t="n"/>
+      <c r="F977" s="5" t="n"/>
+      <c r="G977" s="4" t="inlineStr">
+        <is>
+          <t>王 一 土 十 小 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H977" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I977" s="3" t="n"/>
+      <c r="J977" s="5" t="n"/>
+      <c r="K977" s="5" t="n"/>
+      <c r="L977" s="7" t="n"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>仲</t>
+        </is>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C978" s="4" t="inlineStr">
+        <is>
+          <t>亻 中</t>
+        </is>
+      </c>
+      <c r="D978" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E978" s="5" t="n"/>
+      <c r="F978" s="5" t="n"/>
+      <c r="G978" s="4" t="inlineStr">
+        <is>
+          <t>亻 中 口 丨</t>
+        </is>
+      </c>
+      <c r="H978" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I978" s="3" t="n"/>
+      <c r="J978" s="5" t="n"/>
+      <c r="K978" s="5" t="n"/>
+      <c r="L978" s="7" t="n"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="inlineStr">
+        <is>
+          <t>賺</t>
+        </is>
+      </c>
+      <c r="B979" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C979" s="4" t="inlineStr">
+        <is>
+          <t>貝 兼</t>
+        </is>
+      </c>
+      <c r="D979" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E979" s="5" t="n"/>
+      <c r="F979" s="5" t="n"/>
+      <c r="G979" s="4" t="inlineStr">
+        <is>
+          <t>貝 目 八 兼 丷 一</t>
+        </is>
+      </c>
+      <c r="H979" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I979" s="3" t="n"/>
+      <c r="J979" s="5" t="n"/>
+      <c r="K979" s="5" t="n"/>
+      <c r="L979" s="7" t="n"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>穎</t>
+        </is>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C980" s="4" t="inlineStr">
+        <is>
+          <t>匕 禾 頁</t>
+        </is>
+      </c>
+      <c r="D980" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E980" s="5" t="n"/>
+      <c r="F980" s="5" t="n"/>
+      <c r="G980" s="4" t="inlineStr">
+        <is>
+          <t>匕 乚 一 禾 丿 木 頁</t>
+        </is>
+      </c>
+      <c r="H980" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I980" s="3" t="n"/>
+      <c r="J980" s="5" t="n"/>
+      <c r="K980" s="5" t="n"/>
+      <c r="L980" s="7" t="n"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="inlineStr">
+        <is>
+          <t>惋</t>
+        </is>
+      </c>
+      <c r="B981" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C981" s="4" t="inlineStr">
+        <is>
+          <t>忄 宛</t>
+        </is>
+      </c>
+      <c r="D981" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E981" s="5" t="n"/>
+      <c r="F981" s="5" t="n"/>
+      <c r="G981" s="4" t="inlineStr">
+        <is>
+          <t>忄 宛 宀 夗 夕 𠂊 丶 㔾</t>
+        </is>
+      </c>
+      <c r="H981" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I981" s="3" t="n"/>
+      <c r="J981" s="5" t="n"/>
+      <c r="K981" s="5" t="n"/>
+      <c r="L981" s="7" t="n"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>欠</t>
+        </is>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C982" s="4" t="n"/>
+      <c r="D982" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E982" s="5" t="n"/>
+      <c r="F982" s="5" t="n"/>
+      <c r="G982" s="4" t="n"/>
+      <c r="H982" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I982" s="3" t="n"/>
+      <c r="J982" s="5" t="n"/>
+      <c r="K982" s="5" t="n"/>
+      <c r="L982" s="7" t="n"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="inlineStr">
+        <is>
+          <t>驕</t>
+        </is>
+      </c>
+      <c r="B983" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C983" s="4" t="inlineStr">
+        <is>
+          <t>馬 喬</t>
+        </is>
+      </c>
+      <c r="D983" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E983" s="5" t="n"/>
+      <c r="F983" s="5" t="n"/>
+      <c r="G983" s="4" t="inlineStr">
+        <is>
+          <t>馬 灬 喬 呑 夭 丿 大 一 人 口 冋 冂</t>
+        </is>
+      </c>
+      <c r="H983" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I983" s="3" t="n"/>
+      <c r="J983" s="5" t="n"/>
+      <c r="K983" s="5" t="n"/>
+      <c r="L983" s="7" t="n"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>傲</t>
+        </is>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C984" s="4" t="inlineStr">
+        <is>
+          <t>亻 敖</t>
+        </is>
+      </c>
+      <c r="D984" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E984" s="5" t="n"/>
+      <c r="F984" s="5" t="n"/>
+      <c r="G984" s="4" t="inlineStr">
+        <is>
+          <t>亻 敖 士 十 一 方 亠 丶 丿 𠃌 攵</t>
+        </is>
+      </c>
+      <c r="H984" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I984" s="3" t="n"/>
+      <c r="J984" s="5" t="n"/>
+      <c r="K984" s="5" t="n"/>
+      <c r="L984" s="7" t="n"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="inlineStr">
+        <is>
+          <t>昨</t>
+        </is>
+      </c>
+      <c r="B985" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C985" s="4" t="inlineStr">
+        <is>
+          <t>日 乍</t>
+        </is>
+      </c>
+      <c r="D985" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E985" s="5" t="n"/>
+      <c r="F985" s="5" t="n"/>
+      <c r="G985" s="4" t="inlineStr">
+        <is>
+          <t>日 乍</t>
+        </is>
+      </c>
+      <c r="H985" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I985" s="3" t="n"/>
+      <c r="J985" s="5" t="n"/>
+      <c r="K985" s="5" t="n"/>
+      <c r="L985" s="7" t="n"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>耘</t>
+        </is>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C986" s="4" t="inlineStr">
+        <is>
+          <t>耒 云</t>
+        </is>
+      </c>
+      <c r="D986" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E986" s="5" t="n"/>
+      <c r="F986" s="5" t="n"/>
+      <c r="G986" s="4" t="inlineStr">
+        <is>
+          <t>耒 丿 未 云 二 一 厶</t>
+        </is>
+      </c>
+      <c r="H986" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I986" s="3" t="n"/>
+      <c r="J986" s="5" t="n"/>
+      <c r="K986" s="5" t="n"/>
+      <c r="L986" s="7" t="n"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="inlineStr">
+        <is>
+          <t>隔</t>
+        </is>
+      </c>
+      <c r="B987" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C987" s="4" t="inlineStr">
+        <is>
+          <t>阝 鬲</t>
+        </is>
+      </c>
+      <c r="D987" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E987" s="5" t="n"/>
+      <c r="F987" s="5" t="n"/>
+      <c r="G987" s="4" t="inlineStr">
+        <is>
+          <t>阝 鬲 一 口 冂 儿 丿 乚 丅 丨</t>
+        </is>
+      </c>
+      <c r="H987" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I987" s="3" t="n"/>
+      <c r="J987" s="5" t="n"/>
+      <c r="K987" s="5" t="n"/>
+      <c r="L987" s="7" t="n"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="inlineStr">
+        <is>
+          <t>茁</t>
+        </is>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C988" s="4" t="inlineStr">
+        <is>
+          <t>艹 出</t>
+        </is>
+      </c>
+      <c r="D988" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E988" s="5" t="n"/>
+      <c r="F988" s="5" t="n"/>
+      <c r="G988" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 出 屮 凵 丨</t>
+        </is>
+      </c>
+      <c r="H988" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I988" s="3" t="n"/>
+      <c r="J988" s="5" t="n"/>
+      <c r="K988" s="5" t="n"/>
+      <c r="L988" s="7" t="n"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="inlineStr">
+        <is>
+          <t>鼎</t>
+        </is>
+      </c>
+      <c r="B989" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C989" s="4" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="D989" s="4" t="inlineStr">
+        <is>
+          <t>下方包圍</t>
+        </is>
+      </c>
+      <c r="E989" s="5" t="n"/>
+      <c r="F989" s="5" t="n"/>
+      <c r="G989" s="4" t="inlineStr">
+        <is>
+          <t>目</t>
+        </is>
+      </c>
+      <c r="H989" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I989" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件</t>
+        </is>
+      </c>
+      <c r="J989" s="5" t="n"/>
+      <c r="K989" s="5" t="n"/>
+      <c r="L989" s="7" t="n"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="inlineStr">
+        <is>
+          <t>廚</t>
+        </is>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C990" s="4" t="inlineStr">
+        <is>
+          <t>广 尌</t>
+        </is>
+      </c>
+      <c r="D990" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E990" s="5" t="n"/>
+      <c r="F990" s="5" t="n"/>
+      <c r="G990" s="4" t="inlineStr">
+        <is>
+          <t>广 尌 壴 十 豆 寸</t>
+        </is>
+      </c>
+      <c r="H990" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I990" s="3" t="n"/>
+      <c r="J990" s="5" t="n"/>
+      <c r="K990" s="5" t="n"/>
+      <c r="L990" s="7" t="n"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="inlineStr">
+        <is>
+          <t>淋</t>
+        </is>
+      </c>
+      <c r="B991" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C991" s="4" t="inlineStr">
+        <is>
+          <t>氵 林</t>
+        </is>
+      </c>
+      <c r="D991" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E991" s="5" t="n"/>
+      <c r="F991" s="5" t="n"/>
+      <c r="G991" s="4" t="inlineStr">
+        <is>
+          <t>氵 林 木</t>
+        </is>
+      </c>
+      <c r="H991" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I991" s="3" t="n"/>
+      <c r="J991" s="5" t="n"/>
+      <c r="K991" s="5" t="n"/>
+      <c r="L991" s="7" t="n"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="inlineStr">
+        <is>
+          <t>晒</t>
+        </is>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C992" s="4" t="inlineStr">
+        <is>
+          <t>日 西</t>
+        </is>
+      </c>
+      <c r="D992" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E992" s="5" t="n"/>
+      <c r="F992" s="5" t="n"/>
+      <c r="G992" s="4" t="inlineStr">
+        <is>
+          <t>日 西 一 儿 丿 乚 口</t>
+        </is>
+      </c>
+      <c r="H992" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I992" s="3" t="n"/>
+      <c r="J992" s="5" t="n"/>
+      <c r="K992" s="5" t="n"/>
+      <c r="L992" s="7" t="n"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="inlineStr">
+        <is>
+          <t>覆</t>
+        </is>
+      </c>
+      <c r="B993" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C993" s="4" t="inlineStr">
+        <is>
+          <t>覀 復</t>
+        </is>
+      </c>
+      <c r="D993" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E993" s="5" t="n"/>
+      <c r="F993" s="5" t="n"/>
+      <c r="G993" s="4" t="inlineStr">
+        <is>
+          <t>覀 一 口 丨 復 彳 复 𠂉 日 夊</t>
+        </is>
+      </c>
+      <c r="H993" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I993" s="3" t="n"/>
+      <c r="J993" s="5" t="n"/>
+      <c r="K993" s="5" t="n"/>
+      <c r="L993" s="7" t="n"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="inlineStr">
+        <is>
+          <t>筍</t>
+        </is>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C994" s="4" t="inlineStr">
+        <is>
+          <t>竹 旬</t>
+        </is>
+      </c>
+      <c r="D994" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E994" s="5" t="n"/>
+      <c r="F994" s="5" t="n"/>
+      <c r="G994" s="4" t="inlineStr">
+        <is>
+          <t>竹 亇 𠂉 亅 旬 勹 日</t>
+        </is>
+      </c>
+      <c r="H994" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I994" s="3" t="n"/>
+      <c r="J994" s="5" t="n"/>
+      <c r="K994" s="5" t="n"/>
+      <c r="L994" s="7" t="n"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="inlineStr">
+        <is>
+          <t>醃</t>
+        </is>
+      </c>
+      <c r="B995" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C995" s="4" t="inlineStr">
+        <is>
+          <t>酉 奄</t>
+        </is>
+      </c>
+      <c r="D995" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E995" s="5" t="n"/>
+      <c r="F995" s="5" t="n"/>
+      <c r="G995" s="4" t="inlineStr">
+        <is>
+          <t>酉 奄 大 一 人 电 日 乚</t>
+        </is>
+      </c>
+      <c r="H995" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I995" s="3" t="n"/>
+      <c r="J995" s="5" t="n"/>
+      <c r="K995" s="5" t="n"/>
+      <c r="L995" s="7" t="n"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="inlineStr">
+        <is>
+          <t>攪</t>
+        </is>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C996" s="4" t="inlineStr">
+        <is>
+          <t>扌 覺</t>
+        </is>
+      </c>
+      <c r="D996" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E996" s="5" t="n"/>
+      <c r="F996" s="5" t="n"/>
+      <c r="G996" s="4" t="inlineStr">
+        <is>
+          <t>扌 覺 彐 冖 爻 㐅 乂 丿 乀 見 目 儿 乚</t>
+        </is>
+      </c>
+      <c r="H996" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I996" s="3" t="n"/>
+      <c r="J996" s="5" t="n"/>
+      <c r="K996" s="5" t="n"/>
+      <c r="L996" s="7" t="n"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="inlineStr">
+        <is>
+          <t>炸</t>
+        </is>
+      </c>
+      <c r="B997" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C997" s="4" t="inlineStr">
+        <is>
+          <t>火 乍</t>
+        </is>
+      </c>
+      <c r="D997" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E997" s="5" t="n"/>
+      <c r="F997" s="5" t="n"/>
+      <c r="G997" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 乍</t>
+        </is>
+      </c>
+      <c r="H997" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I997" s="3" t="n"/>
+      <c r="J997" s="5" t="n"/>
+      <c r="K997" s="5" t="n"/>
+      <c r="L997" s="7" t="n"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="inlineStr">
+        <is>
+          <t>瑩</t>
+        </is>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C998" s="4" t="inlineStr">
+        <is>
+          <t>炏 冖 玉</t>
+        </is>
+      </c>
+      <c r="D998" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E998" s="5" t="n"/>
+      <c r="F998" s="5" t="n"/>
+      <c r="G998" s="4" t="inlineStr">
+        <is>
+          <t>炏 火 八 人 冖 玉 王 一 土 十 丶</t>
+        </is>
+      </c>
+      <c r="H998" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I998" s="3" t="n"/>
+      <c r="J998" s="5" t="n"/>
+      <c r="K998" s="5" t="n"/>
+      <c r="L998" s="7" t="n"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="inlineStr">
+        <is>
+          <t>饗</t>
+        </is>
+      </c>
+      <c r="B999" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C999" s="4" t="inlineStr">
+        <is>
+          <t>鄉 食</t>
+        </is>
+      </c>
+      <c r="D999" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E999" s="5" t="n"/>
+      <c r="F999" s="5" t="n"/>
+      <c r="G999" s="4" t="inlineStr">
+        <is>
+          <t>鄉 乡 郎 丶 阝 食 人 良 艮</t>
+        </is>
+      </c>
+      <c r="H999" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I999" s="3" t="n"/>
+      <c r="J999" s="5" t="n"/>
+      <c r="K999" s="5" t="n"/>
+      <c r="L999" s="7" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="inlineStr">
+        <is>
+          <t>宴</t>
+        </is>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C1000" s="4" t="inlineStr">
+        <is>
+          <t>宀 妟</t>
+        </is>
+      </c>
+      <c r="D1000" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1000" s="5" t="n"/>
+      <c r="F1000" s="5" t="n"/>
+      <c r="G1000" s="4" t="inlineStr">
+        <is>
+          <t>宀 妟 日 女</t>
+        </is>
+      </c>
+      <c r="H1000" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1000" s="3" t="n"/>
+      <c r="J1000" s="5" t="n"/>
+      <c r="K1000" s="5" t="n"/>
+      <c r="L1000" s="7" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2" t="inlineStr">
+        <is>
+          <t>彰</t>
+        </is>
+      </c>
+      <c r="B1001" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C1001" s="4" t="inlineStr">
+        <is>
+          <t>章 彡</t>
+        </is>
+      </c>
+      <c r="D1001" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1001" s="5" t="n"/>
+      <c r="F1001" s="5" t="n"/>
+      <c r="G1001" s="4" t="inlineStr">
+        <is>
+          <t>章 立 亠 丶 一 丷 早 日 十 彡</t>
+        </is>
+      </c>
+      <c r="H1001" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1001" s="3" t="n"/>
+      <c r="J1001" s="5" t="n"/>
+      <c r="K1001" s="5" t="n"/>
+      <c r="L1001" s="7" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="inlineStr">
+        <is>
+          <t>煮</t>
+        </is>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C1002" s="4" t="inlineStr">
+        <is>
+          <t>者 灬</t>
+        </is>
+      </c>
+      <c r="D1002" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1002" s="5" t="n"/>
+      <c r="F1002" s="5" t="n"/>
+      <c r="G1002" s="4" t="inlineStr">
+        <is>
+          <t>者 耂 日 灬</t>
+        </is>
+      </c>
+      <c r="H1002" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1002" s="3" t="n"/>
+      <c r="J1002" s="5" t="n"/>
+      <c r="K1002" s="5" t="n"/>
+      <c r="L1002" s="7" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="inlineStr">
+        <is>
+          <t>豬</t>
+        </is>
+      </c>
+      <c r="B1003" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C1003" s="4" t="inlineStr">
+        <is>
+          <t>豕 者</t>
+        </is>
+      </c>
+      <c r="D1003" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1003" s="5" t="n"/>
+      <c r="F1003" s="5" t="n"/>
+      <c r="G1003" s="4" t="inlineStr">
+        <is>
+          <t>豕 一 𧰨 者 耂 日</t>
+        </is>
+      </c>
+      <c r="H1003" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1003" s="3" t="n"/>
+      <c r="J1003" s="5" t="n"/>
+      <c r="K1003" s="5" t="n"/>
+      <c r="L1003" s="7" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="inlineStr">
+        <is>
+          <t>削</t>
+        </is>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1004" s="4" t="inlineStr">
+        <is>
+          <t>肖 刂</t>
+        </is>
+      </c>
+      <c r="D1004" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1004" s="5" t="n"/>
+      <c r="F1004" s="5" t="n"/>
+      <c r="G1004" s="4" t="inlineStr">
+        <is>
+          <t>肖 ⺌ ⺼ ⺆ 冫 刂</t>
+        </is>
+      </c>
+      <c r="H1004" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1004" s="3" t="n"/>
+      <c r="J1004" s="5" t="n"/>
+      <c r="K1004" s="5" t="n"/>
+      <c r="L1004" s="7" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="inlineStr">
+        <is>
+          <t>沫</t>
+        </is>
+      </c>
+      <c r="B1005" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1005" s="4" t="inlineStr">
+        <is>
+          <t>氵 末</t>
+        </is>
+      </c>
+      <c r="D1005" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1005" s="5" t="n"/>
+      <c r="F1005" s="5" t="n"/>
+      <c r="G1005" s="4" t="inlineStr">
+        <is>
+          <t>氵 末</t>
+        </is>
+      </c>
+      <c r="H1005" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1005" s="3" t="n"/>
+      <c r="J1005" s="5" t="n"/>
+      <c r="K1005" s="5" t="n"/>
+      <c r="L1005" s="7" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="inlineStr">
+        <is>
+          <t>茶</t>
+        </is>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1006" s="4" t="inlineStr">
+        <is>
+          <t>艹 人 朩</t>
+        </is>
+      </c>
+      <c r="D1006" s="4" t="inlineStr">
+        <is>
+          <t>上中下</t>
+        </is>
+      </c>
+      <c r="E1006" s="5" t="n"/>
+      <c r="F1006" s="5" t="n"/>
+      <c r="G1006" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 人 朩</t>
+        </is>
+      </c>
+      <c r="H1006" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1006" s="3" t="n"/>
+      <c r="J1006" s="5" t="n"/>
+      <c r="K1006" s="5" t="n"/>
+      <c r="L1006" s="7" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="inlineStr">
+        <is>
+          <t>嗅</t>
+        </is>
+      </c>
+      <c r="B1007" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1007" s="4" t="inlineStr">
+        <is>
+          <t>口 臭</t>
+        </is>
+      </c>
+      <c r="D1007" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1007" s="5" t="n"/>
+      <c r="F1007" s="5" t="n"/>
+      <c r="G1007" s="4" t="inlineStr">
+        <is>
+          <t>口 臭 自 犬</t>
+        </is>
+      </c>
+      <c r="H1007" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1007" s="3" t="n"/>
+      <c r="J1007" s="5" t="n"/>
+      <c r="K1007" s="5" t="n"/>
+      <c r="L1007" s="7" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="inlineStr">
+        <is>
+          <t>按</t>
+        </is>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1008" s="4" t="inlineStr">
+        <is>
+          <t>扌 安</t>
+        </is>
+      </c>
+      <c r="D1008" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1008" s="5" t="n"/>
+      <c r="F1008" s="5" t="n"/>
+      <c r="G1008" s="4" t="inlineStr">
+        <is>
+          <t>扌 安 宀 女</t>
+        </is>
+      </c>
+      <c r="H1008" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1008" s="3" t="n"/>
+      <c r="J1008" s="5" t="n"/>
+      <c r="K1008" s="5" t="n"/>
+      <c r="L1008" s="7" t="n"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="inlineStr">
+        <is>
+          <t>舍</t>
+        </is>
+      </c>
+      <c r="B1009" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1009" s="4" t="inlineStr">
+        <is>
+          <t>人 舌</t>
+        </is>
+      </c>
+      <c r="D1009" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1009" s="5" t="n"/>
+      <c r="F1009" s="5" t="n"/>
+      <c r="G1009" s="4" t="inlineStr">
+        <is>
+          <t>人 舌 干 口</t>
+        </is>
+      </c>
+      <c r="H1009" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1009" s="3" t="n"/>
+      <c r="J1009" s="5" t="n"/>
+      <c r="K1009" s="5" t="n"/>
+      <c r="L1009" s="7" t="n"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="inlineStr">
+        <is>
+          <t>熬</t>
+        </is>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1010" s="4" t="inlineStr">
+        <is>
+          <t>敖 灬</t>
+        </is>
+      </c>
+      <c r="D1010" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1010" s="5" t="n"/>
+      <c r="F1010" s="5" t="n"/>
+      <c r="G1010" s="4" t="inlineStr">
+        <is>
+          <t>敖 士 十 一 方 亠 丶 丿 𠃌 攵 灬</t>
+        </is>
+      </c>
+      <c r="H1010" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1010" s="3" t="n"/>
+      <c r="J1010" s="5" t="n"/>
+      <c r="K1010" s="5" t="n"/>
+      <c r="L1010" s="7" t="n"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="inlineStr">
+        <is>
+          <t>砂</t>
+        </is>
+      </c>
+      <c r="B1011" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1011" s="4" t="inlineStr">
+        <is>
+          <t>石 少</t>
+        </is>
+      </c>
+      <c r="D1011" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1011" s="5" t="n"/>
+      <c r="F1011" s="5" t="n"/>
+      <c r="G1011" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 少 小</t>
+        </is>
+      </c>
+      <c r="H1011" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1011" s="3" t="n"/>
+      <c r="J1011" s="5" t="n"/>
+      <c r="K1011" s="5" t="n"/>
+      <c r="L1011" s="7" t="n"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="inlineStr">
+        <is>
+          <t>混</t>
+        </is>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1012" s="4" t="inlineStr">
+        <is>
+          <t>氵 昆</t>
+        </is>
+      </c>
+      <c r="D1012" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1012" s="5" t="n"/>
+      <c r="F1012" s="5" t="n"/>
+      <c r="G1012" s="4" t="inlineStr">
+        <is>
+          <t>氵 昆 日 比</t>
+        </is>
+      </c>
+      <c r="H1012" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1012" s="3" t="n"/>
+      <c r="J1012" s="5" t="n"/>
+      <c r="K1012" s="5" t="n"/>
+      <c r="L1012" s="7" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="inlineStr">
+        <is>
+          <t>焦</t>
+        </is>
+      </c>
+      <c r="B1013" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1013" s="4" t="inlineStr">
+        <is>
+          <t>隹 灬</t>
+        </is>
+      </c>
+      <c r="D1013" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1013" s="5" t="n"/>
+      <c r="F1013" s="5" t="n"/>
+      <c r="G1013" s="4" t="inlineStr">
+        <is>
+          <t>隹 灬</t>
+        </is>
+      </c>
+      <c r="H1013" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1013" s="3" t="n"/>
+      <c r="J1013" s="5" t="n"/>
+      <c r="K1013" s="5" t="n"/>
+      <c r="L1013" s="7" t="n"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="inlineStr">
+        <is>
+          <t>舀</t>
+        </is>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1014" s="4" t="inlineStr">
+        <is>
+          <t>爫 臼</t>
+        </is>
+      </c>
+      <c r="D1014" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1014" s="5" t="n"/>
+      <c r="F1014" s="5" t="n"/>
+      <c r="G1014" s="4" t="inlineStr">
+        <is>
+          <t>爫 丿 丶 臼</t>
+        </is>
+      </c>
+      <c r="H1014" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1014" s="3" t="n"/>
+      <c r="J1014" s="5" t="n"/>
+      <c r="K1014" s="5" t="n"/>
+      <c r="L1014" s="7" t="n"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="inlineStr">
+        <is>
+          <t>勺</t>
+        </is>
+      </c>
+      <c r="B1015" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1015" s="4" t="inlineStr">
+        <is>
+          <t>勹 丶</t>
+        </is>
+      </c>
+      <c r="D1015" s="4" t="inlineStr">
+        <is>
+          <t>右上包圍</t>
+        </is>
+      </c>
+      <c r="E1015" s="5" t="n"/>
+      <c r="F1015" s="5" t="n"/>
+      <c r="G1015" s="4" t="inlineStr">
+        <is>
+          <t>勹 丶</t>
+        </is>
+      </c>
+      <c r="H1015" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1015" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1015" s="5" t="n"/>
+      <c r="K1015" s="5" t="n"/>
+      <c r="L1015" s="7" t="n"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="inlineStr">
+        <is>
+          <t>判</t>
+        </is>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1016" s="4" t="inlineStr">
+        <is>
+          <t>半 刂</t>
+        </is>
+      </c>
+      <c r="D1016" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1016" s="5" t="n"/>
+      <c r="F1016" s="5" t="n"/>
+      <c r="G1016" s="4" t="inlineStr">
+        <is>
+          <t>半 丷 二 一 丨 刂</t>
+        </is>
+      </c>
+      <c r="H1016" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1016" s="3" t="n"/>
+      <c r="J1016" s="5" t="n"/>
+      <c r="K1016" s="5" t="n"/>
+      <c r="L1016" s="7" t="n"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="inlineStr">
+        <is>
+          <t>熄</t>
+        </is>
+      </c>
+      <c r="B1017" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1017" s="4" t="inlineStr">
+        <is>
+          <t>火 息</t>
+        </is>
+      </c>
+      <c r="D1017" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1017" s="5" t="n"/>
+      <c r="F1017" s="5" t="n"/>
+      <c r="G1017" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 息 自 心</t>
+        </is>
+      </c>
+      <c r="H1017" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1017" s="3" t="n"/>
+      <c r="J1017" s="5" t="n"/>
+      <c r="K1017" s="5" t="n"/>
+      <c r="L1017" s="7" t="n"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="inlineStr">
+        <is>
+          <t>騰</t>
+        </is>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1018" s="4" t="inlineStr">
+        <is>
+          <t>月 駦</t>
+        </is>
+      </c>
+      <c r="D1018" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1018" s="5" t="n"/>
+      <c r="F1018" s="5" t="n"/>
+      <c r="G1018" s="4" t="inlineStr">
+        <is>
+          <t>月 駦 龹 丷 夫 二 一 人 馬 灬</t>
+        </is>
+      </c>
+      <c r="H1018" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1018" s="3" t="n"/>
+      <c r="J1018" s="5" t="n"/>
+      <c r="K1018" s="5" t="n"/>
+      <c r="L1018" s="7" t="n"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="inlineStr">
+        <is>
+          <t>啜</t>
+        </is>
+      </c>
+      <c r="B1019" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1019" s="4" t="inlineStr">
+        <is>
+          <t>口 叕</t>
+        </is>
+      </c>
+      <c r="D1019" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1019" s="5" t="n"/>
+      <c r="F1019" s="5" t="n"/>
+      <c r="G1019" s="4" t="inlineStr">
+        <is>
+          <t>口 叕 双 又</t>
+        </is>
+      </c>
+      <c r="H1019" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1019" s="3" t="n"/>
+      <c r="J1019" s="5" t="n"/>
+      <c r="K1019" s="5" t="n"/>
+      <c r="L1019" s="7" t="n"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="inlineStr">
+        <is>
+          <t>淌</t>
+        </is>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1020" s="4" t="inlineStr">
+        <is>
+          <t>氵 尚</t>
+        </is>
+      </c>
+      <c r="D1020" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1020" s="5" t="n"/>
+      <c r="F1020" s="5" t="n"/>
+      <c r="G1020" s="4" t="inlineStr">
+        <is>
+          <t>氵 尚 ⺌ 冋 冂 口</t>
+        </is>
+      </c>
+      <c r="H1020" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1020" s="3" t="n"/>
+      <c r="J1020" s="5" t="n"/>
+      <c r="K1020" s="5" t="n"/>
+      <c r="L1020" s="7" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="inlineStr">
+        <is>
+          <t>沛</t>
+        </is>
+      </c>
+      <c r="B1021" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1021" s="4" t="inlineStr">
+        <is>
+          <t>氵 巿</t>
+        </is>
+      </c>
+      <c r="D1021" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1021" s="5" t="n"/>
+      <c r="F1021" s="5" t="n"/>
+      <c r="G1021" s="4" t="inlineStr">
+        <is>
+          <t>氵 巿 一 巾</t>
+        </is>
+      </c>
+      <c r="H1021" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1021" s="3" t="n"/>
+      <c r="J1021" s="5" t="n"/>
+      <c r="K1021" s="5" t="n"/>
+      <c r="L1021" s="7" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="inlineStr">
+        <is>
+          <t>舔</t>
+        </is>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1022" s="4" t="inlineStr">
+        <is>
+          <t>舌 忝</t>
+        </is>
+      </c>
+      <c r="D1022" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1022" s="5" t="n"/>
+      <c r="F1022" s="5" t="n"/>
+      <c r="G1022" s="4" t="inlineStr">
+        <is>
+          <t>舌 干 口 忝 天 一 大 人 小 丶</t>
+        </is>
+      </c>
+      <c r="H1022" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1022" s="3" t="n"/>
+      <c r="J1022" s="5" t="n"/>
+      <c r="K1022" s="5" t="n"/>
+      <c r="L1022" s="7" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="inlineStr">
+        <is>
+          <t>歐</t>
+        </is>
+      </c>
+      <c r="B1023" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1023" s="4" t="inlineStr">
+        <is>
+          <t>區 欠</t>
+        </is>
+      </c>
+      <c r="D1023" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1023" s="5" t="n"/>
+      <c r="F1023" s="5" t="n"/>
+      <c r="G1023" s="4" t="inlineStr">
+        <is>
+          <t>區 匸 品 口 吅 欠</t>
+        </is>
+      </c>
+      <c r="H1023" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1023" s="3" t="n"/>
+      <c r="J1023" s="5" t="n"/>
+      <c r="K1023" s="5" t="n"/>
+      <c r="L1023" s="7" t="n"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="inlineStr">
+        <is>
+          <t>榜</t>
+        </is>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1024" s="4" t="inlineStr">
+        <is>
+          <t>木 旁</t>
+        </is>
+      </c>
+      <c r="D1024" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1024" s="5" t="n"/>
+      <c r="F1024" s="5" t="n"/>
+      <c r="G1024" s="4" t="inlineStr">
+        <is>
+          <t>木 旁 亠 丶 一 丷 冖 方 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1024" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1024" s="3" t="n"/>
+      <c r="J1024" s="5" t="n"/>
+      <c r="K1024" s="5" t="n"/>
+      <c r="L1024" s="7" t="n"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="inlineStr">
+        <is>
+          <t>嫁</t>
+        </is>
+      </c>
+      <c r="B1025" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1025" s="4" t="inlineStr">
+        <is>
+          <t>女 家</t>
+        </is>
+      </c>
+      <c r="D1025" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1025" s="5" t="n"/>
+      <c r="F1025" s="5" t="n"/>
+      <c r="G1025" s="4" t="inlineStr">
+        <is>
+          <t>女 家 宀 豕 一 𧰨</t>
+        </is>
+      </c>
+      <c r="H1025" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1025" s="3" t="n"/>
+      <c r="J1025" s="5" t="n"/>
+      <c r="K1025" s="5" t="n"/>
+      <c r="L1025" s="7" t="n"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="inlineStr">
+        <is>
+          <t>烹</t>
+        </is>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1026" s="4" t="inlineStr">
+        <is>
+          <t>亨 灬</t>
+        </is>
+      </c>
+      <c r="D1026" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1026" s="5" t="n"/>
+      <c r="F1026" s="5" t="n"/>
+      <c r="G1026" s="4" t="inlineStr">
+        <is>
+          <t>亨 亠 丶 一 口 了 乛 亅 灬</t>
+        </is>
+      </c>
+      <c r="H1026" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1026" s="3" t="n"/>
+      <c r="J1026" s="5" t="n"/>
+      <c r="K1026" s="5" t="n"/>
+      <c r="L1026" s="7" t="n"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="inlineStr">
+        <is>
+          <t>薯</t>
+        </is>
+      </c>
+      <c r="B1027" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1027" s="4" t="inlineStr">
+        <is>
+          <t>艹 署</t>
+        </is>
+      </c>
+      <c r="D1027" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1027" s="5" t="n"/>
+      <c r="F1027" s="5" t="n"/>
+      <c r="G1027" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 署 罒 者 耂 日</t>
+        </is>
+      </c>
+      <c r="H1027" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1027" s="3" t="n"/>
+      <c r="J1027" s="5" t="n"/>
+      <c r="K1027" s="5" t="n"/>
+      <c r="L1027" s="7" t="n"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>末</t>
+        </is>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1028" s="4" t="n"/>
+      <c r="D1028" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1028" s="5" t="n"/>
+      <c r="F1028" s="5" t="n"/>
+      <c r="G1028" s="4" t="n"/>
+      <c r="H1028" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1028" s="3" t="n"/>
+      <c r="J1028" s="5" t="n"/>
+      <c r="K1028" s="5" t="n"/>
+      <c r="L1028" s="7" t="n"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="inlineStr">
+        <is>
+          <t>勁</t>
+        </is>
+      </c>
+      <c r="B1029" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1029" s="4" t="inlineStr">
+        <is>
+          <t>巠 力</t>
+        </is>
+      </c>
+      <c r="D1029" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1029" s="5" t="n"/>
+      <c r="F1029" s="5" t="n"/>
+      <c r="G1029" s="4" t="inlineStr">
+        <is>
+          <t>巠 一 巛 𡿨 工 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1029" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1029" s="3" t="n"/>
+      <c r="J1029" s="5" t="n"/>
+      <c r="K1029" s="5" t="n"/>
+      <c r="L1029" s="7" t="n"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="inlineStr">
+        <is>
+          <t>稠</t>
+        </is>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1030" s="4" t="inlineStr">
+        <is>
+          <t>禾 周</t>
+        </is>
+      </c>
+      <c r="D1030" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1030" s="5" t="n"/>
+      <c r="F1030" s="5" t="n"/>
+      <c r="G1030" s="4" t="inlineStr">
+        <is>
+          <t>禾 丿 木 周 ⺆ 土 十 一 口</t>
+        </is>
+      </c>
+      <c r="H1030" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1030" s="3" t="n"/>
+      <c r="J1030" s="5" t="n"/>
+      <c r="K1030" s="5" t="n"/>
+      <c r="L1030" s="7" t="n"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2" t="inlineStr">
+        <is>
+          <t>遂</t>
+        </is>
+      </c>
+      <c r="B1031" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1031" s="4" t="inlineStr">
+        <is>
+          <t>辶 丷 豕</t>
+        </is>
+      </c>
+      <c r="D1031" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1031" s="5" t="n"/>
+      <c r="F1031" s="5" t="n"/>
+      <c r="G1031" s="4" t="inlineStr">
+        <is>
+          <t>辶 丷 豕 一 𧰨</t>
+        </is>
+      </c>
+      <c r="H1031" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1031" s="3" t="n"/>
+      <c r="J1031" s="5" t="n"/>
+      <c r="K1031" s="5" t="n"/>
+      <c r="L1031" s="7" t="n"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="inlineStr">
+        <is>
+          <t>添</t>
+        </is>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1032" s="4" t="inlineStr">
+        <is>
+          <t>氵 忝</t>
+        </is>
+      </c>
+      <c r="D1032" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1032" s="5" t="n"/>
+      <c r="F1032" s="5" t="n"/>
+      <c r="G1032" s="4" t="inlineStr">
+        <is>
+          <t>氵 忝 天 一 大 人 小 丶</t>
+        </is>
+      </c>
+      <c r="H1032" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1032" s="3" t="n"/>
+      <c r="J1032" s="5" t="n"/>
+      <c r="K1032" s="5" t="n"/>
+      <c r="L1032" s="7" t="n"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2" t="inlineStr">
+        <is>
+          <t>含</t>
+        </is>
+      </c>
+      <c r="B1033" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1033" s="4" t="inlineStr">
+        <is>
+          <t>今 口</t>
+        </is>
+      </c>
+      <c r="D1033" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1033" s="5" t="n"/>
+      <c r="F1033" s="5" t="n"/>
+      <c r="G1033" s="4" t="inlineStr">
+        <is>
+          <t>今 亼 人 一 ㇇ 口</t>
+        </is>
+      </c>
+      <c r="H1033" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1033" s="3" t="n"/>
+      <c r="J1033" s="5" t="n"/>
+      <c r="K1033" s="5" t="n"/>
+      <c r="L1033" s="7" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="inlineStr">
+        <is>
+          <t>脂</t>
+        </is>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1034" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 旨</t>
+        </is>
+      </c>
+      <c r="D1034" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1034" s="5" t="n"/>
+      <c r="F1034" s="5" t="n"/>
+      <c r="G1034" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 旨 匕 乚 一 日</t>
+        </is>
+      </c>
+      <c r="H1034" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1034" s="3" t="n"/>
+      <c r="J1034" s="5" t="n"/>
+      <c r="K1034" s="5" t="n"/>
+      <c r="L1034" s="7" t="n"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" s="2" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="B1035" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1035" s="4" t="inlineStr">
+        <is>
+          <t>臣 𠂉 鹵 皿</t>
+        </is>
+      </c>
+      <c r="D1035" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1035" s="5" t="n"/>
+      <c r="F1035" s="5" t="n"/>
+      <c r="G1035" s="4" t="inlineStr">
+        <is>
+          <t>臣 𠂉 鹵 ⺊ 囗 㐅 丶 皿</t>
+        </is>
+      </c>
+      <c r="H1035" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1035" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1035" s="5" t="n"/>
+      <c r="K1035" s="5" t="n"/>
+      <c r="L1035" s="7" t="n"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" s="2" t="inlineStr">
+        <is>
+          <t>呈</t>
+        </is>
+      </c>
+      <c r="B1036" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1036" s="4" t="inlineStr">
+        <is>
+          <t>口 丿 土</t>
+        </is>
+      </c>
+      <c r="D1036" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1036" s="5" t="n"/>
+      <c r="F1036" s="5" t="n"/>
+      <c r="G1036" s="4" t="inlineStr">
+        <is>
+          <t>口 丿 土 十 一</t>
+        </is>
+      </c>
+      <c r="H1036" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1036" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1036" s="5" t="n"/>
+      <c r="K1036" s="5" t="n"/>
+      <c r="L1036" s="7" t="n"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" s="2" t="inlineStr">
+        <is>
+          <t>慣</t>
+        </is>
+      </c>
+      <c r="B1037" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1037" s="4" t="inlineStr">
+        <is>
+          <t>忄 貫</t>
+        </is>
+      </c>
+      <c r="D1037" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1037" s="5" t="n"/>
+      <c r="F1037" s="5" t="n"/>
+      <c r="G1037" s="4" t="inlineStr">
+        <is>
+          <t>忄 貫 毌 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1037" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1037" s="3" t="n"/>
+      <c r="J1037" s="5" t="n"/>
+      <c r="K1037" s="5" t="n"/>
+      <c r="L1037" s="7" t="n"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" s="2" t="inlineStr">
+        <is>
+          <t>徜</t>
+        </is>
+      </c>
+      <c r="B1038" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1038" s="4" t="inlineStr">
+        <is>
+          <t>彳 尚</t>
+        </is>
+      </c>
+      <c r="D1038" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1038" s="5" t="n"/>
+      <c r="F1038" s="5" t="n"/>
+      <c r="G1038" s="4" t="inlineStr">
+        <is>
+          <t>彳 尚 ⺌ 冋 冂 口</t>
+        </is>
+      </c>
+      <c r="H1038" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1038" s="3" t="n"/>
+      <c r="J1038" s="5" t="n"/>
+      <c r="K1038" s="5" t="n"/>
+      <c r="L1038" s="7" t="n"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" s="2" t="inlineStr">
+        <is>
+          <t>徉</t>
+        </is>
+      </c>
+      <c r="B1039" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1039" s="4" t="inlineStr">
+        <is>
+          <t>彳 羊</t>
+        </is>
+      </c>
+      <c r="D1039" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1039" s="5" t="n"/>
+      <c r="F1039" s="5" t="n"/>
+      <c r="G1039" s="4" t="inlineStr">
+        <is>
+          <t>彳 羊 丷 一 二 丨</t>
+        </is>
+      </c>
+      <c r="H1039" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1039" s="3" t="n"/>
+      <c r="J1039" s="5" t="n"/>
+      <c r="K1039" s="5" t="n"/>
+      <c r="L1039" s="7" t="n"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" s="2" t="inlineStr">
+        <is>
+          <t>仰</t>
+        </is>
+      </c>
+      <c r="B1040" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1040" s="4" t="inlineStr">
+        <is>
+          <t>亻 卬</t>
+        </is>
+      </c>
+      <c r="D1040" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1040" s="5" t="n"/>
+      <c r="F1040" s="5" t="n"/>
+      <c r="G1040" s="4" t="inlineStr">
+        <is>
+          <t>亻 卬 卩</t>
+        </is>
+      </c>
+      <c r="H1040" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1040" s="3" t="n"/>
+      <c r="J1040" s="5" t="n"/>
+      <c r="K1040" s="5" t="n"/>
+      <c r="L1040" s="7" t="n"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="2" t="inlineStr">
+        <is>
+          <t>緬</t>
+        </is>
+      </c>
+      <c r="B1041" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1041" s="4" t="inlineStr">
+        <is>
+          <t>糹 面</t>
+        </is>
+      </c>
+      <c r="D1041" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1041" s="5" t="n"/>
+      <c r="F1041" s="5" t="n"/>
+      <c r="G1041" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 面 丆 一 丿 囬 囗</t>
+        </is>
+      </c>
+      <c r="H1041" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1041" s="3" t="n"/>
+      <c r="J1041" s="5" t="n"/>
+      <c r="K1041" s="5" t="n"/>
+      <c r="L1041" s="7" t="n"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" s="2" t="inlineStr">
+        <is>
+          <t>甸</t>
+        </is>
+      </c>
+      <c r="B1042" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1042" s="4" t="inlineStr">
+        <is>
+          <t>勹 田</t>
+        </is>
+      </c>
+      <c r="D1042" s="4" t="inlineStr">
+        <is>
+          <t>右上包圍</t>
+        </is>
+      </c>
+      <c r="E1042" s="5" t="n"/>
+      <c r="F1042" s="5" t="n"/>
+      <c r="G1042" s="4" t="inlineStr">
+        <is>
+          <t>勹 田</t>
+        </is>
+      </c>
+      <c r="H1042" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1042" s="3" t="n"/>
+      <c r="J1042" s="5" t="n"/>
+      <c r="K1042" s="5" t="n"/>
+      <c r="L1042" s="7" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" s="2" t="inlineStr">
+        <is>
+          <t>踝</t>
+        </is>
+      </c>
+      <c r="B1043" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1043" s="4" t="inlineStr">
+        <is>
+          <t>口 止 果</t>
+        </is>
+      </c>
+      <c r="D1043" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1043" s="5" t="n"/>
+      <c r="F1043" s="5" t="n"/>
+      <c r="G1043" s="4" t="inlineStr">
+        <is>
+          <t>口 止 果 日 木</t>
+        </is>
+      </c>
+      <c r="H1043" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1043" s="3" t="n"/>
+      <c r="J1043" s="5" t="n"/>
+      <c r="K1043" s="5" t="n"/>
+      <c r="L1043" s="7" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" s="2" t="inlineStr">
+        <is>
+          <t>絨</t>
+        </is>
+      </c>
+      <c r="B1044" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1044" s="4" t="inlineStr">
+        <is>
+          <t>糹 戎</t>
+        </is>
+      </c>
+      <c r="D1044" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1044" s="5" t="n"/>
+      <c r="F1044" s="5" t="n"/>
+      <c r="G1044" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 戎 戈 弋 一 乚 丿 𠂇</t>
+        </is>
+      </c>
+      <c r="H1044" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1044" s="3" t="n"/>
+      <c r="J1044" s="5" t="n"/>
+      <c r="K1044" s="5" t="n"/>
+      <c r="L1044" s="7" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" s="2" t="inlineStr">
+        <is>
+          <t>濺</t>
+        </is>
+      </c>
+      <c r="B1045" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1045" s="4" t="inlineStr">
+        <is>
+          <t>氵 賤</t>
+        </is>
+      </c>
+      <c r="D1045" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1045" s="5" t="n"/>
+      <c r="F1045" s="5" t="n"/>
+      <c r="G1045" s="4" t="inlineStr">
+        <is>
+          <t>氵 賤 貝 目 八 戔 戈 弋 一 乚 丶 丿</t>
+        </is>
+      </c>
+      <c r="H1045" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1045" s="3" t="n"/>
+      <c r="J1045" s="5" t="n"/>
+      <c r="K1045" s="5" t="n"/>
+      <c r="L1045" s="7" t="n"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" s="2" t="inlineStr">
+        <is>
+          <t>襬</t>
+        </is>
+      </c>
+      <c r="B1046" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1046" s="4" t="inlineStr">
+        <is>
+          <t>衤 罷</t>
+        </is>
+      </c>
+      <c r="D1046" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1046" s="5" t="n"/>
+      <c r="F1046" s="5" t="n"/>
+      <c r="G1046" s="4" t="inlineStr">
+        <is>
+          <t>衤 罷 罒 能 厶 ⺼ ⺆ 冫 匕 乚 一</t>
+        </is>
+      </c>
+      <c r="H1046" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1046" s="3" t="n"/>
+      <c r="J1046" s="5" t="n"/>
+      <c r="K1046" s="5" t="n"/>
+      <c r="L1046" s="7" t="n"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" s="2" t="inlineStr">
+        <is>
+          <t>弄</t>
+        </is>
+      </c>
+      <c r="B1047" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1047" s="4" t="inlineStr">
+        <is>
+          <t>王 廾</t>
+        </is>
+      </c>
+      <c r="D1047" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1047" s="5" t="n"/>
+      <c r="F1047" s="5" t="n"/>
+      <c r="G1047" s="4" t="inlineStr">
+        <is>
+          <t>王 一 土 十 廾 丿 丨</t>
+        </is>
+      </c>
+      <c r="H1047" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1047" s="3" t="n"/>
+      <c r="J1047" s="5" t="n"/>
+      <c r="K1047" s="5" t="n"/>
+      <c r="L1047" s="7" t="n"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" s="2" t="inlineStr">
+        <is>
+          <t>恣</t>
+        </is>
+      </c>
+      <c r="B1048" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1048" s="4" t="inlineStr">
+        <is>
+          <t>次 心</t>
+        </is>
+      </c>
+      <c r="D1048" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1048" s="5" t="n"/>
+      <c r="F1048" s="5" t="n"/>
+      <c r="G1048" s="4" t="inlineStr">
+        <is>
+          <t>次 二 一 欠 心</t>
+        </is>
+      </c>
+      <c r="H1048" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1048" s="3" t="n"/>
+      <c r="J1048" s="5" t="n"/>
+      <c r="K1048" s="5" t="n"/>
+      <c r="L1048" s="7" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" s="2" t="inlineStr">
+        <is>
+          <t>批</t>
+        </is>
+      </c>
+      <c r="B1049" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1049" s="4" t="inlineStr">
+        <is>
+          <t>扌 比</t>
+        </is>
+      </c>
+      <c r="D1049" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1049" s="5" t="n"/>
+      <c r="F1049" s="5" t="n"/>
+      <c r="G1049" s="4" t="inlineStr">
+        <is>
+          <t>扌 比</t>
+        </is>
+      </c>
+      <c r="H1049" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1049" s="3" t="n"/>
+      <c r="J1049" s="5" t="n"/>
+      <c r="K1049" s="5" t="n"/>
+      <c r="L1049" s="7" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" s="2" t="inlineStr">
+        <is>
+          <t>徑</t>
+        </is>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1050" s="4" t="inlineStr">
+        <is>
+          <t>彳 巠</t>
+        </is>
+      </c>
+      <c r="D1050" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1050" s="5" t="n"/>
+      <c r="F1050" s="5" t="n"/>
+      <c r="G1050" s="4" t="inlineStr">
+        <is>
+          <t>彳 巠 一 巛 𡿨 工</t>
+        </is>
+      </c>
+      <c r="H1050" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1050" s="3" t="n"/>
+      <c r="J1050" s="5" t="n"/>
+      <c r="K1050" s="5" t="n"/>
+      <c r="L1050" s="7" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" s="2" t="inlineStr">
+        <is>
+          <t>謹</t>
+        </is>
+      </c>
+      <c r="B1051" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1051" s="4" t="inlineStr">
+        <is>
+          <t>言 堇</t>
+        </is>
+      </c>
+      <c r="D1051" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1051" s="5" t="n"/>
+      <c r="F1051" s="5" t="n"/>
+      <c r="G1051" s="4" t="inlineStr">
+        <is>
+          <t>言 堇 廿 口 龶</t>
+        </is>
+      </c>
+      <c r="H1051" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1051" s="3" t="n"/>
+      <c r="J1051" s="5" t="n"/>
+      <c r="K1051" s="5" t="n"/>
+      <c r="L1051" s="7" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" s="2" t="inlineStr">
+        <is>
+          <t>恰</t>
+        </is>
+      </c>
+      <c r="B1052" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1052" s="4" t="inlineStr">
+        <is>
+          <t>忄 合</t>
+        </is>
+      </c>
+      <c r="D1052" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1052" s="5" t="n"/>
+      <c r="F1052" s="5" t="n"/>
+      <c r="G1052" s="4" t="inlineStr">
+        <is>
+          <t>忄 合 亼 人 一 口</t>
+        </is>
+      </c>
+      <c r="H1052" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1052" s="3" t="n"/>
+      <c r="J1052" s="5" t="n"/>
+      <c r="K1052" s="5" t="n"/>
+      <c r="L1052" s="7" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" s="2" t="inlineStr">
+        <is>
+          <t>乏</t>
+        </is>
+      </c>
+      <c r="B1053" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1053" s="4" t="inlineStr">
+        <is>
+          <t>丿 之</t>
+        </is>
+      </c>
+      <c r="D1053" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1053" s="5" t="n"/>
+      <c r="F1053" s="5" t="n"/>
+      <c r="G1053" s="4" t="inlineStr">
+        <is>
+          <t>丿 之 丶</t>
+        </is>
+      </c>
+      <c r="H1053" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1053" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1053" s="5" t="n"/>
+      <c r="K1053" s="5" t="n"/>
+      <c r="L1053" s="7" t="n"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" s="2" t="inlineStr">
+        <is>
+          <t>皆</t>
+        </is>
+      </c>
+      <c r="B1054" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1054" s="4" t="inlineStr">
+        <is>
+          <t>比 白</t>
+        </is>
+      </c>
+      <c r="D1054" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1054" s="5" t="n"/>
+      <c r="F1054" s="5" t="n"/>
+      <c r="G1054" s="4" t="inlineStr">
+        <is>
+          <t>比 白</t>
+        </is>
+      </c>
+      <c r="H1054" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1054" s="3" t="n"/>
+      <c r="J1054" s="5" t="n"/>
+      <c r="K1054" s="5" t="n"/>
+      <c r="L1054" s="7" t="n"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="2" t="inlineStr">
+        <is>
+          <t>嗤</t>
+        </is>
+      </c>
+      <c r="B1055" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1055" s="4" t="inlineStr">
+        <is>
+          <t>口 蚩</t>
+        </is>
+      </c>
+      <c r="D1055" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1055" s="5" t="n"/>
+      <c r="F1055" s="5" t="n"/>
+      <c r="G1055" s="4" t="inlineStr">
+        <is>
+          <t>口 蚩 屮 凵 丨 一 虫</t>
+        </is>
+      </c>
+      <c r="H1055" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1055" s="3" t="n"/>
+      <c r="J1055" s="5" t="n"/>
+      <c r="K1055" s="5" t="n"/>
+      <c r="L1055" s="7" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="2" t="inlineStr">
+        <is>
+          <t>嗯</t>
+        </is>
+      </c>
+      <c r="B1056" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第7課</t>
+        </is>
+      </c>
+      <c r="C1056" s="4" t="inlineStr">
+        <is>
+          <t>口 恩</t>
+        </is>
+      </c>
+      <c r="D1056" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1056" s="5" t="n"/>
+      <c r="F1056" s="5" t="n"/>
+      <c r="G1056" s="4" t="inlineStr">
+        <is>
+          <t>口 恩 因 囗 大 一 人 心</t>
+        </is>
+      </c>
+      <c r="H1056" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1056" s="3" t="n"/>
+      <c r="J1056" s="5" t="n"/>
+      <c r="K1056" s="5" t="n"/>
+      <c r="L1056" s="7" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="2" t="inlineStr">
+        <is>
+          <t>隙</t>
+        </is>
+      </c>
+      <c r="B1057" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1057" s="4" t="inlineStr">
+        <is>
+          <t>阝 小 白 小</t>
+        </is>
+      </c>
+      <c r="D1057" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1057" s="5" t="n"/>
+      <c r="F1057" s="5" t="n"/>
+      <c r="G1057" s="4" t="inlineStr">
+        <is>
+          <t>阝 小 白</t>
+        </is>
+      </c>
+      <c r="H1057" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1057" s="3" t="n"/>
+      <c r="J1057" s="5" t="n"/>
+      <c r="K1057" s="5" t="n"/>
+      <c r="L1057" s="7" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="2" t="inlineStr">
+        <is>
+          <t>竄</t>
+        </is>
+      </c>
+      <c r="B1058" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1058" s="4" t="inlineStr">
+        <is>
+          <t>穴 鼠</t>
+        </is>
+      </c>
+      <c r="D1058" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1058" s="5" t="n"/>
+      <c r="F1058" s="5" t="n"/>
+      <c r="G1058" s="4" t="inlineStr">
+        <is>
+          <t>穴 宀 八 鼠 臼</t>
+        </is>
+      </c>
+      <c r="H1058" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1058" s="3" t="n"/>
+      <c r="J1058" s="5" t="n"/>
+      <c r="K1058" s="5" t="n"/>
+      <c r="L1058" s="7" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" s="2" t="inlineStr">
+        <is>
+          <t>旨</t>
+        </is>
+      </c>
+      <c r="B1059" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1059" s="4" t="inlineStr">
+        <is>
+          <t>匕 日</t>
+        </is>
+      </c>
+      <c r="D1059" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1059" s="5" t="n"/>
+      <c r="F1059" s="5" t="n"/>
+      <c r="G1059" s="4" t="inlineStr">
+        <is>
+          <t>匕 乚 一 日</t>
+        </is>
+      </c>
+      <c r="H1059" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1059" s="3" t="n"/>
+      <c r="J1059" s="5" t="n"/>
+      <c r="K1059" s="5" t="n"/>
+      <c r="L1059" s="7" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" s="2" t="inlineStr">
+        <is>
+          <t>悠</t>
+        </is>
+      </c>
+      <c r="B1060" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1060" s="4" t="inlineStr">
+        <is>
+          <t>攸 心</t>
+        </is>
+      </c>
+      <c r="D1060" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1060" s="5" t="n"/>
+      <c r="F1060" s="5" t="n"/>
+      <c r="G1060" s="4" t="inlineStr">
+        <is>
+          <t>攸 亻 丨 攵 心</t>
+        </is>
+      </c>
+      <c r="H1060" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1060" s="3" t="n"/>
+      <c r="J1060" s="5" t="n"/>
+      <c r="K1060" s="5" t="n"/>
+      <c r="L1060" s="7" t="n"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" s="2" t="inlineStr">
+        <is>
+          <t>寓</t>
+        </is>
+      </c>
+      <c r="B1061" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1061" s="4" t="inlineStr">
+        <is>
+          <t>宀 禺</t>
+        </is>
+      </c>
+      <c r="D1061" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1061" s="5" t="n"/>
+      <c r="F1061" s="5" t="n"/>
+      <c r="G1061" s="4" t="inlineStr">
+        <is>
+          <t>宀 禺</t>
+        </is>
+      </c>
+      <c r="H1061" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1061" s="3" t="n"/>
+      <c r="J1061" s="5" t="n"/>
+      <c r="K1061" s="5" t="n"/>
+      <c r="L1061" s="7" t="n"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" s="2" t="inlineStr">
+        <is>
+          <t>鷸</t>
+        </is>
+      </c>
+      <c r="B1062" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1062" s="4" t="inlineStr">
+        <is>
+          <t>矞 鳥</t>
+        </is>
+      </c>
+      <c r="D1062" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1062" s="5" t="n"/>
+      <c r="F1062" s="5" t="n"/>
+      <c r="G1062" s="4" t="inlineStr">
+        <is>
+          <t>矞 矛 龴 乛 亅 丿 冏 冂 儿 乚 口 鳥 灬</t>
+        </is>
+      </c>
+      <c r="H1062" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1062" s="3" t="n"/>
+      <c r="J1062" s="5" t="n"/>
+      <c r="K1062" s="5" t="n"/>
+      <c r="L1062" s="7" t="n"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" s="2" t="inlineStr">
+        <is>
+          <t>狡</t>
+        </is>
+      </c>
+      <c r="B1063" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1063" s="4" t="inlineStr">
+        <is>
+          <t>犭 交</t>
+        </is>
+      </c>
+      <c r="D1063" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1063" s="5" t="n"/>
+      <c r="F1063" s="5" t="n"/>
+      <c r="G1063" s="4" t="inlineStr">
+        <is>
+          <t>犭 交 亠 丶 一 父 八 乂 丿 乀</t>
+        </is>
+      </c>
+      <c r="H1063" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1063" s="3" t="n"/>
+      <c r="J1063" s="5" t="n"/>
+      <c r="K1063" s="5" t="n"/>
+      <c r="L1063" s="7" t="n"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" s="2" t="inlineStr">
+        <is>
+          <t>窟</t>
+        </is>
+      </c>
+      <c r="B1064" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1064" s="4" t="inlineStr">
+        <is>
+          <t>穴 屈</t>
+        </is>
+      </c>
+      <c r="D1064" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1064" s="5" t="n"/>
+      <c r="F1064" s="5" t="n"/>
+      <c r="G1064" s="4" t="inlineStr">
+        <is>
+          <t>穴 宀 八 屈 尸 出 屮 凵 丨</t>
+        </is>
+      </c>
+      <c r="H1064" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1064" s="3" t="n"/>
+      <c r="J1064" s="5" t="n"/>
+      <c r="K1064" s="5" t="n"/>
+      <c r="L1064" s="7" t="n"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" s="2" t="inlineStr">
+        <is>
+          <t>猾</t>
+        </is>
+      </c>
+      <c r="B1065" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1065" s="4" t="inlineStr">
+        <is>
+          <t>犭 骨</t>
+        </is>
+      </c>
+      <c r="D1065" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1065" s="5" t="n"/>
+      <c r="F1065" s="5" t="n"/>
+      <c r="G1065" s="4" t="inlineStr">
+        <is>
+          <t>犭 骨 ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1065" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1065" s="3" t="n"/>
+      <c r="J1065" s="5" t="n"/>
+      <c r="K1065" s="5" t="n"/>
+      <c r="L1065" s="7" t="n"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" s="2" t="inlineStr">
+        <is>
+          <t>騙</t>
+        </is>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1066" s="4" t="inlineStr">
+        <is>
+          <t>馬 扁</t>
+        </is>
+      </c>
+      <c r="D1066" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1066" s="5" t="n"/>
+      <c r="F1066" s="5" t="n"/>
+      <c r="G1066" s="4" t="inlineStr">
+        <is>
+          <t>馬 灬 扁 戶 丿 尸 冂 卄 十 丨</t>
+        </is>
+      </c>
+      <c r="H1066" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1066" s="3" t="n"/>
+      <c r="J1066" s="5" t="n"/>
+      <c r="K1066" s="5" t="n"/>
+      <c r="L1066" s="7" t="n"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" s="2" t="inlineStr">
+        <is>
+          <t>偽</t>
+        </is>
+      </c>
+      <c r="B1067" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1067" s="4" t="inlineStr">
+        <is>
+          <t>亻 為</t>
+        </is>
+      </c>
+      <c r="D1067" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1067" s="5" t="n"/>
+      <c r="F1067" s="5" t="n"/>
+      <c r="G1067" s="4" t="inlineStr">
+        <is>
+          <t>亻 為</t>
+        </is>
+      </c>
+      <c r="H1067" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1067" s="3" t="n"/>
+      <c r="J1067" s="5" t="n"/>
+      <c r="K1067" s="5" t="n"/>
+      <c r="L1067" s="7" t="n"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" s="2" t="inlineStr">
+        <is>
+          <t>誇</t>
+        </is>
+      </c>
+      <c r="B1068" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1068" s="4" t="inlineStr">
+        <is>
+          <t>言 夸</t>
+        </is>
+      </c>
+      <c r="D1068" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1068" s="5" t="n"/>
+      <c r="F1068" s="5" t="n"/>
+      <c r="G1068" s="4" t="inlineStr">
+        <is>
+          <t>言 夸 大 一 人 亏 丂 ㇉</t>
+        </is>
+      </c>
+      <c r="H1068" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1068" s="3" t="n"/>
+      <c r="J1068" s="5" t="n"/>
+      <c r="K1068" s="5" t="n"/>
+      <c r="L1068" s="7" t="n"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" s="2" t="inlineStr">
+        <is>
+          <t>辨</t>
+        </is>
+      </c>
+      <c r="B1069" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1069" s="4" t="inlineStr">
+        <is>
+          <t>辛 辛</t>
+        </is>
+      </c>
+      <c r="D1069" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E1069" s="5" t="n"/>
+      <c r="F1069" s="5" t="n"/>
+      <c r="G1069" s="4" t="inlineStr">
+        <is>
+          <t>辛 立 亠 丶 一 丷 十</t>
+        </is>
+      </c>
+      <c r="H1069" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1069" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件</t>
+        </is>
+      </c>
+      <c r="J1069" s="5" t="n"/>
+      <c r="K1069" s="5" t="n"/>
+      <c r="L1069" s="7" t="n"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" s="2" t="inlineStr">
+        <is>
+          <t>謊</t>
+        </is>
+      </c>
+      <c r="B1070" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1070" s="4" t="inlineStr">
+        <is>
+          <t>言 荒</t>
+        </is>
+      </c>
+      <c r="D1070" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1070" s="5" t="n"/>
+      <c r="F1070" s="5" t="n"/>
+      <c r="G1070" s="4" t="inlineStr">
+        <is>
+          <t>言 荒 艹 十 巟 亡 亠 丶 一 𠃊 儿 丿 乚 丨</t>
+        </is>
+      </c>
+      <c r="H1070" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1070" s="3" t="n"/>
+      <c r="J1070" s="5" t="n"/>
+      <c r="K1070" s="5" t="n"/>
+      <c r="L1070" s="7" t="n"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" s="2" t="inlineStr">
+        <is>
+          <t>諷</t>
+        </is>
+      </c>
+      <c r="B1071" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1071" s="4" t="inlineStr">
+        <is>
+          <t>言 風</t>
+        </is>
+      </c>
+      <c r="D1071" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1071" s="5" t="n"/>
+      <c r="F1071" s="5" t="n"/>
+      <c r="G1071" s="4" t="inlineStr">
+        <is>
+          <t>言 風 几 丿 虫</t>
+        </is>
+      </c>
+      <c r="H1071" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1071" s="3" t="n"/>
+      <c r="J1071" s="5" t="n"/>
+      <c r="K1071" s="5" t="n"/>
+      <c r="L1071" s="7" t="n"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" s="2" t="inlineStr">
+        <is>
+          <t>惕</t>
+        </is>
+      </c>
+      <c r="B1072" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1072" s="4" t="inlineStr">
+        <is>
+          <t>忄 易</t>
+        </is>
+      </c>
+      <c r="D1072" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1072" s="5" t="n"/>
+      <c r="F1072" s="5" t="n"/>
+      <c r="G1072" s="4" t="inlineStr">
+        <is>
+          <t>忄 易 日 勿 勹 丿</t>
+        </is>
+      </c>
+      <c r="H1072" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1072" s="3" t="n"/>
+      <c r="J1072" s="5" t="n"/>
+      <c r="K1072" s="5" t="n"/>
+      <c r="L1072" s="7" t="n"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" s="2" t="inlineStr">
+        <is>
+          <t>察</t>
+        </is>
+      </c>
+      <c r="B1073" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1073" s="4" t="inlineStr">
+        <is>
+          <t>宀 祭</t>
+        </is>
+      </c>
+      <c r="D1073" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1073" s="5" t="n"/>
+      <c r="F1073" s="5" t="n"/>
+      <c r="G1073" s="4" t="inlineStr">
+        <is>
+          <t>宀 祭 𠂊 冫 示</t>
+        </is>
+      </c>
+      <c r="H1073" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1073" s="3" t="n"/>
+      <c r="J1073" s="5" t="n"/>
+      <c r="K1073" s="5" t="n"/>
+      <c r="L1073" s="7" t="n"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" s="2" t="inlineStr">
+        <is>
+          <t>蔽</t>
+        </is>
+      </c>
+      <c r="B1074" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1074" s="4" t="inlineStr">
+        <is>
+          <t>艹 敝</t>
+        </is>
+      </c>
+      <c r="D1074" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1074" s="5" t="n"/>
+      <c r="F1074" s="5" t="n"/>
+      <c r="G1074" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 敝 丷 巾 八 攵</t>
+        </is>
+      </c>
+      <c r="H1074" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1074" s="3" t="n"/>
+      <c r="J1074" s="5" t="n"/>
+      <c r="K1074" s="5" t="n"/>
+      <c r="L1074" s="7" t="n"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2" t="inlineStr">
+        <is>
+          <t>虛</t>
+        </is>
+      </c>
+      <c r="B1075" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1075" s="4" t="inlineStr">
+        <is>
+          <t>虍</t>
+        </is>
+      </c>
+      <c r="D1075" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1075" s="5" t="n"/>
+      <c r="F1075" s="5" t="n"/>
+      <c r="G1075" s="4" t="inlineStr">
+        <is>
+          <t>虍 ⺊ 七 ㇀ 乚</t>
+        </is>
+      </c>
+      <c r="H1075" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1075" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件</t>
+        </is>
+      </c>
+      <c r="J1075" s="5" t="n"/>
+      <c r="K1075" s="5" t="n"/>
+      <c r="L1075" s="7" t="n"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2" t="inlineStr">
+        <is>
+          <t>亭</t>
+        </is>
+      </c>
+      <c r="B1076" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1076" s="4" t="inlineStr">
+        <is>
+          <t>亠 口 冖 丁</t>
+        </is>
+      </c>
+      <c r="D1076" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1076" s="5" t="n"/>
+      <c r="F1076" s="5" t="n"/>
+      <c r="G1076" s="4" t="inlineStr">
+        <is>
+          <t>亠 丶 一 口 冖 丁 亅</t>
+        </is>
+      </c>
+      <c r="H1076" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1076" s="3" t="n"/>
+      <c r="J1076" s="5" t="n"/>
+      <c r="K1076" s="5" t="n"/>
+      <c r="L1076" s="7" t="n"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="2" t="inlineStr">
+        <is>
+          <t>支</t>
+        </is>
+      </c>
+      <c r="B1077" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1077" s="4" t="inlineStr">
+        <is>
+          <t>十 又</t>
+        </is>
+      </c>
+      <c r="D1077" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1077" s="5" t="n"/>
+      <c r="F1077" s="5" t="n"/>
+      <c r="G1077" s="4" t="inlineStr">
+        <is>
+          <t>十 又</t>
+        </is>
+      </c>
+      <c r="H1077" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1077" s="3" t="n"/>
+      <c r="J1077" s="5" t="n"/>
+      <c r="K1077" s="5" t="n"/>
+      <c r="L1077" s="7" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2" t="inlineStr">
+        <is>
+          <t>誘</t>
+        </is>
+      </c>
+      <c r="B1078" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1078" s="4" t="inlineStr">
+        <is>
+          <t>言 秀</t>
+        </is>
+      </c>
+      <c r="D1078" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1078" s="5" t="n"/>
+      <c r="F1078" s="5" t="n"/>
+      <c r="G1078" s="4" t="inlineStr">
+        <is>
+          <t>言 秀 禾 丿 木 乃 𠄎</t>
+        </is>
+      </c>
+      <c r="H1078" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1078" s="3" t="n"/>
+      <c r="J1078" s="5" t="n"/>
+      <c r="K1078" s="5" t="n"/>
+      <c r="L1078" s="7" t="n"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="2" t="inlineStr">
+        <is>
+          <t>縣</t>
+        </is>
+      </c>
+      <c r="B1079" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1079" s="4" t="inlineStr">
+        <is>
+          <t>且 一 小 系</t>
+        </is>
+      </c>
+      <c r="D1079" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1079" s="5" t="n"/>
+      <c r="F1079" s="5" t="n"/>
+      <c r="G1079" s="4" t="inlineStr">
+        <is>
+          <t>且 一 小 系 丿 糸 幺 丶</t>
+        </is>
+      </c>
+      <c r="H1079" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1079" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1079" s="5" t="n"/>
+      <c r="K1079" s="5" t="n"/>
+      <c r="L1079" s="7" t="n"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" s="2" t="inlineStr">
+        <is>
+          <t>懿</t>
+        </is>
+      </c>
+      <c r="B1080" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1080" s="4" t="inlineStr">
+        <is>
+          <t>壹 恣</t>
+        </is>
+      </c>
+      <c r="D1080" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1080" s="5" t="n"/>
+      <c r="F1080" s="5" t="n"/>
+      <c r="G1080" s="4" t="inlineStr">
+        <is>
+          <t>壹 士 十 一 冖 豆 恣 次 二 欠 心</t>
+        </is>
+      </c>
+      <c r="H1080" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1080" s="3" t="n"/>
+      <c r="J1080" s="5" t="n"/>
+      <c r="K1080" s="5" t="n"/>
+      <c r="L1080" s="7" t="n"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" s="2" t="inlineStr">
+        <is>
+          <t>魏</t>
+        </is>
+      </c>
+      <c r="B1081" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1081" s="4" t="inlineStr">
+        <is>
+          <t>委 鬼</t>
+        </is>
+      </c>
+      <c r="D1081" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1081" s="5" t="n"/>
+      <c r="F1081" s="5" t="n"/>
+      <c r="G1081" s="4" t="inlineStr">
+        <is>
+          <t>委 禾 丿 木 女 鬼 甶 田 儿 乚 厶</t>
+        </is>
+      </c>
+      <c r="H1081" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1081" s="3" t="n"/>
+      <c r="J1081" s="5" t="n"/>
+      <c r="K1081" s="5" t="n"/>
+      <c r="L1081" s="7" t="n"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" s="2" t="inlineStr">
+        <is>
+          <t>旗</t>
+        </is>
+      </c>
+      <c r="B1082" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1082" s="4" t="inlineStr">
+        <is>
+          <t>方 𠂉 其</t>
+        </is>
+      </c>
+      <c r="D1082" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1082" s="5" t="n"/>
+      <c r="F1082" s="5" t="n"/>
+      <c r="G1082" s="4" t="inlineStr">
+        <is>
+          <t>方 亠 丶 一 丿 𠃌 𠂉 其 八</t>
+        </is>
+      </c>
+      <c r="H1082" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1082" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1082" s="5" t="n"/>
+      <c r="K1082" s="5" t="n"/>
+      <c r="L1082" s="7" t="n"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" s="2" t="inlineStr">
+        <is>
+          <t>幟</t>
+        </is>
+      </c>
+      <c r="B1083" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1083" s="4" t="inlineStr">
+        <is>
+          <t>巾 戠</t>
+        </is>
+      </c>
+      <c r="D1083" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1083" s="5" t="n"/>
+      <c r="F1083" s="5" t="n"/>
+      <c r="G1083" s="4" t="inlineStr">
+        <is>
+          <t>巾 戠 音 立 亠 丶 一 丷 日 戈 弋 乚 丿</t>
+        </is>
+      </c>
+      <c r="H1083" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1083" s="3" t="n"/>
+      <c r="J1083" s="5" t="n"/>
+      <c r="K1083" s="5" t="n"/>
+      <c r="L1083" s="7" t="n"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" s="2" t="inlineStr">
+        <is>
+          <t>崗</t>
+        </is>
+      </c>
+      <c r="B1084" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1084" s="4" t="inlineStr">
+        <is>
+          <t>山 岡</t>
+        </is>
+      </c>
+      <c r="D1084" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1084" s="5" t="n"/>
+      <c r="F1084" s="5" t="n"/>
+      <c r="G1084" s="4" t="inlineStr">
+        <is>
+          <t>山 岡 冂 丷 一</t>
+        </is>
+      </c>
+      <c r="H1084" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1084" s="3" t="n"/>
+      <c r="J1084" s="5" t="n"/>
+      <c r="K1084" s="5" t="n"/>
+      <c r="L1084" s="7" t="n"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" s="2" t="inlineStr">
+        <is>
+          <t>姓</t>
+        </is>
+      </c>
+      <c r="B1085" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1085" s="4" t="inlineStr">
+        <is>
+          <t>女 生</t>
+        </is>
+      </c>
+      <c r="D1085" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1085" s="5" t="n"/>
+      <c r="F1085" s="5" t="n"/>
+      <c r="G1085" s="4" t="inlineStr">
+        <is>
+          <t>女 生</t>
+        </is>
+      </c>
+      <c r="H1085" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1085" s="3" t="n"/>
+      <c r="J1085" s="5" t="n"/>
+      <c r="K1085" s="5" t="n"/>
+      <c r="L1085" s="7" t="n"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" s="2" t="inlineStr">
+        <is>
+          <t>倘</t>
+        </is>
+      </c>
+      <c r="B1086" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1086" s="4" t="inlineStr">
+        <is>
+          <t>亻 尚</t>
+        </is>
+      </c>
+      <c r="D1086" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1086" s="5" t="n"/>
+      <c r="F1086" s="5" t="n"/>
+      <c r="G1086" s="4" t="inlineStr">
+        <is>
+          <t>亻 尚 ⺌ 冋 冂 口</t>
+        </is>
+      </c>
+      <c r="H1086" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1086" s="3" t="n"/>
+      <c r="J1086" s="5" t="n"/>
+      <c r="K1086" s="5" t="n"/>
+      <c r="L1086" s="7" t="n"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" s="2" t="inlineStr">
+        <is>
+          <t>僮</t>
+        </is>
+      </c>
+      <c r="B1087" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1087" s="4" t="inlineStr">
+        <is>
+          <t>亻 童</t>
+        </is>
+      </c>
+      <c r="D1087" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1087" s="5" t="n"/>
+      <c r="F1087" s="5" t="n"/>
+      <c r="G1087" s="4" t="inlineStr">
+        <is>
+          <t>亻 童 立 亠 丶 一 丷 里 甲</t>
+        </is>
+      </c>
+      <c r="H1087" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1087" s="3" t="n"/>
+      <c r="J1087" s="5" t="n"/>
+      <c r="K1087" s="5" t="n"/>
+      <c r="L1087" s="7" t="n"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" s="2" t="inlineStr">
+        <is>
+          <t>薰</t>
+        </is>
+      </c>
+      <c r="B1088" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1088" s="4" t="inlineStr">
+        <is>
+          <t>艹 熏</t>
+        </is>
+      </c>
+      <c r="D1088" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1088" s="5" t="n"/>
+      <c r="F1088" s="5" t="n"/>
+      <c r="G1088" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 熏</t>
+        </is>
+      </c>
+      <c r="H1088" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1088" s="3" t="n"/>
+      <c r="J1088" s="5" t="n"/>
+      <c r="K1088" s="5" t="n"/>
+      <c r="L1088" s="7" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" s="2" t="inlineStr">
+        <is>
+          <t>撤</t>
+        </is>
+      </c>
+      <c r="B1089" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1089" s="4" t="inlineStr">
+        <is>
+          <t>扌 育 攵</t>
+        </is>
+      </c>
+      <c r="D1089" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E1089" s="5" t="n"/>
+      <c r="F1089" s="5" t="n"/>
+      <c r="G1089" s="4" t="inlineStr">
+        <is>
+          <t>扌 育 一 厶 ⺼ ⺆ 冫 攵</t>
+        </is>
+      </c>
+      <c r="H1089" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1089" s="3" t="n"/>
+      <c r="J1089" s="5" t="n"/>
+      <c r="K1089" s="5" t="n"/>
+      <c r="L1089" s="7" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" s="2" t="inlineStr">
+        <is>
+          <t>諸</t>
+        </is>
+      </c>
+      <c r="B1090" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1090" s="4" t="inlineStr">
+        <is>
+          <t>言 者</t>
+        </is>
+      </c>
+      <c r="D1090" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1090" s="5" t="n"/>
+      <c r="F1090" s="5" t="n"/>
+      <c r="G1090" s="4" t="inlineStr">
+        <is>
+          <t>言 者 耂 日</t>
+        </is>
+      </c>
+      <c r="H1090" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1090" s="3" t="n"/>
+      <c r="J1090" s="5" t="n"/>
+      <c r="K1090" s="5" t="n"/>
+      <c r="L1090" s="7" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" s="2" t="inlineStr">
+        <is>
+          <t>葛</t>
+        </is>
+      </c>
+      <c r="B1091" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1091" s="4" t="inlineStr">
+        <is>
+          <t>艹 曷</t>
+        </is>
+      </c>
+      <c r="D1091" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1091" s="5" t="n"/>
+      <c r="F1091" s="5" t="n"/>
+      <c r="G1091" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 曷 日 匃 勹 亾 𠃊 人</t>
+        </is>
+      </c>
+      <c r="H1091" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1091" s="3" t="n"/>
+      <c r="J1091" s="5" t="n"/>
+      <c r="K1091" s="5" t="n"/>
+      <c r="L1091" s="7" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="2" t="inlineStr">
+        <is>
+          <t>慎</t>
+        </is>
+      </c>
+      <c r="B1092" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1092" s="4" t="inlineStr">
+        <is>
+          <t>忄 真</t>
+        </is>
+      </c>
+      <c r="D1092" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1092" s="5" t="n"/>
+      <c r="F1092" s="5" t="n"/>
+      <c r="G1092" s="4" t="inlineStr">
+        <is>
+          <t>忄 真 十 具 且 一 八</t>
+        </is>
+      </c>
+      <c r="H1092" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1092" s="3" t="n"/>
+      <c r="J1092" s="5" t="n"/>
+      <c r="K1092" s="5" t="n"/>
+      <c r="L1092" s="7" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="2" t="inlineStr">
+        <is>
+          <t>丞</t>
+        </is>
+      </c>
+      <c r="B1093" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第9課</t>
+        </is>
+      </c>
+      <c r="C1093" s="4" t="inlineStr">
+        <is>
+          <t>氶 一</t>
+        </is>
+      </c>
+      <c r="D1093" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1093" s="5" t="n"/>
+      <c r="F1093" s="5" t="n"/>
+      <c r="G1093" s="4" t="inlineStr">
+        <is>
+          <t>氶 乛 水 ㇇ 亅 乀 丿 一</t>
+        </is>
+      </c>
+      <c r="H1093" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1093" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1093" s="5" t="n"/>
+      <c r="K1093" s="5" t="n"/>
+      <c r="L1093" s="7" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="2" t="inlineStr">
+        <is>
+          <t>耶</t>
+        </is>
+      </c>
+      <c r="B1094" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1094" s="4" t="inlineStr">
+        <is>
+          <t>耳 阝</t>
+        </is>
+      </c>
+      <c r="D1094" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1094" s="5" t="n"/>
+      <c r="F1094" s="5" t="n"/>
+      <c r="G1094" s="4" t="inlineStr">
+        <is>
+          <t>耳 阝</t>
+        </is>
+      </c>
+      <c r="H1094" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1094" s="3" t="n"/>
+      <c r="J1094" s="5" t="n"/>
+      <c r="K1094" s="5" t="n"/>
+      <c r="L1094" s="7" t="n"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="2" t="inlineStr">
+        <is>
+          <t>慈</t>
+        </is>
+      </c>
+      <c r="B1095" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1095" s="4" t="inlineStr">
+        <is>
+          <t>兹 心</t>
+        </is>
+      </c>
+      <c r="D1095" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1095" s="5" t="n"/>
+      <c r="F1095" s="5" t="n"/>
+      <c r="G1095" s="4" t="inlineStr">
+        <is>
+          <t>兹 丷 一 幺 丶 心</t>
+        </is>
+      </c>
+      <c r="H1095" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1095" s="3" t="n"/>
+      <c r="J1095" s="5" t="n"/>
+      <c r="K1095" s="5" t="n"/>
+      <c r="L1095" s="7" t="n"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" s="2" t="inlineStr">
+        <is>
+          <t>祥</t>
+        </is>
+      </c>
+      <c r="B1096" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1096" s="4" t="inlineStr">
+        <is>
+          <t>礻 羊</t>
+        </is>
+      </c>
+      <c r="D1096" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1096" s="5" t="n"/>
+      <c r="F1096" s="5" t="n"/>
+      <c r="G1096" s="4" t="inlineStr">
+        <is>
+          <t>礻 羊 丷 一 二 丨</t>
+        </is>
+      </c>
+      <c r="H1096" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1096" s="3" t="n"/>
+      <c r="J1096" s="5" t="n"/>
+      <c r="K1096" s="5" t="n"/>
+      <c r="L1096" s="7" t="n"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" s="2" t="inlineStr">
+        <is>
+          <t>劈</t>
+        </is>
+      </c>
+      <c r="B1097" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1097" s="4" t="inlineStr">
+        <is>
+          <t>辟 刀</t>
+        </is>
+      </c>
+      <c r="D1097" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1097" s="5" t="n"/>
+      <c r="F1097" s="5" t="n"/>
+      <c r="G1097" s="4" t="inlineStr">
+        <is>
+          <t>辟 尸 口 辛 立 亠 丶 一 丷 十 刀 𠃌 丿</t>
+        </is>
+      </c>
+      <c r="H1097" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1097" s="3" t="n"/>
+      <c r="J1097" s="5" t="n"/>
+      <c r="K1097" s="5" t="n"/>
+      <c r="L1097" s="7" t="n"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" s="2" t="inlineStr">
+        <is>
+          <t>啪</t>
+        </is>
+      </c>
+      <c r="B1098" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1098" s="4" t="inlineStr">
+        <is>
+          <t>口 拍</t>
+        </is>
+      </c>
+      <c r="D1098" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1098" s="5" t="n"/>
+      <c r="F1098" s="5" t="n"/>
+      <c r="G1098" s="4" t="inlineStr">
+        <is>
+          <t>口 拍 扌 白</t>
+        </is>
+      </c>
+      <c r="H1098" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1098" s="3" t="n"/>
+      <c r="J1098" s="5" t="n"/>
+      <c r="K1098" s="5" t="n"/>
+      <c r="L1098" s="7" t="n"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" s="2" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="B1099" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1099" s="4" t="inlineStr">
+        <is>
+          <t>雨 令</t>
+        </is>
+      </c>
+      <c r="D1099" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1099" s="5" t="n"/>
+      <c r="F1099" s="5" t="n"/>
+      <c r="G1099" s="4" t="inlineStr">
+        <is>
+          <t>雨 一 冂 丨 丷 八 令 亼 人 龴</t>
+        </is>
+      </c>
+      <c r="H1099" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1099" s="3" t="n"/>
+      <c r="J1099" s="5" t="n"/>
+      <c r="K1099" s="5" t="n"/>
+      <c r="L1099" s="7" t="n"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="2" t="inlineStr">
+        <is>
+          <t>厭</t>
+        </is>
+      </c>
+      <c r="B1100" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1100" s="4" t="inlineStr">
+        <is>
+          <t>厂 猒</t>
+        </is>
+      </c>
+      <c r="D1100" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1100" s="5" t="n"/>
+      <c r="F1100" s="5" t="n"/>
+      <c r="G1100" s="4" t="inlineStr">
+        <is>
+          <t>厂 猒 冐 日 月 犬</t>
+        </is>
+      </c>
+      <c r="H1100" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1100" s="3" t="n"/>
+      <c r="J1100" s="5" t="n"/>
+      <c r="K1100" s="5" t="n"/>
+      <c r="L1100" s="7" t="n"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" s="2" t="inlineStr">
+        <is>
+          <t>倦</t>
+        </is>
+      </c>
+      <c r="B1101" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1101" s="4" t="inlineStr">
+        <is>
+          <t>亻 卷</t>
+        </is>
+      </c>
+      <c r="D1101" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1101" s="5" t="n"/>
+      <c r="F1101" s="5" t="n"/>
+      <c r="G1101" s="4" t="inlineStr">
+        <is>
+          <t>亻 卷 龹 丷 夫 二 一 人 㔾</t>
+        </is>
+      </c>
+      <c r="H1101" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1101" s="3" t="n"/>
+      <c r="J1101" s="5" t="n"/>
+      <c r="K1101" s="5" t="n"/>
+      <c r="L1101" s="7" t="n"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" s="2" t="inlineStr">
+        <is>
+          <t>辯</t>
+        </is>
+      </c>
+      <c r="B1102" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1102" s="4" t="inlineStr">
+        <is>
+          <t>辛 言 辛</t>
+        </is>
+      </c>
+      <c r="D1102" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E1102" s="5" t="n"/>
+      <c r="F1102" s="5" t="n"/>
+      <c r="G1102" s="4" t="inlineStr">
+        <is>
+          <t>辛 立 亠 丶 一 丷 十 言</t>
+        </is>
+      </c>
+      <c r="H1102" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1102" s="3" t="n"/>
+      <c r="J1102" s="5" t="n"/>
+      <c r="K1102" s="5" t="n"/>
+      <c r="L1102" s="7" t="n"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" s="2" t="inlineStr">
+        <is>
+          <t>私</t>
+        </is>
+      </c>
+      <c r="B1103" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1103" s="4" t="inlineStr">
+        <is>
+          <t>禾 厶</t>
+        </is>
+      </c>
+      <c r="D1103" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1103" s="5" t="n"/>
+      <c r="F1103" s="5" t="n"/>
+      <c r="G1103" s="4" t="inlineStr">
+        <is>
+          <t>禾 丿 木 厶</t>
+        </is>
+      </c>
+      <c r="H1103" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1103" s="3" t="n"/>
+      <c r="J1103" s="5" t="n"/>
+      <c r="K1103" s="5" t="n"/>
+      <c r="L1103" s="7" t="n"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" s="2" t="inlineStr">
+        <is>
+          <t>貧</t>
+        </is>
+      </c>
+      <c r="B1104" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1104" s="4" t="inlineStr">
+        <is>
+          <t>分 貝</t>
+        </is>
+      </c>
+      <c r="D1104" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1104" s="5" t="n"/>
+      <c r="F1104" s="5" t="n"/>
+      <c r="G1104" s="4" t="inlineStr">
+        <is>
+          <t>分 八 刀 𠃌 丿 貝 目</t>
+        </is>
+      </c>
+      <c r="H1104" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1104" s="3" t="n"/>
+      <c r="J1104" s="5" t="n"/>
+      <c r="K1104" s="5" t="n"/>
+      <c r="L1104" s="7" t="n"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" s="2" t="inlineStr">
+        <is>
+          <t>係</t>
+        </is>
+      </c>
+      <c r="B1105" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1105" s="4" t="inlineStr">
+        <is>
+          <t>亻 系</t>
+        </is>
+      </c>
+      <c r="D1105" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1105" s="5" t="n"/>
+      <c r="F1105" s="5" t="n"/>
+      <c r="G1105" s="4" t="inlineStr">
+        <is>
+          <t>亻 系 丿 糸 幺 丶 小</t>
+        </is>
+      </c>
+      <c r="H1105" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1105" s="3" t="n"/>
+      <c r="J1105" s="5" t="n"/>
+      <c r="K1105" s="5" t="n"/>
+      <c r="L1105" s="7" t="n"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" s="2" t="inlineStr">
+        <is>
+          <t>趁</t>
+        </is>
+      </c>
+      <c r="B1106" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1106" s="4" t="inlineStr">
+        <is>
+          <t>走 人 彡</t>
+        </is>
+      </c>
+      <c r="D1106" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1106" s="5" t="n"/>
+      <c r="F1106" s="5" t="n"/>
+      <c r="G1106" s="4" t="inlineStr">
+        <is>
+          <t>走 土 十 一 龰 人 彡</t>
+        </is>
+      </c>
+      <c r="H1106" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1106" s="3" t="n"/>
+      <c r="J1106" s="5" t="n"/>
+      <c r="K1106" s="5" t="n"/>
+      <c r="L1106" s="7" t="n"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" s="2" t="inlineStr">
+        <is>
+          <t>稍</t>
+        </is>
+      </c>
+      <c r="B1107" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1107" s="4" t="inlineStr">
+        <is>
+          <t>禾 肖</t>
+        </is>
+      </c>
+      <c r="D1107" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1107" s="5" t="n"/>
+      <c r="F1107" s="5" t="n"/>
+      <c r="G1107" s="4" t="inlineStr">
+        <is>
+          <t>禾 丿 木 肖 ⺌ ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1107" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1107" s="3" t="n"/>
+      <c r="J1107" s="5" t="n"/>
+      <c r="K1107" s="5" t="n"/>
+      <c r="L1107" s="7" t="n"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" s="2" t="inlineStr">
+        <is>
+          <t>烘</t>
+        </is>
+      </c>
+      <c r="B1108" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1108" s="4" t="inlineStr">
+        <is>
+          <t>火 共</t>
+        </is>
+      </c>
+      <c r="D1108" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1108" s="5" t="n"/>
+      <c r="F1108" s="5" t="n"/>
+      <c r="G1108" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 共 龷 卄 十 丨 一</t>
+        </is>
+      </c>
+      <c r="H1108" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1108" s="3" t="n"/>
+      <c r="J1108" s="5" t="n"/>
+      <c r="K1108" s="5" t="n"/>
+      <c r="L1108" s="7" t="n"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" s="2" t="inlineStr">
+        <is>
+          <t>衷</t>
+        </is>
+      </c>
+      <c r="B1109" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1109" s="4" t="inlineStr">
+        <is>
+          <t>亠 中 𧘇</t>
+        </is>
+      </c>
+      <c r="D1109" s="4" t="inlineStr">
+        <is>
+          <t>上中下</t>
+        </is>
+      </c>
+      <c r="E1109" s="5" t="n"/>
+      <c r="F1109" s="5" t="n"/>
+      <c r="G1109" s="4" t="inlineStr">
+        <is>
+          <t>亠 丶 一 中 口 丨 𧘇</t>
+        </is>
+      </c>
+      <c r="H1109" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1109" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1109" s="5" t="n"/>
+      <c r="K1109" s="5" t="n"/>
+      <c r="L1109" s="7" t="n"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" s="2" t="inlineStr">
+        <is>
+          <t>鋼</t>
+        </is>
+      </c>
+      <c r="B1110" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1110" s="4" t="inlineStr">
+        <is>
+          <t>金 岡</t>
+        </is>
+      </c>
+      <c r="D1110" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1110" s="5" t="n"/>
+      <c r="F1110" s="5" t="n"/>
+      <c r="G1110" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 岡 冂 山</t>
+        </is>
+      </c>
+      <c r="H1110" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1110" s="3" t="n"/>
+      <c r="J1110" s="5" t="n"/>
+      <c r="K1110" s="5" t="n"/>
+      <c r="L1110" s="7" t="n"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" s="2" t="inlineStr">
+        <is>
+          <t>楓</t>
+        </is>
+      </c>
+      <c r="B1111" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1111" s="4" t="inlineStr">
+        <is>
+          <t>木 風</t>
+        </is>
+      </c>
+      <c r="D1111" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1111" s="5" t="n"/>
+      <c r="F1111" s="5" t="n"/>
+      <c r="G1111" s="4" t="inlineStr">
+        <is>
+          <t>木 風 几 丿 虫</t>
+        </is>
+      </c>
+      <c r="H1111" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1111" s="3" t="n"/>
+      <c r="J1111" s="5" t="n"/>
+      <c r="K1111" s="5" t="n"/>
+      <c r="L1111" s="7" t="n"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" s="2" t="inlineStr">
+        <is>
+          <t>恢</t>
+        </is>
+      </c>
+      <c r="B1112" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1112" s="4" t="inlineStr">
+        <is>
+          <t>忄 灰</t>
+        </is>
+      </c>
+      <c r="D1112" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1112" s="5" t="n"/>
+      <c r="F1112" s="5" t="n"/>
+      <c r="G1112" s="4" t="inlineStr">
+        <is>
+          <t>忄 灰 𠂇 火 八 人</t>
+        </is>
+      </c>
+      <c r="H1112" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1112" s="3" t="n"/>
+      <c r="J1112" s="5" t="n"/>
+      <c r="K1112" s="5" t="n"/>
+      <c r="L1112" s="7" t="n"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" s="2" t="inlineStr">
+        <is>
+          <t>潑</t>
+        </is>
+      </c>
+      <c r="B1113" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1113" s="4" t="inlineStr">
+        <is>
+          <t>氵 發</t>
+        </is>
+      </c>
+      <c r="D1113" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1113" s="5" t="n"/>
+      <c r="F1113" s="5" t="n"/>
+      <c r="G1113" s="4" t="inlineStr">
+        <is>
+          <t>氵 發 癶 弓 殳 𠘧 又</t>
+        </is>
+      </c>
+      <c r="H1113" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1113" s="3" t="n"/>
+      <c r="J1113" s="5" t="n"/>
+      <c r="K1113" s="5" t="n"/>
+      <c r="L1113" s="7" t="n"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" s="2" t="inlineStr">
+        <is>
+          <t>莓</t>
+        </is>
+      </c>
+      <c r="B1114" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1114" s="4" t="inlineStr">
+        <is>
+          <t>艹 每</t>
+        </is>
+      </c>
+      <c r="D1114" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1114" s="5" t="n"/>
+      <c r="F1114" s="5" t="n"/>
+      <c r="G1114" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 每 𠂉 母</t>
+        </is>
+      </c>
+      <c r="H1114" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1114" s="3" t="n"/>
+      <c r="J1114" s="5" t="n"/>
+      <c r="K1114" s="5" t="n"/>
+      <c r="L1114" s="7" t="n"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" s="2" t="inlineStr">
+        <is>
+          <t>廳</t>
+        </is>
+      </c>
+      <c r="B1115" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1115" s="4" t="inlineStr">
+        <is>
+          <t>广 聽</t>
+        </is>
+      </c>
+      <c r="D1115" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1115" s="5" t="n"/>
+      <c r="F1115" s="5" t="n"/>
+      <c r="G1115" s="4" t="inlineStr">
+        <is>
+          <t>广 聽 耳 壬 一 士 十 罒 心</t>
+        </is>
+      </c>
+      <c r="H1115" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1115" s="3" t="n"/>
+      <c r="J1115" s="5" t="n"/>
+      <c r="K1115" s="5" t="n"/>
+      <c r="L1115" s="7" t="n"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" s="2" t="inlineStr">
+        <is>
+          <t>額</t>
+        </is>
+      </c>
+      <c r="B1116" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1116" s="4" t="inlineStr">
+        <is>
+          <t>客 頁</t>
+        </is>
+      </c>
+      <c r="D1116" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1116" s="5" t="n"/>
+      <c r="F1116" s="5" t="n"/>
+      <c r="G1116" s="4" t="inlineStr">
+        <is>
+          <t>客 宀 各 夂 口 頁</t>
+        </is>
+      </c>
+      <c r="H1116" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1116" s="3" t="n"/>
+      <c r="J1116" s="5" t="n"/>
+      <c r="K1116" s="5" t="n"/>
+      <c r="L1116" s="7" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" s="2" t="inlineStr">
+        <is>
+          <t>灌</t>
+        </is>
+      </c>
+      <c r="B1117" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1117" s="4" t="inlineStr">
+        <is>
+          <t>氵 雚</t>
+        </is>
+      </c>
+      <c r="D1117" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1117" s="5" t="n"/>
+      <c r="F1117" s="5" t="n"/>
+      <c r="G1117" s="4" t="inlineStr">
+        <is>
+          <t>氵 雚 艹 十 吅 口 隹</t>
+        </is>
+      </c>
+      <c r="H1117" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1117" s="3" t="n"/>
+      <c r="J1117" s="5" t="n"/>
+      <c r="K1117" s="5" t="n"/>
+      <c r="L1117" s="7" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" s="2" t="inlineStr">
+        <is>
+          <t>醉</t>
+        </is>
+      </c>
+      <c r="B1118" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1118" s="4" t="inlineStr">
+        <is>
+          <t>酉 卒</t>
+        </is>
+      </c>
+      <c r="D1118" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1118" s="5" t="n"/>
+      <c r="F1118" s="5" t="n"/>
+      <c r="G1118" s="4" t="inlineStr">
+        <is>
+          <t>酉 卒 亠 丶 一 从 人 十</t>
+        </is>
+      </c>
+      <c r="H1118" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1118" s="3" t="n"/>
+      <c r="J1118" s="5" t="n"/>
+      <c r="K1118" s="5" t="n"/>
+      <c r="L1118" s="7" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" s="2" t="inlineStr">
+        <is>
+          <t>釀</t>
+        </is>
+      </c>
+      <c r="B1119" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1119" s="4" t="inlineStr">
+        <is>
+          <t>酉 襄</t>
+        </is>
+      </c>
+      <c r="D1119" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1119" s="5" t="n"/>
+      <c r="F1119" s="5" t="n"/>
+      <c r="G1119" s="4" t="inlineStr">
+        <is>
+          <t>酉 襄 亠 丶 一 吅 口 井 𧘇</t>
+        </is>
+      </c>
+      <c r="H1119" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1119" s="3" t="n"/>
+      <c r="J1119" s="5" t="n"/>
+      <c r="K1119" s="5" t="n"/>
+      <c r="L1119" s="7" t="n"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" s="2" t="inlineStr">
+        <is>
+          <t>替</t>
+        </is>
+      </c>
+      <c r="B1120" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1120" s="4" t="inlineStr">
+        <is>
+          <t>夫 夫 日</t>
+        </is>
+      </c>
+      <c r="D1120" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1120" s="5" t="n"/>
+      <c r="F1120" s="5" t="n"/>
+      <c r="G1120" s="4" t="inlineStr">
+        <is>
+          <t>夫 二 一 人 日</t>
+        </is>
+      </c>
+      <c r="H1120" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1120" s="3" t="n"/>
+      <c r="J1120" s="5" t="n"/>
+      <c r="K1120" s="5" t="n"/>
+      <c r="L1120" s="7" t="n"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" s="2" t="inlineStr">
+        <is>
+          <t>諒</t>
+        </is>
+      </c>
+      <c r="B1121" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1121" s="4" t="inlineStr">
+        <is>
+          <t>言 京</t>
+        </is>
+      </c>
+      <c r="D1121" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1121" s="5" t="n"/>
+      <c r="F1121" s="5" t="n"/>
+      <c r="G1121" s="4" t="inlineStr">
+        <is>
+          <t>言 京 亠 丶 一 口 小</t>
+        </is>
+      </c>
+      <c r="H1121" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1121" s="3" t="n"/>
+      <c r="J1121" s="5" t="n"/>
+      <c r="K1121" s="5" t="n"/>
+      <c r="L1121" s="7" t="n"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" s="2" t="inlineStr">
+        <is>
+          <t>脣</t>
+        </is>
+      </c>
+      <c r="B1122" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1122" s="4" t="inlineStr">
+        <is>
+          <t>辰 ⺼</t>
+        </is>
+      </c>
+      <c r="D1122" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1122" s="5" t="n"/>
+      <c r="F1122" s="5" t="n"/>
+      <c r="G1122" s="4" t="inlineStr">
+        <is>
+          <t>辰 厂 二 一 𠄌 乀 丿 ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1122" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1122" s="3" t="n"/>
+      <c r="J1122" s="5" t="n"/>
+      <c r="K1122" s="5" t="n"/>
+      <c r="L1122" s="7" t="n"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" s="2" t="inlineStr">
+        <is>
+          <t>奔</t>
+        </is>
+      </c>
+      <c r="B1123" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1123" s="4" t="inlineStr">
+        <is>
+          <t>大 卉</t>
+        </is>
+      </c>
+      <c r="D1123" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1123" s="5" t="n"/>
+      <c r="F1123" s="5" t="n"/>
+      <c r="G1123" s="4" t="inlineStr">
+        <is>
+          <t>大 一 人 卉 十 廾 丿 丨</t>
+        </is>
+      </c>
+      <c r="H1123" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1123" s="3" t="n"/>
+      <c r="J1123" s="5" t="n"/>
+      <c r="K1123" s="5" t="n"/>
+      <c r="L1123" s="7" t="n"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" s="2" t="inlineStr">
+        <is>
+          <t>乞</t>
+        </is>
+      </c>
+      <c r="B1124" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1124" s="4" t="inlineStr">
+        <is>
+          <t>𠂉 乙</t>
+        </is>
+      </c>
+      <c r="D1124" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1124" s="5" t="n"/>
+      <c r="F1124" s="5" t="n"/>
+      <c r="G1124" s="4" t="inlineStr">
+        <is>
+          <t>𠂉 乙</t>
+        </is>
+      </c>
+      <c r="H1124" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1124" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1124" s="5" t="n"/>
+      <c r="K1124" s="5" t="n"/>
+      <c r="L1124" s="7" t="n"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" s="2" t="inlineStr">
+        <is>
+          <t>某</t>
+        </is>
+      </c>
+      <c r="B1125" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1125" s="4" t="inlineStr">
+        <is>
+          <t>甘 朩</t>
+        </is>
+      </c>
+      <c r="D1125" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1125" s="5" t="n"/>
+      <c r="F1125" s="5" t="n"/>
+      <c r="G1125" s="4" t="inlineStr">
+        <is>
+          <t>甘 朩</t>
+        </is>
+      </c>
+      <c r="H1125" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1125" s="3" t="n"/>
+      <c r="J1125" s="5" t="n"/>
+      <c r="K1125" s="5" t="n"/>
+      <c r="L1125" s="7" t="n"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" s="2" t="inlineStr">
+        <is>
+          <t>煥</t>
+        </is>
+      </c>
+      <c r="B1126" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1126" s="4" t="inlineStr">
+        <is>
+          <t>火 奐</t>
+        </is>
+      </c>
+      <c r="D1126" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1126" s="5" t="n"/>
+      <c r="F1126" s="5" t="n"/>
+      <c r="G1126" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 奐 𠂊 冂 大 一</t>
+        </is>
+      </c>
+      <c r="H1126" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1126" s="3" t="n"/>
+      <c r="J1126" s="5" t="n"/>
+      <c r="K1126" s="5" t="n"/>
+      <c r="L1126" s="7" t="n"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" s="2" t="inlineStr">
+        <is>
+          <t>橇</t>
+        </is>
+      </c>
+      <c r="B1127" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1127" s="4" t="inlineStr">
+        <is>
+          <t>木 毳</t>
+        </is>
+      </c>
+      <c r="D1127" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1127" s="5" t="n"/>
+      <c r="F1127" s="5" t="n"/>
+      <c r="G1127" s="4" t="inlineStr">
+        <is>
+          <t>木 毳 毛 丿 二 一 乚</t>
+        </is>
+      </c>
+      <c r="H1127" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1127" s="3" t="n"/>
+      <c r="J1127" s="5" t="n"/>
+      <c r="K1127" s="5" t="n"/>
+      <c r="L1127" s="7" t="n"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" s="2" t="inlineStr">
+        <is>
+          <t>鈴</t>
+        </is>
+      </c>
+      <c r="B1128" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1128" s="4" t="inlineStr">
+        <is>
+          <t>金 令</t>
+        </is>
+      </c>
+      <c r="D1128" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1128" s="5" t="n"/>
+      <c r="F1128" s="5" t="n"/>
+      <c r="G1128" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 令 亼 龴</t>
+        </is>
+      </c>
+      <c r="H1128" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1128" s="3" t="n"/>
+      <c r="J1128" s="5" t="n"/>
+      <c r="K1128" s="5" t="n"/>
+      <c r="L1128" s="7" t="n"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" s="2" t="inlineStr">
+        <is>
+          <t>迴</t>
+        </is>
+      </c>
+      <c r="B1129" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第11課</t>
+        </is>
+      </c>
+      <c r="C1129" s="4" t="inlineStr">
+        <is>
+          <t>辶 回</t>
+        </is>
+      </c>
+      <c r="D1129" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1129" s="5" t="n"/>
+      <c r="F1129" s="5" t="n"/>
+      <c r="G1129" s="4" t="inlineStr">
+        <is>
+          <t>辶 回 囗 口</t>
+        </is>
+      </c>
+      <c r="H1129" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1129" s="3" t="n"/>
+      <c r="J1129" s="5" t="n"/>
+      <c r="K1129" s="5" t="n"/>
+      <c r="L1129" s="7" t="n"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" s="2" t="inlineStr">
+        <is>
+          <t>頰</t>
+        </is>
+      </c>
+      <c r="B1130" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1130" s="4" t="inlineStr">
+        <is>
+          <t>夾 頁</t>
+        </is>
+      </c>
+      <c r="D1130" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1130" s="5" t="n"/>
+      <c r="F1130" s="5" t="n"/>
+      <c r="G1130" s="4" t="inlineStr">
+        <is>
+          <t>夾 大 一 人 从 頁</t>
+        </is>
+      </c>
+      <c r="H1130" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1130" s="3" t="n"/>
+      <c r="J1130" s="5" t="n"/>
+      <c r="K1130" s="5" t="n"/>
+      <c r="L1130" s="7" t="n"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" s="2" t="inlineStr">
+        <is>
+          <t>蓬</t>
+        </is>
+      </c>
+      <c r="B1131" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1131" s="4" t="inlineStr">
+        <is>
+          <t>艹 逢</t>
+        </is>
+      </c>
+      <c r="D1131" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1131" s="5" t="n"/>
+      <c r="F1131" s="5" t="n"/>
+      <c r="G1131" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 逢 辶 夆 夂 丰 丿 二 一 丨</t>
+        </is>
+      </c>
+      <c r="H1131" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1131" s="3" t="n"/>
+      <c r="J1131" s="5" t="n"/>
+      <c r="K1131" s="5" t="n"/>
+      <c r="L1131" s="7" t="n"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" s="2" t="inlineStr">
+        <is>
+          <t>勃</t>
+        </is>
+      </c>
+      <c r="B1132" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1132" s="4" t="inlineStr">
+        <is>
+          <t>孛 力</t>
+        </is>
+      </c>
+      <c r="D1132" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1132" s="5" t="n"/>
+      <c r="F1132" s="5" t="n"/>
+      <c r="G1132" s="4" t="inlineStr">
+        <is>
+          <t>孛 十 冖 子 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1132" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1132" s="3" t="n"/>
+      <c r="J1132" s="5" t="n"/>
+      <c r="K1132" s="5" t="n"/>
+      <c r="L1132" s="7" t="n"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" s="2" t="inlineStr">
+        <is>
+          <t>庭</t>
+        </is>
+      </c>
+      <c r="B1133" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1133" s="4" t="inlineStr">
+        <is>
+          <t>广 廷</t>
+        </is>
+      </c>
+      <c r="D1133" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1133" s="5" t="n"/>
+      <c r="F1133" s="5" t="n"/>
+      <c r="G1133" s="4" t="inlineStr">
+        <is>
+          <t>广 廷 廴 丿 土 十 一</t>
+        </is>
+      </c>
+      <c r="H1133" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1133" s="3" t="n"/>
+      <c r="J1133" s="5" t="n"/>
+      <c r="K1133" s="5" t="n"/>
+      <c r="L1133" s="7" t="n"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" s="2" t="inlineStr">
+        <is>
+          <t>肅</t>
+        </is>
+      </c>
+      <c r="B1134" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1134" s="4" t="n"/>
+      <c r="D1134" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1134" s="5" t="n"/>
+      <c r="F1134" s="5" t="n"/>
+      <c r="G1134" s="4" t="n"/>
+      <c r="H1134" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1134" s="3" t="n"/>
+      <c r="J1134" s="5" t="n"/>
+      <c r="K1134" s="5" t="n"/>
+      <c r="L1134" s="7" t="n"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" s="2" t="inlineStr">
+        <is>
+          <t>薔</t>
+        </is>
+      </c>
+      <c r="B1135" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1135" s="4" t="inlineStr">
+        <is>
+          <t>艹 嗇</t>
+        </is>
+      </c>
+      <c r="D1135" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1135" s="5" t="n"/>
+      <c r="F1135" s="5" t="n"/>
+      <c r="G1135" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 嗇 土 一 从 人 回 囗 口</t>
+        </is>
+      </c>
+      <c r="H1135" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1135" s="3" t="n"/>
+      <c r="J1135" s="5" t="n"/>
+      <c r="K1135" s="5" t="n"/>
+      <c r="L1135" s="7" t="n"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" s="2" t="inlineStr">
+        <is>
+          <t>薇</t>
+        </is>
+      </c>
+      <c r="B1136" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1136" s="4" t="inlineStr">
+        <is>
+          <t>艹 微</t>
+        </is>
+      </c>
+      <c r="D1136" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1136" s="5" t="n"/>
+      <c r="F1136" s="5" t="n"/>
+      <c r="G1136" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 微 彳 山 兀 一 儿 丿 乚 攵</t>
+        </is>
+      </c>
+      <c r="H1136" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1136" s="3" t="n"/>
+      <c r="J1136" s="5" t="n"/>
+      <c r="K1136" s="5" t="n"/>
+      <c r="L1136" s="7" t="n"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" s="2" t="inlineStr">
+        <is>
+          <t>瀰</t>
+        </is>
+      </c>
+      <c r="B1137" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1137" s="4" t="inlineStr">
+        <is>
+          <t>氵 彌</t>
+        </is>
+      </c>
+      <c r="D1137" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1137" s="5" t="n"/>
+      <c r="F1137" s="5" t="n"/>
+      <c r="G1137" s="4" t="inlineStr">
+        <is>
+          <t>氵 彌 弓 爾 一 八 巾 爻 㐅 乂 丿 乀</t>
+        </is>
+      </c>
+      <c r="H1137" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1137" s="3" t="n"/>
+      <c r="J1137" s="5" t="n"/>
+      <c r="K1137" s="5" t="n"/>
+      <c r="L1137" s="7" t="n"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" s="2" t="inlineStr">
+        <is>
+          <t>刮</t>
+        </is>
+      </c>
+      <c r="B1138" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1138" s="4" t="inlineStr">
+        <is>
+          <t>舌 刂</t>
+        </is>
+      </c>
+      <c r="D1138" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1138" s="5" t="n"/>
+      <c r="F1138" s="5" t="n"/>
+      <c r="G1138" s="4" t="inlineStr">
+        <is>
+          <t>舌 干 口 刂</t>
+        </is>
+      </c>
+      <c r="H1138" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1138" s="3" t="n"/>
+      <c r="J1138" s="5" t="n"/>
+      <c r="K1138" s="5" t="n"/>
+      <c r="L1138" s="7" t="n"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" s="2" t="inlineStr">
+        <is>
+          <t>括</t>
+        </is>
+      </c>
+      <c r="B1139" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1139" s="4" t="inlineStr">
+        <is>
+          <t>扌 舌</t>
+        </is>
+      </c>
+      <c r="D1139" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1139" s="5" t="n"/>
+      <c r="F1139" s="5" t="n"/>
+      <c r="G1139" s="4" t="inlineStr">
+        <is>
+          <t>扌 舌 干 口</t>
+        </is>
+      </c>
+      <c r="H1139" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1139" s="3" t="n"/>
+      <c r="J1139" s="5" t="n"/>
+      <c r="K1139" s="5" t="n"/>
+      <c r="L1139" s="7" t="n"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" s="2" t="inlineStr">
+        <is>
+          <t>螞</t>
+        </is>
+      </c>
+      <c r="B1140" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1140" s="4" t="inlineStr">
+        <is>
+          <t>虫 馬</t>
+        </is>
+      </c>
+      <c r="D1140" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1140" s="5" t="n"/>
+      <c r="F1140" s="5" t="n"/>
+      <c r="G1140" s="4" t="inlineStr">
+        <is>
+          <t>虫 馬 灬</t>
+        </is>
+      </c>
+      <c r="H1140" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1140" s="3" t="n"/>
+      <c r="J1140" s="5" t="n"/>
+      <c r="K1140" s="5" t="n"/>
+      <c r="L1140" s="7" t="n"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" s="2" t="inlineStr">
+        <is>
+          <t>蟻</t>
+        </is>
+      </c>
+      <c r="B1141" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1141" s="4" t="inlineStr">
+        <is>
+          <t>虫 義</t>
+        </is>
+      </c>
+      <c r="D1141" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1141" s="5" t="n"/>
+      <c r="F1141" s="5" t="n"/>
+      <c r="G1141" s="4" t="inlineStr">
+        <is>
+          <t>虫 義 丷 一 土 十 我</t>
+        </is>
+      </c>
+      <c r="H1141" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1141" s="3" t="n"/>
+      <c r="J1141" s="5" t="n"/>
+      <c r="K1141" s="5" t="n"/>
+      <c r="L1141" s="7" t="n"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" s="2" t="inlineStr">
+        <is>
+          <t>儘</t>
+        </is>
+      </c>
+      <c r="B1142" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1142" s="4" t="inlineStr">
+        <is>
+          <t>亻 盡</t>
+        </is>
+      </c>
+      <c r="D1142" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1142" s="5" t="n"/>
+      <c r="F1142" s="5" t="n"/>
+      <c r="G1142" s="4" t="inlineStr">
+        <is>
+          <t>亻 盡 聿 肀 一 丨 二 灬 皿</t>
+        </is>
+      </c>
+      <c r="H1142" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1142" s="3" t="n"/>
+      <c r="J1142" s="5" t="n"/>
+      <c r="K1142" s="5" t="n"/>
+      <c r="L1142" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L936"/>
+  <autoFilter ref="A1:L1142"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K936" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"左右,上下,左中右,上中下,全包圍,上方包圍,下方包圍,左方包圍,左上包圍,右上包圍,左下包圍,交疊,獨體字"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/parts-table.xlsx
+++ b/docs/parts-table.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$1142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$1351</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1142"/>
+  <dimension ref="A1:L1351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第1課</t>
+          <t>翰林2上第1課、康軒5上第11課</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課</t>
+          <t>翰林2上第7課、康軒5上第12課</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第10課、南一2上第6課</t>
+          <t>翰林2上第10課、南一2上第6課、康軒5上第9課</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第11課</t>
+          <t>翰林2上第11課、康軒5上第10課</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第11課</t>
+          <t>翰林2上第11課、康軒5上第8課</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第12課</t>
+          <t>翰林2上第12課、康軒5上第10課</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第12課</t>
+          <t>翰林2上第12課、康軒5上第5課</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>南一2上第1課</t>
+          <t>南一2上第1課、康軒5上第7課</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="B327" s="3" t="inlineStr">
         <is>
-          <t>南一2上第6課</t>
+          <t>南一2上第6課、康軒5上第4課</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
@@ -15164,7 +15164,7 @@
       </c>
       <c r="B386" s="3" t="inlineStr">
         <is>
-          <t>南一2上第10課</t>
+          <t>南一2上第10課、康軒5上第4課</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="B616" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第12課</t>
+          <t>康軒2上第12課、康軒5上第7課</t>
         </is>
       </c>
       <c r="C616" s="4" t="inlineStr">
@@ -30052,7 +30052,7 @@
       </c>
       <c r="B778" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第12課</t>
+          <t>康軒3上第12課、康軒5上第5課</t>
         </is>
       </c>
       <c r="C778" s="4" t="inlineStr">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B980" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第3課</t>
+          <t>康軒6上第3課、康軒5上第6課</t>
         </is>
       </c>
       <c r="C980" s="4" t="inlineStr">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="B1016" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第5課</t>
+          <t>康軒6上第5課、康軒5上第6課</t>
         </is>
       </c>
       <c r="C1016" s="4" t="inlineStr">
@@ -39586,7 +39586,7 @@
       </c>
       <c r="B1029" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第6課</t>
+          <t>康軒6上第6課、康軒5上第3課</t>
         </is>
       </c>
       <c r="C1029" s="4" t="inlineStr">
@@ -43942,10 +43942,8004 @@
       <c r="K1142" s="5" t="n"/>
       <c r="L1142" s="7" t="n"/>
     </row>
+    <row r="1143">
+      <c r="A1143" s="2" t="inlineStr">
+        <is>
+          <t>蚊</t>
+        </is>
+      </c>
+      <c r="B1143" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1143" s="4" t="inlineStr">
+        <is>
+          <t>虫 文</t>
+        </is>
+      </c>
+      <c r="D1143" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1143" s="5" t="n"/>
+      <c r="F1143" s="5" t="n"/>
+      <c r="G1143" s="4" t="inlineStr">
+        <is>
+          <t>虫 文 亠 丶 一 乂 丿 乀</t>
+        </is>
+      </c>
+      <c r="H1143" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1143" s="3" t="n"/>
+      <c r="J1143" s="5" t="n"/>
+      <c r="K1143" s="5" t="n"/>
+      <c r="L1143" s="7" t="n"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" s="2" t="inlineStr">
+        <is>
+          <t>帳</t>
+        </is>
+      </c>
+      <c r="B1144" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1144" s="4" t="inlineStr">
+        <is>
+          <t>巾 長</t>
+        </is>
+      </c>
+      <c r="D1144" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1144" s="5" t="n"/>
+      <c r="F1144" s="5" t="n"/>
+      <c r="G1144" s="4" t="inlineStr">
+        <is>
+          <t>巾 長 一 𠄌 乀 丿</t>
+        </is>
+      </c>
+      <c r="H1144" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1144" s="3" t="n"/>
+      <c r="J1144" s="5" t="n"/>
+      <c r="K1144" s="5" t="n"/>
+      <c r="L1144" s="7" t="n"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" s="2" t="inlineStr">
+        <is>
+          <t>洲</t>
+        </is>
+      </c>
+      <c r="B1145" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1145" s="4" t="inlineStr">
+        <is>
+          <t>氵 州</t>
+        </is>
+      </c>
+      <c r="D1145" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1145" s="5" t="n"/>
+      <c r="F1145" s="5" t="n"/>
+      <c r="G1145" s="4" t="inlineStr">
+        <is>
+          <t>氵 州</t>
+        </is>
+      </c>
+      <c r="H1145" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1145" s="3" t="n"/>
+      <c r="J1145" s="5" t="n"/>
+      <c r="K1145" s="5" t="n"/>
+      <c r="L1145" s="7" t="n"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" s="2" t="inlineStr">
+        <is>
+          <t>瘧</t>
+        </is>
+      </c>
+      <c r="B1146" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1146" s="4" t="inlineStr">
+        <is>
+          <t>疒 虐</t>
+        </is>
+      </c>
+      <c r="D1146" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1146" s="5" t="n"/>
+      <c r="F1146" s="5" t="n"/>
+      <c r="G1146" s="4" t="inlineStr">
+        <is>
+          <t>疒 虐 虍 ⺊ 七 ㇀ 乚 匚 一</t>
+        </is>
+      </c>
+      <c r="H1146" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1146" s="3" t="n"/>
+      <c r="J1146" s="5" t="n"/>
+      <c r="K1146" s="5" t="n"/>
+      <c r="L1146" s="7" t="n"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" s="2" t="inlineStr">
+        <is>
+          <t>疾</t>
+        </is>
+      </c>
+      <c r="B1147" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1147" s="4" t="inlineStr">
+        <is>
+          <t>疒 矢</t>
+        </is>
+      </c>
+      <c r="D1147" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1147" s="5" t="n"/>
+      <c r="F1147" s="5" t="n"/>
+      <c r="G1147" s="4" t="inlineStr">
+        <is>
+          <t>疒 矢 𠂉 大 一 人</t>
+        </is>
+      </c>
+      <c r="H1147" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1147" s="3" t="n"/>
+      <c r="J1147" s="5" t="n"/>
+      <c r="K1147" s="5" t="n"/>
+      <c r="L1147" s="7" t="n"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" s="2" t="inlineStr">
+        <is>
+          <t>死</t>
+        </is>
+      </c>
+      <c r="B1148" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1148" s="4" t="inlineStr">
+        <is>
+          <t>歹 匕</t>
+        </is>
+      </c>
+      <c r="D1148" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1148" s="5" t="n"/>
+      <c r="F1148" s="5" t="n"/>
+      <c r="G1148" s="4" t="inlineStr">
+        <is>
+          <t>歹 一 夕 𠂊 丶 匕 乚</t>
+        </is>
+      </c>
+      <c r="H1148" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1148" s="3" t="n"/>
+      <c r="J1148" s="5" t="n"/>
+      <c r="K1148" s="5" t="n"/>
+      <c r="L1148" s="7" t="n"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" s="2" t="inlineStr">
+        <is>
+          <t>叮</t>
+        </is>
+      </c>
+      <c r="B1149" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1149" s="4" t="inlineStr">
+        <is>
+          <t>口 丁</t>
+        </is>
+      </c>
+      <c r="D1149" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1149" s="5" t="n"/>
+      <c r="F1149" s="5" t="n"/>
+      <c r="G1149" s="4" t="inlineStr">
+        <is>
+          <t>口 丁 一 亅</t>
+        </is>
+      </c>
+      <c r="H1149" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1149" s="3" t="n"/>
+      <c r="J1149" s="5" t="n"/>
+      <c r="K1149" s="5" t="n"/>
+      <c r="L1149" s="7" t="n"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" s="2" t="inlineStr">
+        <is>
+          <t>存</t>
+        </is>
+      </c>
+      <c r="B1150" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1150" s="4" t="inlineStr">
+        <is>
+          <t>子</t>
+        </is>
+      </c>
+      <c r="D1150" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1150" s="5" t="n"/>
+      <c r="F1150" s="5" t="n"/>
+      <c r="G1150" s="4" t="inlineStr">
+        <is>
+          <t>子</t>
+        </is>
+      </c>
+      <c r="H1150" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1150" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件</t>
+        </is>
+      </c>
+      <c r="J1150" s="5" t="n"/>
+      <c r="K1150" s="5" t="n"/>
+      <c r="L1150" s="7" t="n"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" s="2" t="inlineStr">
+        <is>
+          <t>募</t>
+        </is>
+      </c>
+      <c r="B1151" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1151" s="4" t="inlineStr">
+        <is>
+          <t>莫 力</t>
+        </is>
+      </c>
+      <c r="D1151" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1151" s="5" t="n"/>
+      <c r="F1151" s="5" t="n"/>
+      <c r="G1151" s="4" t="inlineStr">
+        <is>
+          <t>莫 艹 十 旲 日 大 一 人 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1151" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1151" s="3" t="n"/>
+      <c r="J1151" s="5" t="n"/>
+      <c r="K1151" s="5" t="n"/>
+      <c r="L1151" s="7" t="n"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" s="2" t="inlineStr">
+        <is>
+          <t>集</t>
+        </is>
+      </c>
+      <c r="B1152" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1152" s="4" t="inlineStr">
+        <is>
+          <t>隹 朩</t>
+        </is>
+      </c>
+      <c r="D1152" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1152" s="5" t="n"/>
+      <c r="F1152" s="5" t="n"/>
+      <c r="G1152" s="4" t="inlineStr">
+        <is>
+          <t>隹 朩</t>
+        </is>
+      </c>
+      <c r="H1152" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1152" s="3" t="n"/>
+      <c r="J1152" s="5" t="n"/>
+      <c r="K1152" s="5" t="n"/>
+      <c r="L1152" s="7" t="n"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" s="2" t="inlineStr">
+        <is>
+          <t>寄</t>
+        </is>
+      </c>
+      <c r="B1153" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1153" s="4" t="inlineStr">
+        <is>
+          <t>宀 奇</t>
+        </is>
+      </c>
+      <c r="D1153" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1153" s="5" t="n"/>
+      <c r="F1153" s="5" t="n"/>
+      <c r="G1153" s="4" t="inlineStr">
+        <is>
+          <t>宀 奇 大 一 人 可 丁 亅 口</t>
+        </is>
+      </c>
+      <c r="H1153" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1153" s="3" t="n"/>
+      <c r="J1153" s="5" t="n"/>
+      <c r="K1153" s="5" t="n"/>
+      <c r="L1153" s="7" t="n"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" s="2" t="inlineStr">
+        <is>
+          <t>贈</t>
+        </is>
+      </c>
+      <c r="B1154" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1154" s="4" t="inlineStr">
+        <is>
+          <t>貝 曾</t>
+        </is>
+      </c>
+      <c r="D1154" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1154" s="5" t="n"/>
+      <c r="F1154" s="5" t="n"/>
+      <c r="G1154" s="4" t="inlineStr">
+        <is>
+          <t>貝 目 八 曾 丷 田 日</t>
+        </is>
+      </c>
+      <c r="H1154" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1154" s="3" t="n"/>
+      <c r="J1154" s="5" t="n"/>
+      <c r="K1154" s="5" t="n"/>
+      <c r="L1154" s="7" t="n"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" s="2" t="inlineStr">
+        <is>
+          <t>獎</t>
+        </is>
+      </c>
+      <c r="B1155" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1155" s="4" t="inlineStr">
+        <is>
+          <t>將 犬</t>
+        </is>
+      </c>
+      <c r="D1155" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1155" s="5" t="n"/>
+      <c r="F1155" s="5" t="n"/>
+      <c r="G1155" s="4" t="inlineStr">
+        <is>
+          <t>將 爿 𠂊 冫 寸 犬</t>
+        </is>
+      </c>
+      <c r="H1155" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1155" s="3" t="n"/>
+      <c r="J1155" s="5" t="n"/>
+      <c r="K1155" s="5" t="n"/>
+      <c r="L1155" s="7" t="n"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" s="2" t="inlineStr">
+        <is>
+          <t>狀</t>
+        </is>
+      </c>
+      <c r="B1156" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1156" s="4" t="inlineStr">
+        <is>
+          <t>爿 犬</t>
+        </is>
+      </c>
+      <c r="D1156" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1156" s="5" t="n"/>
+      <c r="F1156" s="5" t="n"/>
+      <c r="G1156" s="4" t="inlineStr">
+        <is>
+          <t>爿 犬</t>
+        </is>
+      </c>
+      <c r="H1156" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1156" s="3" t="n"/>
+      <c r="J1156" s="5" t="n"/>
+      <c r="K1156" s="5" t="n"/>
+      <c r="L1156" s="7" t="n"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" s="2" t="inlineStr">
+        <is>
+          <t>藏</t>
+        </is>
+      </c>
+      <c r="B1157" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1157" s="4" t="inlineStr">
+        <is>
+          <t>艹 臧</t>
+        </is>
+      </c>
+      <c r="D1157" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1157" s="5" t="n"/>
+      <c r="F1157" s="5" t="n"/>
+      <c r="G1157" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 臧 戕 爿 戈 弋 一 乚 丶 丿 臣</t>
+        </is>
+      </c>
+      <c r="H1157" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1157" s="3" t="n"/>
+      <c r="J1157" s="5" t="n"/>
+      <c r="K1157" s="5" t="n"/>
+      <c r="L1157" s="7" t="n"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" s="2" t="inlineStr">
+        <is>
+          <t>誌</t>
+        </is>
+      </c>
+      <c r="B1158" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1158" s="4" t="inlineStr">
+        <is>
+          <t>言 志</t>
+        </is>
+      </c>
+      <c r="D1158" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1158" s="5" t="n"/>
+      <c r="F1158" s="5" t="n"/>
+      <c r="G1158" s="4" t="inlineStr">
+        <is>
+          <t>言 志 士 十 一 心</t>
+        </is>
+      </c>
+      <c r="H1158" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1158" s="3" t="n"/>
+      <c r="J1158" s="5" t="n"/>
+      <c r="K1158" s="5" t="n"/>
+      <c r="L1158" s="7" t="n"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" s="2" t="inlineStr">
+        <is>
+          <t>基</t>
+        </is>
+      </c>
+      <c r="B1159" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1159" s="4" t="inlineStr">
+        <is>
+          <t>其 土</t>
+        </is>
+      </c>
+      <c r="D1159" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1159" s="5" t="n"/>
+      <c r="F1159" s="5" t="n"/>
+      <c r="G1159" s="4" t="inlineStr">
+        <is>
+          <t>其 一 八 土 十</t>
+        </is>
+      </c>
+      <c r="H1159" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1159" s="3" t="n"/>
+      <c r="J1159" s="5" t="n"/>
+      <c r="K1159" s="5" t="n"/>
+      <c r="L1159" s="7" t="n"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" s="2" t="inlineStr">
+        <is>
+          <t>赴</t>
+        </is>
+      </c>
+      <c r="B1160" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第1課</t>
+        </is>
+      </c>
+      <c r="C1160" s="4" t="inlineStr">
+        <is>
+          <t>走 卜</t>
+        </is>
+      </c>
+      <c r="D1160" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1160" s="5" t="n"/>
+      <c r="F1160" s="5" t="n"/>
+      <c r="G1160" s="4" t="inlineStr">
+        <is>
+          <t>走 土 十 一 龰 卜</t>
+        </is>
+      </c>
+      <c r="H1160" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1160" s="3" t="n"/>
+      <c r="J1160" s="5" t="n"/>
+      <c r="K1160" s="5" t="n"/>
+      <c r="L1160" s="7" t="n"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" s="2" t="inlineStr">
+        <is>
+          <t>德</t>
+        </is>
+      </c>
+      <c r="B1161" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1161" s="4" t="inlineStr">
+        <is>
+          <t>彳 十 罒 一 心</t>
+        </is>
+      </c>
+      <c r="D1161" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1161" s="5" t="n"/>
+      <c r="F1161" s="5" t="n"/>
+      <c r="G1161" s="4" t="inlineStr">
+        <is>
+          <t>彳 十 罒 一 心</t>
+        </is>
+      </c>
+      <c r="H1161" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1161" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1161" s="5" t="n"/>
+      <c r="K1161" s="5" t="n"/>
+      <c r="L1161" s="7" t="n"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" s="2" t="inlineStr">
+        <is>
+          <t>乎</t>
+        </is>
+      </c>
+      <c r="B1162" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1162" s="4" t="n"/>
+      <c r="D1162" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1162" s="5" t="n"/>
+      <c r="F1162" s="5" t="n"/>
+      <c r="G1162" s="4" t="n"/>
+      <c r="H1162" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1162" s="3" t="n"/>
+      <c r="J1162" s="5" t="n"/>
+      <c r="K1162" s="5" t="n"/>
+      <c r="L1162" s="7" t="n"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" s="2" t="inlineStr">
+        <is>
+          <t>血</t>
+        </is>
+      </c>
+      <c r="B1163" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1163" s="4" t="inlineStr">
+        <is>
+          <t>丿 皿</t>
+        </is>
+      </c>
+      <c r="D1163" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1163" s="5" t="n"/>
+      <c r="F1163" s="5" t="n"/>
+      <c r="G1163" s="4" t="inlineStr">
+        <is>
+          <t>丿 皿</t>
+        </is>
+      </c>
+      <c r="H1163" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1163" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1163" s="5" t="n"/>
+      <c r="K1163" s="5" t="n"/>
+      <c r="L1163" s="7" t="n"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" s="2" t="inlineStr">
+        <is>
+          <t>攝</t>
+        </is>
+      </c>
+      <c r="B1164" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1164" s="4" t="inlineStr">
+        <is>
+          <t>扌 聶</t>
+        </is>
+      </c>
+      <c r="D1164" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1164" s="5" t="n"/>
+      <c r="F1164" s="5" t="n"/>
+      <c r="G1164" s="4" t="inlineStr">
+        <is>
+          <t>扌 聶 耳 聑</t>
+        </is>
+      </c>
+      <c r="H1164" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1164" s="3" t="n"/>
+      <c r="J1164" s="5" t="n"/>
+      <c r="K1164" s="5" t="n"/>
+      <c r="L1164" s="7" t="n"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" s="2" t="inlineStr">
+        <is>
+          <t>颱</t>
+        </is>
+      </c>
+      <c r="B1165" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1165" s="4" t="inlineStr">
+        <is>
+          <t>風 台</t>
+        </is>
+      </c>
+      <c r="D1165" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1165" s="5" t="n"/>
+      <c r="F1165" s="5" t="n"/>
+      <c r="G1165" s="4" t="inlineStr">
+        <is>
+          <t>風 几 丿 虫 台 厶 口</t>
+        </is>
+      </c>
+      <c r="H1165" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1165" s="3" t="n"/>
+      <c r="J1165" s="5" t="n"/>
+      <c r="K1165" s="5" t="n"/>
+      <c r="L1165" s="7" t="n"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" s="2" t="inlineStr">
+        <is>
+          <t>錄</t>
+        </is>
+      </c>
+      <c r="B1166" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1166" s="4" t="inlineStr">
+        <is>
+          <t>金 彔</t>
+        </is>
+      </c>
+      <c r="D1166" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1166" s="5" t="n"/>
+      <c r="F1166" s="5" t="n"/>
+      <c r="G1166" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 彔 彑 氺 亅 八</t>
+        </is>
+      </c>
+      <c r="H1166" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1166" s="3" t="n"/>
+      <c r="J1166" s="5" t="n"/>
+      <c r="K1166" s="5" t="n"/>
+      <c r="L1166" s="7" t="n"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" s="2" t="inlineStr">
+        <is>
+          <t>哀</t>
+        </is>
+      </c>
+      <c r="B1167" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1167" s="4" t="inlineStr">
+        <is>
+          <t>亠 口 𧘇</t>
+        </is>
+      </c>
+      <c r="D1167" s="4" t="inlineStr">
+        <is>
+          <t>上中下</t>
+        </is>
+      </c>
+      <c r="E1167" s="5" t="n"/>
+      <c r="F1167" s="5" t="n"/>
+      <c r="G1167" s="4" t="inlineStr">
+        <is>
+          <t>亠 丶 一 口 𧘇</t>
+        </is>
+      </c>
+      <c r="H1167" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1167" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1167" s="5" t="n"/>
+      <c r="K1167" s="5" t="n"/>
+      <c r="L1167" s="7" t="n"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" s="2" t="inlineStr">
+        <is>
+          <t>巒</t>
+        </is>
+      </c>
+      <c r="B1168" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1168" s="4" t="inlineStr">
+        <is>
+          <t>糸 言 糸 山</t>
+        </is>
+      </c>
+      <c r="D1168" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1168" s="5" t="n"/>
+      <c r="F1168" s="5" t="n"/>
+      <c r="G1168" s="4" t="inlineStr">
+        <is>
+          <t>糸 幺 丶 小 言 山</t>
+        </is>
+      </c>
+      <c r="H1168" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1168" s="3" t="n"/>
+      <c r="J1168" s="5" t="n"/>
+      <c r="K1168" s="5" t="n"/>
+      <c r="L1168" s="7" t="n"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" s="2" t="inlineStr">
+        <is>
+          <t>縱</t>
+        </is>
+      </c>
+      <c r="B1169" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1169" s="4" t="inlineStr">
+        <is>
+          <t>糹 從</t>
+        </is>
+      </c>
+      <c r="D1169" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1169" s="5" t="n"/>
+      <c r="F1169" s="5" t="n"/>
+      <c r="G1169" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 從 彳 从 人 龰</t>
+        </is>
+      </c>
+      <c r="H1169" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1169" s="3" t="n"/>
+      <c r="J1169" s="5" t="n"/>
+      <c r="K1169" s="5" t="n"/>
+      <c r="L1169" s="7" t="n"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="2" t="inlineStr">
+        <is>
+          <t>臍</t>
+        </is>
+      </c>
+      <c r="B1170" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1170" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 齊</t>
+        </is>
+      </c>
+      <c r="D1170" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1170" s="5" t="n"/>
+      <c r="F1170" s="5" t="n"/>
+      <c r="G1170" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 齊 亠 丶 一 刀 𠃌 丿 丫 丷 丨 二</t>
+        </is>
+      </c>
+      <c r="H1170" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1170" s="3" t="n"/>
+      <c r="J1170" s="5" t="n"/>
+      <c r="K1170" s="5" t="n"/>
+      <c r="L1170" s="7" t="n"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="2" t="inlineStr">
+        <is>
+          <t>禍</t>
+        </is>
+      </c>
+      <c r="B1171" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1171" s="4" t="inlineStr">
+        <is>
+          <t>礻 咼</t>
+        </is>
+      </c>
+      <c r="D1171" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1171" s="5" t="n"/>
+      <c r="F1171" s="5" t="n"/>
+      <c r="G1171" s="4" t="inlineStr">
+        <is>
+          <t>礻 咼 冎 冂 口</t>
+        </is>
+      </c>
+      <c r="H1171" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1171" s="3" t="n"/>
+      <c r="J1171" s="5" t="n"/>
+      <c r="K1171" s="5" t="n"/>
+      <c r="L1171" s="7" t="n"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="2" t="inlineStr">
+        <is>
+          <t>殘</t>
+        </is>
+      </c>
+      <c r="B1172" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1172" s="4" t="inlineStr">
+        <is>
+          <t>歹 戔</t>
+        </is>
+      </c>
+      <c r="D1172" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1172" s="5" t="n"/>
+      <c r="F1172" s="5" t="n"/>
+      <c r="G1172" s="4" t="inlineStr">
+        <is>
+          <t>歹 一 夕 𠂊 丶 戔 戈 弋 乚 丿</t>
+        </is>
+      </c>
+      <c r="H1172" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1172" s="3" t="n"/>
+      <c r="J1172" s="5" t="n"/>
+      <c r="K1172" s="5" t="n"/>
+      <c r="L1172" s="7" t="n"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="2" t="inlineStr">
+        <is>
+          <t>檳</t>
+        </is>
+      </c>
+      <c r="B1173" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1173" s="4" t="inlineStr">
+        <is>
+          <t>木 賓</t>
+        </is>
+      </c>
+      <c r="D1173" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1173" s="5" t="n"/>
+      <c r="F1173" s="5" t="n"/>
+      <c r="G1173" s="4" t="inlineStr">
+        <is>
+          <t>木 賓 宀 一 𣥂 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1173" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1173" s="3" t="n"/>
+      <c r="J1173" s="5" t="n"/>
+      <c r="K1173" s="5" t="n"/>
+      <c r="L1173" s="7" t="n"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="2" t="inlineStr">
+        <is>
+          <t>榔</t>
+        </is>
+      </c>
+      <c r="B1174" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1174" s="4" t="inlineStr">
+        <is>
+          <t>木 郎</t>
+        </is>
+      </c>
+      <c r="D1174" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1174" s="5" t="n"/>
+      <c r="F1174" s="5" t="n"/>
+      <c r="G1174" s="4" t="inlineStr">
+        <is>
+          <t>木 郎 丶 阝</t>
+        </is>
+      </c>
+      <c r="H1174" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1174" s="3" t="n"/>
+      <c r="J1174" s="5" t="n"/>
+      <c r="K1174" s="5" t="n"/>
+      <c r="L1174" s="7" t="n"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="2" t="inlineStr">
+        <is>
+          <t>降</t>
+        </is>
+      </c>
+      <c r="B1175" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1175" s="4" t="inlineStr">
+        <is>
+          <t>阝 夅</t>
+        </is>
+      </c>
+      <c r="D1175" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1175" s="5" t="n"/>
+      <c r="F1175" s="5" t="n"/>
+      <c r="G1175" s="4" t="inlineStr">
+        <is>
+          <t>阝 夅 夂 㐄</t>
+        </is>
+      </c>
+      <c r="H1175" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1175" s="3" t="n"/>
+      <c r="J1175" s="5" t="n"/>
+      <c r="K1175" s="5" t="n"/>
+      <c r="L1175" s="7" t="n"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="2" t="inlineStr">
+        <is>
+          <t>鏟</t>
+        </is>
+      </c>
+      <c r="B1176" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1176" s="4" t="inlineStr">
+        <is>
+          <t>金 產</t>
+        </is>
+      </c>
+      <c r="D1176" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1176" s="5" t="n"/>
+      <c r="F1176" s="5" t="n"/>
+      <c r="G1176" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 產 文 亠 丶 乂 丿 乀 厂 生</t>
+        </is>
+      </c>
+      <c r="H1176" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1176" s="3" t="n"/>
+      <c r="J1176" s="5" t="n"/>
+      <c r="K1176" s="5" t="n"/>
+      <c r="L1176" s="7" t="n"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="2" t="inlineStr">
+        <is>
+          <t>汙</t>
+        </is>
+      </c>
+      <c r="B1177" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1177" s="4" t="inlineStr">
+        <is>
+          <t>氵 于</t>
+        </is>
+      </c>
+      <c r="D1177" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1177" s="5" t="n"/>
+      <c r="F1177" s="5" t="n"/>
+      <c r="G1177" s="4" t="inlineStr">
+        <is>
+          <t>氵 于</t>
+        </is>
+      </c>
+      <c r="H1177" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1177" s="3" t="n"/>
+      <c r="J1177" s="5" t="n"/>
+      <c r="K1177" s="5" t="n"/>
+      <c r="L1177" s="7" t="n"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="2" t="inlineStr">
+        <is>
+          <t>斷</t>
+        </is>
+      </c>
+      <c r="B1178" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第2課</t>
+        </is>
+      </c>
+      <c r="C1178" s="4" t="inlineStr">
+        <is>
+          <t>𠃊 幺 幺 𠃊 幺 幺 斤</t>
+        </is>
+      </c>
+      <c r="D1178" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1178" s="5" t="n"/>
+      <c r="F1178" s="5" t="n"/>
+      <c r="G1178" s="4" t="inlineStr">
+        <is>
+          <t>𠃊 幺 丶 斤 𠂆 丅 一 丨</t>
+        </is>
+      </c>
+      <c r="H1178" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1178" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1178" s="5" t="n"/>
+      <c r="K1178" s="5" t="n"/>
+      <c r="L1178" s="7" t="n"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="2" t="inlineStr">
+        <is>
+          <t>峭</t>
+        </is>
+      </c>
+      <c r="B1179" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1179" s="4" t="inlineStr">
+        <is>
+          <t>山 肖</t>
+        </is>
+      </c>
+      <c r="D1179" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1179" s="5" t="n"/>
+      <c r="F1179" s="5" t="n"/>
+      <c r="G1179" s="4" t="inlineStr">
+        <is>
+          <t>山 肖 ⺌ ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1179" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1179" s="3" t="n"/>
+      <c r="J1179" s="5" t="n"/>
+      <c r="K1179" s="5" t="n"/>
+      <c r="L1179" s="7" t="n"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="2" t="inlineStr">
+        <is>
+          <t>聳</t>
+        </is>
+      </c>
+      <c r="B1180" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1180" s="4" t="inlineStr">
+        <is>
+          <t>從 耳</t>
+        </is>
+      </c>
+      <c r="D1180" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1180" s="5" t="n"/>
+      <c r="F1180" s="5" t="n"/>
+      <c r="G1180" s="4" t="inlineStr">
+        <is>
+          <t>從 彳 从 人 龰 耳</t>
+        </is>
+      </c>
+      <c r="H1180" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1180" s="3" t="n"/>
+      <c r="J1180" s="5" t="n"/>
+      <c r="K1180" s="5" t="n"/>
+      <c r="L1180" s="7" t="n"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="2" t="inlineStr">
+        <is>
+          <t>飢</t>
+        </is>
+      </c>
+      <c r="B1181" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1181" s="4" t="inlineStr">
+        <is>
+          <t>飠 几</t>
+        </is>
+      </c>
+      <c r="D1181" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1181" s="5" t="n"/>
+      <c r="F1181" s="5" t="n"/>
+      <c r="G1181" s="4" t="inlineStr">
+        <is>
+          <t>飠 人 丶 几</t>
+        </is>
+      </c>
+      <c r="H1181" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1181" s="3" t="n"/>
+      <c r="J1181" s="5" t="n"/>
+      <c r="K1181" s="5" t="n"/>
+      <c r="L1181" s="7" t="n"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="2" t="inlineStr">
+        <is>
+          <t>隱</t>
+        </is>
+      </c>
+      <c r="B1182" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1182" s="4" t="inlineStr">
+        <is>
+          <t>阝 爫 工 一 心</t>
+        </is>
+      </c>
+      <c r="D1182" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1182" s="5" t="n"/>
+      <c r="F1182" s="5" t="n"/>
+      <c r="G1182" s="4" t="inlineStr">
+        <is>
+          <t>阝 爫 丿 丶 工 一 心</t>
+        </is>
+      </c>
+      <c r="H1182" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1182" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1182" s="5" t="n"/>
+      <c r="K1182" s="5" t="n"/>
+      <c r="L1182" s="7" t="n"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="2" t="inlineStr">
+        <is>
+          <t>扯</t>
+        </is>
+      </c>
+      <c r="B1183" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1183" s="4" t="inlineStr">
+        <is>
+          <t>扌 止</t>
+        </is>
+      </c>
+      <c r="D1183" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1183" s="5" t="n"/>
+      <c r="F1183" s="5" t="n"/>
+      <c r="G1183" s="4" t="inlineStr">
+        <is>
+          <t>扌 止</t>
+        </is>
+      </c>
+      <c r="H1183" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1183" s="3" t="n"/>
+      <c r="J1183" s="5" t="n"/>
+      <c r="K1183" s="5" t="n"/>
+      <c r="L1183" s="7" t="n"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="2" t="inlineStr">
+        <is>
+          <t>銳</t>
+        </is>
+      </c>
+      <c r="B1184" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1184" s="4" t="inlineStr">
+        <is>
+          <t>金 兌</t>
+        </is>
+      </c>
+      <c r="D1184" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1184" s="5" t="n"/>
+      <c r="F1184" s="5" t="n"/>
+      <c r="G1184" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 兌 八 兄 口 儿 丿 乚</t>
+        </is>
+      </c>
+      <c r="H1184" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1184" s="3" t="n"/>
+      <c r="J1184" s="5" t="n"/>
+      <c r="K1184" s="5" t="n"/>
+      <c r="L1184" s="7" t="n"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="2" t="inlineStr">
+        <is>
+          <t>箭</t>
+        </is>
+      </c>
+      <c r="B1185" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1185" s="4" t="inlineStr">
+        <is>
+          <t>竹 前</t>
+        </is>
+      </c>
+      <c r="D1185" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1185" s="5" t="n"/>
+      <c r="F1185" s="5" t="n"/>
+      <c r="G1185" s="4" t="inlineStr">
+        <is>
+          <t>竹 亇 𠂉 亅 前 丷 一 刖 月 刂</t>
+        </is>
+      </c>
+      <c r="H1185" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1185" s="3" t="n"/>
+      <c r="J1185" s="5" t="n"/>
+      <c r="K1185" s="5" t="n"/>
+      <c r="L1185" s="7" t="n"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="2" t="inlineStr">
+        <is>
+          <t>韌</t>
+        </is>
+      </c>
+      <c r="B1186" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1186" s="4" t="inlineStr">
+        <is>
+          <t>韋 刃</t>
+        </is>
+      </c>
+      <c r="D1186" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1186" s="5" t="n"/>
+      <c r="F1186" s="5" t="n"/>
+      <c r="G1186" s="4" t="inlineStr">
+        <is>
+          <t>韋 𫝀 口 㐄 刃 刀 𠃌 丿 丶</t>
+        </is>
+      </c>
+      <c r="H1186" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1186" s="3" t="n"/>
+      <c r="J1186" s="5" t="n"/>
+      <c r="K1186" s="5" t="n"/>
+      <c r="L1186" s="7" t="n"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="2" t="inlineStr">
+        <is>
+          <t>虯</t>
+        </is>
+      </c>
+      <c r="B1187" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1187" s="4" t="inlineStr">
+        <is>
+          <t>虫 丩</t>
+        </is>
+      </c>
+      <c r="D1187" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1187" s="5" t="n"/>
+      <c r="F1187" s="5" t="n"/>
+      <c r="G1187" s="4" t="inlineStr">
+        <is>
+          <t>虫 丩</t>
+        </is>
+      </c>
+      <c r="H1187" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1187" s="3" t="n"/>
+      <c r="J1187" s="5" t="n"/>
+      <c r="K1187" s="5" t="n"/>
+      <c r="L1187" s="7" t="n"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="2" t="inlineStr">
+        <is>
+          <t>鬚</t>
+        </is>
+      </c>
+      <c r="B1188" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1188" s="4" t="inlineStr">
+        <is>
+          <t>髟 須</t>
+        </is>
+      </c>
+      <c r="D1188" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1188" s="5" t="n"/>
+      <c r="F1188" s="5" t="n"/>
+      <c r="G1188" s="4" t="inlineStr">
+        <is>
+          <t>髟 镸 一 厶 彡 須 頁</t>
+        </is>
+      </c>
+      <c r="H1188" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1188" s="3" t="n"/>
+      <c r="J1188" s="5" t="n"/>
+      <c r="K1188" s="5" t="n"/>
+      <c r="L1188" s="7" t="n"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="2" t="inlineStr">
+        <is>
+          <t>茂</t>
+        </is>
+      </c>
+      <c r="B1189" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1189" s="4" t="inlineStr">
+        <is>
+          <t>艹 戊</t>
+        </is>
+      </c>
+      <c r="D1189" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1189" s="5" t="n"/>
+      <c r="F1189" s="5" t="n"/>
+      <c r="G1189" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 戊</t>
+        </is>
+      </c>
+      <c r="H1189" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1189" s="3" t="n"/>
+      <c r="J1189" s="5" t="n"/>
+      <c r="K1189" s="5" t="n"/>
+      <c r="L1189" s="7" t="n"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="2" t="inlineStr">
+        <is>
+          <t>止</t>
+        </is>
+      </c>
+      <c r="B1190" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1190" s="4" t="n"/>
+      <c r="D1190" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1190" s="5" t="n"/>
+      <c r="F1190" s="5" t="n"/>
+      <c r="G1190" s="4" t="n"/>
+      <c r="H1190" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1190" s="3" t="n"/>
+      <c r="J1190" s="5" t="n"/>
+      <c r="K1190" s="5" t="n"/>
+      <c r="L1190" s="7" t="n"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="2" t="inlineStr">
+        <is>
+          <t>蔓</t>
+        </is>
+      </c>
+      <c r="B1191" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1191" s="4" t="inlineStr">
+        <is>
+          <t>艹 曼</t>
+        </is>
+      </c>
+      <c r="D1191" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1191" s="5" t="n"/>
+      <c r="F1191" s="5" t="n"/>
+      <c r="G1191" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 曼 冃 冂 二 一 罒 又</t>
+        </is>
+      </c>
+      <c r="H1191" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1191" s="3" t="n"/>
+      <c r="J1191" s="5" t="n"/>
+      <c r="K1191" s="5" t="n"/>
+      <c r="L1191" s="7" t="n"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="2" t="inlineStr">
+        <is>
+          <t>藉</t>
+        </is>
+      </c>
+      <c r="B1192" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1192" s="4" t="inlineStr">
+        <is>
+          <t>艹 耤</t>
+        </is>
+      </c>
+      <c r="D1192" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1192" s="5" t="n"/>
+      <c r="F1192" s="5" t="n"/>
+      <c r="G1192" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 耤 耒 丿 未 昔 龷 卄 丨 一 日</t>
+        </is>
+      </c>
+      <c r="H1192" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1192" s="3" t="n"/>
+      <c r="J1192" s="5" t="n"/>
+      <c r="K1192" s="5" t="n"/>
+      <c r="L1192" s="7" t="n"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="2" t="inlineStr">
+        <is>
+          <t>豐</t>
+        </is>
+      </c>
+      <c r="B1193" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1193" s="4" t="inlineStr">
+        <is>
+          <t>山 丰 丰 豆</t>
+        </is>
+      </c>
+      <c r="D1193" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1193" s="5" t="n"/>
+      <c r="F1193" s="5" t="n"/>
+      <c r="G1193" s="4" t="inlineStr">
+        <is>
+          <t>山 丰 丿 二 一 丨 豆</t>
+        </is>
+      </c>
+      <c r="H1193" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1193" s="3" t="n"/>
+      <c r="J1193" s="5" t="n"/>
+      <c r="K1193" s="5" t="n"/>
+      <c r="L1193" s="7" t="n"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="2" t="inlineStr">
+        <is>
+          <t>挫</t>
+        </is>
+      </c>
+      <c r="B1194" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1194" s="4" t="inlineStr">
+        <is>
+          <t>扌 坐</t>
+        </is>
+      </c>
+      <c r="D1194" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1194" s="5" t="n"/>
+      <c r="F1194" s="5" t="n"/>
+      <c r="G1194" s="4" t="inlineStr">
+        <is>
+          <t>扌 坐 土 十 一 从 人</t>
+        </is>
+      </c>
+      <c r="H1194" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1194" s="3" t="n"/>
+      <c r="J1194" s="5" t="n"/>
+      <c r="K1194" s="5" t="n"/>
+      <c r="L1194" s="7" t="n"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="2" t="inlineStr">
+        <is>
+          <t>折</t>
+        </is>
+      </c>
+      <c r="B1195" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第3課</t>
+        </is>
+      </c>
+      <c r="C1195" s="4" t="inlineStr">
+        <is>
+          <t>扌 斤</t>
+        </is>
+      </c>
+      <c r="D1195" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1195" s="5" t="n"/>
+      <c r="F1195" s="5" t="n"/>
+      <c r="G1195" s="4" t="inlineStr">
+        <is>
+          <t>扌 斤 𠂆 丅 一 丨</t>
+        </is>
+      </c>
+      <c r="H1195" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1195" s="3" t="n"/>
+      <c r="J1195" s="5" t="n"/>
+      <c r="K1195" s="5" t="n"/>
+      <c r="L1195" s="7" t="n"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="2" t="inlineStr">
+        <is>
+          <t>恆</t>
+        </is>
+      </c>
+      <c r="B1196" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1196" s="4" t="inlineStr">
+        <is>
+          <t>忄 亙</t>
+        </is>
+      </c>
+      <c r="D1196" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1196" s="5" t="n"/>
+      <c r="F1196" s="5" t="n"/>
+      <c r="G1196" s="4" t="inlineStr">
+        <is>
+          <t>忄 亙 一</t>
+        </is>
+      </c>
+      <c r="H1196" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1196" s="3" t="n"/>
+      <c r="J1196" s="5" t="n"/>
+      <c r="K1196" s="5" t="n"/>
+      <c r="L1196" s="7" t="n"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="2" t="inlineStr">
+        <is>
+          <t>澄</t>
+        </is>
+      </c>
+      <c r="B1197" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1197" s="4" t="inlineStr">
+        <is>
+          <t>氵 登</t>
+        </is>
+      </c>
+      <c r="D1197" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1197" s="5" t="n"/>
+      <c r="F1197" s="5" t="n"/>
+      <c r="G1197" s="4" t="inlineStr">
+        <is>
+          <t>氵 登 癶 豆</t>
+        </is>
+      </c>
+      <c r="H1197" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1197" s="3" t="n"/>
+      <c r="J1197" s="5" t="n"/>
+      <c r="K1197" s="5" t="n"/>
+      <c r="L1197" s="7" t="n"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="2" t="inlineStr">
+        <is>
+          <t>穗</t>
+        </is>
+      </c>
+      <c r="B1198" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1198" s="4" t="inlineStr">
+        <is>
+          <t>禾 惠</t>
+        </is>
+      </c>
+      <c r="D1198" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1198" s="5" t="n"/>
+      <c r="F1198" s="5" t="n"/>
+      <c r="G1198" s="4" t="inlineStr">
+        <is>
+          <t>禾 丿 木 惠 心</t>
+        </is>
+      </c>
+      <c r="H1198" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1198" s="3" t="n"/>
+      <c r="J1198" s="5" t="n"/>
+      <c r="K1198" s="5" t="n"/>
+      <c r="L1198" s="7" t="n"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="2" t="inlineStr">
+        <is>
+          <t>養</t>
+        </is>
+      </c>
+      <c r="B1199" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1199" s="4" t="inlineStr">
+        <is>
+          <t>丷 一 土 食</t>
+        </is>
+      </c>
+      <c r="D1199" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1199" s="5" t="n"/>
+      <c r="F1199" s="5" t="n"/>
+      <c r="G1199" s="4" t="inlineStr">
+        <is>
+          <t>丷 一 土 十 食 人 良 丶 艮</t>
+        </is>
+      </c>
+      <c r="H1199" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1199" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1199" s="5" t="n"/>
+      <c r="K1199" s="5" t="n"/>
+      <c r="L1199" s="7" t="n"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="2" t="inlineStr">
+        <is>
+          <t>源</t>
+        </is>
+      </c>
+      <c r="B1200" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1200" s="4" t="inlineStr">
+        <is>
+          <t>氵 原</t>
+        </is>
+      </c>
+      <c r="D1200" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1200" s="5" t="n"/>
+      <c r="F1200" s="5" t="n"/>
+      <c r="G1200" s="4" t="inlineStr">
+        <is>
+          <t>氵 原 厂 白 小</t>
+        </is>
+      </c>
+      <c r="H1200" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1200" s="3" t="n"/>
+      <c r="J1200" s="5" t="n"/>
+      <c r="K1200" s="5" t="n"/>
+      <c r="L1200" s="7" t="n"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="2" t="inlineStr">
+        <is>
+          <t>藝</t>
+        </is>
+      </c>
+      <c r="B1201" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1201" s="4" t="inlineStr">
+        <is>
+          <t>蓺 云</t>
+        </is>
+      </c>
+      <c r="D1201" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1201" s="5" t="n"/>
+      <c r="F1201" s="5" t="n"/>
+      <c r="G1201" s="4" t="inlineStr">
+        <is>
+          <t>蓺 艹 十 埶 坴 圥 土 一 儿 丿 乚 丸 九 丶 云 二 厶</t>
+        </is>
+      </c>
+      <c r="H1201" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1201" s="3" t="n"/>
+      <c r="J1201" s="5" t="n"/>
+      <c r="K1201" s="5" t="n"/>
+      <c r="L1201" s="7" t="n"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="2" t="inlineStr">
+        <is>
+          <t>樸</t>
+        </is>
+      </c>
+      <c r="B1202" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1202" s="4" t="inlineStr">
+        <is>
+          <t>木 菐</t>
+        </is>
+      </c>
+      <c r="D1202" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1202" s="5" t="n"/>
+      <c r="F1202" s="5" t="n"/>
+      <c r="G1202" s="4" t="inlineStr">
+        <is>
+          <t>木 菐 业 一 丷 夫 二 人</t>
+        </is>
+      </c>
+      <c r="H1202" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1202" s="3" t="n"/>
+      <c r="J1202" s="5" t="n"/>
+      <c r="K1202" s="5" t="n"/>
+      <c r="L1202" s="7" t="n"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="2" t="inlineStr">
+        <is>
+          <t>巾</t>
+        </is>
+      </c>
+      <c r="B1203" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1203" s="4" t="n"/>
+      <c r="D1203" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1203" s="5" t="n"/>
+      <c r="F1203" s="5" t="n"/>
+      <c r="G1203" s="4" t="n"/>
+      <c r="H1203" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1203" s="3" t="n"/>
+      <c r="J1203" s="5" t="n"/>
+      <c r="K1203" s="5" t="n"/>
+      <c r="L1203" s="7" t="n"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="2" t="inlineStr">
+        <is>
+          <t>痠</t>
+        </is>
+      </c>
+      <c r="B1204" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1204" s="4" t="inlineStr">
+        <is>
+          <t>疒 夋</t>
+        </is>
+      </c>
+      <c r="D1204" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1204" s="5" t="n"/>
+      <c r="F1204" s="5" t="n"/>
+      <c r="G1204" s="4" t="inlineStr">
+        <is>
+          <t>疒 夋 允 厶 儿 丿 乚 夊</t>
+        </is>
+      </c>
+      <c r="H1204" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1204" s="3" t="n"/>
+      <c r="J1204" s="5" t="n"/>
+      <c r="K1204" s="5" t="n"/>
+      <c r="L1204" s="7" t="n"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="2" t="inlineStr">
+        <is>
+          <t>素</t>
+        </is>
+      </c>
+      <c r="B1205" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1205" s="4" t="inlineStr">
+        <is>
+          <t>龶 糸</t>
+        </is>
+      </c>
+      <c r="D1205" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1205" s="5" t="n"/>
+      <c r="F1205" s="5" t="n"/>
+      <c r="G1205" s="4" t="inlineStr">
+        <is>
+          <t>龶 糸 幺 丶 小</t>
+        </is>
+      </c>
+      <c r="H1205" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1205" s="3" t="n"/>
+      <c r="J1205" s="5" t="n"/>
+      <c r="K1205" s="5" t="n"/>
+      <c r="L1205" s="7" t="n"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="2" t="inlineStr">
+        <is>
+          <t>尊</t>
+        </is>
+      </c>
+      <c r="B1206" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1206" s="4" t="inlineStr">
+        <is>
+          <t>酋 寸</t>
+        </is>
+      </c>
+      <c r="D1206" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1206" s="5" t="n"/>
+      <c r="F1206" s="5" t="n"/>
+      <c r="G1206" s="4" t="inlineStr">
+        <is>
+          <t>酋 丷 酉 寸</t>
+        </is>
+      </c>
+      <c r="H1206" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1206" s="3" t="n"/>
+      <c r="J1206" s="5" t="n"/>
+      <c r="K1206" s="5" t="n"/>
+      <c r="L1206" s="7" t="n"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="2" t="inlineStr">
+        <is>
+          <t>嚴</t>
+        </is>
+      </c>
+      <c r="B1207" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1207" s="4" t="inlineStr">
+        <is>
+          <t>吅 厂 敢</t>
+        </is>
+      </c>
+      <c r="D1207" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1207" s="5" t="n"/>
+      <c r="F1207" s="5" t="n"/>
+      <c r="G1207" s="4" t="inlineStr">
+        <is>
+          <t>吅 口 厂 敢 丅 一 丨 耳 攵</t>
+        </is>
+      </c>
+      <c r="H1207" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1207" s="3" t="n"/>
+      <c r="J1207" s="5" t="n"/>
+      <c r="K1207" s="5" t="n"/>
+      <c r="L1207" s="7" t="n"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="2" t="inlineStr">
+        <is>
+          <t>勞</t>
+        </is>
+      </c>
+      <c r="B1208" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1208" s="4" t="inlineStr">
+        <is>
+          <t>炏 冖 力</t>
+        </is>
+      </c>
+      <c r="D1208" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1208" s="5" t="n"/>
+      <c r="F1208" s="5" t="n"/>
+      <c r="G1208" s="4" t="inlineStr">
+        <is>
+          <t>炏 火 八 人 冖 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1208" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1208" s="3" t="n"/>
+      <c r="J1208" s="5" t="n"/>
+      <c r="K1208" s="5" t="n"/>
+      <c r="L1208" s="7" t="n"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="2" t="inlineStr">
+        <is>
+          <t>怨</t>
+        </is>
+      </c>
+      <c r="B1209" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1209" s="4" t="inlineStr">
+        <is>
+          <t>夗 心</t>
+        </is>
+      </c>
+      <c r="D1209" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1209" s="5" t="n"/>
+      <c r="F1209" s="5" t="n"/>
+      <c r="G1209" s="4" t="inlineStr">
+        <is>
+          <t>夗 夕 𠂊 丶 㔾 心</t>
+        </is>
+      </c>
+      <c r="H1209" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1209" s="3" t="n"/>
+      <c r="J1209" s="5" t="n"/>
+      <c r="K1209" s="5" t="n"/>
+      <c r="L1209" s="7" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="2" t="inlineStr">
+        <is>
+          <t>慷</t>
+        </is>
+      </c>
+      <c r="B1210" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1210" s="4" t="inlineStr">
+        <is>
+          <t>忄 康</t>
+        </is>
+      </c>
+      <c r="D1210" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1210" s="5" t="n"/>
+      <c r="F1210" s="5" t="n"/>
+      <c r="G1210" s="4" t="inlineStr">
+        <is>
+          <t>忄 康 广 隶</t>
+        </is>
+      </c>
+      <c r="H1210" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1210" s="3" t="n"/>
+      <c r="J1210" s="5" t="n"/>
+      <c r="K1210" s="5" t="n"/>
+      <c r="L1210" s="7" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="2" t="inlineStr">
+        <is>
+          <t>慨</t>
+        </is>
+      </c>
+      <c r="B1211" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1211" s="4" t="inlineStr">
+        <is>
+          <t>忄 既</t>
+        </is>
+      </c>
+      <c r="D1211" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1211" s="5" t="n"/>
+      <c r="F1211" s="5" t="n"/>
+      <c r="G1211" s="4" t="inlineStr">
+        <is>
+          <t>忄 既 旡</t>
+        </is>
+      </c>
+      <c r="H1211" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1211" s="3" t="n"/>
+      <c r="J1211" s="5" t="n"/>
+      <c r="K1211" s="5" t="n"/>
+      <c r="L1211" s="7" t="n"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="2" t="inlineStr">
+        <is>
+          <t>滋</t>
+        </is>
+      </c>
+      <c r="B1212" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第4課</t>
+        </is>
+      </c>
+      <c r="C1212" s="4" t="inlineStr">
+        <is>
+          <t>氵 兹</t>
+        </is>
+      </c>
+      <c r="D1212" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1212" s="5" t="n"/>
+      <c r="F1212" s="5" t="n"/>
+      <c r="G1212" s="4" t="inlineStr">
+        <is>
+          <t>氵 兹 丷 一 幺 丶</t>
+        </is>
+      </c>
+      <c r="H1212" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1212" s="3" t="n"/>
+      <c r="J1212" s="5" t="n"/>
+      <c r="K1212" s="5" t="n"/>
+      <c r="L1212" s="7" t="n"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="2" t="inlineStr">
+        <is>
+          <t>譽</t>
+        </is>
+      </c>
+      <c r="B1213" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1213" s="4" t="inlineStr">
+        <is>
+          <t>與 言</t>
+        </is>
+      </c>
+      <c r="D1213" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1213" s="5" t="n"/>
+      <c r="F1213" s="5" t="n"/>
+      <c r="G1213" s="4" t="inlineStr">
+        <is>
+          <t>與 彐 一 八 丿 言</t>
+        </is>
+      </c>
+      <c r="H1213" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1213" s="3" t="n"/>
+      <c r="J1213" s="5" t="n"/>
+      <c r="K1213" s="5" t="n"/>
+      <c r="L1213" s="7" t="n"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="2" t="inlineStr">
+        <is>
+          <t>務</t>
+        </is>
+      </c>
+      <c r="B1214" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1214" s="4" t="inlineStr">
+        <is>
+          <t>矛 攵 力</t>
+        </is>
+      </c>
+      <c r="D1214" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1214" s="5" t="n"/>
+      <c r="F1214" s="5" t="n"/>
+      <c r="G1214" s="4" t="inlineStr">
+        <is>
+          <t>矛 龴 乛 亅 丿 攵 力 𠃌</t>
+        </is>
+      </c>
+      <c r="H1214" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1214" s="3" t="n"/>
+      <c r="J1214" s="5" t="n"/>
+      <c r="K1214" s="5" t="n"/>
+      <c r="L1214" s="7" t="n"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="2" t="inlineStr">
+        <is>
+          <t>聯</t>
+        </is>
+      </c>
+      <c r="B1215" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1215" s="4" t="inlineStr">
+        <is>
+          <t>耳 幺 幺 丱</t>
+        </is>
+      </c>
+      <c r="D1215" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1215" s="5" t="n"/>
+      <c r="F1215" s="5" t="n"/>
+      <c r="G1215" s="4" t="inlineStr">
+        <is>
+          <t>耳 幺 丶 丱</t>
+        </is>
+      </c>
+      <c r="H1215" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1215" s="3" t="n"/>
+      <c r="J1215" s="5" t="n"/>
+      <c r="K1215" s="5" t="n"/>
+      <c r="L1215" s="7" t="n"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="2" t="inlineStr">
+        <is>
+          <t>核</t>
+        </is>
+      </c>
+      <c r="B1216" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1216" s="4" t="inlineStr">
+        <is>
+          <t>木 亥</t>
+        </is>
+      </c>
+      <c r="D1216" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1216" s="5" t="n"/>
+      <c r="F1216" s="5" t="n"/>
+      <c r="G1216" s="4" t="inlineStr">
+        <is>
+          <t>木 亥 亠 丶 一 𠃋 丿 人</t>
+        </is>
+      </c>
+      <c r="H1216" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1216" s="3" t="n"/>
+      <c r="J1216" s="5" t="n"/>
+      <c r="K1216" s="5" t="n"/>
+      <c r="L1216" s="7" t="n"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="2" t="inlineStr">
+        <is>
+          <t>申</t>
+        </is>
+      </c>
+      <c r="B1217" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1217" s="4" t="n"/>
+      <c r="D1217" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1217" s="5" t="n"/>
+      <c r="F1217" s="5" t="n"/>
+      <c r="G1217" s="4" t="n"/>
+      <c r="H1217" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1217" s="3" t="n"/>
+      <c r="J1217" s="5" t="n"/>
+      <c r="K1217" s="5" t="n"/>
+      <c r="L1217" s="7" t="n"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="2" t="inlineStr">
+        <is>
+          <t>局</t>
+        </is>
+      </c>
+      <c r="B1218" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1218" s="4" t="inlineStr">
+        <is>
+          <t>尸 𠃌 口</t>
+        </is>
+      </c>
+      <c r="D1218" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1218" s="5" t="n"/>
+      <c r="F1218" s="5" t="n"/>
+      <c r="G1218" s="4" t="inlineStr">
+        <is>
+          <t>尸 𠃌 口</t>
+        </is>
+      </c>
+      <c r="H1218" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1218" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1218" s="5" t="n"/>
+      <c r="K1218" s="5" t="n"/>
+      <c r="L1218" s="7" t="n"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="2" t="inlineStr">
+        <is>
+          <t>註</t>
+        </is>
+      </c>
+      <c r="B1219" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1219" s="4" t="inlineStr">
+        <is>
+          <t>言 主</t>
+        </is>
+      </c>
+      <c r="D1219" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1219" s="5" t="n"/>
+      <c r="F1219" s="5" t="n"/>
+      <c r="G1219" s="4" t="inlineStr">
+        <is>
+          <t>言 主 亠 丶 一 土 十</t>
+        </is>
+      </c>
+      <c r="H1219" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1219" s="3" t="n"/>
+      <c r="J1219" s="5" t="n"/>
+      <c r="K1219" s="5" t="n"/>
+      <c r="L1219" s="7" t="n"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="2" t="inlineStr">
+        <is>
+          <t>冊</t>
+        </is>
+      </c>
+      <c r="B1220" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1220" s="4" t="inlineStr">
+        <is>
+          <t>冂 丨 丨 一</t>
+        </is>
+      </c>
+      <c r="D1220" s="4" t="inlineStr">
+        <is>
+          <t>交疊</t>
+        </is>
+      </c>
+      <c r="E1220" s="5" t="n"/>
+      <c r="F1220" s="5" t="n"/>
+      <c r="G1220" s="4" t="inlineStr">
+        <is>
+          <t>冂 丨 一</t>
+        </is>
+      </c>
+      <c r="H1220" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1220" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1220" s="5" t="n"/>
+      <c r="K1220" s="5" t="n"/>
+      <c r="L1220" s="7" t="n"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="2" t="inlineStr">
+        <is>
+          <t>企</t>
+        </is>
+      </c>
+      <c r="B1221" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1221" s="4" t="inlineStr">
+        <is>
+          <t>人 止</t>
+        </is>
+      </c>
+      <c r="D1221" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1221" s="5" t="n"/>
+      <c r="F1221" s="5" t="n"/>
+      <c r="G1221" s="4" t="inlineStr">
+        <is>
+          <t>人 止</t>
+        </is>
+      </c>
+      <c r="H1221" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1221" s="3" t="n"/>
+      <c r="J1221" s="5" t="n"/>
+      <c r="K1221" s="5" t="n"/>
+      <c r="L1221" s="7" t="n"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="2" t="inlineStr">
+        <is>
+          <t>毅</t>
+        </is>
+      </c>
+      <c r="B1222" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1222" s="4" t="inlineStr">
+        <is>
+          <t>豙 殳</t>
+        </is>
+      </c>
+      <c r="D1222" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1222" s="5" t="n"/>
+      <c r="F1222" s="5" t="n"/>
+      <c r="G1222" s="4" t="inlineStr">
+        <is>
+          <t>豙 立 亠 丶 一 丷 𧰨 殳 𠘧 又</t>
+        </is>
+      </c>
+      <c r="H1222" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1222" s="3" t="n"/>
+      <c r="J1222" s="5" t="n"/>
+      <c r="K1222" s="5" t="n"/>
+      <c r="L1222" s="7" t="n"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="2" t="inlineStr">
+        <is>
+          <t>歷</t>
+        </is>
+      </c>
+      <c r="B1223" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1223" s="4" t="inlineStr">
+        <is>
+          <t>厤 止</t>
+        </is>
+      </c>
+      <c r="D1223" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1223" s="5" t="n"/>
+      <c r="F1223" s="5" t="n"/>
+      <c r="G1223" s="4" t="inlineStr">
+        <is>
+          <t>厤 厂 秝 禾 丿 木 止</t>
+        </is>
+      </c>
+      <c r="H1223" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1223" s="3" t="n"/>
+      <c r="J1223" s="5" t="n"/>
+      <c r="K1223" s="5" t="n"/>
+      <c r="L1223" s="7" t="n"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="2" t="inlineStr">
+        <is>
+          <t>英</t>
+        </is>
+      </c>
+      <c r="B1224" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1224" s="4" t="inlineStr">
+        <is>
+          <t>艹 央</t>
+        </is>
+      </c>
+      <c r="D1224" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1224" s="5" t="n"/>
+      <c r="F1224" s="5" t="n"/>
+      <c r="G1224" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 央</t>
+        </is>
+      </c>
+      <c r="H1224" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1224" s="3" t="n"/>
+      <c r="J1224" s="5" t="n"/>
+      <c r="K1224" s="5" t="n"/>
+      <c r="L1224" s="7" t="n"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="2" t="inlineStr">
+        <is>
+          <t>銷</t>
+        </is>
+      </c>
+      <c r="B1225" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1225" s="4" t="inlineStr">
+        <is>
+          <t>金 肖</t>
+        </is>
+      </c>
+      <c r="D1225" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1225" s="5" t="n"/>
+      <c r="F1225" s="5" t="n"/>
+      <c r="G1225" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 肖 ⺌ ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1225" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1225" s="3" t="n"/>
+      <c r="J1225" s="5" t="n"/>
+      <c r="K1225" s="5" t="n"/>
+      <c r="L1225" s="7" t="n"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="2" t="inlineStr">
+        <is>
+          <t>售</t>
+        </is>
+      </c>
+      <c r="B1226" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1226" s="4" t="inlineStr">
+        <is>
+          <t>隹 口</t>
+        </is>
+      </c>
+      <c r="D1226" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1226" s="5" t="n"/>
+      <c r="F1226" s="5" t="n"/>
+      <c r="G1226" s="4" t="inlineStr">
+        <is>
+          <t>隹 口</t>
+        </is>
+      </c>
+      <c r="H1226" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1226" s="3" t="n"/>
+      <c r="J1226" s="5" t="n"/>
+      <c r="K1226" s="5" t="n"/>
+      <c r="L1226" s="7" t="n"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="2" t="inlineStr">
+        <is>
+          <t>勝</t>
+        </is>
+      </c>
+      <c r="B1227" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1227" s="4" t="inlineStr">
+        <is>
+          <t>月 劵</t>
+        </is>
+      </c>
+      <c r="D1227" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1227" s="5" t="n"/>
+      <c r="F1227" s="5" t="n"/>
+      <c r="G1227" s="4" t="inlineStr">
+        <is>
+          <t>月 劵 龹 丷 夫 二 一 人 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1227" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1227" s="3" t="n"/>
+      <c r="J1227" s="5" t="n"/>
+      <c r="K1227" s="5" t="n"/>
+      <c r="L1227" s="7" t="n"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="2" t="inlineStr">
+        <is>
+          <t>霸</t>
+        </is>
+      </c>
+      <c r="B1228" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第5課</t>
+        </is>
+      </c>
+      <c r="C1228" s="4" t="inlineStr">
+        <is>
+          <t>雨 革 月</t>
+        </is>
+      </c>
+      <c r="D1228" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1228" s="5" t="n"/>
+      <c r="F1228" s="5" t="n"/>
+      <c r="G1228" s="4" t="inlineStr">
+        <is>
+          <t>雨 一 冂 丨 丷 八 革 月</t>
+        </is>
+      </c>
+      <c r="H1228" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1228" s="3" t="n"/>
+      <c r="J1228" s="5" t="n"/>
+      <c r="K1228" s="5" t="n"/>
+      <c r="L1228" s="7" t="n"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="2" t="inlineStr">
+        <is>
+          <t>娛</t>
+        </is>
+      </c>
+      <c r="B1229" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1229" s="4" t="inlineStr">
+        <is>
+          <t>女 吳</t>
+        </is>
+      </c>
+      <c r="D1229" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1229" s="5" t="n"/>
+      <c r="F1229" s="5" t="n"/>
+      <c r="G1229" s="4" t="inlineStr">
+        <is>
+          <t>女 吳 𠃑 大 一 人 口</t>
+        </is>
+      </c>
+      <c r="H1229" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1229" s="3" t="n"/>
+      <c r="J1229" s="5" t="n"/>
+      <c r="K1229" s="5" t="n"/>
+      <c r="L1229" s="7" t="n"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="2" t="inlineStr">
+        <is>
+          <t>汽</t>
+        </is>
+      </c>
+      <c r="B1230" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1230" s="4" t="inlineStr">
+        <is>
+          <t>氵 气</t>
+        </is>
+      </c>
+      <c r="D1230" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1230" s="5" t="n"/>
+      <c r="F1230" s="5" t="n"/>
+      <c r="G1230" s="4" t="inlineStr">
+        <is>
+          <t>氵 气 𠂉 一 乁</t>
+        </is>
+      </c>
+      <c r="H1230" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1230" s="3" t="n"/>
+      <c r="J1230" s="5" t="n"/>
+      <c r="K1230" s="5" t="n"/>
+      <c r="L1230" s="7" t="n"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="2" t="inlineStr">
+        <is>
+          <t>哨</t>
+        </is>
+      </c>
+      <c r="B1231" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1231" s="4" t="inlineStr">
+        <is>
+          <t>口 肖</t>
+        </is>
+      </c>
+      <c r="D1231" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1231" s="5" t="n"/>
+      <c r="F1231" s="5" t="n"/>
+      <c r="G1231" s="4" t="inlineStr">
+        <is>
+          <t>口 肖 ⺌ ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1231" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1231" s="3" t="n"/>
+      <c r="J1231" s="5" t="n"/>
+      <c r="K1231" s="5" t="n"/>
+      <c r="L1231" s="7" t="n"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="2" t="inlineStr">
+        <is>
+          <t>典</t>
+        </is>
+      </c>
+      <c r="B1232" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1232" s="4" t="inlineStr">
+        <is>
+          <t>八</t>
+        </is>
+      </c>
+      <c r="D1232" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1232" s="5" t="n"/>
+      <c r="F1232" s="5" t="n"/>
+      <c r="G1232" s="4" t="inlineStr">
+        <is>
+          <t>八</t>
+        </is>
+      </c>
+      <c r="H1232" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1232" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件</t>
+        </is>
+      </c>
+      <c r="J1232" s="5" t="n"/>
+      <c r="K1232" s="5" t="n"/>
+      <c r="L1232" s="7" t="n"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="2" t="inlineStr">
+        <is>
+          <t>框</t>
+        </is>
+      </c>
+      <c r="B1233" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1233" s="4" t="inlineStr">
+        <is>
+          <t>木 匡</t>
+        </is>
+      </c>
+      <c r="D1233" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1233" s="5" t="n"/>
+      <c r="F1233" s="5" t="n"/>
+      <c r="G1233" s="4" t="inlineStr">
+        <is>
+          <t>木 匡 匚 王 一 土 十</t>
+        </is>
+      </c>
+      <c r="H1233" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1233" s="3" t="n"/>
+      <c r="J1233" s="5" t="n"/>
+      <c r="K1233" s="5" t="n"/>
+      <c r="L1233" s="7" t="n"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="2" t="inlineStr">
+        <is>
+          <t>劇</t>
+        </is>
+      </c>
+      <c r="B1234" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1234" s="4" t="inlineStr">
+        <is>
+          <t>豦 刂</t>
+        </is>
+      </c>
+      <c r="D1234" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1234" s="5" t="n"/>
+      <c r="F1234" s="5" t="n"/>
+      <c r="G1234" s="4" t="inlineStr">
+        <is>
+          <t>豦 虍 ⺊ 七 ㇀ 乚 豕 一 𧰨 刂</t>
+        </is>
+      </c>
+      <c r="H1234" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1234" s="3" t="n"/>
+      <c r="J1234" s="5" t="n"/>
+      <c r="K1234" s="5" t="n"/>
+      <c r="L1234" s="7" t="n"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="2" t="inlineStr">
+        <is>
+          <t>父</t>
+        </is>
+      </c>
+      <c r="B1235" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1235" s="4" t="inlineStr">
+        <is>
+          <t>八 乂</t>
+        </is>
+      </c>
+      <c r="D1235" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1235" s="5" t="n"/>
+      <c r="F1235" s="5" t="n"/>
+      <c r="G1235" s="4" t="inlineStr">
+        <is>
+          <t>八 乂 丿 乀</t>
+        </is>
+      </c>
+      <c r="H1235" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1235" s="3" t="n"/>
+      <c r="J1235" s="5" t="n"/>
+      <c r="K1235" s="5" t="n"/>
+      <c r="L1235" s="7" t="n"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="2" t="inlineStr">
+        <is>
+          <t>責</t>
+        </is>
+      </c>
+      <c r="B1236" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1236" s="4" t="inlineStr">
+        <is>
+          <t>龶 貝</t>
+        </is>
+      </c>
+      <c r="D1236" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1236" s="5" t="n"/>
+      <c r="F1236" s="5" t="n"/>
+      <c r="G1236" s="4" t="inlineStr">
+        <is>
+          <t>龶 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1236" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1236" s="3" t="n"/>
+      <c r="J1236" s="5" t="n"/>
+      <c r="K1236" s="5" t="n"/>
+      <c r="L1236" s="7" t="n"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="2" t="inlineStr">
+        <is>
+          <t>鳴</t>
+        </is>
+      </c>
+      <c r="B1237" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1237" s="4" t="inlineStr">
+        <is>
+          <t>口 鳥</t>
+        </is>
+      </c>
+      <c r="D1237" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1237" s="5" t="n"/>
+      <c r="F1237" s="5" t="n"/>
+      <c r="G1237" s="4" t="inlineStr">
+        <is>
+          <t>口 鳥 灬</t>
+        </is>
+      </c>
+      <c r="H1237" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1237" s="3" t="n"/>
+      <c r="J1237" s="5" t="n"/>
+      <c r="K1237" s="5" t="n"/>
+      <c r="L1237" s="7" t="n"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="2" t="inlineStr">
+        <is>
+          <t>獲</t>
+        </is>
+      </c>
+      <c r="B1238" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1238" s="4" t="inlineStr">
+        <is>
+          <t>犭 蒦</t>
+        </is>
+      </c>
+      <c r="D1238" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1238" s="5" t="n"/>
+      <c r="F1238" s="5" t="n"/>
+      <c r="G1238" s="4" t="inlineStr">
+        <is>
+          <t>犭 蒦 艹 十 隻 隹 又</t>
+        </is>
+      </c>
+      <c r="H1238" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1238" s="3" t="n"/>
+      <c r="J1238" s="5" t="n"/>
+      <c r="K1238" s="5" t="n"/>
+      <c r="L1238" s="7" t="n"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="2" t="inlineStr">
+        <is>
+          <t>佳</t>
+        </is>
+      </c>
+      <c r="B1239" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1239" s="4" t="inlineStr">
+        <is>
+          <t>亻 圭</t>
+        </is>
+      </c>
+      <c r="D1239" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1239" s="5" t="n"/>
+      <c r="F1239" s="5" t="n"/>
+      <c r="G1239" s="4" t="inlineStr">
+        <is>
+          <t>亻 圭 土 十 一</t>
+        </is>
+      </c>
+      <c r="H1239" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1239" s="3" t="n"/>
+      <c r="J1239" s="5" t="n"/>
+      <c r="K1239" s="5" t="n"/>
+      <c r="L1239" s="7" t="n"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="2" t="inlineStr">
+        <is>
+          <t>膩</t>
+        </is>
+      </c>
+      <c r="B1240" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1240" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 貳</t>
+        </is>
+      </c>
+      <c r="D1240" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1240" s="5" t="n"/>
+      <c r="F1240" s="5" t="n"/>
+      <c r="G1240" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 貳 弋 一 乚 丶 二 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1240" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1240" s="3" t="n"/>
+      <c r="J1240" s="5" t="n"/>
+      <c r="K1240" s="5" t="n"/>
+      <c r="L1240" s="7" t="n"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="2" t="inlineStr">
+        <is>
+          <t>效</t>
+        </is>
+      </c>
+      <c r="B1241" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1241" s="4" t="inlineStr">
+        <is>
+          <t>交 攵</t>
+        </is>
+      </c>
+      <c r="D1241" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1241" s="5" t="n"/>
+      <c r="F1241" s="5" t="n"/>
+      <c r="G1241" s="4" t="inlineStr">
+        <is>
+          <t>交 亠 丶 一 父 八 乂 丿 乀 攵</t>
+        </is>
+      </c>
+      <c r="H1241" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1241" s="3" t="n"/>
+      <c r="J1241" s="5" t="n"/>
+      <c r="K1241" s="5" t="n"/>
+      <c r="L1241" s="7" t="n"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="2" t="inlineStr">
+        <is>
+          <t>隊</t>
+        </is>
+      </c>
+      <c r="B1242" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1242" s="4" t="inlineStr">
+        <is>
+          <t>阝 丷 豕</t>
+        </is>
+      </c>
+      <c r="D1242" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1242" s="5" t="n"/>
+      <c r="F1242" s="5" t="n"/>
+      <c r="G1242" s="4" t="inlineStr">
+        <is>
+          <t>阝 丷 豕 一 𧰨</t>
+        </is>
+      </c>
+      <c r="H1242" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1242" s="3" t="n"/>
+      <c r="J1242" s="5" t="n"/>
+      <c r="K1242" s="5" t="n"/>
+      <c r="L1242" s="7" t="n"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="2" t="inlineStr">
+        <is>
+          <t>益</t>
+        </is>
+      </c>
+      <c r="B1243" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1243" s="4" t="inlineStr">
+        <is>
+          <t>丷 一 八 皿</t>
+        </is>
+      </c>
+      <c r="D1243" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1243" s="5" t="n"/>
+      <c r="F1243" s="5" t="n"/>
+      <c r="G1243" s="4" t="inlineStr">
+        <is>
+          <t>丷 一 八 皿</t>
+        </is>
+      </c>
+      <c r="H1243" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1243" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1243" s="5" t="n"/>
+      <c r="K1243" s="5" t="n"/>
+      <c r="L1243" s="7" t="n"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" s="2" t="inlineStr">
+        <is>
+          <t>貌</t>
+        </is>
+      </c>
+      <c r="B1244" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1244" s="4" t="inlineStr">
+        <is>
+          <t>豸 皃</t>
+        </is>
+      </c>
+      <c r="D1244" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1244" s="5" t="n"/>
+      <c r="F1244" s="5" t="n"/>
+      <c r="G1244" s="4" t="inlineStr">
+        <is>
+          <t>豸 皃 白 儿 丿 乚</t>
+        </is>
+      </c>
+      <c r="H1244" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1244" s="3" t="n"/>
+      <c r="J1244" s="5" t="n"/>
+      <c r="K1244" s="5" t="n"/>
+      <c r="L1244" s="7" t="n"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="2" t="inlineStr">
+        <is>
+          <t>官</t>
+        </is>
+      </c>
+      <c r="B1245" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1245" s="4" t="inlineStr">
+        <is>
+          <t>宀 㠯</t>
+        </is>
+      </c>
+      <c r="D1245" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1245" s="5" t="n"/>
+      <c r="F1245" s="5" t="n"/>
+      <c r="G1245" s="4" t="inlineStr">
+        <is>
+          <t>宀 㠯</t>
+        </is>
+      </c>
+      <c r="H1245" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1245" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1245" s="5" t="n"/>
+      <c r="K1245" s="5" t="n"/>
+      <c r="L1245" s="7" t="n"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="2" t="inlineStr">
+        <is>
+          <t>增</t>
+        </is>
+      </c>
+      <c r="B1246" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第6課</t>
+        </is>
+      </c>
+      <c r="C1246" s="4" t="inlineStr">
+        <is>
+          <t>土 曾</t>
+        </is>
+      </c>
+      <c r="D1246" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1246" s="5" t="n"/>
+      <c r="F1246" s="5" t="n"/>
+      <c r="G1246" s="4" t="inlineStr">
+        <is>
+          <t>土 十 一 曾 丷 田 日</t>
+        </is>
+      </c>
+      <c r="H1246" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1246" s="3" t="n"/>
+      <c r="J1246" s="5" t="n"/>
+      <c r="K1246" s="5" t="n"/>
+      <c r="L1246" s="7" t="n"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="2" t="inlineStr">
+        <is>
+          <t>逆</t>
+        </is>
+      </c>
+      <c r="B1247" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1247" s="4" t="inlineStr">
+        <is>
+          <t>辶 屰</t>
+        </is>
+      </c>
+      <c r="D1247" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1247" s="5" t="n"/>
+      <c r="F1247" s="5" t="n"/>
+      <c r="G1247" s="4" t="inlineStr">
+        <is>
+          <t>辶 屰 丷 一 屮 凵 丨</t>
+        </is>
+      </c>
+      <c r="H1247" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1247" s="3" t="n"/>
+      <c r="J1247" s="5" t="n"/>
+      <c r="K1247" s="5" t="n"/>
+      <c r="L1247" s="7" t="n"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="2" t="inlineStr">
+        <is>
+          <t>穩</t>
+        </is>
+      </c>
+      <c r="B1248" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1248" s="4" t="inlineStr">
+        <is>
+          <t>禾 爫 工 一 心</t>
+        </is>
+      </c>
+      <c r="D1248" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1248" s="5" t="n"/>
+      <c r="F1248" s="5" t="n"/>
+      <c r="G1248" s="4" t="inlineStr">
+        <is>
+          <t>禾 丿 木 爫 丶 工 一 心</t>
+        </is>
+      </c>
+      <c r="H1248" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1248" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1248" s="5" t="n"/>
+      <c r="K1248" s="5" t="n"/>
+      <c r="L1248" s="7" t="n"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="2" t="inlineStr">
+        <is>
+          <t>憐</t>
+        </is>
+      </c>
+      <c r="B1249" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1249" s="4" t="inlineStr">
+        <is>
+          <t>忄 粦</t>
+        </is>
+      </c>
+      <c r="D1249" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1249" s="5" t="n"/>
+      <c r="F1249" s="5" t="n"/>
+      <c r="G1249" s="4" t="inlineStr">
+        <is>
+          <t>忄 粦 米 舛 夕 𠂊 丶 㐄</t>
+        </is>
+      </c>
+      <c r="H1249" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1249" s="3" t="n"/>
+      <c r="J1249" s="5" t="n"/>
+      <c r="K1249" s="5" t="n"/>
+      <c r="L1249" s="7" t="n"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="2" t="inlineStr">
+        <is>
+          <t>競</t>
+        </is>
+      </c>
+      <c r="B1250" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1250" s="4" t="inlineStr">
+        <is>
+          <t>竞 竞</t>
+        </is>
+      </c>
+      <c r="D1250" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1250" s="5" t="n"/>
+      <c r="F1250" s="5" t="n"/>
+      <c r="G1250" s="4" t="inlineStr">
+        <is>
+          <t>竞 立 亠 丶 一 丷 兄 口 儿 丿 乚</t>
+        </is>
+      </c>
+      <c r="H1250" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1250" s="3" t="n"/>
+      <c r="J1250" s="5" t="n"/>
+      <c r="K1250" s="5" t="n"/>
+      <c r="L1250" s="7" t="n"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="2" t="inlineStr">
+        <is>
+          <t>抗</t>
+        </is>
+      </c>
+      <c r="B1251" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1251" s="4" t="inlineStr">
+        <is>
+          <t>扌 亢</t>
+        </is>
+      </c>
+      <c r="D1251" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1251" s="5" t="n"/>
+      <c r="F1251" s="5" t="n"/>
+      <c r="G1251" s="4" t="inlineStr">
+        <is>
+          <t>扌 亢 亠 丶 一 几</t>
+        </is>
+      </c>
+      <c r="H1251" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1251" s="3" t="n"/>
+      <c r="J1251" s="5" t="n"/>
+      <c r="K1251" s="5" t="n"/>
+      <c r="L1251" s="7" t="n"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="2" t="inlineStr">
+        <is>
+          <t>逸</t>
+        </is>
+      </c>
+      <c r="B1252" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1252" s="4" t="inlineStr">
+        <is>
+          <t>辶 兔</t>
+        </is>
+      </c>
+      <c r="D1252" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1252" s="5" t="n"/>
+      <c r="F1252" s="5" t="n"/>
+      <c r="G1252" s="4" t="inlineStr">
+        <is>
+          <t>辶 兔 免 𠂊 丶</t>
+        </is>
+      </c>
+      <c r="H1252" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1252" s="3" t="n"/>
+      <c r="J1252" s="5" t="n"/>
+      <c r="K1252" s="5" t="n"/>
+      <c r="L1252" s="7" t="n"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="2" t="inlineStr">
+        <is>
+          <t>鄰</t>
+        </is>
+      </c>
+      <c r="B1253" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1253" s="4" t="inlineStr">
+        <is>
+          <t>粦 阝</t>
+        </is>
+      </c>
+      <c r="D1253" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1253" s="5" t="n"/>
+      <c r="F1253" s="5" t="n"/>
+      <c r="G1253" s="4" t="inlineStr">
+        <is>
+          <t>粦 米 舛 夕 𠂊 丶 㐄 阝</t>
+        </is>
+      </c>
+      <c r="H1253" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1253" s="3" t="n"/>
+      <c r="J1253" s="5" t="n"/>
+      <c r="K1253" s="5" t="n"/>
+      <c r="L1253" s="7" t="n"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="2" t="inlineStr">
+        <is>
+          <t>脈</t>
+        </is>
+      </c>
+      <c r="B1254" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1254" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 𠂆</t>
+        </is>
+      </c>
+      <c r="D1254" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1254" s="5" t="n"/>
+      <c r="F1254" s="5" t="n"/>
+      <c r="G1254" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 𠂆</t>
+        </is>
+      </c>
+      <c r="H1254" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1254" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1254" s="5" t="n"/>
+      <c r="K1254" s="5" t="n"/>
+      <c r="L1254" s="7" t="n"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="2" t="inlineStr">
+        <is>
+          <t>緻</t>
+        </is>
+      </c>
+      <c r="B1255" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1255" s="4" t="inlineStr">
+        <is>
+          <t>糹 致</t>
+        </is>
+      </c>
+      <c r="D1255" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1255" s="5" t="n"/>
+      <c r="F1255" s="5" t="n"/>
+      <c r="G1255" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 致 至 一 厶 土 十 夊</t>
+        </is>
+      </c>
+      <c r="H1255" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1255" s="3" t="n"/>
+      <c r="J1255" s="5" t="n"/>
+      <c r="K1255" s="5" t="n"/>
+      <c r="L1255" s="7" t="n"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="2" t="inlineStr">
+        <is>
+          <t>弱</t>
+        </is>
+      </c>
+      <c r="B1256" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1256" s="4" t="inlineStr">
+        <is>
+          <t>弓 冫 弓 冫</t>
+        </is>
+      </c>
+      <c r="D1256" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1256" s="5" t="n"/>
+      <c r="F1256" s="5" t="n"/>
+      <c r="G1256" s="4" t="inlineStr">
+        <is>
+          <t>弓 冫</t>
+        </is>
+      </c>
+      <c r="H1256" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1256" s="3" t="n"/>
+      <c r="J1256" s="5" t="n"/>
+      <c r="K1256" s="5" t="n"/>
+      <c r="L1256" s="7" t="n"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="2" t="inlineStr">
+        <is>
+          <t>嚏</t>
+        </is>
+      </c>
+      <c r="B1257" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1257" s="4" t="inlineStr">
+        <is>
+          <t>口 疐</t>
+        </is>
+      </c>
+      <c r="D1257" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1257" s="5" t="n"/>
+      <c r="F1257" s="5" t="n"/>
+      <c r="G1257" s="4" t="inlineStr">
+        <is>
+          <t>口 疐 十 冖 田 疋</t>
+        </is>
+      </c>
+      <c r="H1257" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1257" s="3" t="n"/>
+      <c r="J1257" s="5" t="n"/>
+      <c r="K1257" s="5" t="n"/>
+      <c r="L1257" s="7" t="n"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="2" t="inlineStr">
+        <is>
+          <t>織</t>
+        </is>
+      </c>
+      <c r="B1258" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1258" s="4" t="inlineStr">
+        <is>
+          <t>糹 戠</t>
+        </is>
+      </c>
+      <c r="D1258" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1258" s="5" t="n"/>
+      <c r="F1258" s="5" t="n"/>
+      <c r="G1258" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 戠 音 立 亠 一 丷 日 戈 弋 乚 丿</t>
+        </is>
+      </c>
+      <c r="H1258" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1258" s="3" t="n"/>
+      <c r="J1258" s="5" t="n"/>
+      <c r="K1258" s="5" t="n"/>
+      <c r="L1258" s="7" t="n"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="2" t="inlineStr">
+        <is>
+          <t>碌</t>
+        </is>
+      </c>
+      <c r="B1259" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1259" s="4" t="inlineStr">
+        <is>
+          <t>石 彔</t>
+        </is>
+      </c>
+      <c r="D1259" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1259" s="5" t="n"/>
+      <c r="F1259" s="5" t="n"/>
+      <c r="G1259" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 彔 彑 氺 亅 丷 八</t>
+        </is>
+      </c>
+      <c r="H1259" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1259" s="3" t="n"/>
+      <c r="J1259" s="5" t="n"/>
+      <c r="K1259" s="5" t="n"/>
+      <c r="L1259" s="7" t="n"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="2" t="inlineStr">
+        <is>
+          <t>盎</t>
+        </is>
+      </c>
+      <c r="B1260" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1260" s="4" t="inlineStr">
+        <is>
+          <t>央 皿</t>
+        </is>
+      </c>
+      <c r="D1260" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1260" s="5" t="n"/>
+      <c r="F1260" s="5" t="n"/>
+      <c r="G1260" s="4" t="inlineStr">
+        <is>
+          <t>央 皿</t>
+        </is>
+      </c>
+      <c r="H1260" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1260" s="3" t="n"/>
+      <c r="J1260" s="5" t="n"/>
+      <c r="K1260" s="5" t="n"/>
+      <c r="L1260" s="7" t="n"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="2" t="inlineStr">
+        <is>
+          <t>膽</t>
+        </is>
+      </c>
+      <c r="B1261" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1261" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 詹</t>
+        </is>
+      </c>
+      <c r="D1261" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1261" s="5" t="n"/>
+      <c r="F1261" s="5" t="n"/>
+      <c r="G1261" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 詹 厃 𠂊 厂 儿 丿 乚 言</t>
+        </is>
+      </c>
+      <c r="H1261" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1261" s="3" t="n"/>
+      <c r="J1261" s="5" t="n"/>
+      <c r="K1261" s="5" t="n"/>
+      <c r="L1261" s="7" t="n"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="2" t="inlineStr">
+        <is>
+          <t>圈</t>
+        </is>
+      </c>
+      <c r="B1262" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1262" s="4" t="inlineStr">
+        <is>
+          <t>囗 卷</t>
+        </is>
+      </c>
+      <c r="D1262" s="4" t="inlineStr">
+        <is>
+          <t>全包圍</t>
+        </is>
+      </c>
+      <c r="E1262" s="5" t="n"/>
+      <c r="F1262" s="5" t="n"/>
+      <c r="G1262" s="4" t="inlineStr">
+        <is>
+          <t>囗 卷 龹 丷 夫 二 一 人 㔾</t>
+        </is>
+      </c>
+      <c r="H1262" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1262" s="3" t="n"/>
+      <c r="J1262" s="5" t="n"/>
+      <c r="K1262" s="5" t="n"/>
+      <c r="L1262" s="7" t="n"/>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="2" t="inlineStr">
+        <is>
+          <t>疲</t>
+        </is>
+      </c>
+      <c r="B1263" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第7課</t>
+        </is>
+      </c>
+      <c r="C1263" s="4" t="inlineStr">
+        <is>
+          <t>疒 皮</t>
+        </is>
+      </c>
+      <c r="D1263" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1263" s="5" t="n"/>
+      <c r="F1263" s="5" t="n"/>
+      <c r="G1263" s="4" t="inlineStr">
+        <is>
+          <t>疒 皮</t>
+        </is>
+      </c>
+      <c r="H1263" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1263" s="3" t="n"/>
+      <c r="J1263" s="5" t="n"/>
+      <c r="K1263" s="5" t="n"/>
+      <c r="L1263" s="7" t="n"/>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="2" t="inlineStr">
+        <is>
+          <t>坦</t>
+        </is>
+      </c>
+      <c r="B1264" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1264" s="4" t="inlineStr">
+        <is>
+          <t>土 旦</t>
+        </is>
+      </c>
+      <c r="D1264" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1264" s="5" t="n"/>
+      <c r="F1264" s="5" t="n"/>
+      <c r="G1264" s="4" t="inlineStr">
+        <is>
+          <t>土 十 一 旦 日</t>
+        </is>
+      </c>
+      <c r="H1264" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1264" s="3" t="n"/>
+      <c r="J1264" s="5" t="n"/>
+      <c r="K1264" s="5" t="n"/>
+      <c r="L1264" s="7" t="n"/>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="2" t="inlineStr">
+        <is>
+          <t>性</t>
+        </is>
+      </c>
+      <c r="B1265" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1265" s="4" t="inlineStr">
+        <is>
+          <t>忄 生</t>
+        </is>
+      </c>
+      <c r="D1265" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1265" s="5" t="n"/>
+      <c r="F1265" s="5" t="n"/>
+      <c r="G1265" s="4" t="inlineStr">
+        <is>
+          <t>忄 生</t>
+        </is>
+      </c>
+      <c r="H1265" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1265" s="3" t="n"/>
+      <c r="J1265" s="5" t="n"/>
+      <c r="K1265" s="5" t="n"/>
+      <c r="L1265" s="7" t="n"/>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="inlineStr">
+        <is>
+          <t>恐</t>
+        </is>
+      </c>
+      <c r="B1266" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1266" s="4" t="inlineStr">
+        <is>
+          <t>巩 心</t>
+        </is>
+      </c>
+      <c r="D1266" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1266" s="5" t="n"/>
+      <c r="F1266" s="5" t="n"/>
+      <c r="G1266" s="4" t="inlineStr">
+        <is>
+          <t>巩 工 卂 ⺄ 十 心</t>
+        </is>
+      </c>
+      <c r="H1266" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1266" s="3" t="n"/>
+      <c r="J1266" s="5" t="n"/>
+      <c r="K1266" s="5" t="n"/>
+      <c r="L1266" s="7" t="n"/>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2" t="inlineStr">
+        <is>
+          <t>怖</t>
+        </is>
+      </c>
+      <c r="B1267" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1267" s="4" t="inlineStr">
+        <is>
+          <t>忄 布</t>
+        </is>
+      </c>
+      <c r="D1267" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1267" s="5" t="n"/>
+      <c r="F1267" s="5" t="n"/>
+      <c r="G1267" s="4" t="inlineStr">
+        <is>
+          <t>忄 布 𠂇 巾</t>
+        </is>
+      </c>
+      <c r="H1267" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1267" s="3" t="n"/>
+      <c r="J1267" s="5" t="n"/>
+      <c r="K1267" s="5" t="n"/>
+      <c r="L1267" s="7" t="n"/>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2" t="inlineStr">
+        <is>
+          <t>組</t>
+        </is>
+      </c>
+      <c r="B1268" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1268" s="4" t="inlineStr">
+        <is>
+          <t>糹 且</t>
+        </is>
+      </c>
+      <c r="D1268" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1268" s="5" t="n"/>
+      <c r="F1268" s="5" t="n"/>
+      <c r="G1268" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 且</t>
+        </is>
+      </c>
+      <c r="H1268" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1268" s="3" t="n"/>
+      <c r="J1268" s="5" t="n"/>
+      <c r="K1268" s="5" t="n"/>
+      <c r="L1268" s="7" t="n"/>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="2" t="inlineStr">
+        <is>
+          <t>占</t>
+        </is>
+      </c>
+      <c r="B1269" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1269" s="4" t="inlineStr">
+        <is>
+          <t>⺊ 口</t>
+        </is>
+      </c>
+      <c r="D1269" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1269" s="5" t="n"/>
+      <c r="F1269" s="5" t="n"/>
+      <c r="G1269" s="4" t="inlineStr">
+        <is>
+          <t>⺊ 口</t>
+        </is>
+      </c>
+      <c r="H1269" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1269" s="3" t="n"/>
+      <c r="J1269" s="5" t="n"/>
+      <c r="K1269" s="5" t="n"/>
+      <c r="L1269" s="7" t="n"/>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2" t="inlineStr">
+        <is>
+          <t>控</t>
+        </is>
+      </c>
+      <c r="B1270" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1270" s="4" t="inlineStr">
+        <is>
+          <t>扌 空</t>
+        </is>
+      </c>
+      <c r="D1270" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1270" s="5" t="n"/>
+      <c r="F1270" s="5" t="n"/>
+      <c r="G1270" s="4" t="inlineStr">
+        <is>
+          <t>扌 空 穴 宀 八 工</t>
+        </is>
+      </c>
+      <c r="H1270" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1270" s="3" t="n"/>
+      <c r="J1270" s="5" t="n"/>
+      <c r="K1270" s="5" t="n"/>
+      <c r="L1270" s="7" t="n"/>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="2" t="inlineStr">
+        <is>
+          <t>制</t>
+        </is>
+      </c>
+      <c r="B1271" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1271" s="4" t="inlineStr">
+        <is>
+          <t>牛 冂 刂</t>
+        </is>
+      </c>
+      <c r="D1271" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1271" s="5" t="n"/>
+      <c r="F1271" s="5" t="n"/>
+      <c r="G1271" s="4" t="inlineStr">
+        <is>
+          <t>牛 冂 刂</t>
+        </is>
+      </c>
+      <c r="H1271" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1271" s="3" t="n"/>
+      <c r="J1271" s="5" t="n"/>
+      <c r="K1271" s="5" t="n"/>
+      <c r="L1271" s="7" t="n"/>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="2" t="inlineStr">
+        <is>
+          <t>傷</t>
+        </is>
+      </c>
+      <c r="B1272" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1272" s="4" t="inlineStr">
+        <is>
+          <t>亻 𠂉 昜</t>
+        </is>
+      </c>
+      <c r="D1272" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1272" s="5" t="n"/>
+      <c r="F1272" s="5" t="n"/>
+      <c r="G1272" s="4" t="inlineStr">
+        <is>
+          <t>亻 𠂉 昜 旦 日 一 勿 勹 丿</t>
+        </is>
+      </c>
+      <c r="H1272" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1272" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1272" s="5" t="n"/>
+      <c r="K1272" s="5" t="n"/>
+      <c r="L1272" s="7" t="n"/>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="2" t="inlineStr">
+        <is>
+          <t>攻</t>
+        </is>
+      </c>
+      <c r="B1273" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1273" s="4" t="inlineStr">
+        <is>
+          <t>工 攵</t>
+        </is>
+      </c>
+      <c r="D1273" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1273" s="5" t="n"/>
+      <c r="F1273" s="5" t="n"/>
+      <c r="G1273" s="4" t="inlineStr">
+        <is>
+          <t>工 攵</t>
+        </is>
+      </c>
+      <c r="H1273" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1273" s="3" t="n"/>
+      <c r="J1273" s="5" t="n"/>
+      <c r="K1273" s="5" t="n"/>
+      <c r="L1273" s="7" t="n"/>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="2" t="inlineStr">
+        <is>
+          <t>擊</t>
+        </is>
+      </c>
+      <c r="B1274" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1274" s="4" t="inlineStr">
+        <is>
+          <t>車 凵 殳 手</t>
+        </is>
+      </c>
+      <c r="D1274" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1274" s="5" t="n"/>
+      <c r="F1274" s="5" t="n"/>
+      <c r="G1274" s="4" t="inlineStr">
+        <is>
+          <t>車 凵 殳 𠘧 又 手</t>
+        </is>
+      </c>
+      <c r="H1274" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1274" s="3" t="n"/>
+      <c r="J1274" s="5" t="n"/>
+      <c r="K1274" s="5" t="n"/>
+      <c r="L1274" s="7" t="n"/>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="2" t="inlineStr">
+        <is>
+          <t>權</t>
+        </is>
+      </c>
+      <c r="B1275" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1275" s="4" t="inlineStr">
+        <is>
+          <t>木 雚</t>
+        </is>
+      </c>
+      <c r="D1275" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1275" s="5" t="n"/>
+      <c r="F1275" s="5" t="n"/>
+      <c r="G1275" s="4" t="inlineStr">
+        <is>
+          <t>木 雚 艹 十 吅 口 隹</t>
+        </is>
+      </c>
+      <c r="H1275" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1275" s="3" t="n"/>
+      <c r="J1275" s="5" t="n"/>
+      <c r="K1275" s="5" t="n"/>
+      <c r="L1275" s="7" t="n"/>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2" t="inlineStr">
+        <is>
+          <t>脅</t>
+        </is>
+      </c>
+      <c r="B1276" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1276" s="4" t="inlineStr">
+        <is>
+          <t>劦 ⺼</t>
+        </is>
+      </c>
+      <c r="D1276" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1276" s="5" t="n"/>
+      <c r="F1276" s="5" t="n"/>
+      <c r="G1276" s="4" t="inlineStr">
+        <is>
+          <t>劦 力 丿 𠃌 ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1276" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1276" s="3" t="n"/>
+      <c r="J1276" s="5" t="n"/>
+      <c r="K1276" s="5" t="n"/>
+      <c r="L1276" s="7" t="n"/>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="2" t="inlineStr">
+        <is>
+          <t>復</t>
+        </is>
+      </c>
+      <c r="B1277" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1277" s="4" t="inlineStr">
+        <is>
+          <t>彳 复</t>
+        </is>
+      </c>
+      <c r="D1277" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1277" s="5" t="n"/>
+      <c r="F1277" s="5" t="n"/>
+      <c r="G1277" s="4" t="inlineStr">
+        <is>
+          <t>彳 复 𠂉 日 夊</t>
+        </is>
+      </c>
+      <c r="H1277" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1277" s="3" t="n"/>
+      <c r="J1277" s="5" t="n"/>
+      <c r="K1277" s="5" t="n"/>
+      <c r="L1277" s="7" t="n"/>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2" t="inlineStr">
+        <is>
+          <t>武</t>
+        </is>
+      </c>
+      <c r="B1278" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1278" s="4" t="inlineStr">
+        <is>
+          <t>弋 一 止</t>
+        </is>
+      </c>
+      <c r="D1278" s="4" t="inlineStr">
+        <is>
+          <t>右上包圍</t>
+        </is>
+      </c>
+      <c r="E1278" s="5" t="n"/>
+      <c r="F1278" s="5" t="n"/>
+      <c r="G1278" s="4" t="inlineStr">
+        <is>
+          <t>弋 一 乚 丶 止</t>
+        </is>
+      </c>
+      <c r="H1278" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1278" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1278" s="5" t="n"/>
+      <c r="K1278" s="5" t="n"/>
+      <c r="L1278" s="7" t="n"/>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="2" t="inlineStr">
+        <is>
+          <t>撼</t>
+        </is>
+      </c>
+      <c r="B1279" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1279" s="4" t="inlineStr">
+        <is>
+          <t>扌 感</t>
+        </is>
+      </c>
+      <c r="D1279" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1279" s="5" t="n"/>
+      <c r="F1279" s="5" t="n"/>
+      <c r="G1279" s="4" t="inlineStr">
+        <is>
+          <t>扌 感 咸 戌 戊 一 口 心</t>
+        </is>
+      </c>
+      <c r="H1279" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1279" s="3" t="n"/>
+      <c r="J1279" s="5" t="n"/>
+      <c r="K1279" s="5" t="n"/>
+      <c r="L1279" s="7" t="n"/>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2" t="inlineStr">
+        <is>
+          <t>懼</t>
+        </is>
+      </c>
+      <c r="B1280" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第8課</t>
+        </is>
+      </c>
+      <c r="C1280" s="4" t="inlineStr">
+        <is>
+          <t>忄 瞿</t>
+        </is>
+      </c>
+      <c r="D1280" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1280" s="5" t="n"/>
+      <c r="F1280" s="5" t="n"/>
+      <c r="G1280" s="4" t="inlineStr">
+        <is>
+          <t>忄 瞿 目 隹</t>
+        </is>
+      </c>
+      <c r="H1280" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1280" s="3" t="n"/>
+      <c r="J1280" s="5" t="n"/>
+      <c r="K1280" s="5" t="n"/>
+      <c r="L1280" s="7" t="n"/>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="2" t="inlineStr">
+        <is>
+          <t>維</t>
+        </is>
+      </c>
+      <c r="B1281" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1281" s="4" t="inlineStr">
+        <is>
+          <t>糹 隹</t>
+        </is>
+      </c>
+      <c r="D1281" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1281" s="5" t="n"/>
+      <c r="F1281" s="5" t="n"/>
+      <c r="G1281" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 隹</t>
+        </is>
+      </c>
+      <c r="H1281" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1281" s="3" t="n"/>
+      <c r="J1281" s="5" t="n"/>
+      <c r="K1281" s="5" t="n"/>
+      <c r="L1281" s="7" t="n"/>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2" t="inlineStr">
+        <is>
+          <t>戰</t>
+        </is>
+      </c>
+      <c r="B1282" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1282" s="4" t="inlineStr">
+        <is>
+          <t>單 戈</t>
+        </is>
+      </c>
+      <c r="D1282" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1282" s="5" t="n"/>
+      <c r="F1282" s="5" t="n"/>
+      <c r="G1282" s="4" t="inlineStr">
+        <is>
+          <t>單 吅 口 甲 一 戈 弋 乚 丶 丿</t>
+        </is>
+      </c>
+      <c r="H1282" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1282" s="3" t="n"/>
+      <c r="J1282" s="5" t="n"/>
+      <c r="K1282" s="5" t="n"/>
+      <c r="L1282" s="7" t="n"/>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="2" t="inlineStr">
+        <is>
+          <t>崎</t>
+        </is>
+      </c>
+      <c r="B1283" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1283" s="4" t="inlineStr">
+        <is>
+          <t>山 奇</t>
+        </is>
+      </c>
+      <c r="D1283" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1283" s="5" t="n"/>
+      <c r="F1283" s="5" t="n"/>
+      <c r="G1283" s="4" t="inlineStr">
+        <is>
+          <t>山 奇 大 一 人 可 丁 亅 口</t>
+        </is>
+      </c>
+      <c r="H1283" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1283" s="3" t="n"/>
+      <c r="J1283" s="5" t="n"/>
+      <c r="K1283" s="5" t="n"/>
+      <c r="L1283" s="7" t="n"/>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="2" t="inlineStr">
+        <is>
+          <t>嶇</t>
+        </is>
+      </c>
+      <c r="B1284" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1284" s="4" t="inlineStr">
+        <is>
+          <t>山 區</t>
+        </is>
+      </c>
+      <c r="D1284" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1284" s="5" t="n"/>
+      <c r="F1284" s="5" t="n"/>
+      <c r="G1284" s="4" t="inlineStr">
+        <is>
+          <t>山 區 匸 品 口 吅</t>
+        </is>
+      </c>
+      <c r="H1284" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1284" s="3" t="n"/>
+      <c r="J1284" s="5" t="n"/>
+      <c r="K1284" s="5" t="n"/>
+      <c r="L1284" s="7" t="n"/>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="2" t="inlineStr">
+        <is>
+          <t>拳</t>
+        </is>
+      </c>
+      <c r="B1285" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1285" s="4" t="inlineStr">
+        <is>
+          <t>龹 手</t>
+        </is>
+      </c>
+      <c r="D1285" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1285" s="5" t="n"/>
+      <c r="F1285" s="5" t="n"/>
+      <c r="G1285" s="4" t="inlineStr">
+        <is>
+          <t>龹 丷 夫 二 一 人 手</t>
+        </is>
+      </c>
+      <c r="H1285" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1285" s="3" t="n"/>
+      <c r="J1285" s="5" t="n"/>
+      <c r="K1285" s="5" t="n"/>
+      <c r="L1285" s="7" t="n"/>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2" t="inlineStr">
+        <is>
+          <t>癌</t>
+        </is>
+      </c>
+      <c r="B1286" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1286" s="4" t="inlineStr">
+        <is>
+          <t>疒 嵒</t>
+        </is>
+      </c>
+      <c r="D1286" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1286" s="5" t="n"/>
+      <c r="F1286" s="5" t="n"/>
+      <c r="G1286" s="4" t="inlineStr">
+        <is>
+          <t>疒 嵒 品 口 吅 山</t>
+        </is>
+      </c>
+      <c r="H1286" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1286" s="3" t="n"/>
+      <c r="J1286" s="5" t="n"/>
+      <c r="K1286" s="5" t="n"/>
+      <c r="L1286" s="7" t="n"/>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="2" t="inlineStr">
+        <is>
+          <t>症</t>
+        </is>
+      </c>
+      <c r="B1287" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1287" s="4" t="inlineStr">
+        <is>
+          <t>疒 正</t>
+        </is>
+      </c>
+      <c r="D1287" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1287" s="5" t="n"/>
+      <c r="F1287" s="5" t="n"/>
+      <c r="G1287" s="4" t="inlineStr">
+        <is>
+          <t>疒 正 一 止</t>
+        </is>
+      </c>
+      <c r="H1287" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1287" s="3" t="n"/>
+      <c r="J1287" s="5" t="n"/>
+      <c r="K1287" s="5" t="n"/>
+      <c r="L1287" s="7" t="n"/>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="B1288" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1288" s="4" t="inlineStr">
+        <is>
+          <t>金 同</t>
+        </is>
+      </c>
+      <c r="D1288" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1288" s="5" t="n"/>
+      <c r="F1288" s="5" t="n"/>
+      <c r="G1288" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 同 冂 口</t>
+        </is>
+      </c>
+      <c r="H1288" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1288" s="3" t="n"/>
+      <c r="J1288" s="5" t="n"/>
+      <c r="K1288" s="5" t="n"/>
+      <c r="L1288" s="7" t="n"/>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="2" t="inlineStr">
+        <is>
+          <t>牌</t>
+        </is>
+      </c>
+      <c r="B1289" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1289" s="4" t="inlineStr">
+        <is>
+          <t>片 卑</t>
+        </is>
+      </c>
+      <c r="D1289" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1289" s="5" t="n"/>
+      <c r="F1289" s="5" t="n"/>
+      <c r="G1289" s="4" t="inlineStr">
+        <is>
+          <t>片 卑 白 丿 十</t>
+        </is>
+      </c>
+      <c r="H1289" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1289" s="3" t="n"/>
+      <c r="J1289" s="5" t="n"/>
+      <c r="K1289" s="5" t="n"/>
+      <c r="L1289" s="7" t="n"/>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2" t="inlineStr">
+        <is>
+          <t>屢</t>
+        </is>
+      </c>
+      <c r="B1290" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1290" s="4" t="inlineStr">
+        <is>
+          <t>尸 婁</t>
+        </is>
+      </c>
+      <c r="D1290" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1290" s="5" t="n"/>
+      <c r="F1290" s="5" t="n"/>
+      <c r="G1290" s="4" t="inlineStr">
+        <is>
+          <t>尸 婁 女</t>
+        </is>
+      </c>
+      <c r="H1290" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1290" s="3" t="n"/>
+      <c r="J1290" s="5" t="n"/>
+      <c r="K1290" s="5" t="n"/>
+      <c r="L1290" s="7" t="n"/>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="2" t="inlineStr">
+        <is>
+          <t>予</t>
+        </is>
+      </c>
+      <c r="B1291" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1291" s="4" t="inlineStr">
+        <is>
+          <t>龴 乛 亅</t>
+        </is>
+      </c>
+      <c r="D1291" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1291" s="5" t="n"/>
+      <c r="F1291" s="5" t="n"/>
+      <c r="G1291" s="4" t="inlineStr">
+        <is>
+          <t>龴 乛 亅</t>
+        </is>
+      </c>
+      <c r="H1291" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1291" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1291" s="5" t="n"/>
+      <c r="K1291" s="5" t="n"/>
+      <c r="L1291" s="7" t="n"/>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2" t="inlineStr">
+        <is>
+          <t>幼</t>
+        </is>
+      </c>
+      <c r="B1292" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1292" s="4" t="inlineStr">
+        <is>
+          <t>幺 力</t>
+        </is>
+      </c>
+      <c r="D1292" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1292" s="5" t="n"/>
+      <c r="F1292" s="5" t="n"/>
+      <c r="G1292" s="4" t="inlineStr">
+        <is>
+          <t>幺 丶 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1292" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1292" s="3" t="n"/>
+      <c r="J1292" s="5" t="n"/>
+      <c r="K1292" s="5" t="n"/>
+      <c r="L1292" s="7" t="n"/>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="2" t="inlineStr">
+        <is>
+          <t>椰</t>
+        </is>
+      </c>
+      <c r="B1293" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1293" s="4" t="inlineStr">
+        <is>
+          <t>木 耶</t>
+        </is>
+      </c>
+      <c r="D1293" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1293" s="5" t="n"/>
+      <c r="F1293" s="5" t="n"/>
+      <c r="G1293" s="4" t="inlineStr">
+        <is>
+          <t>木 耶 耳 阝</t>
+        </is>
+      </c>
+      <c r="H1293" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1293" s="3" t="n"/>
+      <c r="J1293" s="5" t="n"/>
+      <c r="K1293" s="5" t="n"/>
+      <c r="L1293" s="7" t="n"/>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2" t="inlineStr">
+        <is>
+          <t>即</t>
+        </is>
+      </c>
+      <c r="B1294" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1294" s="4" t="inlineStr">
+        <is>
+          <t>卩</t>
+        </is>
+      </c>
+      <c r="D1294" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1294" s="5" t="n"/>
+      <c r="F1294" s="5" t="n"/>
+      <c r="G1294" s="4" t="inlineStr">
+        <is>
+          <t>卩</t>
+        </is>
+      </c>
+      <c r="H1294" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1294" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件</t>
+        </is>
+      </c>
+      <c r="J1294" s="5" t="n"/>
+      <c r="K1294" s="5" t="n"/>
+      <c r="L1294" s="7" t="n"/>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="2" t="inlineStr">
+        <is>
+          <t>腐</t>
+        </is>
+      </c>
+      <c r="B1295" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1295" s="4" t="inlineStr">
+        <is>
+          <t>府 肉</t>
+        </is>
+      </c>
+      <c r="D1295" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1295" s="5" t="n"/>
+      <c r="F1295" s="5" t="n"/>
+      <c r="G1295" s="4" t="inlineStr">
+        <is>
+          <t>府 广 付 亻 寸 肉</t>
+        </is>
+      </c>
+      <c r="H1295" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1295" s="3" t="n"/>
+      <c r="J1295" s="5" t="n"/>
+      <c r="K1295" s="5" t="n"/>
+      <c r="L1295" s="7" t="n"/>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2" t="inlineStr">
+        <is>
+          <t>衝</t>
+        </is>
+      </c>
+      <c r="B1296" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1296" s="4" t="inlineStr">
+        <is>
+          <t>彳 重 亍</t>
+        </is>
+      </c>
+      <c r="D1296" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E1296" s="5" t="n"/>
+      <c r="F1296" s="5" t="n"/>
+      <c r="G1296" s="4" t="inlineStr">
+        <is>
+          <t>彳 重 亍 一 丁 亅</t>
+        </is>
+      </c>
+      <c r="H1296" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1296" s="3" t="n"/>
+      <c r="J1296" s="5" t="n"/>
+      <c r="K1296" s="5" t="n"/>
+      <c r="L1296" s="7" t="n"/>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="2" t="inlineStr">
+        <is>
+          <t>鍛</t>
+        </is>
+      </c>
+      <c r="B1297" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1297" s="4" t="inlineStr">
+        <is>
+          <t>金 段</t>
+        </is>
+      </c>
+      <c r="D1297" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1297" s="5" t="n"/>
+      <c r="F1297" s="5" t="n"/>
+      <c r="G1297" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 段 殳 𠘧 又</t>
+        </is>
+      </c>
+      <c r="H1297" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1297" s="3" t="n"/>
+      <c r="J1297" s="5" t="n"/>
+      <c r="K1297" s="5" t="n"/>
+      <c r="L1297" s="7" t="n"/>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2" t="inlineStr">
+        <is>
+          <t>鍊</t>
+        </is>
+      </c>
+      <c r="B1298" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第9課</t>
+        </is>
+      </c>
+      <c r="C1298" s="4" t="inlineStr">
+        <is>
+          <t>金 柬</t>
+        </is>
+      </c>
+      <c r="D1298" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1298" s="5" t="n"/>
+      <c r="F1298" s="5" t="n"/>
+      <c r="G1298" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 柬</t>
+        </is>
+      </c>
+      <c r="H1298" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1298" s="3" t="n"/>
+      <c r="J1298" s="5" t="n"/>
+      <c r="K1298" s="5" t="n"/>
+      <c r="L1298" s="7" t="n"/>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="2" t="inlineStr">
+        <is>
+          <t>唐</t>
+        </is>
+      </c>
+      <c r="B1299" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1299" s="4" t="inlineStr">
+        <is>
+          <t>广 肀 口</t>
+        </is>
+      </c>
+      <c r="D1299" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1299" s="5" t="n"/>
+      <c r="F1299" s="5" t="n"/>
+      <c r="G1299" s="4" t="inlineStr">
+        <is>
+          <t>广 肀 一 丨 口</t>
+        </is>
+      </c>
+      <c r="H1299" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1299" s="3" t="n"/>
+      <c r="J1299" s="5" t="n"/>
+      <c r="K1299" s="5" t="n"/>
+      <c r="L1299" s="7" t="n"/>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="2" t="inlineStr">
+        <is>
+          <t>恬</t>
+        </is>
+      </c>
+      <c r="B1300" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1300" s="4" t="inlineStr">
+        <is>
+          <t>忄 舌</t>
+        </is>
+      </c>
+      <c r="D1300" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1300" s="5" t="n"/>
+      <c r="F1300" s="5" t="n"/>
+      <c r="G1300" s="4" t="inlineStr">
+        <is>
+          <t>忄 舌 干 口</t>
+        </is>
+      </c>
+      <c r="H1300" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1300" s="3" t="n"/>
+      <c r="J1300" s="5" t="n"/>
+      <c r="K1300" s="5" t="n"/>
+      <c r="L1300" s="7" t="n"/>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="2" t="inlineStr">
+        <is>
+          <t>罷</t>
+        </is>
+      </c>
+      <c r="B1301" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1301" s="4" t="inlineStr">
+        <is>
+          <t>罒 能</t>
+        </is>
+      </c>
+      <c r="D1301" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1301" s="5" t="n"/>
+      <c r="F1301" s="5" t="n"/>
+      <c r="G1301" s="4" t="inlineStr">
+        <is>
+          <t>罒 能 厶 ⺼ ⺆ 冫 匕 乚 一</t>
+        </is>
+      </c>
+      <c r="H1301" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1301" s="3" t="n"/>
+      <c r="J1301" s="5" t="n"/>
+      <c r="K1301" s="5" t="n"/>
+      <c r="L1301" s="7" t="n"/>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2" t="inlineStr">
+        <is>
+          <t>暮</t>
+        </is>
+      </c>
+      <c r="B1302" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1302" s="4" t="inlineStr">
+        <is>
+          <t>莫 日</t>
+        </is>
+      </c>
+      <c r="D1302" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1302" s="5" t="n"/>
+      <c r="F1302" s="5" t="n"/>
+      <c r="G1302" s="4" t="inlineStr">
+        <is>
+          <t>莫 艹 十 旲 日 大 一 人</t>
+        </is>
+      </c>
+      <c r="H1302" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1302" s="3" t="n"/>
+      <c r="J1302" s="5" t="n"/>
+      <c r="K1302" s="5" t="n"/>
+      <c r="L1302" s="7" t="n"/>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="2" t="inlineStr">
+        <is>
+          <t>掩</t>
+        </is>
+      </c>
+      <c r="B1303" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1303" s="4" t="inlineStr">
+        <is>
+          <t>扌 奄</t>
+        </is>
+      </c>
+      <c r="D1303" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1303" s="5" t="n"/>
+      <c r="F1303" s="5" t="n"/>
+      <c r="G1303" s="4" t="inlineStr">
+        <is>
+          <t>扌 奄 大 一 人 电 日 乚</t>
+        </is>
+      </c>
+      <c r="H1303" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1303" s="3" t="n"/>
+      <c r="J1303" s="5" t="n"/>
+      <c r="K1303" s="5" t="n"/>
+      <c r="L1303" s="7" t="n"/>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2" t="inlineStr">
+        <is>
+          <t>柴</t>
+        </is>
+      </c>
+      <c r="B1304" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1304" s="4" t="inlineStr">
+        <is>
+          <t>此 朩</t>
+        </is>
+      </c>
+      <c r="D1304" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1304" s="5" t="n"/>
+      <c r="F1304" s="5" t="n"/>
+      <c r="G1304" s="4" t="inlineStr">
+        <is>
+          <t>此 止 匕 乚 一 朩</t>
+        </is>
+      </c>
+      <c r="H1304" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1304" s="3" t="n"/>
+      <c r="J1304" s="5" t="n"/>
+      <c r="K1304" s="5" t="n"/>
+      <c r="L1304" s="7" t="n"/>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="2" t="inlineStr">
+        <is>
+          <t>扉</t>
+        </is>
+      </c>
+      <c r="B1305" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1305" s="4" t="inlineStr">
+        <is>
+          <t>戶 非</t>
+        </is>
+      </c>
+      <c r="D1305" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1305" s="5" t="n"/>
+      <c r="F1305" s="5" t="n"/>
+      <c r="G1305" s="4" t="inlineStr">
+        <is>
+          <t>戶 丿 尸 非</t>
+        </is>
+      </c>
+      <c r="H1305" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1305" s="3" t="n"/>
+      <c r="J1305" s="5" t="n"/>
+      <c r="K1305" s="5" t="n"/>
+      <c r="L1305" s="7" t="n"/>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2" t="inlineStr">
+        <is>
+          <t>歸</t>
+        </is>
+      </c>
+      <c r="B1306" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1306" s="4" t="inlineStr">
+        <is>
+          <t>丿 㠯 止 帚</t>
+        </is>
+      </c>
+      <c r="D1306" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1306" s="5" t="n"/>
+      <c r="F1306" s="5" t="n"/>
+      <c r="G1306" s="4" t="inlineStr">
+        <is>
+          <t>丿 㠯 止 帚 一 冖 巾</t>
+        </is>
+      </c>
+      <c r="H1306" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1306" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1306" s="5" t="n"/>
+      <c r="K1306" s="5" t="n"/>
+      <c r="L1306" s="7" t="n"/>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="2" t="inlineStr">
+        <is>
+          <t>畢</t>
+        </is>
+      </c>
+      <c r="B1307" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1307" s="4" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="D1307" s="4" t="inlineStr">
+        <is>
+          <t>交疊</t>
+        </is>
+      </c>
+      <c r="E1307" s="5" t="n"/>
+      <c r="F1307" s="5" t="n"/>
+      <c r="G1307" s="4" t="inlineStr">
+        <is>
+          <t>一</t>
+        </is>
+      </c>
+      <c r="H1307" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1307" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件；只有一個部件；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1307" s="5" t="n"/>
+      <c r="K1307" s="5" t="n"/>
+      <c r="L1307" s="7" t="n"/>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2" t="inlineStr">
+        <is>
+          <t>陋</t>
+        </is>
+      </c>
+      <c r="B1308" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1308" s="4" t="inlineStr">
+        <is>
+          <t>阝 𠃊 丙</t>
+        </is>
+      </c>
+      <c r="D1308" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1308" s="5" t="n"/>
+      <c r="F1308" s="5" t="n"/>
+      <c r="G1308" s="4" t="inlineStr">
+        <is>
+          <t>阝 𠃊 丙 一 内 冂 人</t>
+        </is>
+      </c>
+      <c r="H1308" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1308" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1308" s="5" t="n"/>
+      <c r="K1308" s="5" t="n"/>
+      <c r="L1308" s="7" t="n"/>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="2" t="inlineStr">
+        <is>
+          <t>傍</t>
+        </is>
+      </c>
+      <c r="B1309" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1309" s="4" t="inlineStr">
+        <is>
+          <t>亻 旁</t>
+        </is>
+      </c>
+      <c r="D1309" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1309" s="5" t="n"/>
+      <c r="F1309" s="5" t="n"/>
+      <c r="G1309" s="4" t="inlineStr">
+        <is>
+          <t>亻 旁 亠 丶 一 丷 冖 方 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1309" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1309" s="3" t="n"/>
+      <c r="J1309" s="5" t="n"/>
+      <c r="K1309" s="5" t="n"/>
+      <c r="L1309" s="7" t="n"/>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2" t="inlineStr">
+        <is>
+          <t>確</t>
+        </is>
+      </c>
+      <c r="B1310" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1310" s="4" t="inlineStr">
+        <is>
+          <t>石 隺</t>
+        </is>
+      </c>
+      <c r="D1310" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1310" s="5" t="n"/>
+      <c r="F1310" s="5" t="n"/>
+      <c r="G1310" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 隺 冖 隹</t>
+        </is>
+      </c>
+      <c r="H1310" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1310" s="3" t="n"/>
+      <c r="J1310" s="5" t="n"/>
+      <c r="K1310" s="5" t="n"/>
+      <c r="L1310" s="7" t="n"/>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="2" t="inlineStr">
+        <is>
+          <t>幽</t>
+        </is>
+      </c>
+      <c r="B1311" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1311" s="4" t="inlineStr">
+        <is>
+          <t>山 幺 幺</t>
+        </is>
+      </c>
+      <c r="D1311" s="4" t="inlineStr">
+        <is>
+          <t>交疊</t>
+        </is>
+      </c>
+      <c r="E1311" s="5" t="n"/>
+      <c r="F1311" s="5" t="n"/>
+      <c r="G1311" s="4" t="inlineStr">
+        <is>
+          <t>山 幺 丶</t>
+        </is>
+      </c>
+      <c r="H1311" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1311" s="3" t="n"/>
+      <c r="J1311" s="5" t="n"/>
+      <c r="K1311" s="5" t="n"/>
+      <c r="L1311" s="7" t="n"/>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2" t="inlineStr">
+        <is>
+          <t>眠</t>
+        </is>
+      </c>
+      <c r="B1312" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1312" s="4" t="inlineStr">
+        <is>
+          <t>目 民</t>
+        </is>
+      </c>
+      <c r="D1312" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1312" s="5" t="n"/>
+      <c r="F1312" s="5" t="n"/>
+      <c r="G1312" s="4" t="inlineStr">
+        <is>
+          <t>目 民</t>
+        </is>
+      </c>
+      <c r="H1312" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1312" s="3" t="n"/>
+      <c r="J1312" s="5" t="n"/>
+      <c r="K1312" s="5" t="n"/>
+      <c r="L1312" s="7" t="n"/>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="2" t="inlineStr">
+        <is>
+          <t>職</t>
+        </is>
+      </c>
+      <c r="B1313" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1313" s="4" t="inlineStr">
+        <is>
+          <t>耳 戠</t>
+        </is>
+      </c>
+      <c r="D1313" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1313" s="5" t="n"/>
+      <c r="F1313" s="5" t="n"/>
+      <c r="G1313" s="4" t="inlineStr">
+        <is>
+          <t>耳 戠 音 立 亠 丶 一 丷 日 戈 弋 乚 丿</t>
+        </is>
+      </c>
+      <c r="H1313" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1313" s="3" t="n"/>
+      <c r="J1313" s="5" t="n"/>
+      <c r="K1313" s="5" t="n"/>
+      <c r="L1313" s="7" t="n"/>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2" t="inlineStr">
+        <is>
+          <t>吟</t>
+        </is>
+      </c>
+      <c r="B1314" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1314" s="4" t="inlineStr">
+        <is>
+          <t>口 今</t>
+        </is>
+      </c>
+      <c r="D1314" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1314" s="5" t="n"/>
+      <c r="F1314" s="5" t="n"/>
+      <c r="G1314" s="4" t="inlineStr">
+        <is>
+          <t>口 今 亼 人 一 ㇇</t>
+        </is>
+      </c>
+      <c r="H1314" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1314" s="3" t="n"/>
+      <c r="J1314" s="5" t="n"/>
+      <c r="K1314" s="5" t="n"/>
+      <c r="L1314" s="7" t="n"/>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="2" t="inlineStr">
+        <is>
+          <t>曠</t>
+        </is>
+      </c>
+      <c r="B1315" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第10課</t>
+        </is>
+      </c>
+      <c r="C1315" s="4" t="inlineStr">
+        <is>
+          <t>日 廣</t>
+        </is>
+      </c>
+      <c r="D1315" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1315" s="5" t="n"/>
+      <c r="F1315" s="5" t="n"/>
+      <c r="G1315" s="4" t="inlineStr">
+        <is>
+          <t>日 廣 广 黃 廿 一 田 八</t>
+        </is>
+      </c>
+      <c r="H1315" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1315" s="3" t="n"/>
+      <c r="J1315" s="5" t="n"/>
+      <c r="K1315" s="5" t="n"/>
+      <c r="L1315" s="7" t="n"/>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2" t="inlineStr">
+        <is>
+          <t>駭</t>
+        </is>
+      </c>
+      <c r="B1316" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1316" s="4" t="inlineStr">
+        <is>
+          <t>馬 亥</t>
+        </is>
+      </c>
+      <c r="D1316" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1316" s="5" t="n"/>
+      <c r="F1316" s="5" t="n"/>
+      <c r="G1316" s="4" t="inlineStr">
+        <is>
+          <t>馬 灬 亥 亠 丶 一 𠃋 丿 人</t>
+        </is>
+      </c>
+      <c r="H1316" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1316" s="3" t="n"/>
+      <c r="J1316" s="5" t="n"/>
+      <c r="K1316" s="5" t="n"/>
+      <c r="L1316" s="7" t="n"/>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="2" t="inlineStr">
+        <is>
+          <t>疤</t>
+        </is>
+      </c>
+      <c r="B1317" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1317" s="4" t="inlineStr">
+        <is>
+          <t>疒 巴</t>
+        </is>
+      </c>
+      <c r="D1317" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1317" s="5" t="n"/>
+      <c r="F1317" s="5" t="n"/>
+      <c r="G1317" s="4" t="inlineStr">
+        <is>
+          <t>疒 巴</t>
+        </is>
+      </c>
+      <c r="H1317" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1317" s="3" t="n"/>
+      <c r="J1317" s="5" t="n"/>
+      <c r="K1317" s="5" t="n"/>
+      <c r="L1317" s="7" t="n"/>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2" t="inlineStr">
+        <is>
+          <t>痕</t>
+        </is>
+      </c>
+      <c r="B1318" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1318" s="4" t="inlineStr">
+        <is>
+          <t>疒 艮</t>
+        </is>
+      </c>
+      <c r="D1318" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1318" s="5" t="n"/>
+      <c r="F1318" s="5" t="n"/>
+      <c r="G1318" s="4" t="inlineStr">
+        <is>
+          <t>疒 艮</t>
+        </is>
+      </c>
+      <c r="H1318" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1318" s="3" t="n"/>
+      <c r="J1318" s="5" t="n"/>
+      <c r="K1318" s="5" t="n"/>
+      <c r="L1318" s="7" t="n"/>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="2" t="inlineStr">
+        <is>
+          <t>罐</t>
+        </is>
+      </c>
+      <c r="B1319" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1319" s="4" t="inlineStr">
+        <is>
+          <t>缶 雚</t>
+        </is>
+      </c>
+      <c r="D1319" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1319" s="5" t="n"/>
+      <c r="F1319" s="5" t="n"/>
+      <c r="G1319" s="4" t="inlineStr">
+        <is>
+          <t>缶 雚 艹 十 吅 口 隹</t>
+        </is>
+      </c>
+      <c r="H1319" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1319" s="3" t="n"/>
+      <c r="J1319" s="5" t="n"/>
+      <c r="K1319" s="5" t="n"/>
+      <c r="L1319" s="7" t="n"/>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2" t="inlineStr">
+        <is>
+          <t>咚</t>
+        </is>
+      </c>
+      <c r="B1320" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1320" s="4" t="inlineStr">
+        <is>
+          <t>口 冬</t>
+        </is>
+      </c>
+      <c r="D1320" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1320" s="5" t="n"/>
+      <c r="F1320" s="5" t="n"/>
+      <c r="G1320" s="4" t="inlineStr">
+        <is>
+          <t>口 冬 夂 ⺀ 丶</t>
+        </is>
+      </c>
+      <c r="H1320" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1320" s="3" t="n"/>
+      <c r="J1320" s="5" t="n"/>
+      <c r="K1320" s="5" t="n"/>
+      <c r="L1320" s="7" t="n"/>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="2" t="inlineStr">
+        <is>
+          <t>碰</t>
+        </is>
+      </c>
+      <c r="B1321" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1321" s="4" t="inlineStr">
+        <is>
+          <t>石 並</t>
+        </is>
+      </c>
+      <c r="D1321" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1321" s="5" t="n"/>
+      <c r="F1321" s="5" t="n"/>
+      <c r="G1321" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 並 丷 业</t>
+        </is>
+      </c>
+      <c r="H1321" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1321" s="3" t="n"/>
+      <c r="J1321" s="5" t="n"/>
+      <c r="K1321" s="5" t="n"/>
+      <c r="L1321" s="7" t="n"/>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2" t="inlineStr">
+        <is>
+          <t>寮</t>
+        </is>
+      </c>
+      <c r="B1322" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1322" s="4" t="inlineStr">
+        <is>
+          <t>宀 尞</t>
+        </is>
+      </c>
+      <c r="D1322" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1322" s="5" t="n"/>
+      <c r="F1322" s="5" t="n"/>
+      <c r="G1322" s="4" t="inlineStr">
+        <is>
+          <t>宀 尞 昚 大 一 人 丷 日 小</t>
+        </is>
+      </c>
+      <c r="H1322" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1322" s="3" t="n"/>
+      <c r="J1322" s="5" t="n"/>
+      <c r="K1322" s="5" t="n"/>
+      <c r="L1322" s="7" t="n"/>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="2" t="inlineStr">
+        <is>
+          <t>營</t>
+        </is>
+      </c>
+      <c r="B1323" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1323" s="4" t="inlineStr">
+        <is>
+          <t>炏 冖 吕</t>
+        </is>
+      </c>
+      <c r="D1323" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1323" s="5" t="n"/>
+      <c r="F1323" s="5" t="n"/>
+      <c r="G1323" s="4" t="inlineStr">
+        <is>
+          <t>炏 火 八 人 冖 吕 口</t>
+        </is>
+      </c>
+      <c r="H1323" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1323" s="3" t="n"/>
+      <c r="J1323" s="5" t="n"/>
+      <c r="K1323" s="5" t="n"/>
+      <c r="L1323" s="7" t="n"/>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2" t="inlineStr">
+        <is>
+          <t>殺</t>
+        </is>
+      </c>
+      <c r="B1324" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1324" s="4" t="inlineStr">
+        <is>
+          <t>㐅 朮 殳</t>
+        </is>
+      </c>
+      <c r="D1324" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1324" s="5" t="n"/>
+      <c r="F1324" s="5" t="n"/>
+      <c r="G1324" s="4" t="inlineStr">
+        <is>
+          <t>㐅 朮 𣎳 丶 殳 𠘧 又</t>
+        </is>
+      </c>
+      <c r="H1324" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1324" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1324" s="5" t="n"/>
+      <c r="K1324" s="5" t="n"/>
+      <c r="L1324" s="7" t="n"/>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="2" t="inlineStr">
+        <is>
+          <t>崇</t>
+        </is>
+      </c>
+      <c r="B1325" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1325" s="4" t="inlineStr">
+        <is>
+          <t>山 宗</t>
+        </is>
+      </c>
+      <c r="D1325" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1325" s="5" t="n"/>
+      <c r="F1325" s="5" t="n"/>
+      <c r="G1325" s="4" t="inlineStr">
+        <is>
+          <t>山 宗 宀 示</t>
+        </is>
+      </c>
+      <c r="H1325" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1325" s="3" t="n"/>
+      <c r="J1325" s="5" t="n"/>
+      <c r="K1325" s="5" t="n"/>
+      <c r="L1325" s="7" t="n"/>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2" t="inlineStr">
+        <is>
+          <t>置</t>
+        </is>
+      </c>
+      <c r="B1326" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1326" s="4" t="inlineStr">
+        <is>
+          <t>罒 直</t>
+        </is>
+      </c>
+      <c r="D1326" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1326" s="5" t="n"/>
+      <c r="F1326" s="5" t="n"/>
+      <c r="G1326" s="4" t="inlineStr">
+        <is>
+          <t>罒 直 十 且 一</t>
+        </is>
+      </c>
+      <c r="H1326" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1326" s="3" t="n"/>
+      <c r="J1326" s="5" t="n"/>
+      <c r="K1326" s="5" t="n"/>
+      <c r="L1326" s="7" t="n"/>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="2" t="inlineStr">
+        <is>
+          <t>奄</t>
+        </is>
+      </c>
+      <c r="B1327" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1327" s="4" t="inlineStr">
+        <is>
+          <t>大 电</t>
+        </is>
+      </c>
+      <c r="D1327" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1327" s="5" t="n"/>
+      <c r="F1327" s="5" t="n"/>
+      <c r="G1327" s="4" t="inlineStr">
+        <is>
+          <t>大 一 人 电 日 乚</t>
+        </is>
+      </c>
+      <c r="H1327" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1327" s="3" t="n"/>
+      <c r="J1327" s="5" t="n"/>
+      <c r="K1327" s="5" t="n"/>
+      <c r="L1327" s="7" t="n"/>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2" t="inlineStr">
+        <is>
+          <t>翼</t>
+        </is>
+      </c>
+      <c r="B1328" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1328" s="4" t="inlineStr">
+        <is>
+          <t>羽 異</t>
+        </is>
+      </c>
+      <c r="D1328" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1328" s="5" t="n"/>
+      <c r="F1328" s="5" t="n"/>
+      <c r="G1328" s="4" t="inlineStr">
+        <is>
+          <t>羽 习 𠃌 冫 異 田 共 龷 卄 十 丨 一 八</t>
+        </is>
+      </c>
+      <c r="H1328" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1328" s="3" t="n"/>
+      <c r="J1328" s="5" t="n"/>
+      <c r="K1328" s="5" t="n"/>
+      <c r="L1328" s="7" t="n"/>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="2" t="inlineStr">
+        <is>
+          <t>祈</t>
+        </is>
+      </c>
+      <c r="B1329" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1329" s="4" t="inlineStr">
+        <is>
+          <t>礻 斤</t>
+        </is>
+      </c>
+      <c r="D1329" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1329" s="5" t="n"/>
+      <c r="F1329" s="5" t="n"/>
+      <c r="G1329" s="4" t="inlineStr">
+        <is>
+          <t>礻 斤 𠂆 丅 一 丨</t>
+        </is>
+      </c>
+      <c r="H1329" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1329" s="3" t="n"/>
+      <c r="J1329" s="5" t="n"/>
+      <c r="K1329" s="5" t="n"/>
+      <c r="L1329" s="7" t="n"/>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2" t="inlineStr">
+        <is>
+          <t>禱</t>
+        </is>
+      </c>
+      <c r="B1330" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1330" s="4" t="inlineStr">
+        <is>
+          <t>礻 壽</t>
+        </is>
+      </c>
+      <c r="D1330" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1330" s="5" t="n"/>
+      <c r="F1330" s="5" t="n"/>
+      <c r="G1330" s="4" t="inlineStr">
+        <is>
+          <t>礻 壽 士 十 一 乛 工 吋 口 寸</t>
+        </is>
+      </c>
+      <c r="H1330" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1330" s="3" t="n"/>
+      <c r="J1330" s="5" t="n"/>
+      <c r="K1330" s="5" t="n"/>
+      <c r="L1330" s="7" t="n"/>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="2" t="inlineStr">
+        <is>
+          <t>吼</t>
+        </is>
+      </c>
+      <c r="B1331" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1331" s="4" t="inlineStr">
+        <is>
+          <t>口 孔</t>
+        </is>
+      </c>
+      <c r="D1331" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1331" s="5" t="n"/>
+      <c r="F1331" s="5" t="n"/>
+      <c r="G1331" s="4" t="inlineStr">
+        <is>
+          <t>口 孔 子 乚</t>
+        </is>
+      </c>
+      <c r="H1331" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1331" s="3" t="n"/>
+      <c r="J1331" s="5" t="n"/>
+      <c r="K1331" s="5" t="n"/>
+      <c r="L1331" s="7" t="n"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2" t="inlineStr">
+        <is>
+          <t>喉</t>
+        </is>
+      </c>
+      <c r="B1332" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1332" s="4" t="inlineStr">
+        <is>
+          <t>口 侯</t>
+        </is>
+      </c>
+      <c r="D1332" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1332" s="5" t="n"/>
+      <c r="F1332" s="5" t="n"/>
+      <c r="G1332" s="4" t="inlineStr">
+        <is>
+          <t>口 侯 亻 矢 𠂉 大 一 人</t>
+        </is>
+      </c>
+      <c r="H1332" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1332" s="3" t="n"/>
+      <c r="J1332" s="5" t="n"/>
+      <c r="K1332" s="5" t="n"/>
+      <c r="L1332" s="7" t="n"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="2" t="inlineStr">
+        <is>
+          <t>嚨</t>
+        </is>
+      </c>
+      <c r="B1333" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第11課</t>
+        </is>
+      </c>
+      <c r="C1333" s="4" t="inlineStr">
+        <is>
+          <t>口 龍</t>
+        </is>
+      </c>
+      <c r="D1333" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1333" s="5" t="n"/>
+      <c r="F1333" s="5" t="n"/>
+      <c r="G1333" s="4" t="inlineStr">
+        <is>
+          <t>口 龍 立 亠 丶 一 丷 月</t>
+        </is>
+      </c>
+      <c r="H1333" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1333" s="3" t="n"/>
+      <c r="J1333" s="5" t="n"/>
+      <c r="K1333" s="5" t="n"/>
+      <c r="L1333" s="7" t="n"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2" t="inlineStr">
+        <is>
+          <t>烈</t>
+        </is>
+      </c>
+      <c r="B1334" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1334" s="4" t="inlineStr">
+        <is>
+          <t>列 灬</t>
+        </is>
+      </c>
+      <c r="D1334" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1334" s="5" t="n"/>
+      <c r="F1334" s="5" t="n"/>
+      <c r="G1334" s="4" t="inlineStr">
+        <is>
+          <t>列 歹 一 夕 𠂊 丶 刂 灬</t>
+        </is>
+      </c>
+      <c r="H1334" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1334" s="3" t="n"/>
+      <c r="J1334" s="5" t="n"/>
+      <c r="K1334" s="5" t="n"/>
+      <c r="L1334" s="7" t="n"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="2" t="inlineStr">
+        <is>
+          <t>暈</t>
+        </is>
+      </c>
+      <c r="B1335" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1335" s="4" t="inlineStr">
+        <is>
+          <t>日 軍</t>
+        </is>
+      </c>
+      <c r="D1335" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1335" s="5" t="n"/>
+      <c r="F1335" s="5" t="n"/>
+      <c r="G1335" s="4" t="inlineStr">
+        <is>
+          <t>日 軍 冖 車</t>
+        </is>
+      </c>
+      <c r="H1335" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1335" s="3" t="n"/>
+      <c r="J1335" s="5" t="n"/>
+      <c r="K1335" s="5" t="n"/>
+      <c r="L1335" s="7" t="n"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2" t="inlineStr">
+        <is>
+          <t>昏</t>
+        </is>
+      </c>
+      <c r="B1336" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1336" s="4" t="inlineStr">
+        <is>
+          <t>氏 日</t>
+        </is>
+      </c>
+      <c r="D1336" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1336" s="5" t="n"/>
+      <c r="F1336" s="5" t="n"/>
+      <c r="G1336" s="4" t="inlineStr">
+        <is>
+          <t>氏 日</t>
+        </is>
+      </c>
+      <c r="H1336" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1336" s="3" t="n"/>
+      <c r="J1336" s="5" t="n"/>
+      <c r="K1336" s="5" t="n"/>
+      <c r="L1336" s="7" t="n"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="2" t="inlineStr">
+        <is>
+          <t>艙</t>
+        </is>
+      </c>
+      <c r="B1337" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1337" s="4" t="inlineStr">
+        <is>
+          <t>舟 倉</t>
+        </is>
+      </c>
+      <c r="D1337" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1337" s="5" t="n"/>
+      <c r="F1337" s="5" t="n"/>
+      <c r="G1337" s="4" t="inlineStr">
+        <is>
+          <t>舟 倉 亼 人 一 尸 口</t>
+        </is>
+      </c>
+      <c r="H1337" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1337" s="3" t="n"/>
+      <c r="J1337" s="5" t="n"/>
+      <c r="K1337" s="5" t="n"/>
+      <c r="L1337" s="7" t="n"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2" t="inlineStr">
+        <is>
+          <t>途</t>
+        </is>
+      </c>
+      <c r="B1338" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1338" s="4" t="inlineStr">
+        <is>
+          <t>辶 余</t>
+        </is>
+      </c>
+      <c r="D1338" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1338" s="5" t="n"/>
+      <c r="F1338" s="5" t="n"/>
+      <c r="G1338" s="4" t="inlineStr">
+        <is>
+          <t>辶 余 亼 人 一 朩</t>
+        </is>
+      </c>
+      <c r="H1338" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1338" s="3" t="n"/>
+      <c r="J1338" s="5" t="n"/>
+      <c r="K1338" s="5" t="n"/>
+      <c r="L1338" s="7" t="n"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="2" t="inlineStr">
+        <is>
+          <t>喪</t>
+        </is>
+      </c>
+      <c r="B1339" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1339" s="4" t="inlineStr">
+        <is>
+          <t>土 吅 𠄌 乀 丿</t>
+        </is>
+      </c>
+      <c r="D1339" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1339" s="5" t="n"/>
+      <c r="F1339" s="5" t="n"/>
+      <c r="G1339" s="4" t="inlineStr">
+        <is>
+          <t>土 十 一 吅 口 𠄌 乀 丿</t>
+        </is>
+      </c>
+      <c r="H1339" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1339" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1339" s="5" t="n"/>
+      <c r="K1339" s="5" t="n"/>
+      <c r="L1339" s="7" t="n"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2" t="inlineStr">
+        <is>
+          <t>獸</t>
+        </is>
+      </c>
+      <c r="B1340" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1340" s="4" t="inlineStr">
+        <is>
+          <t>嘼 犬</t>
+        </is>
+      </c>
+      <c r="D1340" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1340" s="5" t="n"/>
+      <c r="F1340" s="5" t="n"/>
+      <c r="G1340" s="4" t="inlineStr">
+        <is>
+          <t>嘼 吅 口 田 一 犬</t>
+        </is>
+      </c>
+      <c r="H1340" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1340" s="3" t="n"/>
+      <c r="J1340" s="5" t="n"/>
+      <c r="K1340" s="5" t="n"/>
+      <c r="L1340" s="7" t="n"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="2" t="inlineStr">
+        <is>
+          <t>渾</t>
+        </is>
+      </c>
+      <c r="B1341" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1341" s="4" t="inlineStr">
+        <is>
+          <t>氵 軍</t>
+        </is>
+      </c>
+      <c r="D1341" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1341" s="5" t="n"/>
+      <c r="F1341" s="5" t="n"/>
+      <c r="G1341" s="4" t="inlineStr">
+        <is>
+          <t>氵 軍 冖 車</t>
+        </is>
+      </c>
+      <c r="H1341" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1341" s="3" t="n"/>
+      <c r="J1341" s="5" t="n"/>
+      <c r="K1341" s="5" t="n"/>
+      <c r="L1341" s="7" t="n"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2" t="inlineStr">
+        <is>
+          <t>擱</t>
+        </is>
+      </c>
+      <c r="B1342" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1342" s="4" t="inlineStr">
+        <is>
+          <t>扌 閣</t>
+        </is>
+      </c>
+      <c r="D1342" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1342" s="5" t="n"/>
+      <c r="F1342" s="5" t="n"/>
+      <c r="G1342" s="4" t="inlineStr">
+        <is>
+          <t>扌 閣 門 𠁣 𠃛 各 夂 口</t>
+        </is>
+      </c>
+      <c r="H1342" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1342" s="3" t="n"/>
+      <c r="J1342" s="5" t="n"/>
+      <c r="K1342" s="5" t="n"/>
+      <c r="L1342" s="7" t="n"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="2" t="inlineStr">
+        <is>
+          <t>礁</t>
+        </is>
+      </c>
+      <c r="B1343" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1343" s="4" t="inlineStr">
+        <is>
+          <t>石 焦</t>
+        </is>
+      </c>
+      <c r="D1343" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1343" s="5" t="n"/>
+      <c r="F1343" s="5" t="n"/>
+      <c r="G1343" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 焦 隹 灬</t>
+        </is>
+      </c>
+      <c r="H1343" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1343" s="3" t="n"/>
+      <c r="J1343" s="5" t="n"/>
+      <c r="K1343" s="5" t="n"/>
+      <c r="L1343" s="7" t="n"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2" t="inlineStr">
+        <is>
+          <t>筏</t>
+        </is>
+      </c>
+      <c r="B1344" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1344" s="4" t="inlineStr">
+        <is>
+          <t>竹 伐</t>
+        </is>
+      </c>
+      <c r="D1344" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1344" s="5" t="n"/>
+      <c r="F1344" s="5" t="n"/>
+      <c r="G1344" s="4" t="inlineStr">
+        <is>
+          <t>竹 亇 𠂉 亅 伐 亻 戈 弋 一 乚 丶 丿</t>
+        </is>
+      </c>
+      <c r="H1344" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1344" s="3" t="n"/>
+      <c r="J1344" s="5" t="n"/>
+      <c r="K1344" s="5" t="n"/>
+      <c r="L1344" s="7" t="n"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="2" t="inlineStr">
+        <is>
+          <t>塌</t>
+        </is>
+      </c>
+      <c r="B1345" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1345" s="4" t="inlineStr">
+        <is>
+          <t>土 日 羽</t>
+        </is>
+      </c>
+      <c r="D1345" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1345" s="5" t="n"/>
+      <c r="F1345" s="5" t="n"/>
+      <c r="G1345" s="4" t="inlineStr">
+        <is>
+          <t>土 十 一 日 羽 习 𠃌 冫</t>
+        </is>
+      </c>
+      <c r="H1345" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1345" s="3" t="n"/>
+      <c r="J1345" s="5" t="n"/>
+      <c r="K1345" s="5" t="n"/>
+      <c r="L1345" s="7" t="n"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="2" t="inlineStr">
+        <is>
+          <t>捏</t>
+        </is>
+      </c>
+      <c r="B1346" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1346" s="4" t="inlineStr">
+        <is>
+          <t>扌 圼</t>
+        </is>
+      </c>
+      <c r="D1346" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1346" s="5" t="n"/>
+      <c r="F1346" s="5" t="n"/>
+      <c r="G1346" s="4" t="inlineStr">
+        <is>
+          <t>扌 圼 日 土 十 一</t>
+        </is>
+      </c>
+      <c r="H1346" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1346" s="3" t="n"/>
+      <c r="J1346" s="5" t="n"/>
+      <c r="K1346" s="5" t="n"/>
+      <c r="L1346" s="7" t="n"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="2" t="inlineStr">
+        <is>
+          <t>燒</t>
+        </is>
+      </c>
+      <c r="B1347" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1347" s="4" t="inlineStr">
+        <is>
+          <t>火 堯</t>
+        </is>
+      </c>
+      <c r="D1347" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1347" s="5" t="n"/>
+      <c r="F1347" s="5" t="n"/>
+      <c r="G1347" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 堯 垚 土 十 一 兀 儿 丿 乚</t>
+        </is>
+      </c>
+      <c r="H1347" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1347" s="3" t="n"/>
+      <c r="J1347" s="5" t="n"/>
+      <c r="K1347" s="5" t="n"/>
+      <c r="L1347" s="7" t="n"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="2" t="inlineStr">
+        <is>
+          <t>臼</t>
+        </is>
+      </c>
+      <c r="B1348" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1348" s="4" t="n"/>
+      <c r="D1348" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1348" s="5" t="n"/>
+      <c r="F1348" s="5" t="n"/>
+      <c r="G1348" s="4" t="n"/>
+      <c r="H1348" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1348" s="3" t="n"/>
+      <c r="J1348" s="5" t="n"/>
+      <c r="K1348" s="5" t="n"/>
+      <c r="L1348" s="7" t="n"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="2" t="inlineStr">
+        <is>
+          <t>烤</t>
+        </is>
+      </c>
+      <c r="B1349" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1349" s="4" t="inlineStr">
+        <is>
+          <t>火 考</t>
+        </is>
+      </c>
+      <c r="D1349" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1349" s="5" t="n"/>
+      <c r="F1349" s="5" t="n"/>
+      <c r="G1349" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 考 耂 丂 一 ㇉</t>
+        </is>
+      </c>
+      <c r="H1349" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1349" s="3" t="n"/>
+      <c r="J1349" s="5" t="n"/>
+      <c r="K1349" s="5" t="n"/>
+      <c r="L1349" s="7" t="n"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="2" t="inlineStr">
+        <is>
+          <t>爐</t>
+        </is>
+      </c>
+      <c r="B1350" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1350" s="4" t="inlineStr">
+        <is>
+          <t>火 盧</t>
+        </is>
+      </c>
+      <c r="D1350" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1350" s="5" t="n"/>
+      <c r="F1350" s="5" t="n"/>
+      <c r="G1350" s="4" t="inlineStr">
+        <is>
+          <t>火 八 人 盧 虍 ⺊ 七 ㇀ 乚 田 皿</t>
+        </is>
+      </c>
+      <c r="H1350" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1350" s="3" t="n"/>
+      <c r="J1350" s="5" t="n"/>
+      <c r="K1350" s="5" t="n"/>
+      <c r="L1350" s="7" t="n"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="2" t="inlineStr">
+        <is>
+          <t>欲</t>
+        </is>
+      </c>
+      <c r="B1351" s="3" t="inlineStr">
+        <is>
+          <t>康軒5上第12課</t>
+        </is>
+      </c>
+      <c r="C1351" s="4" t="inlineStr">
+        <is>
+          <t>谷 欠</t>
+        </is>
+      </c>
+      <c r="D1351" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1351" s="5" t="n"/>
+      <c r="F1351" s="5" t="n"/>
+      <c r="G1351" s="4" t="inlineStr">
+        <is>
+          <t>谷 八 人 口 欠</t>
+        </is>
+      </c>
+      <c r="H1351" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1351" s="3" t="n"/>
+      <c r="J1351" s="5" t="n"/>
+      <c r="K1351" s="5" t="n"/>
+      <c r="L1351" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1142"/>
+  <autoFilter ref="A1:L1351"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K1142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1351" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"左右,上下,左中右,上中下,全包圍,上方包圍,下方包圍,左方包圍,左上包圍,右上包圍,左下包圍,交疊,獨體字"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/parts-table.xlsx
+++ b/docs/parts-table.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$936</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$1034</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L936"/>
+  <dimension ref="A1:L1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第2課</t>
+          <t>翰林2上第2課、南一3上第6課</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第2課、康軒2上第5課(認讀)、康軒4上第1課</t>
+          <t>翰林2上第2課、康軒2上第5課(認讀)、康軒4上第1課、南一3上第5課</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第2課</t>
+          <t>翰林2上第2課、南一3上第4課</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第3課</t>
+          <t>翰林2上第3課、南一3上第9課</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第4課、康軒1上第4課</t>
+          <t>翰林2上第4課、康軒1上第4課、南一3上第11課</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第4課</t>
+          <t>翰林2上第4課、南一3上第9課</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第4課</t>
+          <t>翰林2上第4課、南一3上第10課</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第5課、康軒4上第5課</t>
+          <t>翰林2上第5課、康軒4上第5課、南一3上第5課</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第5課</t>
+          <t>翰林2上第5課、南一3上第12課</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第5課、康軒4上第7課</t>
+          <t>翰林2上第5課、康軒4上第7課、南一3上第10課</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第6課、康軒4上第5課</t>
+          <t>翰林2上第6課、康軒4上第5課、南一3上第3課</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第6課、康軒2上第5課</t>
+          <t>翰林2上第6課、康軒2上第5課、南一3上第12課</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課</t>
+          <t>翰林2上第7課、南一3上第11課</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課</t>
+          <t>翰林2上第7課、南一3上第9課</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課、康軒3上第6課</t>
+          <t>翰林2上第7課、康軒3上第6課、南一3上第1課</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課</t>
+          <t>翰林2上第7課、南一3上第12課</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第7課、康軒2上第6課</t>
+          <t>翰林2上第7課、康軒2上第6課、南一3上第12課</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第9課、康軒2上第9課</t>
+          <t>翰林2上第9課、康軒2上第9課、南一3上第5課</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第10課</t>
+          <t>翰林2上第10課、南一3上第3課</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第10課</t>
+          <t>翰林2上第10課、南一3上第6課</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第10課</t>
+          <t>翰林2上第10課、南一3上第8課</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第11課</t>
+          <t>翰林2上第11課、南一3上第7課</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第12課</t>
+          <t>翰林2上第12課、南一3上第5課</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -19648,7 +19648,7 @@
       </c>
       <c r="B506" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第2課</t>
+          <t>康軒2上第2課、南一3上第7課</t>
         </is>
       </c>
       <c r="C506" s="4" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="B507" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第2課</t>
+          <t>康軒2上第2課、南一3上第5課</t>
         </is>
       </c>
       <c r="C507" s="4" t="inlineStr">
@@ -20070,7 +20070,7 @@
       </c>
       <c r="B517" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第3課</t>
+          <t>康軒2上第3課、南一3上第11課</t>
         </is>
       </c>
       <c r="C517" s="4" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="B525" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第4課</t>
+          <t>康軒2上第4課、南一3上第3課</t>
         </is>
       </c>
       <c r="C525" s="4" t="inlineStr">
@@ -21568,7 +21568,7 @@
       </c>
       <c r="B556" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第7課</t>
+          <t>康軒2上第7課、南一3上第1課</t>
         </is>
       </c>
       <c r="C556" s="4" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="B567" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第8課</t>
+          <t>康軒2上第8課、南一3上第1課</t>
         </is>
       </c>
       <c r="C567" s="4" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="B568" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第8課</t>
+          <t>康軒2上第8課、南一3上第1課</t>
         </is>
       </c>
       <c r="C568" s="4" t="inlineStr">
@@ -22188,7 +22188,7 @@
       </c>
       <c r="B572" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第8課</t>
+          <t>康軒2上第8課、南一3上第3課</t>
         </is>
       </c>
       <c r="C572" s="4" t="inlineStr">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="B575" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第8課(認讀)</t>
+          <t>康軒2上第8課(認讀)、南一3上第10課</t>
         </is>
       </c>
       <c r="C575" s="4" t="inlineStr">
@@ -22378,7 +22378,7 @@
       </c>
       <c r="B577" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第9課</t>
+          <t>康軒2上第9課、南一3上第10課</t>
         </is>
       </c>
       <c r="C577" s="4" t="inlineStr">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="B583" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第9課</t>
+          <t>康軒2上第9課、南一3上第6課</t>
         </is>
       </c>
       <c r="C583" s="4" t="inlineStr">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B590" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第10課</t>
+          <t>康軒2上第10課、南一3上第10課</t>
         </is>
       </c>
       <c r="C590" s="4" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="B593" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第10課</t>
+          <t>康軒2上第10課、南一3上第11課</t>
         </is>
       </c>
       <c r="C593" s="4" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="B596" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第10課</t>
+          <t>康軒2上第10課、南一3上第10課</t>
         </is>
       </c>
       <c r="C596" s="4" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="B599" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第10課</t>
+          <t>康軒2上第10課、南一3上第4課</t>
         </is>
       </c>
       <c r="C599" s="4" t="inlineStr">
@@ -23340,7 +23340,7 @@
       </c>
       <c r="B602" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第10課(認讀)</t>
+          <t>康軒2上第10課(認讀)、南一3上第11課</t>
         </is>
       </c>
       <c r="C602" s="4" t="inlineStr">
@@ -23644,7 +23644,7 @@
       </c>
       <c r="B610" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第11課</t>
+          <t>康軒2上第11課、南一3上第12課</t>
         </is>
       </c>
       <c r="C610" s="4" t="inlineStr">
@@ -23720,7 +23720,7 @@
       </c>
       <c r="B612" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第11課(認讀)</t>
+          <t>康軒2上第11課(認讀)、南一3上第9課</t>
         </is>
       </c>
       <c r="C612" s="4" t="inlineStr">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="B614" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第12課</t>
+          <t>康軒2上第12課、南一3上第6課</t>
         </is>
       </c>
       <c r="C614" s="4" t="inlineStr">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="B621" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第12課</t>
+          <t>康軒2上第12課、南一3上第8課</t>
         </is>
       </c>
       <c r="C621" s="4" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="B623" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第12課</t>
+          <t>康軒2上第12課、南一3上第8課</t>
         </is>
       </c>
       <c r="C623" s="4" t="inlineStr">
@@ -24256,7 +24256,7 @@
       </c>
       <c r="B626" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第12課(認讀)</t>
+          <t>康軒2上第12課(認讀)、南一3上第2課</t>
         </is>
       </c>
       <c r="C626" s="4" t="inlineStr">
@@ -24928,7 +24928,7 @@
       </c>
       <c r="B644" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第2課(認讀)</t>
+          <t>康軒3上第2課(認讀)、南一3上第5課</t>
         </is>
       </c>
       <c r="C644" s="4" t="inlineStr">
@@ -24966,7 +24966,7 @@
       </c>
       <c r="B645" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第2課(認讀)</t>
+          <t>康軒3上第2課(認讀)、南一3上第4課</t>
         </is>
       </c>
       <c r="C645" s="4" t="inlineStr">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="B652" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第3課</t>
+          <t>康軒3上第3課、南一3上第8課</t>
         </is>
       </c>
       <c r="C652" s="4" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="B654" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第3課</t>
+          <t>康軒3上第3課、南一3上第8課</t>
         </is>
       </c>
       <c r="C654" s="4" t="inlineStr">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="B655" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第3課</t>
+          <t>康軒3上第3課、南一3上第10課</t>
         </is>
       </c>
       <c r="C655" s="4" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="B659" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第4課</t>
+          <t>康軒3上第4課、南一3上第6課</t>
         </is>
       </c>
       <c r="C659" s="4" t="inlineStr">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="B661" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第4課</t>
+          <t>康軒3上第4課、南一3上第3課</t>
         </is>
       </c>
       <c r="C661" s="4" t="inlineStr">
@@ -25608,7 +25608,7 @@
       </c>
       <c r="B662" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第4課</t>
+          <t>康軒3上第4課、南一3上第10課</t>
         </is>
       </c>
       <c r="C662" s="4" t="inlineStr">
@@ -25760,7 +25760,7 @@
       </c>
       <c r="B666" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第4課</t>
+          <t>康軒3上第4課、南一3上第9課</t>
         </is>
       </c>
       <c r="C666" s="4" t="inlineStr">
@@ -25836,7 +25836,7 @@
       </c>
       <c r="B668" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第4課</t>
+          <t>康軒3上第4課、南一3上第6課</t>
         </is>
       </c>
       <c r="C668" s="4" t="inlineStr">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="B677" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第5課</t>
+          <t>康軒3上第5課、南一3上第3課</t>
         </is>
       </c>
       <c r="C677" s="4" t="inlineStr">
@@ -27406,7 +27406,7 @@
       </c>
       <c r="B709" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第7課</t>
+          <t>康軒3上第7課、南一3上第10課</t>
         </is>
       </c>
       <c r="C709" s="4" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="B728" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第9課</t>
+          <t>康軒3上第9課、南一3上第6課</t>
         </is>
       </c>
       <c r="C728" s="4" t="inlineStr">
@@ -28710,7 +28710,7 @@
       </c>
       <c r="B743" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第10課</t>
+          <t>康軒3上第10課、南一3上第5課</t>
         </is>
       </c>
       <c r="C743" s="4" t="inlineStr">
@@ -28824,7 +28824,7 @@
       </c>
       <c r="B746" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第10課</t>
+          <t>康軒3上第10課、南一3上第1課</t>
         </is>
       </c>
       <c r="C746" s="4" t="inlineStr">
@@ -28942,7 +28942,7 @@
       </c>
       <c r="B749" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第10課</t>
+          <t>康軒3上第10課、南一3上第11課</t>
         </is>
       </c>
       <c r="C749" s="4" t="inlineStr"/>
@@ -29010,7 +29010,7 @@
       </c>
       <c r="B751" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第10課(認讀)</t>
+          <t>康軒3上第10課(認讀)、南一3上第11課</t>
         </is>
       </c>
       <c r="C751" s="4" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="B758" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第11課</t>
+          <t>康軒3上第11課、南一3上第12課</t>
         </is>
       </c>
       <c r="C758" s="4" t="inlineStr">
@@ -29740,7 +29740,7 @@
       </c>
       <c r="B770" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第11課(認讀)</t>
+          <t>康軒3上第11課(認讀)、南一3上第10課</t>
         </is>
       </c>
       <c r="C770" s="4" t="inlineStr">
@@ -30090,7 +30090,7 @@
       </c>
       <c r="B779" s="3" t="inlineStr">
         <is>
-          <t>康軒3上第12課</t>
+          <t>康軒3上第12課、南一3上第1課</t>
         </is>
       </c>
       <c r="C779" s="4" t="inlineStr">
@@ -30360,7 +30360,7 @@
       </c>
       <c r="B786" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第1課</t>
+          <t>康軒4上第1課、南一3上第9課</t>
         </is>
       </c>
       <c r="C786" s="4" t="inlineStr">
@@ -30664,7 +30664,7 @@
       </c>
       <c r="B794" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第1課</t>
+          <t>康軒4上第1課、南一3上第4課</t>
         </is>
       </c>
       <c r="C794" s="4" t="inlineStr">
@@ -30976,7 +30976,7 @@
       </c>
       <c r="B802" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第2課</t>
+          <t>康軒4上第2課、南一3上第5課</t>
         </is>
       </c>
       <c r="C802" s="4" t="inlineStr">
@@ -31390,7 +31390,7 @@
       </c>
       <c r="B813" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第3課</t>
+          <t>康軒4上第3課、南一3上第8課</t>
         </is>
       </c>
       <c r="C813" s="4" t="inlineStr">
@@ -31698,7 +31698,7 @@
       </c>
       <c r="B821" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第4課</t>
+          <t>康軒4上第4課、南一3上第9課</t>
         </is>
       </c>
       <c r="C821" s="4" t="inlineStr">
@@ -31736,7 +31736,7 @@
       </c>
       <c r="B822" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第4課</t>
+          <t>康軒4上第4課、南一3上第12課</t>
         </is>
       </c>
       <c r="C822" s="4" t="inlineStr">
@@ -31930,7 +31930,7 @@
       </c>
       <c r="B827" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第4課</t>
+          <t>康軒4上第4課、南一3上第9課</t>
         </is>
       </c>
       <c r="C827" s="4" t="inlineStr">
@@ -32390,7 +32390,7 @@
       </c>
       <c r="B839" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第5課</t>
+          <t>康軒4上第5課、南一3上第8課</t>
         </is>
       </c>
       <c r="C839" s="4" t="inlineStr">
@@ -32694,7 +32694,7 @@
       </c>
       <c r="B847" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第6課</t>
+          <t>康軒4上第6課、南一3上第1課</t>
         </is>
       </c>
       <c r="C847" s="4" t="inlineStr">
@@ -33180,7 +33180,7 @@
       </c>
       <c r="B860" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第6課</t>
+          <t>康軒4上第6課、南一3上第3課</t>
         </is>
       </c>
       <c r="C860" s="4" t="inlineStr">
@@ -34484,7 +34484,7 @@
       </c>
       <c r="B894" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第9課</t>
+          <t>康軒4上第9課、南一3上第5課</t>
         </is>
       </c>
       <c r="C894" s="4" t="inlineStr">
@@ -35168,7 +35168,7 @@
       </c>
       <c r="B912" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第11課</t>
+          <t>康軒4上第11課、南一3上第7課</t>
         </is>
       </c>
       <c r="C912" s="4" t="inlineStr">
@@ -35620,7 +35620,7 @@
       </c>
       <c r="B924" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課</t>
+          <t>康軒4上第12課、南一3上第4課</t>
         </is>
       </c>
       <c r="C924" s="4" t="inlineStr">
@@ -35726,7 +35726,7 @@
       </c>
       <c r="B927" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課</t>
+          <t>康軒4上第12課、南一3上第3課</t>
         </is>
       </c>
       <c r="C927" s="4" t="inlineStr">
@@ -35878,7 +35878,7 @@
       </c>
       <c r="B931" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課</t>
+          <t>康軒4上第12課、南一3上第1課</t>
         </is>
       </c>
       <c r="C931" s="4" t="inlineStr">
@@ -35916,7 +35916,7 @@
       </c>
       <c r="B932" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課</t>
+          <t>康軒4上第12課、南一3上第3課</t>
         </is>
       </c>
       <c r="C932" s="4" t="inlineStr">
@@ -36068,7 +36068,7 @@
       </c>
       <c r="B936" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課</t>
+          <t>康軒4上第12課、南一3上第9課</t>
         </is>
       </c>
       <c r="C936" s="4" t="inlineStr">
@@ -36098,10 +36098,3738 @@
       <c r="K936" s="5" t="inlineStr"/>
       <c r="L936" s="7" t="inlineStr"/>
     </row>
+    <row r="937">
+      <c r="A937" s="2" t="inlineStr">
+        <is>
+          <t>化</t>
+        </is>
+      </c>
+      <c r="B937" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C937" s="4" t="inlineStr">
+        <is>
+          <t>亻 匕</t>
+        </is>
+      </c>
+      <c r="D937" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E937" s="5" t="n"/>
+      <c r="F937" s="5" t="n"/>
+      <c r="G937" s="4" t="inlineStr">
+        <is>
+          <t>亻 匕 乚 一</t>
+        </is>
+      </c>
+      <c r="H937" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I937" s="3" t="n"/>
+      <c r="J937" s="5" t="n"/>
+      <c r="K937" s="5" t="n"/>
+      <c r="L937" s="7" t="n"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="inlineStr">
+        <is>
+          <t>雀</t>
+        </is>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C938" s="4" t="inlineStr">
+        <is>
+          <t>小 隹</t>
+        </is>
+      </c>
+      <c r="D938" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E938" s="5" t="n"/>
+      <c r="F938" s="5" t="n"/>
+      <c r="G938" s="4" t="inlineStr">
+        <is>
+          <t>小 隹</t>
+        </is>
+      </c>
+      <c r="H938" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I938" s="3" t="n"/>
+      <c r="J938" s="5" t="n"/>
+      <c r="K938" s="5" t="n"/>
+      <c r="L938" s="7" t="n"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="inlineStr">
+        <is>
+          <t>輕</t>
+        </is>
+      </c>
+      <c r="B939" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C939" s="4" t="inlineStr">
+        <is>
+          <t>車 巠</t>
+        </is>
+      </c>
+      <c r="D939" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E939" s="5" t="n"/>
+      <c r="F939" s="5" t="n"/>
+      <c r="G939" s="4" t="inlineStr">
+        <is>
+          <t>車 巠 一 巛 𡿨 工</t>
+        </is>
+      </c>
+      <c r="H939" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I939" s="3" t="n"/>
+      <c r="J939" s="5" t="n"/>
+      <c r="K939" s="5" t="n"/>
+      <c r="L939" s="7" t="n"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="inlineStr">
+        <is>
+          <t>脆</t>
+        </is>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C940" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 危</t>
+        </is>
+      </c>
+      <c r="D940" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E940" s="5" t="n"/>
+      <c r="F940" s="5" t="n"/>
+      <c r="G940" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 危 厃 𠂊 厂 㔾</t>
+        </is>
+      </c>
+      <c r="H940" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I940" s="3" t="n"/>
+      <c r="J940" s="5" t="n"/>
+      <c r="K940" s="5" t="n"/>
+      <c r="L940" s="7" t="n"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="inlineStr">
+        <is>
+          <t>髮</t>
+        </is>
+      </c>
+      <c r="B941" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C941" s="4" t="inlineStr">
+        <is>
+          <t>髟 犮</t>
+        </is>
+      </c>
+      <c r="D941" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E941" s="5" t="n"/>
+      <c r="F941" s="5" t="n"/>
+      <c r="G941" s="4" t="inlineStr">
+        <is>
+          <t>髟 镸 一 厶 彡 犮 犬 丿</t>
+        </is>
+      </c>
+      <c r="H941" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I941" s="3" t="n"/>
+      <c r="J941" s="5" t="n"/>
+      <c r="K941" s="5" t="n"/>
+      <c r="L941" s="7" t="n"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="inlineStr">
+        <is>
+          <t>處</t>
+        </is>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C942" s="4" t="inlineStr">
+        <is>
+          <t>虍 処</t>
+        </is>
+      </c>
+      <c r="D942" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E942" s="5" t="n"/>
+      <c r="F942" s="5" t="n"/>
+      <c r="G942" s="4" t="inlineStr">
+        <is>
+          <t>虍 ⺊ 七 ㇀ 乚 処 夂 几</t>
+        </is>
+      </c>
+      <c r="H942" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I942" s="3" t="n"/>
+      <c r="J942" s="5" t="n"/>
+      <c r="K942" s="5" t="n"/>
+      <c r="L942" s="7" t="n"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="inlineStr">
+        <is>
+          <t>男</t>
+        </is>
+      </c>
+      <c r="B943" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第1課</t>
+        </is>
+      </c>
+      <c r="C943" s="4" t="inlineStr">
+        <is>
+          <t>田 力</t>
+        </is>
+      </c>
+      <c r="D943" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E943" s="5" t="n"/>
+      <c r="F943" s="5" t="n"/>
+      <c r="G943" s="4" t="inlineStr">
+        <is>
+          <t>田 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H943" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I943" s="3" t="n"/>
+      <c r="J943" s="5" t="n"/>
+      <c r="K943" s="5" t="n"/>
+      <c r="L943" s="7" t="n"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="inlineStr">
+        <is>
+          <t>廊</t>
+        </is>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C944" s="4" t="inlineStr">
+        <is>
+          <t>广 郎</t>
+        </is>
+      </c>
+      <c r="D944" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E944" s="5" t="n"/>
+      <c r="F944" s="5" t="n"/>
+      <c r="G944" s="4" t="inlineStr">
+        <is>
+          <t>广 郎 丶 阝</t>
+        </is>
+      </c>
+      <c r="H944" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I944" s="3" t="n"/>
+      <c r="J944" s="5" t="n"/>
+      <c r="K944" s="5" t="n"/>
+      <c r="L944" s="7" t="n"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="inlineStr">
+        <is>
+          <t>訂</t>
+        </is>
+      </c>
+      <c r="B945" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C945" s="4" t="inlineStr">
+        <is>
+          <t>言 丁</t>
+        </is>
+      </c>
+      <c r="D945" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E945" s="5" t="n"/>
+      <c r="F945" s="5" t="n"/>
+      <c r="G945" s="4" t="inlineStr">
+        <is>
+          <t>言 丁 一 亅</t>
+        </is>
+      </c>
+      <c r="H945" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I945" s="3" t="n"/>
+      <c r="J945" s="5" t="n"/>
+      <c r="K945" s="5" t="n"/>
+      <c r="L945" s="7" t="n"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="inlineStr">
+        <is>
+          <t>班</t>
+        </is>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C946" s="4" t="inlineStr">
+        <is>
+          <t>王 王</t>
+        </is>
+      </c>
+      <c r="D946" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E946" s="5" t="n"/>
+      <c r="F946" s="5" t="n"/>
+      <c r="G946" s="4" t="inlineStr">
+        <is>
+          <t>王 一 土 十</t>
+        </is>
+      </c>
+      <c r="H946" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I946" s="3" t="n"/>
+      <c r="J946" s="5" t="n"/>
+      <c r="K946" s="5" t="n"/>
+      <c r="L946" s="7" t="n"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="inlineStr">
+        <is>
+          <t>級</t>
+        </is>
+      </c>
+      <c r="B947" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C947" s="4" t="inlineStr">
+        <is>
+          <t>糹 及</t>
+        </is>
+      </c>
+      <c r="D947" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E947" s="5" t="n"/>
+      <c r="F947" s="5" t="n"/>
+      <c r="G947" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 及</t>
+        </is>
+      </c>
+      <c r="H947" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I947" s="3" t="n"/>
+      <c r="J947" s="5" t="n"/>
+      <c r="K947" s="5" t="n"/>
+      <c r="L947" s="7" t="n"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="inlineStr">
+        <is>
+          <t>約</t>
+        </is>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C948" s="4" t="inlineStr">
+        <is>
+          <t>糹 勺</t>
+        </is>
+      </c>
+      <c r="D948" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E948" s="5" t="n"/>
+      <c r="F948" s="5" t="n"/>
+      <c r="G948" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 勺 勹</t>
+        </is>
+      </c>
+      <c r="H948" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I948" s="3" t="n"/>
+      <c r="J948" s="5" t="n"/>
+      <c r="K948" s="5" t="n"/>
+      <c r="L948" s="7" t="n"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="inlineStr">
+        <is>
+          <t>紛</t>
+        </is>
+      </c>
+      <c r="B949" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C949" s="4" t="inlineStr">
+        <is>
+          <t>糹 分</t>
+        </is>
+      </c>
+      <c r="D949" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E949" s="5" t="n"/>
+      <c r="F949" s="5" t="n"/>
+      <c r="G949" s="4" t="inlineStr">
+        <is>
+          <t>糹 幺 丶 分 八 刀 𠃌 丿</t>
+        </is>
+      </c>
+      <c r="H949" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I949" s="3" t="n"/>
+      <c r="J949" s="5" t="n"/>
+      <c r="K949" s="5" t="n"/>
+      <c r="L949" s="7" t="n"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="inlineStr">
+        <is>
+          <t>持</t>
+        </is>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C950" s="4" t="inlineStr">
+        <is>
+          <t>扌 寺</t>
+        </is>
+      </c>
+      <c r="D950" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E950" s="5" t="n"/>
+      <c r="F950" s="5" t="n"/>
+      <c r="G950" s="4" t="inlineStr">
+        <is>
+          <t>扌 寺 士 十 一 寸</t>
+        </is>
+      </c>
+      <c r="H950" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I950" s="3" t="n"/>
+      <c r="J950" s="5" t="n"/>
+      <c r="K950" s="5" t="n"/>
+      <c r="L950" s="7" t="n"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="inlineStr">
+        <is>
+          <t>記</t>
+        </is>
+      </c>
+      <c r="B951" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C951" s="4" t="inlineStr">
+        <is>
+          <t>言 己</t>
+        </is>
+      </c>
+      <c r="D951" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E951" s="5" t="n"/>
+      <c r="F951" s="5" t="n"/>
+      <c r="G951" s="4" t="inlineStr">
+        <is>
+          <t>言 己</t>
+        </is>
+      </c>
+      <c r="H951" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I951" s="3" t="n"/>
+      <c r="J951" s="5" t="n"/>
+      <c r="K951" s="5" t="n"/>
+      <c r="L951" s="7" t="n"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="inlineStr">
+        <is>
+          <t>錄</t>
+        </is>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C952" s="4" t="inlineStr">
+        <is>
+          <t>金 彔</t>
+        </is>
+      </c>
+      <c r="D952" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E952" s="5" t="n"/>
+      <c r="F952" s="5" t="n"/>
+      <c r="G952" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 彔 彑 氺 亅 八</t>
+        </is>
+      </c>
+      <c r="H952" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I952" s="3" t="n"/>
+      <c r="J952" s="5" t="n"/>
+      <c r="K952" s="5" t="n"/>
+      <c r="L952" s="7" t="n"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="inlineStr">
+        <is>
+          <t>言</t>
+        </is>
+      </c>
+      <c r="B953" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C953" s="4" t="inlineStr"/>
+      <c r="D953" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E953" s="5" t="n"/>
+      <c r="F953" s="5" t="n"/>
+      <c r="G953" s="4" t="inlineStr"/>
+      <c r="H953" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I953" s="3" t="n"/>
+      <c r="J953" s="5" t="n"/>
+      <c r="K953" s="5" t="n"/>
+      <c r="L953" s="7" t="n"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="inlineStr">
+        <is>
+          <t>烈</t>
+        </is>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C954" s="4" t="inlineStr">
+        <is>
+          <t>列 灬</t>
+        </is>
+      </c>
+      <c r="D954" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E954" s="5" t="n"/>
+      <c r="F954" s="5" t="n"/>
+      <c r="G954" s="4" t="inlineStr">
+        <is>
+          <t>列 歹 一 夕 𠂊 丶 刂 灬</t>
+        </is>
+      </c>
+      <c r="H954" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I954" s="3" t="n"/>
+      <c r="J954" s="5" t="n"/>
+      <c r="K954" s="5" t="n"/>
+      <c r="L954" s="7" t="n"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="inlineStr">
+        <is>
+          <t>些</t>
+        </is>
+      </c>
+      <c r="B955" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C955" s="4" t="inlineStr">
+        <is>
+          <t>此 二</t>
+        </is>
+      </c>
+      <c r="D955" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E955" s="5" t="n"/>
+      <c r="F955" s="5" t="n"/>
+      <c r="G955" s="4" t="inlineStr">
+        <is>
+          <t>此 止 匕 乚 一 二</t>
+        </is>
+      </c>
+      <c r="H955" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I955" s="3" t="n"/>
+      <c r="J955" s="5" t="n"/>
+      <c r="K955" s="5" t="n"/>
+      <c r="L955" s="7" t="n"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="inlineStr">
+        <is>
+          <t>提</t>
+        </is>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C956" s="4" t="inlineStr">
+        <is>
+          <t>扌 是</t>
+        </is>
+      </c>
+      <c r="D956" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E956" s="5" t="n"/>
+      <c r="F956" s="5" t="n"/>
+      <c r="G956" s="4" t="inlineStr">
+        <is>
+          <t>扌 是 日 一 龰</t>
+        </is>
+      </c>
+      <c r="H956" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I956" s="3" t="n"/>
+      <c r="J956" s="5" t="n"/>
+      <c r="K956" s="5" t="n"/>
+      <c r="L956" s="7" t="n"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="2" t="inlineStr">
+        <is>
+          <t>愁</t>
+        </is>
+      </c>
+      <c r="B957" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第2課</t>
+        </is>
+      </c>
+      <c r="C957" s="4" t="inlineStr">
+        <is>
+          <t>秋 心</t>
+        </is>
+      </c>
+      <c r="D957" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E957" s="5" t="n"/>
+      <c r="F957" s="5" t="n"/>
+      <c r="G957" s="4" t="inlineStr">
+        <is>
+          <t>秋 禾 丿 木 火 八 人 心</t>
+        </is>
+      </c>
+      <c r="H957" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I957" s="3" t="n"/>
+      <c r="J957" s="5" t="n"/>
+      <c r="K957" s="5" t="n"/>
+      <c r="L957" s="7" t="n"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="2" t="inlineStr">
+        <is>
+          <t>短</t>
+        </is>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第3課</t>
+        </is>
+      </c>
+      <c r="C958" s="4" t="inlineStr">
+        <is>
+          <t>矢 豆</t>
+        </is>
+      </c>
+      <c r="D958" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E958" s="5" t="n"/>
+      <c r="F958" s="5" t="n"/>
+      <c r="G958" s="4" t="inlineStr">
+        <is>
+          <t>矢 𠂉 大 一 人 豆</t>
+        </is>
+      </c>
+      <c r="H958" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I958" s="3" t="n"/>
+      <c r="J958" s="5" t="n"/>
+      <c r="K958" s="5" t="n"/>
+      <c r="L958" s="7" t="n"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="2" t="inlineStr">
+        <is>
+          <t>鬼</t>
+        </is>
+      </c>
+      <c r="B959" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第3課</t>
+        </is>
+      </c>
+      <c r="C959" s="4" t="inlineStr">
+        <is>
+          <t>甶 儿 厶</t>
+        </is>
+      </c>
+      <c r="D959" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E959" s="5" t="n"/>
+      <c r="F959" s="5" t="n"/>
+      <c r="G959" s="4" t="inlineStr">
+        <is>
+          <t>甶 丿 田 儿 乚 厶</t>
+        </is>
+      </c>
+      <c r="H959" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I959" s="3" t="n"/>
+      <c r="J959" s="5" t="n"/>
+      <c r="K959" s="5" t="n"/>
+      <c r="L959" s="7" t="n"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="2" t="inlineStr">
+        <is>
+          <t>朝</t>
+        </is>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第3課</t>
+        </is>
+      </c>
+      <c r="C960" s="4" t="inlineStr">
+        <is>
+          <t>十 早 月</t>
+        </is>
+      </c>
+      <c r="D960" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E960" s="5" t="n"/>
+      <c r="F960" s="5" t="n"/>
+      <c r="G960" s="4" t="inlineStr">
+        <is>
+          <t>十 早 日 月</t>
+        </is>
+      </c>
+      <c r="H960" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I960" s="3" t="n"/>
+      <c r="J960" s="5" t="n"/>
+      <c r="K960" s="5" t="n"/>
+      <c r="L960" s="7" t="n"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="2" t="inlineStr">
+        <is>
+          <t>暢</t>
+        </is>
+      </c>
+      <c r="B961" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第3課</t>
+        </is>
+      </c>
+      <c r="C961" s="4" t="inlineStr">
+        <is>
+          <t>申 昜</t>
+        </is>
+      </c>
+      <c r="D961" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E961" s="5" t="n"/>
+      <c r="F961" s="5" t="n"/>
+      <c r="G961" s="4" t="inlineStr">
+        <is>
+          <t>申 昜 旦 日 一 勿 勹 丿</t>
+        </is>
+      </c>
+      <c r="H961" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I961" s="3" t="n"/>
+      <c r="J961" s="5" t="n"/>
+      <c r="K961" s="5" t="n"/>
+      <c r="L961" s="7" t="n"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="2" t="inlineStr">
+        <is>
+          <t>無</t>
+        </is>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第3課</t>
+        </is>
+      </c>
+      <c r="C962" s="4" t="inlineStr">
+        <is>
+          <t>𠂉 卌 一 灬</t>
+        </is>
+      </c>
+      <c r="D962" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E962" s="5" t="n"/>
+      <c r="F962" s="5" t="n"/>
+      <c r="G962" s="4" t="inlineStr">
+        <is>
+          <t>𠂉 卌 一 灬</t>
+        </is>
+      </c>
+      <c r="H962" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I962" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J962" s="5" t="n"/>
+      <c r="K962" s="5" t="n"/>
+      <c r="L962" s="7" t="n"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="2" t="inlineStr">
+        <is>
+          <t>責</t>
+        </is>
+      </c>
+      <c r="B963" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第3課</t>
+        </is>
+      </c>
+      <c r="C963" s="4" t="inlineStr">
+        <is>
+          <t>龶 貝</t>
+        </is>
+      </c>
+      <c r="D963" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E963" s="5" t="n"/>
+      <c r="F963" s="5" t="n"/>
+      <c r="G963" s="4" t="inlineStr">
+        <is>
+          <t>龶 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H963" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I963" s="3" t="n"/>
+      <c r="J963" s="5" t="n"/>
+      <c r="K963" s="5" t="n"/>
+      <c r="L963" s="7" t="n"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="2" t="inlineStr">
+        <is>
+          <t>悶</t>
+        </is>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C964" s="4" t="inlineStr">
+        <is>
+          <t>門 心</t>
+        </is>
+      </c>
+      <c r="D964" s="4" t="inlineStr">
+        <is>
+          <t>上方包圍</t>
+        </is>
+      </c>
+      <c r="E964" s="5" t="n"/>
+      <c r="F964" s="5" t="n"/>
+      <c r="G964" s="4" t="inlineStr">
+        <is>
+          <t>門 𠁣 𠃛 心</t>
+        </is>
+      </c>
+      <c r="H964" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I964" s="3" t="n"/>
+      <c r="J964" s="5" t="n"/>
+      <c r="K964" s="5" t="n"/>
+      <c r="L964" s="7" t="n"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="2" t="inlineStr">
+        <is>
+          <t>惱</t>
+        </is>
+      </c>
+      <c r="B965" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C965" s="4" t="inlineStr">
+        <is>
+          <t>忄 巛 囟</t>
+        </is>
+      </c>
+      <c r="D965" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E965" s="5" t="n"/>
+      <c r="F965" s="5" t="n"/>
+      <c r="G965" s="4" t="inlineStr">
+        <is>
+          <t>忄 巛 𡿨 囟 丿 囗 㐅</t>
+        </is>
+      </c>
+      <c r="H965" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I965" s="3" t="n"/>
+      <c r="J965" s="5" t="n"/>
+      <c r="K965" s="5" t="n"/>
+      <c r="L965" s="7" t="n"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="2" t="inlineStr">
+        <is>
+          <t>吵</t>
+        </is>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C966" s="4" t="inlineStr">
+        <is>
+          <t>口 少</t>
+        </is>
+      </c>
+      <c r="D966" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E966" s="5" t="n"/>
+      <c r="F966" s="5" t="n"/>
+      <c r="G966" s="4" t="inlineStr">
+        <is>
+          <t>口 少 小 丿</t>
+        </is>
+      </c>
+      <c r="H966" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I966" s="3" t="n"/>
+      <c r="J966" s="5" t="n"/>
+      <c r="K966" s="5" t="n"/>
+      <c r="L966" s="7" t="n"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="2" t="inlineStr">
+        <is>
+          <t>勉</t>
+        </is>
+      </c>
+      <c r="B967" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C967" s="4" t="inlineStr">
+        <is>
+          <t>免 力</t>
+        </is>
+      </c>
+      <c r="D967" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E967" s="5" t="n"/>
+      <c r="F967" s="5" t="n"/>
+      <c r="G967" s="4" t="inlineStr">
+        <is>
+          <t>免 𠂊 力 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H967" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I967" s="3" t="n"/>
+      <c r="J967" s="5" t="n"/>
+      <c r="K967" s="5" t="n"/>
+      <c r="L967" s="7" t="n"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="2" t="inlineStr">
+        <is>
+          <t>強</t>
+        </is>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C968" s="4" t="inlineStr">
+        <is>
+          <t>弓 厶 虫</t>
+        </is>
+      </c>
+      <c r="D968" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E968" s="5" t="n"/>
+      <c r="F968" s="5" t="n"/>
+      <c r="G968" s="4" t="inlineStr">
+        <is>
+          <t>弓 厶 虫</t>
+        </is>
+      </c>
+      <c r="H968" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I968" s="3" t="n"/>
+      <c r="J968" s="5" t="n"/>
+      <c r="K968" s="5" t="n"/>
+      <c r="L968" s="7" t="n"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="2" t="inlineStr">
+        <is>
+          <t>脾</t>
+        </is>
+      </c>
+      <c r="B969" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C969" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 卑</t>
+        </is>
+      </c>
+      <c r="D969" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E969" s="5" t="n"/>
+      <c r="F969" s="5" t="n"/>
+      <c r="G969" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 卑 白 丿 十</t>
+        </is>
+      </c>
+      <c r="H969" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I969" s="3" t="n"/>
+      <c r="J969" s="5" t="n"/>
+      <c r="K969" s="5" t="n"/>
+      <c r="L969" s="7" t="n"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="2" t="inlineStr">
+        <is>
+          <t>解</t>
+        </is>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C970" s="4" t="inlineStr">
+        <is>
+          <t>角 刀 牛</t>
+        </is>
+      </c>
+      <c r="D970" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E970" s="5" t="n"/>
+      <c r="F970" s="5" t="n"/>
+      <c r="G970" s="4" t="inlineStr">
+        <is>
+          <t>角 刀 𠃌 丿 牛</t>
+        </is>
+      </c>
+      <c r="H970" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I970" s="3" t="n"/>
+      <c r="J970" s="5" t="n"/>
+      <c r="K970" s="5" t="n"/>
+      <c r="L970" s="7" t="n"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="2" t="inlineStr">
+        <is>
+          <t>央</t>
+        </is>
+      </c>
+      <c r="B971" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C971" s="4" t="inlineStr"/>
+      <c r="D971" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E971" s="5" t="n"/>
+      <c r="F971" s="5" t="n"/>
+      <c r="G971" s="4" t="inlineStr"/>
+      <c r="H971" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I971" s="3" t="n"/>
+      <c r="J971" s="5" t="n"/>
+      <c r="K971" s="5" t="n"/>
+      <c r="L971" s="7" t="n"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="2" t="inlineStr">
+        <is>
+          <t>尖</t>
+        </is>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C972" s="4" t="inlineStr">
+        <is>
+          <t>小 大</t>
+        </is>
+      </c>
+      <c r="D972" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E972" s="5" t="n"/>
+      <c r="F972" s="5" t="n"/>
+      <c r="G972" s="4" t="inlineStr">
+        <is>
+          <t>小 大 一 人</t>
+        </is>
+      </c>
+      <c r="H972" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I972" s="3" t="n"/>
+      <c r="J972" s="5" t="n"/>
+      <c r="K972" s="5" t="n"/>
+      <c r="L972" s="7" t="n"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="2" t="inlineStr">
+        <is>
+          <t>嗓</t>
+        </is>
+      </c>
+      <c r="B973" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第4課</t>
+        </is>
+      </c>
+      <c r="C973" s="4" t="inlineStr">
+        <is>
+          <t>口 桑</t>
+        </is>
+      </c>
+      <c r="D973" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E973" s="5" t="n"/>
+      <c r="F973" s="5" t="n"/>
+      <c r="G973" s="4" t="inlineStr">
+        <is>
+          <t>口 桑 叒 又 双 朩</t>
+        </is>
+      </c>
+      <c r="H973" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I973" s="3" t="n"/>
+      <c r="J973" s="5" t="n"/>
+      <c r="K973" s="5" t="n"/>
+      <c r="L973" s="7" t="n"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="2" t="inlineStr">
+        <is>
+          <t>龍</t>
+        </is>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第5課</t>
+        </is>
+      </c>
+      <c r="C974" s="4" t="inlineStr">
+        <is>
+          <t>立 月</t>
+        </is>
+      </c>
+      <c r="D974" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E974" s="5" t="n"/>
+      <c r="F974" s="5" t="n"/>
+      <c r="G974" s="4" t="inlineStr">
+        <is>
+          <t>立 亠 丶 一 丷 月</t>
+        </is>
+      </c>
+      <c r="H974" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I974" s="3" t="n"/>
+      <c r="J974" s="5" t="n"/>
+      <c r="K974" s="5" t="n"/>
+      <c r="L974" s="7" t="n"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="2" t="inlineStr">
+        <is>
+          <t>鈴</t>
+        </is>
+      </c>
+      <c r="B975" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第5課</t>
+        </is>
+      </c>
+      <c r="C975" s="4" t="inlineStr">
+        <is>
+          <t>金 令</t>
+        </is>
+      </c>
+      <c r="D975" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E975" s="5" t="n"/>
+      <c r="F975" s="5" t="n"/>
+      <c r="G975" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 令 亼 龴</t>
+        </is>
+      </c>
+      <c r="H975" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I975" s="3" t="n"/>
+      <c r="J975" s="5" t="n"/>
+      <c r="K975" s="5" t="n"/>
+      <c r="L975" s="7" t="n"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="2" t="inlineStr">
+        <is>
+          <t>員</t>
+        </is>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第5課</t>
+        </is>
+      </c>
+      <c r="C976" s="4" t="inlineStr">
+        <is>
+          <t>口 貝</t>
+        </is>
+      </c>
+      <c r="D976" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E976" s="5" t="n"/>
+      <c r="F976" s="5" t="n"/>
+      <c r="G976" s="4" t="inlineStr">
+        <is>
+          <t>口 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H976" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I976" s="3" t="n"/>
+      <c r="J976" s="5" t="n"/>
+      <c r="K976" s="5" t="n"/>
+      <c r="L976" s="7" t="n"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="2" t="inlineStr">
+        <is>
+          <t>傷</t>
+        </is>
+      </c>
+      <c r="B977" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第5課</t>
+        </is>
+      </c>
+      <c r="C977" s="4" t="inlineStr">
+        <is>
+          <t>亻 𠂉 昜</t>
+        </is>
+      </c>
+      <c r="D977" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E977" s="5" t="n"/>
+      <c r="F977" s="5" t="n"/>
+      <c r="G977" s="4" t="inlineStr">
+        <is>
+          <t>亻 𠂉 昜 旦 日 一 勿 勹 丿</t>
+        </is>
+      </c>
+      <c r="H977" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I977" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J977" s="5" t="n"/>
+      <c r="K977" s="5" t="n"/>
+      <c r="L977" s="7" t="n"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="2" t="inlineStr">
+        <is>
+          <t>死</t>
+        </is>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第5課</t>
+        </is>
+      </c>
+      <c r="C978" s="4" t="inlineStr">
+        <is>
+          <t>歹 匕</t>
+        </is>
+      </c>
+      <c r="D978" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E978" s="5" t="n"/>
+      <c r="F978" s="5" t="n"/>
+      <c r="G978" s="4" t="inlineStr">
+        <is>
+          <t>歹 一 夕 𠂊 丶 匕 乚</t>
+        </is>
+      </c>
+      <c r="H978" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I978" s="3" t="n"/>
+      <c r="J978" s="5" t="n"/>
+      <c r="K978" s="5" t="n"/>
+      <c r="L978" s="7" t="n"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="2" t="inlineStr">
+        <is>
+          <t>諒</t>
+        </is>
+      </c>
+      <c r="B979" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第5課</t>
+        </is>
+      </c>
+      <c r="C979" s="4" t="inlineStr">
+        <is>
+          <t>言 京</t>
+        </is>
+      </c>
+      <c r="D979" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E979" s="5" t="n"/>
+      <c r="F979" s="5" t="n"/>
+      <c r="G979" s="4" t="inlineStr">
+        <is>
+          <t>言 京 亠 丶 一 口 小</t>
+        </is>
+      </c>
+      <c r="H979" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I979" s="3" t="n"/>
+      <c r="J979" s="5" t="n"/>
+      <c r="K979" s="5" t="n"/>
+      <c r="L979" s="7" t="n"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="2" t="inlineStr">
+        <is>
+          <t>幕</t>
+        </is>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C980" s="4" t="inlineStr">
+        <is>
+          <t>莫 巾</t>
+        </is>
+      </c>
+      <c r="D980" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E980" s="5" t="n"/>
+      <c r="F980" s="5" t="n"/>
+      <c r="G980" s="4" t="inlineStr">
+        <is>
+          <t>莫 艹 十 旲 日 大 一 人 巾</t>
+        </is>
+      </c>
+      <c r="H980" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I980" s="3" t="n"/>
+      <c r="J980" s="5" t="n"/>
+      <c r="K980" s="5" t="n"/>
+      <c r="L980" s="7" t="n"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="2" t="inlineStr">
+        <is>
+          <t>杯</t>
+        </is>
+      </c>
+      <c r="B981" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C981" s="4" t="inlineStr">
+        <is>
+          <t>木 不</t>
+        </is>
+      </c>
+      <c r="D981" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E981" s="5" t="n"/>
+      <c r="F981" s="5" t="n"/>
+      <c r="G981" s="4" t="inlineStr">
+        <is>
+          <t>木 不 一</t>
+        </is>
+      </c>
+      <c r="H981" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I981" s="3" t="n"/>
+      <c r="J981" s="5" t="n"/>
+      <c r="K981" s="5" t="n"/>
+      <c r="L981" s="7" t="n"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="2" t="inlineStr">
+        <is>
+          <t>流</t>
+        </is>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C982" s="4" t="inlineStr">
+        <is>
+          <t>氵 一 厶 儿 丨</t>
+        </is>
+      </c>
+      <c r="D982" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E982" s="5" t="n"/>
+      <c r="F982" s="5" t="n"/>
+      <c r="G982" s="4" t="inlineStr">
+        <is>
+          <t>氵 一 厶 儿 丿 乚 丨</t>
+        </is>
+      </c>
+      <c r="H982" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I982" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J982" s="5" t="n"/>
+      <c r="K982" s="5" t="n"/>
+      <c r="L982" s="7" t="n"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="2" t="inlineStr">
+        <is>
+          <t>透</t>
+        </is>
+      </c>
+      <c r="B983" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C983" s="4" t="inlineStr">
+        <is>
+          <t>辶 秀</t>
+        </is>
+      </c>
+      <c r="D983" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E983" s="5" t="n"/>
+      <c r="F983" s="5" t="n"/>
+      <c r="G983" s="4" t="inlineStr">
+        <is>
+          <t>辶 秀 禾 丿 木 乃 𠄎</t>
+        </is>
+      </c>
+      <c r="H983" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I983" s="3" t="n"/>
+      <c r="J983" s="5" t="n"/>
+      <c r="K983" s="5" t="n"/>
+      <c r="L983" s="7" t="n"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="2" t="inlineStr">
+        <is>
+          <t>雙</t>
+        </is>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C984" s="4" t="inlineStr">
+        <is>
+          <t>雔 又</t>
+        </is>
+      </c>
+      <c r="D984" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E984" s="5" t="n"/>
+      <c r="F984" s="5" t="n"/>
+      <c r="G984" s="4" t="inlineStr">
+        <is>
+          <t>雔 隹 又</t>
+        </is>
+      </c>
+      <c r="H984" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I984" s="3" t="n"/>
+      <c r="J984" s="5" t="n"/>
+      <c r="K984" s="5" t="n"/>
+      <c r="L984" s="7" t="n"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="2" t="inlineStr">
+        <is>
+          <t>胸</t>
+        </is>
+      </c>
+      <c r="B985" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C985" s="4" t="inlineStr">
+        <is>
+          <t>⺼ 匈</t>
+        </is>
+      </c>
+      <c r="D985" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E985" s="5" t="n"/>
+      <c r="F985" s="5" t="n"/>
+      <c r="G985" s="4" t="inlineStr">
+        <is>
+          <t>⺼ ⺆ 冫 匈 勹 凶 凵 㐅</t>
+        </is>
+      </c>
+      <c r="H985" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I985" s="3" t="n"/>
+      <c r="J985" s="5" t="n"/>
+      <c r="K985" s="5" t="n"/>
+      <c r="L985" s="7" t="n"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="2" t="inlineStr">
+        <is>
+          <t>逃</t>
+        </is>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C986" s="4" t="inlineStr">
+        <is>
+          <t>辶 兆</t>
+        </is>
+      </c>
+      <c r="D986" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E986" s="5" t="n"/>
+      <c r="F986" s="5" t="n"/>
+      <c r="G986" s="4" t="inlineStr">
+        <is>
+          <t>辶 兆</t>
+        </is>
+      </c>
+      <c r="H986" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I986" s="3" t="n"/>
+      <c r="J986" s="5" t="n"/>
+      <c r="K986" s="5" t="n"/>
+      <c r="L986" s="7" t="n"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="2" t="inlineStr">
+        <is>
+          <t>剪</t>
+        </is>
+      </c>
+      <c r="B987" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第6課</t>
+        </is>
+      </c>
+      <c r="C987" s="4" t="inlineStr">
+        <is>
+          <t>前 刀</t>
+        </is>
+      </c>
+      <c r="D987" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E987" s="5" t="n"/>
+      <c r="F987" s="5" t="n"/>
+      <c r="G987" s="4" t="inlineStr">
+        <is>
+          <t>前 丷 一 刖 月 刂 刀 𠃌 丿</t>
+        </is>
+      </c>
+      <c r="H987" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I987" s="3" t="n"/>
+      <c r="J987" s="5" t="n"/>
+      <c r="K987" s="5" t="n"/>
+      <c r="L987" s="7" t="n"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="2" t="inlineStr">
+        <is>
+          <t>斑</t>
+        </is>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C988" s="4" t="inlineStr">
+        <is>
+          <t>王 文 王</t>
+        </is>
+      </c>
+      <c r="D988" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E988" s="5" t="n"/>
+      <c r="F988" s="5" t="n"/>
+      <c r="G988" s="4" t="inlineStr">
+        <is>
+          <t>王 一 土 十 文 亠 丶 乂 丿 乀</t>
+        </is>
+      </c>
+      <c r="H988" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I988" s="3" t="n"/>
+      <c r="J988" s="5" t="n"/>
+      <c r="K988" s="5" t="n"/>
+      <c r="L988" s="7" t="n"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="2" t="inlineStr">
+        <is>
+          <t>皺</t>
+        </is>
+      </c>
+      <c r="B989" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C989" s="4" t="inlineStr">
+        <is>
+          <t>芻 皮</t>
+        </is>
+      </c>
+      <c r="D989" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E989" s="5" t="n"/>
+      <c r="F989" s="5" t="n"/>
+      <c r="G989" s="4" t="inlineStr">
+        <is>
+          <t>芻 勹 屮 凵 丨 皮</t>
+        </is>
+      </c>
+      <c r="H989" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I989" s="3" t="n"/>
+      <c r="J989" s="5" t="n"/>
+      <c r="K989" s="5" t="n"/>
+      <c r="L989" s="7" t="n"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="2" t="inlineStr">
+        <is>
+          <t>淘</t>
+        </is>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C990" s="4" t="inlineStr">
+        <is>
+          <t>氵 匋</t>
+        </is>
+      </c>
+      <c r="D990" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E990" s="5" t="n"/>
+      <c r="F990" s="5" t="n"/>
+      <c r="G990" s="4" t="inlineStr">
+        <is>
+          <t>氵 匋 勹 缶</t>
+        </is>
+      </c>
+      <c r="H990" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I990" s="3" t="n"/>
+      <c r="J990" s="5" t="n"/>
+      <c r="K990" s="5" t="n"/>
+      <c r="L990" s="7" t="n"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="2" t="inlineStr">
+        <is>
+          <t>懂</t>
+        </is>
+      </c>
+      <c r="B991" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C991" s="4" t="inlineStr">
+        <is>
+          <t>忄 董</t>
+        </is>
+      </c>
+      <c r="D991" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E991" s="5" t="n"/>
+      <c r="F991" s="5" t="n"/>
+      <c r="G991" s="4" t="inlineStr">
+        <is>
+          <t>忄 董 艹 十 重</t>
+        </is>
+      </c>
+      <c r="H991" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I991" s="3" t="n"/>
+      <c r="J991" s="5" t="n"/>
+      <c r="K991" s="5" t="n"/>
+      <c r="L991" s="7" t="n"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="2" t="inlineStr">
+        <is>
+          <t>凡</t>
+        </is>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C992" s="4" t="inlineStr">
+        <is>
+          <t>几 丶</t>
+        </is>
+      </c>
+      <c r="D992" s="4" t="inlineStr">
+        <is>
+          <t>上方包圍</t>
+        </is>
+      </c>
+      <c r="E992" s="5" t="n"/>
+      <c r="F992" s="5" t="n"/>
+      <c r="G992" s="4" t="inlineStr">
+        <is>
+          <t>几 丶</t>
+        </is>
+      </c>
+      <c r="H992" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I992" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J992" s="5" t="n"/>
+      <c r="K992" s="5" t="n"/>
+      <c r="L992" s="7" t="n"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="2" t="inlineStr">
+        <is>
+          <t>梳</t>
+        </is>
+      </c>
+      <c r="B993" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C993" s="4" t="inlineStr">
+        <is>
+          <t>木 一 厶 儿 丨</t>
+        </is>
+      </c>
+      <c r="D993" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E993" s="5" t="n"/>
+      <c r="F993" s="5" t="n"/>
+      <c r="G993" s="4" t="inlineStr">
+        <is>
+          <t>木 一 厶 儿 丿 乚 丨</t>
+        </is>
+      </c>
+      <c r="H993" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I993" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J993" s="5" t="n"/>
+      <c r="K993" s="5" t="n"/>
+      <c r="L993" s="7" t="n"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="2" t="inlineStr">
+        <is>
+          <t>藏</t>
+        </is>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C994" s="4" t="inlineStr">
+        <is>
+          <t>艹 臧</t>
+        </is>
+      </c>
+      <c r="D994" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E994" s="5" t="n"/>
+      <c r="F994" s="5" t="n"/>
+      <c r="G994" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 臧 戕 爿 戈 弋 一 乚 丶 丿 臣</t>
+        </is>
+      </c>
+      <c r="H994" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I994" s="3" t="n"/>
+      <c r="J994" s="5" t="n"/>
+      <c r="K994" s="5" t="n"/>
+      <c r="L994" s="7" t="n"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="2" t="inlineStr">
+        <is>
+          <t>捏</t>
+        </is>
+      </c>
+      <c r="B995" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C995" s="4" t="inlineStr">
+        <is>
+          <t>扌 圼</t>
+        </is>
+      </c>
+      <c r="D995" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E995" s="5" t="n"/>
+      <c r="F995" s="5" t="n"/>
+      <c r="G995" s="4" t="inlineStr">
+        <is>
+          <t>扌 圼 日 土 十 一</t>
+        </is>
+      </c>
+      <c r="H995" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I995" s="3" t="n"/>
+      <c r="J995" s="5" t="n"/>
+      <c r="K995" s="5" t="n"/>
+      <c r="L995" s="7" t="n"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="2" t="inlineStr">
+        <is>
+          <t>摺</t>
+        </is>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C996" s="4" t="inlineStr">
+        <is>
+          <t>扌 習</t>
+        </is>
+      </c>
+      <c r="D996" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E996" s="5" t="n"/>
+      <c r="F996" s="5" t="n"/>
+      <c r="G996" s="4" t="inlineStr">
+        <is>
+          <t>扌 習 羽 习 𠃌 冫 白</t>
+        </is>
+      </c>
+      <c r="H996" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I996" s="3" t="n"/>
+      <c r="J996" s="5" t="n"/>
+      <c r="K996" s="5" t="n"/>
+      <c r="L996" s="7" t="n"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="2" t="inlineStr">
+        <is>
+          <t>藝</t>
+        </is>
+      </c>
+      <c r="B997" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C997" s="4" t="inlineStr">
+        <is>
+          <t>蓺 云</t>
+        </is>
+      </c>
+      <c r="D997" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E997" s="5" t="n"/>
+      <c r="F997" s="5" t="n"/>
+      <c r="G997" s="4" t="inlineStr">
+        <is>
+          <t>蓺 艹 十 埶 坴 圥 土 一 儿 丿 乚 丸 九 丶 云 二 厶</t>
+        </is>
+      </c>
+      <c r="H997" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I997" s="3" t="n"/>
+      <c r="J997" s="5" t="n"/>
+      <c r="K997" s="5" t="n"/>
+      <c r="L997" s="7" t="n"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="2" t="inlineStr">
+        <is>
+          <t>術</t>
+        </is>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C998" s="4" t="inlineStr">
+        <is>
+          <t>彳 朮 亍</t>
+        </is>
+      </c>
+      <c r="D998" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E998" s="5" t="n"/>
+      <c r="F998" s="5" t="n"/>
+      <c r="G998" s="4" t="inlineStr">
+        <is>
+          <t>彳 朮 𣎳 丶 亍 一 丁 亅</t>
+        </is>
+      </c>
+      <c r="H998" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I998" s="3" t="n"/>
+      <c r="J998" s="5" t="n"/>
+      <c r="K998" s="5" t="n"/>
+      <c r="L998" s="7" t="n"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="2" t="inlineStr">
+        <is>
+          <t>創</t>
+        </is>
+      </c>
+      <c r="B999" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第7課</t>
+        </is>
+      </c>
+      <c r="C999" s="4" t="inlineStr">
+        <is>
+          <t>倉 刂</t>
+        </is>
+      </c>
+      <c r="D999" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E999" s="5" t="n"/>
+      <c r="F999" s="5" t="n"/>
+      <c r="G999" s="4" t="inlineStr">
+        <is>
+          <t>倉 亼 人 一 尸 口 刂</t>
+        </is>
+      </c>
+      <c r="H999" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I999" s="3" t="n"/>
+      <c r="J999" s="5" t="n"/>
+      <c r="K999" s="5" t="n"/>
+      <c r="L999" s="7" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="2" t="inlineStr">
+        <is>
+          <t>魔</t>
+        </is>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1000" s="4" t="inlineStr">
+        <is>
+          <t>麻 鬼</t>
+        </is>
+      </c>
+      <c r="D1000" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1000" s="5" t="n"/>
+      <c r="F1000" s="5" t="n"/>
+      <c r="G1000" s="4" t="inlineStr">
+        <is>
+          <t>麻 广 𣎳 鬼 甶 丿 田 儿 乚 厶</t>
+        </is>
+      </c>
+      <c r="H1000" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1000" s="3" t="n"/>
+      <c r="J1000" s="5" t="n"/>
+      <c r="K1000" s="5" t="n"/>
+      <c r="L1000" s="7" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="2" t="inlineStr">
+        <is>
+          <t>巾</t>
+        </is>
+      </c>
+      <c r="B1001" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1001" s="4" t="inlineStr"/>
+      <c r="D1001" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1001" s="5" t="n"/>
+      <c r="F1001" s="5" t="n"/>
+      <c r="G1001" s="4" t="inlineStr"/>
+      <c r="H1001" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1001" s="3" t="n"/>
+      <c r="J1001" s="5" t="n"/>
+      <c r="K1001" s="5" t="n"/>
+      <c r="L1001" s="7" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="2" t="inlineStr">
+        <is>
+          <t>框</t>
+        </is>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1002" s="4" t="inlineStr">
+        <is>
+          <t>木 匡</t>
+        </is>
+      </c>
+      <c r="D1002" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1002" s="5" t="n"/>
+      <c r="F1002" s="5" t="n"/>
+      <c r="G1002" s="4" t="inlineStr">
+        <is>
+          <t>木 匡 匚 王 一 土 十</t>
+        </is>
+      </c>
+      <c r="H1002" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1002" s="3" t="n"/>
+      <c r="J1002" s="5" t="n"/>
+      <c r="K1002" s="5" t="n"/>
+      <c r="L1002" s="7" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="2" t="inlineStr">
+        <is>
+          <t>誤</t>
+        </is>
+      </c>
+      <c r="B1003" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1003" s="4" t="inlineStr">
+        <is>
+          <t>言 吳</t>
+        </is>
+      </c>
+      <c r="D1003" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1003" s="5" t="n"/>
+      <c r="F1003" s="5" t="n"/>
+      <c r="G1003" s="4" t="inlineStr">
+        <is>
+          <t>言 吳 大 一 人 口</t>
+        </is>
+      </c>
+      <c r="H1003" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1003" s="3" t="n"/>
+      <c r="J1003" s="5" t="n"/>
+      <c r="K1003" s="5" t="n"/>
+      <c r="L1003" s="7" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="2" t="inlineStr">
+        <is>
+          <t>桶</t>
+        </is>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1004" s="4" t="inlineStr">
+        <is>
+          <t>木 甬</t>
+        </is>
+      </c>
+      <c r="D1004" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1004" s="5" t="n"/>
+      <c r="F1004" s="5" t="n"/>
+      <c r="G1004" s="4" t="inlineStr">
+        <is>
+          <t>木 甬 龴 用 冂 二 一 丨</t>
+        </is>
+      </c>
+      <c r="H1004" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1004" s="3" t="n"/>
+      <c r="J1004" s="5" t="n"/>
+      <c r="K1004" s="5" t="n"/>
+      <c r="L1004" s="7" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" s="2" t="inlineStr">
+        <is>
+          <t>刀</t>
+        </is>
+      </c>
+      <c r="B1005" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1005" s="4" t="inlineStr">
+        <is>
+          <t>𠃌 丿</t>
+        </is>
+      </c>
+      <c r="D1005" s="4" t="inlineStr">
+        <is>
+          <t>右上包圍</t>
+        </is>
+      </c>
+      <c r="E1005" s="5" t="n"/>
+      <c r="F1005" s="5" t="n"/>
+      <c r="G1005" s="4" t="inlineStr">
+        <is>
+          <t>𠃌 丿</t>
+        </is>
+      </c>
+      <c r="H1005" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1005" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1005" s="5" t="n"/>
+      <c r="K1005" s="5" t="n"/>
+      <c r="L1005" s="7" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="2" t="inlineStr">
+        <is>
+          <t>鏡</t>
+        </is>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1006" s="4" t="inlineStr">
+        <is>
+          <t>金 竟</t>
+        </is>
+      </c>
+      <c r="D1006" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1006" s="5" t="n"/>
+      <c r="F1006" s="5" t="n"/>
+      <c r="G1006" s="4" t="inlineStr">
+        <is>
+          <t>金 人 王 一 土 十 丷 竟 音 立 亠 丶 日 儿 丿 乚</t>
+        </is>
+      </c>
+      <c r="H1006" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1006" s="3" t="n"/>
+      <c r="J1006" s="5" t="n"/>
+      <c r="K1006" s="5" t="n"/>
+      <c r="L1006" s="7" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" s="2" t="inlineStr">
+        <is>
+          <t>齊</t>
+        </is>
+      </c>
+      <c r="B1007" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第8課</t>
+        </is>
+      </c>
+      <c r="C1007" s="4" t="inlineStr">
+        <is>
+          <t>亠 刀 丫 丿 二 丨</t>
+        </is>
+      </c>
+      <c r="D1007" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1007" s="5" t="n"/>
+      <c r="F1007" s="5" t="n"/>
+      <c r="G1007" s="4" t="inlineStr">
+        <is>
+          <t>亠 丶 一 刀 𠃌 丿 丫 丷 丨 二</t>
+        </is>
+      </c>
+      <c r="H1007" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1007" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1007" s="5" t="n"/>
+      <c r="K1007" s="5" t="n"/>
+      <c r="L1007" s="7" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="2" t="inlineStr">
+        <is>
+          <t>袍</t>
+        </is>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第9課</t>
+        </is>
+      </c>
+      <c r="C1008" s="4" t="inlineStr">
+        <is>
+          <t>衤 包</t>
+        </is>
+      </c>
+      <c r="D1008" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1008" s="5" t="n"/>
+      <c r="F1008" s="5" t="n"/>
+      <c r="G1008" s="4" t="inlineStr">
+        <is>
+          <t>衤 包 勹 巳</t>
+        </is>
+      </c>
+      <c r="H1008" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1008" s="3" t="n"/>
+      <c r="J1008" s="5" t="n"/>
+      <c r="K1008" s="5" t="n"/>
+      <c r="L1008" s="7" t="n"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" s="2" t="inlineStr">
+        <is>
+          <t>啄</t>
+        </is>
+      </c>
+      <c r="B1009" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第9課</t>
+        </is>
+      </c>
+      <c r="C1009" s="4" t="inlineStr">
+        <is>
+          <t>口 豖</t>
+        </is>
+      </c>
+      <c r="D1009" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1009" s="5" t="n"/>
+      <c r="F1009" s="5" t="n"/>
+      <c r="G1009" s="4" t="inlineStr">
+        <is>
+          <t>口 豖 豕 一 𧰨 丶</t>
+        </is>
+      </c>
+      <c r="H1009" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1009" s="3" t="n"/>
+      <c r="J1009" s="5" t="n"/>
+      <c r="K1009" s="5" t="n"/>
+      <c r="L1009" s="7" t="n"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" s="2" t="inlineStr">
+        <is>
+          <t>備</t>
+        </is>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第9課</t>
+        </is>
+      </c>
+      <c r="C1010" s="4" t="inlineStr">
+        <is>
+          <t>亻 艹 丆 用</t>
+        </is>
+      </c>
+      <c r="D1010" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1010" s="5" t="n"/>
+      <c r="F1010" s="5" t="n"/>
+      <c r="G1010" s="4" t="inlineStr">
+        <is>
+          <t>亻 艹 十 丆 一 丿 用 冂 二 丨</t>
+        </is>
+      </c>
+      <c r="H1010" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1010" s="3" t="n"/>
+      <c r="J1010" s="5" t="n"/>
+      <c r="K1010" s="5" t="n"/>
+      <c r="L1010" s="7" t="n"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" s="2" t="inlineStr">
+        <is>
+          <t>幹</t>
+        </is>
+      </c>
+      <c r="B1011" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第9課</t>
+        </is>
+      </c>
+      <c r="C1011" s="4" t="inlineStr">
+        <is>
+          <t>十 早 人 干</t>
+        </is>
+      </c>
+      <c r="D1011" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1011" s="5" t="n"/>
+      <c r="F1011" s="5" t="n"/>
+      <c r="G1011" s="4" t="inlineStr">
+        <is>
+          <t>十 早 日 人 干</t>
+        </is>
+      </c>
+      <c r="H1011" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1011" s="3" t="n"/>
+      <c r="J1011" s="5" t="n"/>
+      <c r="K1011" s="5" t="n"/>
+      <c r="L1011" s="7" t="n"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" s="2" t="inlineStr">
+        <is>
+          <t>蘋</t>
+        </is>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第9課</t>
+        </is>
+      </c>
+      <c r="C1012" s="4" t="inlineStr">
+        <is>
+          <t>艹 頻</t>
+        </is>
+      </c>
+      <c r="D1012" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1012" s="5" t="n"/>
+      <c r="F1012" s="5" t="n"/>
+      <c r="G1012" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 頻 步 止 𣥂 頁</t>
+        </is>
+      </c>
+      <c r="H1012" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1012" s="3" t="n"/>
+      <c r="J1012" s="5" t="n"/>
+      <c r="K1012" s="5" t="n"/>
+      <c r="L1012" s="7" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" s="2" t="inlineStr">
+        <is>
+          <t>溫</t>
+        </is>
+      </c>
+      <c r="B1013" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第9課</t>
+        </is>
+      </c>
+      <c r="C1013" s="4" t="inlineStr">
+        <is>
+          <t>氵 囚 皿</t>
+        </is>
+      </c>
+      <c r="D1013" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1013" s="5" t="n"/>
+      <c r="F1013" s="5" t="n"/>
+      <c r="G1013" s="4" t="inlineStr">
+        <is>
+          <t>氵 囚 囗 人 皿</t>
+        </is>
+      </c>
+      <c r="H1013" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1013" s="3" t="n"/>
+      <c r="J1013" s="5" t="n"/>
+      <c r="K1013" s="5" t="n"/>
+      <c r="L1013" s="7" t="n"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" s="2" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第10課</t>
+        </is>
+      </c>
+      <c r="C1014" s="4" t="inlineStr">
+        <is>
+          <t>木 艮</t>
+        </is>
+      </c>
+      <c r="D1014" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1014" s="5" t="n"/>
+      <c r="F1014" s="5" t="n"/>
+      <c r="G1014" s="4" t="inlineStr">
+        <is>
+          <t>木 艮</t>
+        </is>
+      </c>
+      <c r="H1014" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1014" s="3" t="n"/>
+      <c r="J1014" s="5" t="n"/>
+      <c r="K1014" s="5" t="n"/>
+      <c r="L1014" s="7" t="n"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" s="2" t="inlineStr">
+        <is>
+          <t>膚</t>
+        </is>
+      </c>
+      <c r="B1015" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第10課</t>
+        </is>
+      </c>
+      <c r="C1015" s="4" t="inlineStr">
+        <is>
+          <t>虍 胃</t>
+        </is>
+      </c>
+      <c r="D1015" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1015" s="5" t="n"/>
+      <c r="F1015" s="5" t="n"/>
+      <c r="G1015" s="4" t="inlineStr">
+        <is>
+          <t>虍 ⺊ 七 ㇀ 乚 胃 田 ⺼ ⺆ 冫</t>
+        </is>
+      </c>
+      <c r="H1015" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1015" s="3" t="n"/>
+      <c r="J1015" s="5" t="n"/>
+      <c r="K1015" s="5" t="n"/>
+      <c r="L1015" s="7" t="n"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" s="2" t="inlineStr">
+        <is>
+          <t>豬</t>
+        </is>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第10課</t>
+        </is>
+      </c>
+      <c r="C1016" s="4" t="inlineStr">
+        <is>
+          <t>豕 者</t>
+        </is>
+      </c>
+      <c r="D1016" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1016" s="5" t="n"/>
+      <c r="F1016" s="5" t="n"/>
+      <c r="G1016" s="4" t="inlineStr">
+        <is>
+          <t>豕 一 𧰨 者 耂 日</t>
+        </is>
+      </c>
+      <c r="H1016" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1016" s="3" t="n"/>
+      <c r="J1016" s="5" t="n"/>
+      <c r="K1016" s="5" t="n"/>
+      <c r="L1016" s="7" t="n"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" s="2" t="inlineStr">
+        <is>
+          <t>呆</t>
+        </is>
+      </c>
+      <c r="B1017" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第10課</t>
+        </is>
+      </c>
+      <c r="C1017" s="4" t="inlineStr">
+        <is>
+          <t>口 朩</t>
+        </is>
+      </c>
+      <c r="D1017" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1017" s="5" t="n"/>
+      <c r="F1017" s="5" t="n"/>
+      <c r="G1017" s="4" t="inlineStr">
+        <is>
+          <t>口 朩</t>
+        </is>
+      </c>
+      <c r="H1017" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1017" s="3" t="n"/>
+      <c r="J1017" s="5" t="n"/>
+      <c r="K1017" s="5" t="n"/>
+      <c r="L1017" s="7" t="n"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" s="2" t="inlineStr">
+        <is>
+          <t>滾</t>
+        </is>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第10課</t>
+        </is>
+      </c>
+      <c r="C1018" s="4" t="inlineStr">
+        <is>
+          <t>氵 袞</t>
+        </is>
+      </c>
+      <c r="D1018" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1018" s="5" t="n"/>
+      <c r="F1018" s="5" t="n"/>
+      <c r="G1018" s="4" t="inlineStr">
+        <is>
+          <t>氵 袞 亠 丶 一 儿 丿 乚 口 𧘇</t>
+        </is>
+      </c>
+      <c r="H1018" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1018" s="3" t="n"/>
+      <c r="J1018" s="5" t="n"/>
+      <c r="K1018" s="5" t="n"/>
+      <c r="L1018" s="7" t="n"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" s="2" t="inlineStr">
+        <is>
+          <t>額</t>
+        </is>
+      </c>
+      <c r="B1019" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1019" s="4" t="inlineStr">
+        <is>
+          <t>客 頁</t>
+        </is>
+      </c>
+      <c r="D1019" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1019" s="5" t="n"/>
+      <c r="F1019" s="5" t="n"/>
+      <c r="G1019" s="4" t="inlineStr">
+        <is>
+          <t>客 宀 各 夂 口 頁</t>
+        </is>
+      </c>
+      <c r="H1019" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1019" s="3" t="n"/>
+      <c r="J1019" s="5" t="n"/>
+      <c r="K1019" s="5" t="n"/>
+      <c r="L1019" s="7" t="n"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" s="2" t="inlineStr">
+        <is>
+          <t>虎</t>
+        </is>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1020" s="4" t="inlineStr">
+        <is>
+          <t>虍 儿</t>
+        </is>
+      </c>
+      <c r="D1020" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1020" s="5" t="n"/>
+      <c r="F1020" s="5" t="n"/>
+      <c r="G1020" s="4" t="inlineStr">
+        <is>
+          <t>虍 ⺊ 七 ㇀ 乚 儿 丿</t>
+        </is>
+      </c>
+      <c r="H1020" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1020" s="3" t="n"/>
+      <c r="J1020" s="5" t="n"/>
+      <c r="K1020" s="5" t="n"/>
+      <c r="L1020" s="7" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" s="2" t="inlineStr">
+        <is>
+          <t>獨</t>
+        </is>
+      </c>
+      <c r="B1021" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1021" s="4" t="inlineStr">
+        <is>
+          <t>犭 蜀</t>
+        </is>
+      </c>
+      <c r="D1021" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1021" s="5" t="n"/>
+      <c r="F1021" s="5" t="n"/>
+      <c r="G1021" s="4" t="inlineStr">
+        <is>
+          <t>犭 蜀 罒 勹 虫</t>
+        </is>
+      </c>
+      <c r="H1021" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1021" s="3" t="n"/>
+      <c r="J1021" s="5" t="n"/>
+      <c r="K1021" s="5" t="n"/>
+      <c r="L1021" s="7" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" s="2" t="inlineStr">
+        <is>
+          <t>捉</t>
+        </is>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1022" s="4" t="inlineStr">
+        <is>
+          <t>扌 足</t>
+        </is>
+      </c>
+      <c r="D1022" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1022" s="5" t="n"/>
+      <c r="F1022" s="5" t="n"/>
+      <c r="G1022" s="4" t="inlineStr">
+        <is>
+          <t>扌 足 口 龰</t>
+        </is>
+      </c>
+      <c r="H1022" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1022" s="3" t="n"/>
+      <c r="J1022" s="5" t="n"/>
+      <c r="K1022" s="5" t="n"/>
+      <c r="L1022" s="7" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" s="2" t="inlineStr">
+        <is>
+          <t>類</t>
+        </is>
+      </c>
+      <c r="B1023" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1023" s="4" t="inlineStr">
+        <is>
+          <t>类 頁</t>
+        </is>
+      </c>
+      <c r="D1023" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1023" s="5" t="n"/>
+      <c r="F1023" s="5" t="n"/>
+      <c r="G1023" s="4" t="inlineStr">
+        <is>
+          <t>类 米 大 一 人 頁</t>
+        </is>
+      </c>
+      <c r="H1023" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1023" s="3" t="n"/>
+      <c r="J1023" s="5" t="n"/>
+      <c r="K1023" s="5" t="n"/>
+      <c r="L1023" s="7" t="n"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" s="2" t="inlineStr">
+        <is>
+          <t>占</t>
+        </is>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1024" s="4" t="inlineStr">
+        <is>
+          <t>⺊ 口</t>
+        </is>
+      </c>
+      <c r="D1024" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1024" s="5" t="n"/>
+      <c r="F1024" s="5" t="n"/>
+      <c r="G1024" s="4" t="inlineStr">
+        <is>
+          <t>⺊ 口</t>
+        </is>
+      </c>
+      <c r="H1024" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1024" s="3" t="n"/>
+      <c r="J1024" s="5" t="n"/>
+      <c r="K1024" s="5" t="n"/>
+      <c r="L1024" s="7" t="n"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" s="2" t="inlineStr">
+        <is>
+          <t>雞</t>
+        </is>
+      </c>
+      <c r="B1025" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1025" s="4" t="inlineStr">
+        <is>
+          <t>奚 隹</t>
+        </is>
+      </c>
+      <c r="D1025" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1025" s="5" t="n"/>
+      <c r="F1025" s="5" t="n"/>
+      <c r="G1025" s="4" t="inlineStr">
+        <is>
+          <t>奚 爫 丿 丶 幺 大 一 人 隹</t>
+        </is>
+      </c>
+      <c r="H1025" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1025" s="3" t="n"/>
+      <c r="J1025" s="5" t="n"/>
+      <c r="K1025" s="5" t="n"/>
+      <c r="L1025" s="7" t="n"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" s="2" t="inlineStr">
+        <is>
+          <t>威</t>
+        </is>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第11課</t>
+        </is>
+      </c>
+      <c r="C1026" s="4" t="inlineStr">
+        <is>
+          <t>戌 女</t>
+        </is>
+      </c>
+      <c r="D1026" s="4" t="inlineStr">
+        <is>
+          <t>上方包圍</t>
+        </is>
+      </c>
+      <c r="E1026" s="5" t="n"/>
+      <c r="F1026" s="5" t="n"/>
+      <c r="G1026" s="4" t="inlineStr">
+        <is>
+          <t>戌 戊 一 女</t>
+        </is>
+      </c>
+      <c r="H1026" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1026" s="3" t="n"/>
+      <c r="J1026" s="5" t="n"/>
+      <c r="K1026" s="5" t="n"/>
+      <c r="L1026" s="7" t="n"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" s="2" t="inlineStr">
+        <is>
+          <t>昆</t>
+        </is>
+      </c>
+      <c r="B1027" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1027" s="4" t="inlineStr">
+        <is>
+          <t>日 比</t>
+        </is>
+      </c>
+      <c r="D1027" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1027" s="5" t="n"/>
+      <c r="F1027" s="5" t="n"/>
+      <c r="G1027" s="4" t="inlineStr">
+        <is>
+          <t>日 比</t>
+        </is>
+      </c>
+      <c r="H1027" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1027" s="3" t="n"/>
+      <c r="J1027" s="5" t="n"/>
+      <c r="K1027" s="5" t="n"/>
+      <c r="L1027" s="7" t="n"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" s="2" t="inlineStr">
+        <is>
+          <t>攻</t>
+        </is>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1028" s="4" t="inlineStr">
+        <is>
+          <t>工 攵</t>
+        </is>
+      </c>
+      <c r="D1028" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1028" s="5" t="n"/>
+      <c r="F1028" s="5" t="n"/>
+      <c r="G1028" s="4" t="inlineStr">
+        <is>
+          <t>工 攵</t>
+        </is>
+      </c>
+      <c r="H1028" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1028" s="3" t="n"/>
+      <c r="J1028" s="5" t="n"/>
+      <c r="K1028" s="5" t="n"/>
+      <c r="L1028" s="7" t="n"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" s="2" t="inlineStr">
+        <is>
+          <t>擊</t>
+        </is>
+      </c>
+      <c r="B1029" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1029" s="4" t="inlineStr">
+        <is>
+          <t>車 凵 殳 手</t>
+        </is>
+      </c>
+      <c r="D1029" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1029" s="5" t="n"/>
+      <c r="F1029" s="5" t="n"/>
+      <c r="G1029" s="4" t="inlineStr">
+        <is>
+          <t>車 凵 殳 𠘧 又 手</t>
+        </is>
+      </c>
+      <c r="H1029" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1029" s="3" t="n"/>
+      <c r="J1029" s="5" t="n"/>
+      <c r="K1029" s="5" t="n"/>
+      <c r="L1029" s="7" t="n"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" s="2" t="inlineStr">
+        <is>
+          <t>演</t>
+        </is>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1030" s="4" t="inlineStr">
+        <is>
+          <t>氵 寅</t>
+        </is>
+      </c>
+      <c r="D1030" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1030" s="5" t="n"/>
+      <c r="F1030" s="5" t="n"/>
+      <c r="G1030" s="4" t="inlineStr">
+        <is>
+          <t>氵 寅 宀 一 由 八</t>
+        </is>
+      </c>
+      <c r="H1030" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1030" s="3" t="n"/>
+      <c r="J1030" s="5" t="n"/>
+      <c r="K1030" s="5" t="n"/>
+      <c r="L1030" s="7" t="n"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" s="2" t="inlineStr">
+        <is>
+          <t>敵</t>
+        </is>
+      </c>
+      <c r="B1031" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1031" s="4" t="inlineStr">
+        <is>
+          <t>啇 攵</t>
+        </is>
+      </c>
+      <c r="D1031" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1031" s="5" t="n"/>
+      <c r="F1031" s="5" t="n"/>
+      <c r="G1031" s="4" t="inlineStr">
+        <is>
+          <t>啇 亠 丶 一 丷 冂 古 十 口 攵</t>
+        </is>
+      </c>
+      <c r="H1031" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1031" s="3" t="n"/>
+      <c r="J1031" s="5" t="n"/>
+      <c r="K1031" s="5" t="n"/>
+      <c r="L1031" s="7" t="n"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" s="2" t="inlineStr">
+        <is>
+          <t>周</t>
+        </is>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1032" s="4" t="inlineStr">
+        <is>
+          <t>⺆ 土 口</t>
+        </is>
+      </c>
+      <c r="D1032" s="4" t="inlineStr">
+        <is>
+          <t>上方包圍</t>
+        </is>
+      </c>
+      <c r="E1032" s="5" t="n"/>
+      <c r="F1032" s="5" t="n"/>
+      <c r="G1032" s="4" t="inlineStr">
+        <is>
+          <t>⺆ 土 十 一 口</t>
+        </is>
+      </c>
+      <c r="H1032" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1032" s="3" t="n"/>
+      <c r="J1032" s="5" t="n"/>
+      <c r="K1032" s="5" t="n"/>
+      <c r="L1032" s="7" t="n"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" s="2" t="inlineStr">
+        <is>
+          <t>技</t>
+        </is>
+      </c>
+      <c r="B1033" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1033" s="4" t="inlineStr">
+        <is>
+          <t>扌 支</t>
+        </is>
+      </c>
+      <c r="D1033" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1033" s="5" t="n"/>
+      <c r="F1033" s="5" t="n"/>
+      <c r="G1033" s="4" t="inlineStr">
+        <is>
+          <t>扌 支 十 又</t>
+        </is>
+      </c>
+      <c r="H1033" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1033" s="3" t="n"/>
+      <c r="J1033" s="5" t="n"/>
+      <c r="K1033" s="5" t="n"/>
+      <c r="L1033" s="7" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" s="2" t="inlineStr">
+        <is>
+          <t>屁</t>
+        </is>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>南一3上第12課</t>
+        </is>
+      </c>
+      <c r="C1034" s="4" t="inlineStr">
+        <is>
+          <t>尸 比</t>
+        </is>
+      </c>
+      <c r="D1034" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1034" s="5" t="n"/>
+      <c r="F1034" s="5" t="n"/>
+      <c r="G1034" s="4" t="inlineStr">
+        <is>
+          <t>尸 比</t>
+        </is>
+      </c>
+      <c r="H1034" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1034" s="3" t="n"/>
+      <c r="J1034" s="5" t="n"/>
+      <c r="K1034" s="5" t="n"/>
+      <c r="L1034" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L936"/>
+  <autoFilter ref="A1:L1034"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K936" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1034" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"左右,上下,左中右,上中下,全包圍,上方包圍,下方包圍,左方包圍,左上包圍,右上包圍,左下包圍,交疊,獨體字"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/parts-table.xlsx
+++ b/docs/parts-table.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填寫說明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$1430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'生字部件'!$A$1:$L$1474</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1430"/>
+  <dimension ref="A1:L1474"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第10課、康軒6上第12課</t>
+          <t>翰林2上第10課、康軒6上第3課</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>翰林2上第11課、南一2上第1課(認讀)、康軒6上第4課</t>
+          <t>翰林2上第11課、南一2上第1課(認讀)</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="B306" s="3" t="inlineStr">
         <is>
-          <t>南一2上第4課</t>
+          <t>南一2上第4課、康軒6上第9課</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>南一2上第12課、康軒4上第9課、康軒6上第12課</t>
+          <t>南一2上第12課、康軒4上第9課</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="B499" s="3" t="inlineStr">
         <is>
-          <t>康軒2上第1課(認讀)</t>
+          <t>康軒2上第1課(認讀)、康軒6上第12課</t>
         </is>
       </c>
       <c r="C499" s="4" t="inlineStr">
@@ -35916,7 +35916,7 @@
       </c>
       <c r="B932" s="3" t="inlineStr">
         <is>
-          <t>康軒4上第12課、康軒6上第6課、南一3上第3課</t>
+          <t>康軒4上第12課、南一3上第3課</t>
         </is>
       </c>
       <c r="C932" s="4" t="inlineStr">
@@ -36106,7 +36106,7 @@
       </c>
       <c r="B937" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第1課、南一3上第2課</t>
+          <t>南一3上第2課</t>
         </is>
       </c>
       <c r="C937" s="4" t="inlineStr">
@@ -36332,11 +36332,7 @@
           <t>恨</t>
         </is>
       </c>
-      <c r="B943" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第1課</t>
-        </is>
-      </c>
+      <c r="B943" s="3" t="n"/>
       <c r="C943" s="4" t="inlineStr">
         <is>
           <t>忄 艮</t>
@@ -36362,7 +36358,11 @@
       <c r="I943" s="3" t="n"/>
       <c r="J943" s="5" t="n"/>
       <c r="K943" s="5" t="n"/>
-      <c r="L943" s="7" t="n"/>
+      <c r="L943" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="944">
       <c r="A944" s="2" t="inlineStr">
@@ -37348,7 +37348,7 @@
       </c>
       <c r="B970" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第2課、南一3上第7課</t>
+          <t>南一3上第7課</t>
         </is>
       </c>
       <c r="C970" s="4" t="inlineStr">
@@ -37464,11 +37464,7 @@
           <t>揭</t>
         </is>
       </c>
-      <c r="B973" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第3課</t>
-        </is>
-      </c>
+      <c r="B973" s="3" t="n"/>
       <c r="C973" s="4" t="inlineStr">
         <is>
           <t>扌 曷</t>
@@ -37494,7 +37490,11 @@
       <c r="I973" s="3" t="n"/>
       <c r="J973" s="5" t="n"/>
       <c r="K973" s="5" t="n"/>
-      <c r="L973" s="7" t="n"/>
+      <c r="L973" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="974">
       <c r="A974" s="2" t="inlineStr">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="B980" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第3課、康軒5上第6課</t>
+          <t>康軒5上第6課</t>
         </is>
       </c>
       <c r="C980" s="4" t="inlineStr">
@@ -37912,11 +37912,7 @@
           <t>昨</t>
         </is>
       </c>
-      <c r="B985" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第3課</t>
-        </is>
-      </c>
+      <c r="B985" s="3" t="n"/>
       <c r="C985" s="4" t="inlineStr">
         <is>
           <t>日 乍</t>
@@ -37942,7 +37938,11 @@
       <c r="I985" s="3" t="n"/>
       <c r="J985" s="5" t="n"/>
       <c r="K985" s="5" t="n"/>
-      <c r="L985" s="7" t="n"/>
+      <c r="L985" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
@@ -38220,11 +38220,7 @@
           <t>覆</t>
         </is>
       </c>
-      <c r="B993" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第4課</t>
-        </is>
-      </c>
+      <c r="B993" s="3" t="n"/>
       <c r="C993" s="4" t="inlineStr">
         <is>
           <t>覀 復</t>
@@ -38250,7 +38246,11 @@
       <c r="I993" s="3" t="n"/>
       <c r="J993" s="5" t="n"/>
       <c r="K993" s="5" t="n"/>
-      <c r="L993" s="7" t="n"/>
+      <c r="L993" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="2" t="inlineStr">
@@ -39100,7 +39100,7 @@
       </c>
       <c r="B1016" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第5課、康軒5上第6課</t>
+          <t>康軒5上第6課</t>
         </is>
       </c>
       <c r="C1016" s="4" t="inlineStr">
@@ -39364,11 +39364,7 @@
           <t>歐</t>
         </is>
       </c>
-      <c r="B1023" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1023" s="3" t="n"/>
       <c r="C1023" s="4" t="inlineStr">
         <is>
           <t>區 欠</t>
@@ -39394,7 +39390,11 @@
       <c r="I1023" s="3" t="n"/>
       <c r="J1023" s="5" t="n"/>
       <c r="K1023" s="5" t="n"/>
-      <c r="L1023" s="7" t="n"/>
+      <c r="L1023" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1024">
       <c r="A1024" s="2" t="inlineStr">
@@ -39402,11 +39402,7 @@
           <t>榜</t>
         </is>
       </c>
-      <c r="B1024" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1024" s="3" t="n"/>
       <c r="C1024" s="4" t="inlineStr">
         <is>
           <t>木 旁</t>
@@ -39432,7 +39428,11 @@
       <c r="I1024" s="3" t="n"/>
       <c r="J1024" s="5" t="n"/>
       <c r="K1024" s="5" t="n"/>
-      <c r="L1024" s="7" t="n"/>
+      <c r="L1024" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="2" t="inlineStr">
@@ -39586,7 +39586,7 @@
       </c>
       <c r="B1029" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第6課、康軒5上第3課</t>
+          <t>康軒5上第3課</t>
         </is>
       </c>
       <c r="C1029" s="4" t="inlineStr">
@@ -39662,7 +39662,7 @@
       </c>
       <c r="B1031" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第6課</t>
+          <t>康軒6上第8課</t>
         </is>
       </c>
       <c r="C1031" s="4" t="inlineStr">
@@ -39736,11 +39736,7 @@
           <t>含</t>
         </is>
       </c>
-      <c r="B1033" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1033" s="3" t="n"/>
       <c r="C1033" s="4" t="inlineStr">
         <is>
           <t>今 口</t>
@@ -39766,7 +39762,11 @@
       <c r="I1033" s="3" t="n"/>
       <c r="J1033" s="5" t="n"/>
       <c r="K1033" s="5" t="n"/>
-      <c r="L1033" s="7" t="n"/>
+      <c r="L1033" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
@@ -39774,11 +39774,7 @@
           <t>脂</t>
         </is>
       </c>
-      <c r="B1034" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1034" s="3" t="n"/>
       <c r="C1034" s="4" t="inlineStr">
         <is>
           <t>⺼ 旨</t>
@@ -39804,7 +39800,11 @@
       <c r="I1034" s="3" t="n"/>
       <c r="J1034" s="5" t="n"/>
       <c r="K1034" s="5" t="n"/>
-      <c r="L1034" s="7" t="n"/>
+      <c r="L1034" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
@@ -39812,11 +39812,7 @@
           <t>鹽</t>
         </is>
       </c>
-      <c r="B1035" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1035" s="3" t="n"/>
       <c r="C1035" s="4" t="inlineStr">
         <is>
           <t>臣 𠂉 鹵 皿</t>
@@ -39846,7 +39842,11 @@
       </c>
       <c r="J1035" s="5" t="n"/>
       <c r="K1035" s="5" t="n"/>
-      <c r="L1035" s="7" t="n"/>
+      <c r="L1035" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1036">
       <c r="A1036" s="2" t="inlineStr">
@@ -39854,11 +39854,7 @@
           <t>呈</t>
         </is>
       </c>
-      <c r="B1036" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1036" s="3" t="n"/>
       <c r="C1036" s="4" t="inlineStr">
         <is>
           <t>口 丿 土</t>
@@ -39888,7 +39884,11 @@
       </c>
       <c r="J1036" s="5" t="n"/>
       <c r="K1036" s="5" t="n"/>
-      <c r="L1036" s="7" t="n"/>
+      <c r="L1036" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" s="2" t="inlineStr">
@@ -39896,11 +39896,7 @@
           <t>慣</t>
         </is>
       </c>
-      <c r="B1037" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第6課</t>
-        </is>
-      </c>
+      <c r="B1037" s="3" t="n"/>
       <c r="C1037" s="4" t="inlineStr">
         <is>
           <t>忄 貫</t>
@@ -39926,7 +39922,11 @@
       <c r="I1037" s="3" t="n"/>
       <c r="J1037" s="5" t="n"/>
       <c r="K1037" s="5" t="n"/>
-      <c r="L1037" s="7" t="n"/>
+      <c r="L1037" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="inlineStr">
@@ -40660,11 +40660,7 @@
           <t>隙</t>
         </is>
       </c>
-      <c r="B1057" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1057" s="3" t="n"/>
       <c r="C1057" s="4" t="inlineStr">
         <is>
           <t>阝 小 白 小</t>
@@ -40690,7 +40686,11 @@
       <c r="I1057" s="3" t="n"/>
       <c r="J1057" s="5" t="n"/>
       <c r="K1057" s="5" t="n"/>
-      <c r="L1057" s="7" t="n"/>
+      <c r="L1057" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
@@ -40698,11 +40698,7 @@
           <t>竄</t>
         </is>
       </c>
-      <c r="B1058" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1058" s="3" t="n"/>
       <c r="C1058" s="4" t="inlineStr">
         <is>
           <t>穴 鼠</t>
@@ -40728,7 +40724,11 @@
       <c r="I1058" s="3" t="n"/>
       <c r="J1058" s="5" t="n"/>
       <c r="K1058" s="5" t="n"/>
-      <c r="L1058" s="7" t="n"/>
+      <c r="L1058" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
@@ -40736,11 +40736,7 @@
           <t>旨</t>
         </is>
       </c>
-      <c r="B1059" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1059" s="3" t="n"/>
       <c r="C1059" s="4" t="inlineStr">
         <is>
           <t>匕 日</t>
@@ -40766,7 +40762,11 @@
       <c r="I1059" s="3" t="n"/>
       <c r="J1059" s="5" t="n"/>
       <c r="K1059" s="5" t="n"/>
-      <c r="L1059" s="7" t="n"/>
+      <c r="L1059" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
@@ -40774,11 +40774,7 @@
           <t>悠</t>
         </is>
       </c>
-      <c r="B1060" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1060" s="3" t="n"/>
       <c r="C1060" s="4" t="inlineStr">
         <is>
           <t>攸 心</t>
@@ -40804,7 +40800,11 @@
       <c r="I1060" s="3" t="n"/>
       <c r="J1060" s="5" t="n"/>
       <c r="K1060" s="5" t="n"/>
-      <c r="L1060" s="7" t="n"/>
+      <c r="L1060" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
@@ -40888,11 +40888,7 @@
           <t>狡</t>
         </is>
       </c>
-      <c r="B1063" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1063" s="3" t="n"/>
       <c r="C1063" s="4" t="inlineStr">
         <is>
           <t>犭 交</t>
@@ -40918,7 +40914,11 @@
       <c r="I1063" s="3" t="n"/>
       <c r="J1063" s="5" t="n"/>
       <c r="K1063" s="5" t="n"/>
-      <c r="L1063" s="7" t="n"/>
+      <c r="L1063" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1064">
       <c r="A1064" s="2" t="inlineStr">
@@ -40926,11 +40926,7 @@
           <t>窟</t>
         </is>
       </c>
-      <c r="B1064" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1064" s="3" t="n"/>
       <c r="C1064" s="4" t="inlineStr">
         <is>
           <t>穴 屈</t>
@@ -40956,7 +40952,11 @@
       <c r="I1064" s="3" t="n"/>
       <c r="J1064" s="5" t="n"/>
       <c r="K1064" s="5" t="n"/>
-      <c r="L1064" s="7" t="n"/>
+      <c r="L1064" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1065">
       <c r="A1065" s="2" t="inlineStr">
@@ -40964,11 +40964,7 @@
           <t>猾</t>
         </is>
       </c>
-      <c r="B1065" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1065" s="3" t="n"/>
       <c r="C1065" s="4" t="inlineStr">
         <is>
           <t>犭 骨</t>
@@ -40994,7 +40990,11 @@
       <c r="I1065" s="3" t="n"/>
       <c r="J1065" s="5" t="n"/>
       <c r="K1065" s="5" t="n"/>
-      <c r="L1065" s="7" t="n"/>
+      <c r="L1065" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
@@ -41002,11 +41002,7 @@
           <t>騙</t>
         </is>
       </c>
-      <c r="B1066" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1066" s="3" t="n"/>
       <c r="C1066" s="4" t="inlineStr">
         <is>
           <t>馬 扁</t>
@@ -41032,7 +41028,11 @@
       <c r="I1066" s="3" t="n"/>
       <c r="J1066" s="5" t="n"/>
       <c r="K1066" s="5" t="n"/>
-      <c r="L1066" s="7" t="n"/>
+      <c r="L1066" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
@@ -41040,11 +41040,7 @@
           <t>偽</t>
         </is>
       </c>
-      <c r="B1067" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1067" s="3" t="n"/>
       <c r="C1067" s="4" t="inlineStr">
         <is>
           <t>亻 為</t>
@@ -41070,7 +41066,11 @@
       <c r="I1067" s="3" t="n"/>
       <c r="J1067" s="5" t="n"/>
       <c r="K1067" s="5" t="n"/>
-      <c r="L1067" s="7" t="n"/>
+      <c r="L1067" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
@@ -41078,11 +41078,7 @@
           <t>誇</t>
         </is>
       </c>
-      <c r="B1068" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1068" s="3" t="n"/>
       <c r="C1068" s="4" t="inlineStr">
         <is>
           <t>言 夸</t>
@@ -41108,7 +41104,11 @@
       <c r="I1068" s="3" t="n"/>
       <c r="J1068" s="5" t="n"/>
       <c r="K1068" s="5" t="n"/>
-      <c r="L1068" s="7" t="n"/>
+      <c r="L1068" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
@@ -41116,11 +41116,7 @@
           <t>辨</t>
         </is>
       </c>
-      <c r="B1069" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1069" s="3" t="n"/>
       <c r="C1069" s="4" t="inlineStr">
         <is>
           <t>辛 辛</t>
@@ -41150,7 +41146,11 @@
       </c>
       <c r="J1069" s="5" t="n"/>
       <c r="K1069" s="5" t="n"/>
-      <c r="L1069" s="7" t="n"/>
+      <c r="L1069" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
@@ -41158,11 +41158,7 @@
           <t>謊</t>
         </is>
       </c>
-      <c r="B1070" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1070" s="3" t="n"/>
       <c r="C1070" s="4" t="inlineStr">
         <is>
           <t>言 荒</t>
@@ -41188,7 +41184,11 @@
       <c r="I1070" s="3" t="n"/>
       <c r="J1070" s="5" t="n"/>
       <c r="K1070" s="5" t="n"/>
-      <c r="L1070" s="7" t="n"/>
+      <c r="L1070" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
@@ -41234,11 +41234,7 @@
           <t>惕</t>
         </is>
       </c>
-      <c r="B1072" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1072" s="3" t="n"/>
       <c r="C1072" s="4" t="inlineStr">
         <is>
           <t>忄 易</t>
@@ -41264,7 +41260,11 @@
       <c r="I1072" s="3" t="n"/>
       <c r="J1072" s="5" t="n"/>
       <c r="K1072" s="5" t="n"/>
-      <c r="L1072" s="7" t="n"/>
+      <c r="L1072" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
@@ -41272,11 +41272,7 @@
           <t>察</t>
         </is>
       </c>
-      <c r="B1073" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第8課</t>
-        </is>
-      </c>
+      <c r="B1073" s="3" t="n"/>
       <c r="C1073" s="4" t="inlineStr">
         <is>
           <t>宀 祭</t>
@@ -41302,7 +41298,11 @@
       <c r="I1073" s="3" t="n"/>
       <c r="J1073" s="5" t="n"/>
       <c r="K1073" s="5" t="n"/>
-      <c r="L1073" s="7" t="n"/>
+      <c r="L1073" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
@@ -41468,7 +41468,7 @@
       </c>
       <c r="B1078" s="3" t="inlineStr">
         <is>
-          <t>康軒6上第9課</t>
+          <t>康軒6上第8課</t>
         </is>
       </c>
       <c r="C1078" s="4" t="inlineStr">
@@ -43500,11 +43500,7 @@
           <t>蓬</t>
         </is>
       </c>
-      <c r="B1131" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1131" s="3" t="n"/>
       <c r="C1131" s="4" t="inlineStr">
         <is>
           <t>艹 逢</t>
@@ -43530,7 +43526,11 @@
       <c r="I1131" s="3" t="n"/>
       <c r="J1131" s="5" t="n"/>
       <c r="K1131" s="5" t="n"/>
-      <c r="L1131" s="7" t="n"/>
+      <c r="L1131" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1132">
       <c r="A1132" s="2" t="inlineStr">
@@ -43538,11 +43538,7 @@
           <t>勃</t>
         </is>
       </c>
-      <c r="B1132" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1132" s="3" t="n"/>
       <c r="C1132" s="4" t="inlineStr">
         <is>
           <t>孛 力</t>
@@ -43568,7 +43564,11 @@
       <c r="I1132" s="3" t="n"/>
       <c r="J1132" s="5" t="n"/>
       <c r="K1132" s="5" t="n"/>
-      <c r="L1132" s="7" t="n"/>
+      <c r="L1132" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1133">
       <c r="A1133" s="2" t="inlineStr">
@@ -43576,11 +43576,7 @@
           <t>庭</t>
         </is>
       </c>
-      <c r="B1133" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1133" s="3" t="n"/>
       <c r="C1133" s="4" t="inlineStr">
         <is>
           <t>广 廷</t>
@@ -43606,7 +43602,11 @@
       <c r="I1133" s="3" t="n"/>
       <c r="J1133" s="5" t="n"/>
       <c r="K1133" s="5" t="n"/>
-      <c r="L1133" s="7" t="n"/>
+      <c r="L1133" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1134">
       <c r="A1134" s="2" t="inlineStr">
@@ -43614,11 +43614,7 @@
           <t>肅</t>
         </is>
       </c>
-      <c r="B1134" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1134" s="3" t="n"/>
       <c r="C1134" s="4" t="n"/>
       <c r="D1134" s="4" t="inlineStr">
         <is>
@@ -43636,7 +43632,11 @@
       <c r="I1134" s="3" t="n"/>
       <c r="J1134" s="5" t="n"/>
       <c r="K1134" s="5" t="n"/>
-      <c r="L1134" s="7" t="n"/>
+      <c r="L1134" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1135">
       <c r="A1135" s="2" t="inlineStr">
@@ -43644,11 +43644,7 @@
           <t>薔</t>
         </is>
       </c>
-      <c r="B1135" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1135" s="3" t="n"/>
       <c r="C1135" s="4" t="inlineStr">
         <is>
           <t>艹 嗇</t>
@@ -43674,7 +43670,11 @@
       <c r="I1135" s="3" t="n"/>
       <c r="J1135" s="5" t="n"/>
       <c r="K1135" s="5" t="n"/>
-      <c r="L1135" s="7" t="n"/>
+      <c r="L1135" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" s="2" t="inlineStr">
@@ -43682,11 +43682,7 @@
           <t>薇</t>
         </is>
       </c>
-      <c r="B1136" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1136" s="3" t="n"/>
       <c r="C1136" s="4" t="inlineStr">
         <is>
           <t>艹 微</t>
@@ -43712,7 +43708,11 @@
       <c r="I1136" s="3" t="n"/>
       <c r="J1136" s="5" t="n"/>
       <c r="K1136" s="5" t="n"/>
-      <c r="L1136" s="7" t="n"/>
+      <c r="L1136" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1137">
       <c r="A1137" s="2" t="inlineStr">
@@ -43720,11 +43720,7 @@
           <t>瀰</t>
         </is>
       </c>
-      <c r="B1137" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1137" s="3" t="n"/>
       <c r="C1137" s="4" t="inlineStr">
         <is>
           <t>氵 彌</t>
@@ -43750,7 +43746,11 @@
       <c r="I1137" s="3" t="n"/>
       <c r="J1137" s="5" t="n"/>
       <c r="K1137" s="5" t="n"/>
-      <c r="L1137" s="7" t="n"/>
+      <c r="L1137" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1138">
       <c r="A1138" s="2" t="inlineStr">
@@ -43758,11 +43758,7 @@
           <t>刮</t>
         </is>
       </c>
-      <c r="B1138" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1138" s="3" t="n"/>
       <c r="C1138" s="4" t="inlineStr">
         <is>
           <t>舌 刂</t>
@@ -43788,7 +43784,11 @@
       <c r="I1138" s="3" t="n"/>
       <c r="J1138" s="5" t="n"/>
       <c r="K1138" s="5" t="n"/>
-      <c r="L1138" s="7" t="n"/>
+      <c r="L1138" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1139">
       <c r="A1139" s="2" t="inlineStr">
@@ -43796,11 +43796,7 @@
           <t>括</t>
         </is>
       </c>
-      <c r="B1139" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1139" s="3" t="n"/>
       <c r="C1139" s="4" t="inlineStr">
         <is>
           <t>扌 舌</t>
@@ -43826,7 +43822,11 @@
       <c r="I1139" s="3" t="n"/>
       <c r="J1139" s="5" t="n"/>
       <c r="K1139" s="5" t="n"/>
-      <c r="L1139" s="7" t="n"/>
+      <c r="L1139" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1140">
       <c r="A1140" s="2" t="inlineStr">
@@ -43834,11 +43834,7 @@
           <t>螞</t>
         </is>
       </c>
-      <c r="B1140" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1140" s="3" t="n"/>
       <c r="C1140" s="4" t="inlineStr">
         <is>
           <t>虫 馬</t>
@@ -43864,7 +43860,11 @@
       <c r="I1140" s="3" t="n"/>
       <c r="J1140" s="5" t="n"/>
       <c r="K1140" s="5" t="n"/>
-      <c r="L1140" s="7" t="n"/>
+      <c r="L1140" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1141">
       <c r="A1141" s="2" t="inlineStr">
@@ -43872,11 +43872,7 @@
           <t>蟻</t>
         </is>
       </c>
-      <c r="B1141" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1141" s="3" t="n"/>
       <c r="C1141" s="4" t="inlineStr">
         <is>
           <t>虫 義</t>
@@ -43902,7 +43898,11 @@
       <c r="I1141" s="3" t="n"/>
       <c r="J1141" s="5" t="n"/>
       <c r="K1141" s="5" t="n"/>
-      <c r="L1141" s="7" t="n"/>
+      <c r="L1141" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1142">
       <c r="A1142" s="2" t="inlineStr">
@@ -43910,11 +43910,7 @@
           <t>儘</t>
         </is>
       </c>
-      <c r="B1142" s="3" t="inlineStr">
-        <is>
-          <t>康軒6上第12課</t>
-        </is>
-      </c>
+      <c r="B1142" s="3" t="n"/>
       <c r="C1142" s="4" t="inlineStr">
         <is>
           <t>亻 盡</t>
@@ -43940,7 +43936,11 @@
       <c r="I1142" s="3" t="n"/>
       <c r="J1142" s="5" t="n"/>
       <c r="K1142" s="5" t="n"/>
-      <c r="L1142" s="7" t="n"/>
+      <c r="L1142" s="7" t="inlineStr">
+        <is>
+          <t>康軒六上改版後已不在現行課本（2026-10-21）</t>
+        </is>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" s="2" t="inlineStr">
@@ -52814,7 +52814,7 @@
       </c>
       <c r="B1375" s="3" t="inlineStr">
         <is>
-          <t>南一3上第4課</t>
+          <t>南一3上第4課、康軒6上第12課</t>
         </is>
       </c>
       <c r="C1375" s="4" t="inlineStr">
@@ -54942,10 +54942,1694 @@
       <c r="K1430" s="5" t="n"/>
       <c r="L1430" s="7" t="n"/>
     </row>
+    <row r="1431">
+      <c r="A1431" s="2" t="inlineStr">
+        <is>
+          <t>芥</t>
+        </is>
+      </c>
+      <c r="B1431" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C1431" s="4" t="inlineStr">
+        <is>
+          <t>艹 介</t>
+        </is>
+      </c>
+      <c r="D1431" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1431" s="5" t="n"/>
+      <c r="F1431" s="5" t="n"/>
+      <c r="G1431" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 介 人 丿 丨</t>
+        </is>
+      </c>
+      <c r="H1431" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1431" s="3" t="n"/>
+      <c r="J1431" s="5" t="n"/>
+      <c r="K1431" s="5" t="n"/>
+      <c r="L1431" s="7" t="n"/>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="2" t="inlineStr">
+        <is>
+          <t>蒂</t>
+        </is>
+      </c>
+      <c r="B1432" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第1課</t>
+        </is>
+      </c>
+      <c r="C1432" s="4" t="inlineStr">
+        <is>
+          <t>艹 帝</t>
+        </is>
+      </c>
+      <c r="D1432" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1432" s="5" t="n"/>
+      <c r="F1432" s="5" t="n"/>
+      <c r="G1432" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 帝 亠 丶 一 丷 冖 巾</t>
+        </is>
+      </c>
+      <c r="H1432" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1432" s="3" t="n"/>
+      <c r="J1432" s="5" t="n"/>
+      <c r="K1432" s="5" t="n"/>
+      <c r="L1432" s="7" t="n"/>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="2" t="inlineStr">
+        <is>
+          <t>陶</t>
+        </is>
+      </c>
+      <c r="B1433" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C1433" s="4" t="inlineStr">
+        <is>
+          <t>阝 匋</t>
+        </is>
+      </c>
+      <c r="D1433" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1433" s="5" t="n"/>
+      <c r="F1433" s="5" t="n"/>
+      <c r="G1433" s="4" t="inlineStr">
+        <is>
+          <t>阝 匋 勹 缶</t>
+        </is>
+      </c>
+      <c r="H1433" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1433" s="3" t="n"/>
+      <c r="J1433" s="5" t="n"/>
+      <c r="K1433" s="5" t="n"/>
+      <c r="L1433" s="7" t="n"/>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="2" t="inlineStr">
+        <is>
+          <t>施</t>
+        </is>
+      </c>
+      <c r="B1434" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第2課</t>
+        </is>
+      </c>
+      <c r="C1434" s="4" t="inlineStr">
+        <is>
+          <t>方 𠂉 也</t>
+        </is>
+      </c>
+      <c r="D1434" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1434" s="5" t="n"/>
+      <c r="F1434" s="5" t="n"/>
+      <c r="G1434" s="4" t="inlineStr">
+        <is>
+          <t>方 亠 丶 一 丿 𠃌 𠂉 也</t>
+        </is>
+      </c>
+      <c r="H1434" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1434" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1434" s="5" t="n"/>
+      <c r="K1434" s="5" t="n"/>
+      <c r="L1434" s="7" t="n"/>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="2" t="inlineStr">
+        <is>
+          <t>砥</t>
+        </is>
+      </c>
+      <c r="B1435" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C1435" s="4" t="inlineStr">
+        <is>
+          <t>石 氐</t>
+        </is>
+      </c>
+      <c r="D1435" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1435" s="5" t="n"/>
+      <c r="F1435" s="5" t="n"/>
+      <c r="G1435" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 氐 氏</t>
+        </is>
+      </c>
+      <c r="H1435" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1435" s="3" t="n"/>
+      <c r="J1435" s="5" t="n"/>
+      <c r="K1435" s="5" t="n"/>
+      <c r="L1435" s="7" t="n"/>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="2" t="inlineStr">
+        <is>
+          <t>礪</t>
+        </is>
+      </c>
+      <c r="B1436" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第3課</t>
+        </is>
+      </c>
+      <c r="C1436" s="4" t="inlineStr">
+        <is>
+          <t>石 厲</t>
+        </is>
+      </c>
+      <c r="D1436" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1436" s="5" t="n"/>
+      <c r="F1436" s="5" t="n"/>
+      <c r="G1436" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 厲 厂 萬 艹 十 禺</t>
+        </is>
+      </c>
+      <c r="H1436" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1436" s="3" t="n"/>
+      <c r="J1436" s="5" t="n"/>
+      <c r="K1436" s="5" t="n"/>
+      <c r="L1436" s="7" t="n"/>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="2" t="inlineStr">
+        <is>
+          <t>丁</t>
+        </is>
+      </c>
+      <c r="B1437" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第4課</t>
+        </is>
+      </c>
+      <c r="C1437" s="4" t="inlineStr">
+        <is>
+          <t>一 亅</t>
+        </is>
+      </c>
+      <c r="D1437" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1437" s="5" t="n"/>
+      <c r="F1437" s="5" t="n"/>
+      <c r="G1437" s="4" t="inlineStr">
+        <is>
+          <t>一 亅</t>
+        </is>
+      </c>
+      <c r="H1437" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1437" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1437" s="5" t="n"/>
+      <c r="K1437" s="5" t="n"/>
+      <c r="L1437" s="7" t="n"/>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="2" t="inlineStr">
+        <is>
+          <t>碎</t>
+        </is>
+      </c>
+      <c r="B1438" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第5課</t>
+        </is>
+      </c>
+      <c r="C1438" s="4" t="inlineStr">
+        <is>
+          <t>石 卒</t>
+        </is>
+      </c>
+      <c r="D1438" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1438" s="5" t="n"/>
+      <c r="F1438" s="5" t="n"/>
+      <c r="G1438" s="4" t="inlineStr">
+        <is>
+          <t>石 丆 一 丿 口 卒 亠 丶 从 人 十</t>
+        </is>
+      </c>
+      <c r="H1438" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1438" s="3" t="n"/>
+      <c r="J1438" s="5" t="n"/>
+      <c r="K1438" s="5" t="n"/>
+      <c r="L1438" s="7" t="n"/>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="2" t="inlineStr">
+        <is>
+          <t>靡</t>
+        </is>
+      </c>
+      <c r="B1439" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1439" s="4" t="inlineStr">
+        <is>
+          <t>麻 非</t>
+        </is>
+      </c>
+      <c r="D1439" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1439" s="5" t="n"/>
+      <c r="F1439" s="5" t="n"/>
+      <c r="G1439" s="4" t="inlineStr">
+        <is>
+          <t>麻 广 𣎳 非</t>
+        </is>
+      </c>
+      <c r="H1439" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1439" s="3" t="n"/>
+      <c r="J1439" s="5" t="n"/>
+      <c r="K1439" s="5" t="n"/>
+      <c r="L1439" s="7" t="n"/>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="2" t="inlineStr">
+        <is>
+          <t>贊</t>
+        </is>
+      </c>
+      <c r="B1440" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1440" s="4" t="inlineStr">
+        <is>
+          <t>兟 貝</t>
+        </is>
+      </c>
+      <c r="D1440" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1440" s="5" t="n"/>
+      <c r="F1440" s="5" t="n"/>
+      <c r="G1440" s="4" t="inlineStr">
+        <is>
+          <t>兟 先 𠂒 儿 丿 乚 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1440" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1440" s="3" t="n"/>
+      <c r="J1440" s="5" t="n"/>
+      <c r="K1440" s="5" t="n"/>
+      <c r="L1440" s="7" t="n"/>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="2" t="inlineStr">
+        <is>
+          <t>干</t>
+        </is>
+      </c>
+      <c r="B1441" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1441" s="4" t="n"/>
+      <c r="D1441" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1441" s="5" t="n"/>
+      <c r="F1441" s="5" t="n"/>
+      <c r="G1441" s="4" t="n"/>
+      <c r="H1441" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1441" s="3" t="n"/>
+      <c r="J1441" s="5" t="n"/>
+      <c r="K1441" s="5" t="n"/>
+      <c r="L1441" s="7" t="n"/>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="2" t="inlineStr">
+        <is>
+          <t>擴</t>
+        </is>
+      </c>
+      <c r="B1442" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1442" s="4" t="inlineStr">
+        <is>
+          <t>扌 廣</t>
+        </is>
+      </c>
+      <c r="D1442" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1442" s="5" t="n"/>
+      <c r="F1442" s="5" t="n"/>
+      <c r="G1442" s="4" t="inlineStr">
+        <is>
+          <t>扌 廣 广 黃 廿 一 田 八</t>
+        </is>
+      </c>
+      <c r="H1442" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1442" s="3" t="n"/>
+      <c r="J1442" s="5" t="n"/>
+      <c r="K1442" s="5" t="n"/>
+      <c r="L1442" s="7" t="n"/>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="2" t="inlineStr">
+        <is>
+          <t>袂</t>
+        </is>
+      </c>
+      <c r="B1443" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1443" s="4" t="inlineStr">
+        <is>
+          <t>衤 夬</t>
+        </is>
+      </c>
+      <c r="D1443" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1443" s="5" t="n"/>
+      <c r="F1443" s="5" t="n"/>
+      <c r="G1443" s="4" t="inlineStr">
+        <is>
+          <t>衤 夬 𠃍 大 一 人</t>
+        </is>
+      </c>
+      <c r="H1443" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1443" s="3" t="n"/>
+      <c r="J1443" s="5" t="n"/>
+      <c r="K1443" s="5" t="n"/>
+      <c r="L1443" s="7" t="n"/>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="2" t="inlineStr">
+        <is>
+          <t>衡</t>
+        </is>
+      </c>
+      <c r="B1444" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1444" s="4" t="inlineStr">
+        <is>
+          <t>彳 𠂊 田 大 亍</t>
+        </is>
+      </c>
+      <c r="D1444" s="4" t="inlineStr">
+        <is>
+          <t>左中右</t>
+        </is>
+      </c>
+      <c r="E1444" s="5" t="n"/>
+      <c r="F1444" s="5" t="n"/>
+      <c r="G1444" s="4" t="inlineStr">
+        <is>
+          <t>彳 𠂊 田 大 一 人 亍 丁 亅</t>
+        </is>
+      </c>
+      <c r="H1444" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1444" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1444" s="5" t="n"/>
+      <c r="K1444" s="5" t="n"/>
+      <c r="L1444" s="7" t="n"/>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="2" t="inlineStr">
+        <is>
+          <t>撫</t>
+        </is>
+      </c>
+      <c r="B1445" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1445" s="4" t="inlineStr">
+        <is>
+          <t>扌 無</t>
+        </is>
+      </c>
+      <c r="D1445" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1445" s="5" t="n"/>
+      <c r="F1445" s="5" t="n"/>
+      <c r="G1445" s="4" t="inlineStr">
+        <is>
+          <t>扌 無 𠂉 卌 一 灬</t>
+        </is>
+      </c>
+      <c r="H1445" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1445" s="3" t="n"/>
+      <c r="J1445" s="5" t="n"/>
+      <c r="K1445" s="5" t="n"/>
+      <c r="L1445" s="7" t="n"/>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="2" t="inlineStr">
+        <is>
+          <t>薩</t>
+        </is>
+      </c>
+      <c r="B1446" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1446" s="4" t="inlineStr">
+        <is>
+          <t>艹 隡</t>
+        </is>
+      </c>
+      <c r="D1446" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1446" s="5" t="n"/>
+      <c r="F1446" s="5" t="n"/>
+      <c r="G1446" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 隡 阝 產 文 亠 丶 一 乂 丿 乀 厂 生</t>
+        </is>
+      </c>
+      <c r="H1446" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1446" s="3" t="n"/>
+      <c r="J1446" s="5" t="n"/>
+      <c r="K1446" s="5" t="n"/>
+      <c r="L1446" s="7" t="n"/>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="2" t="inlineStr">
+        <is>
+          <t>乳</t>
+        </is>
+      </c>
+      <c r="B1447" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第6課</t>
+        </is>
+      </c>
+      <c r="C1447" s="4" t="inlineStr">
+        <is>
+          <t>孚 乚</t>
+        </is>
+      </c>
+      <c r="D1447" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1447" s="5" t="n"/>
+      <c r="F1447" s="5" t="n"/>
+      <c r="G1447" s="4" t="inlineStr">
+        <is>
+          <t>孚 爫 丿 丶 子 乚</t>
+        </is>
+      </c>
+      <c r="H1447" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1447" s="6" t="inlineStr">
+        <is>
+          <t>拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1447" s="5" t="n"/>
+      <c r="K1447" s="5" t="n"/>
+      <c r="L1447" s="7" t="n"/>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="2" t="inlineStr">
+        <is>
+          <t>策</t>
+        </is>
+      </c>
+      <c r="B1448" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1448" s="4" t="inlineStr">
+        <is>
+          <t>竹 朿</t>
+        </is>
+      </c>
+      <c r="D1448" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1448" s="5" t="n"/>
+      <c r="F1448" s="5" t="n"/>
+      <c r="G1448" s="4" t="inlineStr">
+        <is>
+          <t>竹 亇 𠂉 亅 朿</t>
+        </is>
+      </c>
+      <c r="H1448" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1448" s="3" t="n"/>
+      <c r="J1448" s="5" t="n"/>
+      <c r="K1448" s="5" t="n"/>
+      <c r="L1448" s="7" t="n"/>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="2" t="inlineStr">
+        <is>
+          <t>劉</t>
+        </is>
+      </c>
+      <c r="B1449" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1449" s="4" t="inlineStr">
+        <is>
+          <t>刀 金 刂</t>
+        </is>
+      </c>
+      <c r="D1449" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1449" s="5" t="n"/>
+      <c r="F1449" s="5" t="n"/>
+      <c r="G1449" s="4" t="inlineStr">
+        <is>
+          <t>刀 𠃌 丿 金 人 王 一 土 十 丷 刂</t>
+        </is>
+      </c>
+      <c r="H1449" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1449" s="6" t="inlineStr">
+        <is>
+          <t>只拆出部分部件</t>
+        </is>
+      </c>
+      <c r="J1449" s="5" t="n"/>
+      <c r="K1449" s="5" t="n"/>
+      <c r="L1449" s="7" t="n"/>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="2" t="inlineStr">
+        <is>
+          <t>纂</t>
+        </is>
+      </c>
+      <c r="B1450" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1450" s="4" t="inlineStr">
+        <is>
+          <t>竹 目 大 糸</t>
+        </is>
+      </c>
+      <c r="D1450" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1450" s="5" t="n"/>
+      <c r="F1450" s="5" t="n"/>
+      <c r="G1450" s="4" t="inlineStr">
+        <is>
+          <t>竹 亇 𠂉 亅 目 大 一 人 糸 幺 丶 小</t>
+        </is>
+      </c>
+      <c r="H1450" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1450" s="3" t="n"/>
+      <c r="J1450" s="5" t="n"/>
+      <c r="K1450" s="5" t="n"/>
+      <c r="L1450" s="7" t="n"/>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="2" t="inlineStr">
+        <is>
+          <t>蚌</t>
+        </is>
+      </c>
+      <c r="B1451" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1451" s="4" t="inlineStr">
+        <is>
+          <t>虫 丰</t>
+        </is>
+      </c>
+      <c r="D1451" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1451" s="5" t="n"/>
+      <c r="F1451" s="5" t="n"/>
+      <c r="G1451" s="4" t="inlineStr">
+        <is>
+          <t>虫 丰 丿 二 一 丨</t>
+        </is>
+      </c>
+      <c r="H1451" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1451" s="3" t="n"/>
+      <c r="J1451" s="5" t="n"/>
+      <c r="K1451" s="5" t="n"/>
+      <c r="L1451" s="7" t="n"/>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="2" t="inlineStr">
+        <is>
+          <t>述</t>
+        </is>
+      </c>
+      <c r="B1452" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1452" s="4" t="inlineStr">
+        <is>
+          <t>辶 朮</t>
+        </is>
+      </c>
+      <c r="D1452" s="4" t="inlineStr">
+        <is>
+          <t>左下包圍</t>
+        </is>
+      </c>
+      <c r="E1452" s="5" t="n"/>
+      <c r="F1452" s="5" t="n"/>
+      <c r="G1452" s="4" t="inlineStr">
+        <is>
+          <t>辶 朮 𣎳 丶</t>
+        </is>
+      </c>
+      <c r="H1452" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1452" s="3" t="n"/>
+      <c r="J1452" s="5" t="n"/>
+      <c r="K1452" s="5" t="n"/>
+      <c r="L1452" s="7" t="n"/>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="2" t="inlineStr">
+        <is>
+          <t>赫</t>
+        </is>
+      </c>
+      <c r="B1453" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1453" s="4" t="inlineStr">
+        <is>
+          <t>赤 赤</t>
+        </is>
+      </c>
+      <c r="D1453" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1453" s="5" t="n"/>
+      <c r="F1453" s="5" t="n"/>
+      <c r="G1453" s="4" t="inlineStr">
+        <is>
+          <t>赤 土 十 一</t>
+        </is>
+      </c>
+      <c r="H1453" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1453" s="3" t="n"/>
+      <c r="J1453" s="5" t="n"/>
+      <c r="K1453" s="5" t="n"/>
+      <c r="L1453" s="7" t="n"/>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="2" t="inlineStr">
+        <is>
+          <t>畏</t>
+        </is>
+      </c>
+      <c r="B1454" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1454" s="4" t="inlineStr">
+        <is>
+          <t>田 一 𠄌 乀 丿</t>
+        </is>
+      </c>
+      <c r="D1454" s="4" t="inlineStr">
+        <is>
+          <t>上中下</t>
+        </is>
+      </c>
+      <c r="E1454" s="5" t="n"/>
+      <c r="F1454" s="5" t="n"/>
+      <c r="G1454" s="4" t="inlineStr">
+        <is>
+          <t>田 一 𠄌 乀 丿</t>
+        </is>
+      </c>
+      <c r="H1454" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1454" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框；拆出單一筆畫，可能太細</t>
+        </is>
+      </c>
+      <c r="J1454" s="5" t="n"/>
+      <c r="K1454" s="5" t="n"/>
+      <c r="L1454" s="7" t="n"/>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="2" t="inlineStr">
+        <is>
+          <t>詢</t>
+        </is>
+      </c>
+      <c r="B1455" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1455" s="4" t="inlineStr">
+        <is>
+          <t>言 旬</t>
+        </is>
+      </c>
+      <c r="D1455" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1455" s="5" t="n"/>
+      <c r="F1455" s="5" t="n"/>
+      <c r="G1455" s="4" t="inlineStr">
+        <is>
+          <t>言 旬 勹 日</t>
+        </is>
+      </c>
+      <c r="H1455" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1455" s="3" t="n"/>
+      <c r="J1455" s="5" t="n"/>
+      <c r="K1455" s="5" t="n"/>
+      <c r="L1455" s="7" t="n"/>
+    </row>
+    <row r="1456">
+      <c r="A1456" s="2" t="inlineStr">
+        <is>
+          <t>曰</t>
+        </is>
+      </c>
+      <c r="B1456" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1456" s="4" t="n"/>
+      <c r="D1456" s="4" t="inlineStr">
+        <is>
+          <t>獨體字</t>
+        </is>
+      </c>
+      <c r="E1456" s="5" t="n"/>
+      <c r="F1456" s="5" t="n"/>
+      <c r="G1456" s="4" t="n"/>
+      <c r="H1456" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I1456" s="3" t="n"/>
+      <c r="J1456" s="5" t="n"/>
+      <c r="K1456" s="5" t="n"/>
+      <c r="L1456" s="7" t="n"/>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="2" t="inlineStr">
+        <is>
+          <t>吾</t>
+        </is>
+      </c>
+      <c r="B1457" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1457" s="4" t="inlineStr">
+        <is>
+          <t>五 口</t>
+        </is>
+      </c>
+      <c r="D1457" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1457" s="5" t="n"/>
+      <c r="F1457" s="5" t="n"/>
+      <c r="G1457" s="4" t="inlineStr">
+        <is>
+          <t>五 一 𫝀 口</t>
+        </is>
+      </c>
+      <c r="H1457" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1457" s="3" t="n"/>
+      <c r="J1457" s="5" t="n"/>
+      <c r="K1457" s="5" t="n"/>
+      <c r="L1457" s="7" t="n"/>
+    </row>
+    <row r="1458">
+      <c r="A1458" s="2" t="inlineStr">
+        <is>
+          <t>妨</t>
+        </is>
+      </c>
+      <c r="B1458" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第8課</t>
+        </is>
+      </c>
+      <c r="C1458" s="4" t="inlineStr">
+        <is>
+          <t>女 方</t>
+        </is>
+      </c>
+      <c r="D1458" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1458" s="5" t="n"/>
+      <c r="F1458" s="5" t="n"/>
+      <c r="G1458" s="4" t="inlineStr">
+        <is>
+          <t>女 方 亠 丶 一 丿 𠃌</t>
+        </is>
+      </c>
+      <c r="H1458" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1458" s="3" t="n"/>
+      <c r="J1458" s="5" t="n"/>
+      <c r="K1458" s="5" t="n"/>
+      <c r="L1458" s="7" t="n"/>
+    </row>
+    <row r="1459">
+      <c r="A1459" s="2" t="inlineStr">
+        <is>
+          <t>罕</t>
+        </is>
+      </c>
+      <c r="B1459" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第10課</t>
+        </is>
+      </c>
+      <c r="C1459" s="4" t="inlineStr">
+        <is>
+          <t>冖 儿 干</t>
+        </is>
+      </c>
+      <c r="D1459" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1459" s="5" t="n"/>
+      <c r="F1459" s="5" t="n"/>
+      <c r="G1459" s="4" t="inlineStr">
+        <is>
+          <t>冖 儿 丿 乚 干</t>
+        </is>
+      </c>
+      <c r="H1459" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1459" s="3" t="n"/>
+      <c r="J1459" s="5" t="n"/>
+      <c r="K1459" s="5" t="n"/>
+      <c r="L1459" s="7" t="n"/>
+    </row>
+    <row r="1460">
+      <c r="A1460" s="2" t="inlineStr">
+        <is>
+          <t>廂</t>
+        </is>
+      </c>
+      <c r="B1460" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1460" s="4" t="inlineStr">
+        <is>
+          <t>广 相</t>
+        </is>
+      </c>
+      <c r="D1460" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1460" s="5" t="n"/>
+      <c r="F1460" s="5" t="n"/>
+      <c r="G1460" s="4" t="inlineStr">
+        <is>
+          <t>广 相 木 目</t>
+        </is>
+      </c>
+      <c r="H1460" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1460" s="3" t="n"/>
+      <c r="J1460" s="5" t="n"/>
+      <c r="K1460" s="5" t="n"/>
+      <c r="L1460" s="7" t="n"/>
+    </row>
+    <row r="1461">
+      <c r="A1461" s="2" t="inlineStr">
+        <is>
+          <t>袱</t>
+        </is>
+      </c>
+      <c r="B1461" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1461" s="4" t="inlineStr">
+        <is>
+          <t>衤 伏</t>
+        </is>
+      </c>
+      <c r="D1461" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1461" s="5" t="n"/>
+      <c r="F1461" s="5" t="n"/>
+      <c r="G1461" s="4" t="inlineStr">
+        <is>
+          <t>衤 伏 亻 犬</t>
+        </is>
+      </c>
+      <c r="H1461" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1461" s="3" t="n"/>
+      <c r="J1461" s="5" t="n"/>
+      <c r="K1461" s="5" t="n"/>
+      <c r="L1461" s="7" t="n"/>
+    </row>
+    <row r="1462">
+      <c r="A1462" s="2" t="inlineStr">
+        <is>
+          <t>瘡</t>
+        </is>
+      </c>
+      <c r="B1462" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1462" s="4" t="inlineStr">
+        <is>
+          <t>疒 倉</t>
+        </is>
+      </c>
+      <c r="D1462" s="4" t="inlineStr">
+        <is>
+          <t>左上包圍</t>
+        </is>
+      </c>
+      <c r="E1462" s="5" t="n"/>
+      <c r="F1462" s="5" t="n"/>
+      <c r="G1462" s="4" t="inlineStr">
+        <is>
+          <t>疒 倉 亼 人 一 尸 口</t>
+        </is>
+      </c>
+      <c r="H1462" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1462" s="3" t="n"/>
+      <c r="J1462" s="5" t="n"/>
+      <c r="K1462" s="5" t="n"/>
+      <c r="L1462" s="7" t="n"/>
+    </row>
+    <row r="1463">
+      <c r="A1463" s="2" t="inlineStr">
+        <is>
+          <t>狽</t>
+        </is>
+      </c>
+      <c r="B1463" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1463" s="4" t="inlineStr">
+        <is>
+          <t>犭 貝</t>
+        </is>
+      </c>
+      <c r="D1463" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1463" s="5" t="n"/>
+      <c r="F1463" s="5" t="n"/>
+      <c r="G1463" s="4" t="inlineStr">
+        <is>
+          <t>犭 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1463" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1463" s="3" t="n"/>
+      <c r="J1463" s="5" t="n"/>
+      <c r="K1463" s="5" t="n"/>
+      <c r="L1463" s="7" t="n"/>
+    </row>
+    <row r="1464">
+      <c r="A1464" s="2" t="inlineStr">
+        <is>
+          <t>憊</t>
+        </is>
+      </c>
+      <c r="B1464" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1464" s="4" t="inlineStr">
+        <is>
+          <t>備 心</t>
+        </is>
+      </c>
+      <c r="D1464" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1464" s="5" t="n"/>
+      <c r="F1464" s="5" t="n"/>
+      <c r="G1464" s="4" t="inlineStr">
+        <is>
+          <t>備 亻 艹 十 丆 一 丿 用 冂 二 丨 心</t>
+        </is>
+      </c>
+      <c r="H1464" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1464" s="3" t="n"/>
+      <c r="J1464" s="5" t="n"/>
+      <c r="K1464" s="5" t="n"/>
+      <c r="L1464" s="7" t="n"/>
+    </row>
+    <row r="1465">
+      <c r="A1465" s="2" t="inlineStr">
+        <is>
+          <t>淒</t>
+        </is>
+      </c>
+      <c r="B1465" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1465" s="4" t="inlineStr">
+        <is>
+          <t>氵 妻</t>
+        </is>
+      </c>
+      <c r="D1465" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1465" s="5" t="n"/>
+      <c r="F1465" s="5" t="n"/>
+      <c r="G1465" s="4" t="inlineStr">
+        <is>
+          <t>氵 妻 十 一 女</t>
+        </is>
+      </c>
+      <c r="H1465" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1465" s="3" t="n"/>
+      <c r="J1465" s="5" t="n"/>
+      <c r="K1465" s="5" t="n"/>
+      <c r="L1465" s="7" t="n"/>
+    </row>
+    <row r="1466">
+      <c r="A1466" s="2" t="inlineStr">
+        <is>
+          <t>隧</t>
+        </is>
+      </c>
+      <c r="B1466" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1466" s="4" t="inlineStr">
+        <is>
+          <t>阝 遂</t>
+        </is>
+      </c>
+      <c r="D1466" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1466" s="5" t="n"/>
+      <c r="F1466" s="5" t="n"/>
+      <c r="G1466" s="4" t="inlineStr">
+        <is>
+          <t>阝 遂 辶 丷 豕 一 𧰨</t>
+        </is>
+      </c>
+      <c r="H1466" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1466" s="3" t="n"/>
+      <c r="J1466" s="5" t="n"/>
+      <c r="K1466" s="5" t="n"/>
+      <c r="L1466" s="7" t="n"/>
+    </row>
+    <row r="1467">
+      <c r="A1467" s="2" t="inlineStr">
+        <is>
+          <t>卯</t>
+        </is>
+      </c>
+      <c r="B1467" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1467" s="4" t="inlineStr">
+        <is>
+          <t>𠂎 卩</t>
+        </is>
+      </c>
+      <c r="D1467" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1467" s="5" t="n"/>
+      <c r="F1467" s="5" t="n"/>
+      <c r="G1467" s="4" t="inlineStr">
+        <is>
+          <t>𠂎 卩</t>
+        </is>
+      </c>
+      <c r="H1467" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1467" s="6" t="inlineStr">
+        <is>
+          <t>含罕用部件，可能顯示成方框</t>
+        </is>
+      </c>
+      <c r="J1467" s="5" t="n"/>
+      <c r="K1467" s="5" t="n"/>
+      <c r="L1467" s="7" t="n"/>
+    </row>
+    <row r="1468">
+      <c r="A1468" s="2" t="inlineStr">
+        <is>
+          <t>貫</t>
+        </is>
+      </c>
+      <c r="B1468" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1468" s="4" t="inlineStr">
+        <is>
+          <t>毌 貝</t>
+        </is>
+      </c>
+      <c r="D1468" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1468" s="5" t="n"/>
+      <c r="F1468" s="5" t="n"/>
+      <c r="G1468" s="4" t="inlineStr">
+        <is>
+          <t>毌 貝 目 八</t>
+        </is>
+      </c>
+      <c r="H1468" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1468" s="3" t="n"/>
+      <c r="J1468" s="5" t="n"/>
+      <c r="K1468" s="5" t="n"/>
+      <c r="L1468" s="7" t="n"/>
+    </row>
+    <row r="1469">
+      <c r="A1469" s="2" t="inlineStr">
+        <is>
+          <t>岔</t>
+        </is>
+      </c>
+      <c r="B1469" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1469" s="4" t="inlineStr">
+        <is>
+          <t>分 山</t>
+        </is>
+      </c>
+      <c r="D1469" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1469" s="5" t="n"/>
+      <c r="F1469" s="5" t="n"/>
+      <c r="G1469" s="4" t="inlineStr">
+        <is>
+          <t>分 八 刀 𠃌 丿 山</t>
+        </is>
+      </c>
+      <c r="H1469" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1469" s="3" t="n"/>
+      <c r="J1469" s="5" t="n"/>
+      <c r="K1469" s="5" t="n"/>
+      <c r="L1469" s="7" t="n"/>
+    </row>
+    <row r="1470">
+      <c r="A1470" s="2" t="inlineStr">
+        <is>
+          <t>欄</t>
+        </is>
+      </c>
+      <c r="B1470" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1470" s="4" t="inlineStr">
+        <is>
+          <t>木 闌</t>
+        </is>
+      </c>
+      <c r="D1470" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1470" s="5" t="n"/>
+      <c r="F1470" s="5" t="n"/>
+      <c r="G1470" s="4" t="inlineStr">
+        <is>
+          <t>木 闌 門 𠁣 𠃛 柬</t>
+        </is>
+      </c>
+      <c r="H1470" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1470" s="3" t="n"/>
+      <c r="J1470" s="5" t="n"/>
+      <c r="K1470" s="5" t="n"/>
+      <c r="L1470" s="7" t="n"/>
+    </row>
+    <row r="1471">
+      <c r="A1471" s="2" t="inlineStr">
+        <is>
+          <t>柵</t>
+        </is>
+      </c>
+      <c r="B1471" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1471" s="4" t="inlineStr">
+        <is>
+          <t>木 冊</t>
+        </is>
+      </c>
+      <c r="D1471" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1471" s="5" t="n"/>
+      <c r="F1471" s="5" t="n"/>
+      <c r="G1471" s="4" t="inlineStr">
+        <is>
+          <t>木 冊 冂 丨 一</t>
+        </is>
+      </c>
+      <c r="H1471" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1471" s="3" t="n"/>
+      <c r="J1471" s="5" t="n"/>
+      <c r="K1471" s="5" t="n"/>
+      <c r="L1471" s="7" t="n"/>
+    </row>
+    <row r="1472">
+      <c r="A1472" s="2" t="inlineStr">
+        <is>
+          <t>陰</t>
+        </is>
+      </c>
+      <c r="B1472" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1472" s="4" t="inlineStr">
+        <is>
+          <t>阝 侌</t>
+        </is>
+      </c>
+      <c r="D1472" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1472" s="5" t="n"/>
+      <c r="F1472" s="5" t="n"/>
+      <c r="G1472" s="4" t="inlineStr">
+        <is>
+          <t>阝 侌 今 亼 人 一 ㇇ 云 二 厶</t>
+        </is>
+      </c>
+      <c r="H1472" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1472" s="3" t="n"/>
+      <c r="J1472" s="5" t="n"/>
+      <c r="K1472" s="5" t="n"/>
+      <c r="L1472" s="7" t="n"/>
+    </row>
+    <row r="1473">
+      <c r="A1473" s="2" t="inlineStr">
+        <is>
+          <t>扔</t>
+        </is>
+      </c>
+      <c r="B1473" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1473" s="4" t="inlineStr">
+        <is>
+          <t>扌 乃</t>
+        </is>
+      </c>
+      <c r="D1473" s="4" t="inlineStr">
+        <is>
+          <t>左右</t>
+        </is>
+      </c>
+      <c r="E1473" s="5" t="n"/>
+      <c r="F1473" s="5" t="n"/>
+      <c r="G1473" s="4" t="inlineStr">
+        <is>
+          <t>扌 乃 𠄎 丿</t>
+        </is>
+      </c>
+      <c r="H1473" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1473" s="3" t="n"/>
+      <c r="J1473" s="5" t="n"/>
+      <c r="K1473" s="5" t="n"/>
+      <c r="L1473" s="7" t="n"/>
+    </row>
+    <row r="1474">
+      <c r="A1474" s="2" t="inlineStr">
+        <is>
+          <t>茫</t>
+        </is>
+      </c>
+      <c r="B1474" s="3" t="inlineStr">
+        <is>
+          <t>康軒6上第12課</t>
+        </is>
+      </c>
+      <c r="C1474" s="4" t="inlineStr">
+        <is>
+          <t>艹 汒</t>
+        </is>
+      </c>
+      <c r="D1474" s="4" t="inlineStr">
+        <is>
+          <t>上下</t>
+        </is>
+      </c>
+      <c r="E1474" s="5" t="n"/>
+      <c r="F1474" s="5" t="n"/>
+      <c r="G1474" s="4" t="inlineStr">
+        <is>
+          <t>艹 十 汒 氵 亡 亠 丶 一 𠃊</t>
+        </is>
+      </c>
+      <c r="H1474" s="4" t="inlineStr">
+        <is>
+          <t>自動（parts.js）</t>
+        </is>
+      </c>
+      <c r="I1474" s="3" t="n"/>
+      <c r="J1474" s="5" t="n"/>
+      <c r="K1474" s="5" t="n"/>
+      <c r="L1474" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1430"/>
+  <autoFilter ref="A1:L1474"/>
   <dataValidations count="1">
-    <dataValidation sqref="K2:K1430" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1474" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"左右,上下,左中右,上中下,全包圍,上方包圍,下方包圍,左方包圍,左上包圍,右上包圍,左下包圍,交疊,獨體字"</formula1>
     </dataValidation>
   </dataValidations>
